--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -13,12 +13,13 @@
     <sheet name="Closure_Model" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Growth_Model" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Redistricting" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Alternatives" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Debt_Service" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Runway" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tax_History" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Demographics" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="School_Data" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Transport_Geo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Alternatives" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Debt_Service" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Runway" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Tax_History" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Demographics" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="School_Data" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -120,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,6 +150,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -516,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -672,24 +675,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Student density, route-mile arithmetic, and busing cost scenarios: Transport_Geo tab (backs Section 9).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>CAVEAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Prepared by a former NMES King working alongside Fable 5, an AI research assistant from Anthropic. Estimates are labeled; every figure</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Prepared by a former NMES King working alongside Fable 5, an AI research assistant from Anthropic. Estimates are labeled; every figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>should be re-verified against the cited primary sources before formal use. Nothing here alleges misconduct by any official.</t>
         </is>
@@ -701,6 +711,167 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Reserve Runway: Where the Fund Balance Goes Under Each Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Simplified straight-line projection from the FY2025 ending balance; excludes raises, inflation, and one-time items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Projected ending General Fund balance</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Status quo (current drawdown continues)</t>
+        </is>
+      </c>
+      <c r="B5" s="9">
+        <f>GF_Summary!D9-GF_Summary!$D$16</f>
+        <v/>
+      </c>
+      <c r="C5" s="9">
+        <f>B5-GF_Summary!$D$16</f>
+        <v/>
+      </c>
+      <c r="D5" s="9">
+        <f>C5-GF_Summary!$D$16</f>
+        <v/>
+      </c>
+      <c r="E5" s="9">
+        <f>D5-GF_Summary!$D$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>With alternatives package (conservative midpoint; half effect FY2027, full after)</t>
+        </is>
+      </c>
+      <c r="B6" s="9">
+        <f>GF_Summary!D9-GF_Summary!$D$16</f>
+        <v/>
+      </c>
+      <c r="C6" s="9">
+        <f>B6-GF_Summary!$D$16+0.5*Alternatives!$B$21</f>
+        <v/>
+      </c>
+      <c r="D6" s="9">
+        <f>C6-GF_Summary!$D$16+Alternatives!$B$21</f>
+        <v/>
+      </c>
+      <c r="E6" s="9">
+        <f>D6-GF_Summary!$D$16+Alternatives!$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Closure only (base-case net saving from FY2027)</t>
+        </is>
+      </c>
+      <c r="B7" s="9">
+        <f>GF_Summary!D9-GF_Summary!$D$16</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>B7-GF_Summary!$D$16+Closure_Model!$B$20</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>C7-GF_Summary!$D$16+Closure_Model!$B$20</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>D7-GF_Summary!$D$16+Closure_Model!$B$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2% contingency floor (approx., FY2025 basis)</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>GF_Summary!$D$14</f>
+        <v/>
+      </c>
+      <c r="C8" s="18">
+        <f>GF_Summary!$D$14</f>
+        <v/>
+      </c>
+      <c r="D8" s="18">
+        <f>GF_Summary!$D$14</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>GF_Summary!$D$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Reading: the alternatives package restores balance faster than closure, keeps every school open, and adds enrollment revenue rather than risking it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -745,7 +916,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="28" t="n">
         <v>61.3</v>
       </c>
       <c r="G5" s="25" t="inlineStr">
@@ -760,7 +931,7 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="28" t="n">
         <v>60.6</v>
       </c>
     </row>
@@ -770,7 +941,7 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="28" t="n">
         <v>55.9</v>
       </c>
     </row>
@@ -780,7 +951,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="28" t="n">
         <v>54.2</v>
       </c>
     </row>
@@ -790,7 +961,7 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="28" t="n">
         <v>49.2</v>
       </c>
     </row>
@@ -800,7 +971,7 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="28" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -810,7 +981,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="28" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -820,7 +991,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="28" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -830,7 +1001,7 @@
           <t>Tangible/personal rate (recent)</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="28" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -840,7 +1011,7 @@
           <t>Motor vehicle rate</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="28" t="n">
         <v>54.7</v>
       </c>
     </row>
@@ -867,7 +1038,7 @@
           <t>Fayette County</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="28" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="G19" s="25" t="inlineStr">
@@ -882,7 +1053,7 @@
           <t>Paris Independent</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="28" t="n">
         <v>71.5</v>
       </c>
     </row>
@@ -892,7 +1063,7 @@
           <t>Clark County</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="28" t="n">
         <v>66.8</v>
       </c>
     </row>
@@ -902,7 +1073,7 @@
           <t>Bath County</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="28" t="n">
         <v>63.4</v>
       </c>
     </row>
@@ -912,7 +1083,7 @@
           <t>Scott County</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="28" t="n">
         <v>62.9</v>
       </c>
     </row>
@@ -922,7 +1093,7 @@
           <t>Harrison County</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="28" t="n">
         <v>57.7</v>
       </c>
     </row>
@@ -932,7 +1103,7 @@
           <t>Montgomery County</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="28" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -942,7 +1113,7 @@
           <t>Bourbon County</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="28" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -952,7 +1123,7 @@
           <t>Nicholas County</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="28" t="n">
         <v>43.1</v>
       </c>
     </row>
@@ -962,7 +1133,7 @@
           <t>Statewide school average (DOR Table II, 2025)</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="28" t="n">
         <v>65.13</v>
       </c>
     </row>
@@ -1227,7 +1398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1960,7 +2131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2254,55 +2425,55 @@
           <t>North Middletown (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="28" t="n">
         <v>56.5</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="28" t="n">
         <v>63.9</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="28" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="28" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="28" t="n">
         <v>85.8</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="28" t="n">
         <v>72.5</v>
       </c>
-      <c r="H15" s="26" t="n">
+      <c r="H15" s="28" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I15" s="26" t="n">
+      <c r="I15" s="28" t="n">
         <v>56.6</v>
       </c>
-      <c r="J15" s="26" t="n">
+      <c r="J15" s="28" t="n">
         <v>56.9</v>
       </c>
-      <c r="K15" s="26" t="n">
+      <c r="K15" s="28" t="n">
         <v>48.7</v>
       </c>
-      <c r="L15" s="26" t="n">
+      <c r="L15" s="28" t="n">
         <v>49.3</v>
       </c>
-      <c r="M15" s="26" t="n">
+      <c r="M15" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="N15" s="26" t="n">
+      <c r="N15" s="28" t="n">
         <v>50.4</v>
       </c>
-      <c r="P15" s="26" t="n">
+      <c r="P15" s="28" t="n">
         <v>47.7</v>
       </c>
-      <c r="Q15" s="26" t="n">
+      <c r="Q15" s="28" t="n">
         <v>32.1</v>
       </c>
-      <c r="R15" s="26" t="n">
+      <c r="R15" s="28" t="n">
         <v>54.1</v>
       </c>
-      <c r="S15" s="26" t="n">
+      <c r="S15" s="28" t="n">
         <v>58.2</v>
       </c>
     </row>
@@ -2312,58 +2483,58 @@
           <t>Bourbon Central (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="28" t="n">
         <v>77.5</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="28" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="28" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="28" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="28" t="n">
         <v>63</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="28" t="n">
         <v>74.7</v>
       </c>
-      <c r="H16" s="26" t="n">
+      <c r="H16" s="28" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I16" s="28" t="n">
         <v>51.8</v>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J16" s="28" t="n">
         <v>52.1</v>
       </c>
-      <c r="K16" s="26" t="n">
+      <c r="K16" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="L16" s="26" t="n">
+      <c r="L16" s="28" t="n">
         <v>34</v>
       </c>
-      <c r="M16" s="26" t="n">
+      <c r="M16" s="28" t="n">
         <v>32.8</v>
       </c>
-      <c r="N16" s="26" t="n">
+      <c r="N16" s="28" t="n">
         <v>39.9</v>
       </c>
-      <c r="O16" s="26" t="n">
+      <c r="O16" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="P16" s="26" t="n">
+      <c r="P16" s="28" t="n">
         <v>29.9</v>
       </c>
-      <c r="Q16" s="26" t="n">
+      <c r="Q16" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="R16" s="26" t="n">
+      <c r="R16" s="28" t="n">
         <v>23.8</v>
       </c>
-      <c r="S16" s="26" t="n">
+      <c r="S16" s="28" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -2373,58 +2544,58 @@
           <t>Cane Ridge (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="28" t="n">
         <v>35.2</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="28" t="n">
         <v>50.9</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="28" t="n">
         <v>56.2</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="28" t="n">
         <v>65.5</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="28" t="n">
         <v>34.5</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="28" t="n">
         <v>34</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="28" t="n">
         <v>49.6</v>
       </c>
-      <c r="I17" s="26" t="n">
+      <c r="I17" s="28" t="n">
         <v>51</v>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="28" t="n">
         <v>51.1</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="28" t="n">
         <v>57.5</v>
       </c>
-      <c r="L17" s="26" t="n">
+      <c r="L17" s="28" t="n">
         <v>50.4</v>
       </c>
-      <c r="M17" s="26" t="n">
+      <c r="M17" s="28" t="n">
         <v>41.4</v>
       </c>
-      <c r="N17" s="26" t="n">
+      <c r="N17" s="28" t="n">
         <v>38.8</v>
       </c>
-      <c r="O17" s="26" t="n">
+      <c r="O17" s="28" t="n">
         <v>23.8</v>
       </c>
-      <c r="P17" s="26" t="n">
+      <c r="P17" s="28" t="n">
         <v>38.7</v>
       </c>
-      <c r="Q17" s="26" t="n">
+      <c r="Q17" s="28" t="n">
         <v>34.6</v>
       </c>
-      <c r="R17" s="26" t="n">
+      <c r="R17" s="28" t="n">
         <v>35.8</v>
       </c>
-      <c r="S17" s="26" t="n">
+      <c r="S17" s="28" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -2434,10 +2605,10 @@
           <t>Paris Elementary (Paris Indep.)</t>
         </is>
       </c>
-      <c r="R18" s="26" t="n">
+      <c r="R18" s="28" t="n">
         <v>16.8</v>
       </c>
-      <c r="S18" s="26" t="n">
+      <c r="S18" s="28" t="n">
         <v>12.2</v>
       </c>
     </row>
@@ -2447,10 +2618,10 @@
           <t>Shearer (Clark Co.)</t>
         </is>
       </c>
-      <c r="R19" s="26" t="n">
+      <c r="R19" s="28" t="n">
         <v>30.7</v>
       </c>
-      <c r="S19" s="26" t="n">
+      <c r="S19" s="28" t="n">
         <v>42.3</v>
       </c>
     </row>
@@ -2460,10 +2631,10 @@
           <t>Justice (Clark Co.)</t>
         </is>
       </c>
-      <c r="R20" s="26" t="n">
+      <c r="R20" s="28" t="n">
         <v>43.2</v>
       </c>
-      <c r="S20" s="26" t="n">
+      <c r="S20" s="28" t="n">
         <v>39.3</v>
       </c>
     </row>
@@ -2473,10 +2644,10 @@
           <t>Strode Station (Clark Co.)</t>
         </is>
       </c>
-      <c r="R21" s="26" t="n">
+      <c r="R21" s="28" t="n">
         <v>43.2</v>
       </c>
-      <c r="S21" s="26" t="n">
+      <c r="S21" s="28" t="n">
         <v>34.2</v>
       </c>
     </row>
@@ -2486,10 +2657,10 @@
           <t>Conkwright (Clark Co.)</t>
         </is>
       </c>
-      <c r="R22" s="26" t="n">
+      <c r="R22" s="28" t="n">
         <v>15.6</v>
       </c>
-      <c r="S22" s="26" t="n">
+      <c r="S22" s="28" t="n">
         <v>17.5</v>
       </c>
     </row>
@@ -2499,10 +2670,10 @@
           <t>Northview (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R23" s="26" t="n">
+      <c r="R23" s="28" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="S23" s="26" t="n">
+      <c r="S23" s="28" t="n">
         <v>68.90000000000001</v>
       </c>
     </row>
@@ -2512,10 +2683,10 @@
           <t>Mapleton (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R24" s="26" t="n">
+      <c r="R24" s="28" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="S24" s="26" t="n">
+      <c r="S24" s="28" t="n">
         <v>65.09999999999999</v>
       </c>
     </row>
@@ -2525,7 +2696,7 @@
           <t>Nicholas County Elementary (Nicholas Co.)</t>
         </is>
       </c>
-      <c r="R25" s="26" t="n">
+      <c r="R25" s="28" t="n">
         <v>15.9</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -2635,7 +2806,7 @@
           <t>Composite: economically disadvantaged students</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="28" t="n">
         <v>57.1</v>
       </c>
     </row>
@@ -2645,7 +2816,7 @@
           <t>Composite: female students</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="28" t="n">
         <v>85.7</v>
       </c>
     </row>
@@ -2655,7 +2826,7 @@
           <t>Composite: male students</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="28" t="n">
         <v>28.8</v>
       </c>
     </row>
@@ -4626,6 +4797,544 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Transportation and Geography: Density, Route Miles, and What Closure Adds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Estimates built from public geography (census counts, county land area, highway distances). The district's annual T-1 transportation report, zone map, and geocoded counts are the authoritative dataset; releasing them is a records ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>GEOGRAPHY AND STUDENT DENSITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County land area (square miles)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>290</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Census: 289.7 land square miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Paris city population, 2020</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>10171</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2020 Census</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Millersburg population, 2020</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>747</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2020 Census</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown population, 2020</t>
+        </is>
+      </c>
+      <c r="B8" s="24">
+        <f>Demographics!B29</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Demographics tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>NMES zone share of county area</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Eastern portion of the county; replace with the district's actual zone map</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>NMES zone area (sq mi)</t>
+        </is>
+      </c>
+      <c r="B10" s="26">
+        <f>B5*B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Paris-area zones (sq mi)</t>
+        </is>
+      </c>
+      <c r="B11" s="26">
+        <f>B5-B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>NMES elementary students</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>Assumptions!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Paris-area elementary students</t>
+        </is>
+      </c>
+      <c r="B13" s="24">
+        <f>Redistricting!B8+Redistricting!B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Students per square mile, NMES zone</t>
+        </is>
+      </c>
+      <c r="B14" s="20">
+        <f>B12/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Students per square mile, Paris-area zones</t>
+        </is>
+      </c>
+      <c r="B15" s="20">
+        <f>B13/B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Students per square mile, district elementary overall</t>
+        </is>
+      </c>
+      <c r="B16" s="20">
+        <f>(B12+B13)/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>State law (KRS 157.370) funds transportation on transported pupils per square mile: low density earns a higher per-pupil allotment because it costs more to serve. The statutory calculation has been funded below its own formula in every budget since 2005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>WHAT CLOSURE ADDS: ROUTE-MILE ARITHMETIC (yellow = replace with district T-1 data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Share of NMES students riding the bus</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Riders</t>
+        </is>
+      </c>
+      <c r="B21" s="11">
+        <f>ROUND(B20*B12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Rural routes serving NMES today</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Added distance to the Paris schools, one way (miles)</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>US 460, North Middletown to Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Added bus-miles per route per day (out and back, AM and PM)</t>
+        </is>
+      </c>
+      <c r="B24" s="11">
+        <f>B23*4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>School days per year</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Added bus-miles per year</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
+        <f>B22*B24*B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Marginal cost per bus-mile, low</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Fuel, maintenance, driver time; replace with district cost data</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Marginal cost per bus-mile, high</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Added cost, mileage basis, low</t>
+        </is>
+      </c>
+      <c r="B29" s="9">
+        <f>B26*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Added cost, mileage basis, high</t>
+        </is>
+      </c>
+      <c r="B30" s="9">
+        <f>B26*B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Additional buses if route tiers break (high case)</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>All-in cost per additional bus-year</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Bottom-up added busing cost, low</t>
+        </is>
+      </c>
+      <c r="B33" s="23">
+        <f>B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Bottom-up added busing cost, high</t>
+        </is>
+      </c>
+      <c r="B34" s="22">
+        <f>B30+B31*B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Report's planning range (Closure_Model offset basis)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Between $75,000 and $200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>The bottom-up estimate lands inside the planning range; the $137,500 midpoint used in the Closure_Model stands. Note what closure does not remove: every square mile of the eastern county stays in the coverage area, with longer rides on it, roughly 15 to 20 added minutes each way on US 460.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>WHAT REBALANCING CHANGES (Redistricting tab scenario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Students rezoned to NMES</t>
+        </is>
+      </c>
+      <c r="B39" s="24">
+        <f>Redistricting!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Stem miles saved per affected route, one way</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Rezoned families live closer to NMES than to their assigned school</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Affected routes</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Bus-miles saved per year</t>
+        </is>
+      </c>
+      <c r="B42" s="11">
+        <f>B41*B40*4*B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Transport saving, low</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>B42*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Transport saving, high</t>
+        </is>
+      </c>
+      <c r="B44" s="9">
+        <f>B42*B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Rebalancing is transport-neutral to modestly positive, the opposite sign of closure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>DISTRICT-WIDE CONTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Transportation expense, FY2025</t>
+        </is>
+      </c>
+      <c r="B48" s="18">
+        <f>Assumptions!B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Average Daily Attendance, FY2025</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="n">
+        <v>2242.5</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>FY2025 audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Transportation cost per student in attendance</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>B48/B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Optimization potential at 5 to 10 percent (Alternatives menu)</t>
+        </is>
+      </c>
+      <c r="B51" s="18">
+        <f>Assumptions!B42*Assumptions!B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="18">
+        <f>Assumptions!B42*Assumptions!B44</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4960,7 +5669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5297,7 +6006,7 @@
           <t>Average Daily Attendance, FY2025 (SEEK basis)</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="28" t="n">
         <v>2242.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5354,7 +6063,7 @@
           <t>Annual restricted margin available for new debt (illustrative)</t>
         </is>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="29">
         <f>B23*B24+B25-B26</f>
         <v/>
       </c>
@@ -5418,167 +6127,6 @@
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>the official statement, and the bonding potential statement all public.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Reserve Runway: Where the Fund Balance Goes Under Each Path</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Simplified straight-line projection from the FY2025 ending balance; excludes raises, inflation, and one-time items.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Projected ending General Fund balance</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Status quo (current drawdown continues)</t>
-        </is>
-      </c>
-      <c r="B5" s="9">
-        <f>GF_Summary!D9-GF_Summary!$D$16</f>
-        <v/>
-      </c>
-      <c r="C5" s="9">
-        <f>B5-GF_Summary!$D$16</f>
-        <v/>
-      </c>
-      <c r="D5" s="9">
-        <f>C5-GF_Summary!$D$16</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>D5-GF_Summary!$D$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>With alternatives package (conservative midpoint; half effect FY2027, full after)</t>
-        </is>
-      </c>
-      <c r="B6" s="9">
-        <f>GF_Summary!D9-GF_Summary!$D$16</f>
-        <v/>
-      </c>
-      <c r="C6" s="9">
-        <f>B6-GF_Summary!$D$16+0.5*Alternatives!$B$21</f>
-        <v/>
-      </c>
-      <c r="D6" s="9">
-        <f>C6-GF_Summary!$D$16+Alternatives!$B$21</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>D6-GF_Summary!$D$16+Alternatives!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Closure only (base-case net saving from FY2027)</t>
-        </is>
-      </c>
-      <c r="B7" s="9">
-        <f>GF_Summary!D9-GF_Summary!$D$16</f>
-        <v/>
-      </c>
-      <c r="C7" s="9">
-        <f>B7-GF_Summary!$D$16+Closure_Model!$B$20</f>
-        <v/>
-      </c>
-      <c r="D7" s="9">
-        <f>C7-GF_Summary!$D$16+Closure_Model!$B$20</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>D7-GF_Summary!$D$16+Closure_Model!$B$20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2% contingency floor (approx., FY2025 basis)</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>GF_Summary!$D$14</f>
-        <v/>
-      </c>
-      <c r="C8" s="18">
-        <f>GF_Summary!$D$14</f>
-        <v/>
-      </c>
-      <c r="D8" s="18">
-        <f>GF_Summary!$D$14</f>
-        <v/>
-      </c>
-      <c r="E8" s="18">
-        <f>GF_Summary!$D$14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>Reading: the alternatives package restores balance faster than closure, keeps every school open, and adds enrollment revenue rather than risking it.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -143,13 +143,13 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -656,7 +656,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the 4% three-year path: Tax_History tab (backs Figure 14).</t>
+          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the 4% three-year path: Tax_History tab (backs Figure 15).</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Reading: the alternatives package restores balance faster than closure, keeps every school open, and adds enrollment revenue rather than risking it.</t>
         </is>
@@ -899,7 +899,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Backs Section 9 and Figure 14 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
+          <t>Backs Section 9 and Figure 15 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       <c r="B5" s="28" t="n">
         <v>61.3</v>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>2019 documented as the board taking the 4% option (Bourbon County Citizen, 9/4/2019); other years' rate type undetermined pending KDE levy files</t>
         </is>
@@ -1041,7 +1041,7 @@
       <c r="B19" s="28" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>Fayette and Clark from local reporting of board votes; others from DOR rate books. Bourbon ranks second lowest of the nine. Nicholas shown at its real estate rate of 43.1 (tangible 43.7). Bath 63.4 is the 2025 rate (2024: 60.7).</t>
         </is>
@@ -1153,7 +1153,7 @@
       <c r="B32" s="8" t="n">
         <v>7829060</v>
       </c>
-      <c r="G32" s="25" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>GF vs building-fund CENT split unverified; dollar split is audited. Cent split is a records request in the report.</t>
         </is>
@@ -1238,12 +1238,12 @@
           <t>DELINQUENCY CHECK (collections vs certified yield)</t>
         </is>
       </c>
-      <c r="B41" s="21" t="inlineStr">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="C41" s="21" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1322,7 +1322,7 @@
         <f>C43</f>
         <v/>
       </c>
-      <c r="G48" s="25" t="inlineStr">
+      <c r="G48" s="21" t="inlineStr">
         <is>
           <t>Basis: 4% more revenue from EXISTING real + personal property than the compensating rate; new property excluded (upside); motor vehicle separate; recall applies only above 4%.</t>
         </is>
@@ -1449,7 +1449,7 @@
       <c r="B5" s="10" t="n">
         <v>18476</v>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Sources: FRED series KYBOUR7POP; Envision 2040 plan citing the Kentucky State Data Center</t>
         </is>
@@ -1738,7 +1738,7 @@
         <f>MAX(F33:F51,I33:I50)</f>
         <v/>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>1989</t>
         </is>
@@ -1746,7 +1746,7 @@
       <c r="F33" s="10" t="n">
         <v>261</v>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
@@ -1754,7 +1754,7 @@
       <c r="I33" s="10" t="n">
         <v>224</v>
       </c>
-      <c r="J33" s="25" t="inlineStr">
+      <c r="J33" s="21" t="inlineStr">
         <is>
           <t>1989-2014 compiled by PublicSchoolReview from federal data; 2015-2025 match NCES directly</t>
         </is>
@@ -1770,7 +1770,7 @@
         <f>I50</f>
         <v/>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
@@ -1778,7 +1778,7 @@
       <c r="F34" s="10" t="n">
         <v>255</v>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
@@ -1797,7 +1797,7 @@
         <f>B33-B34</f>
         <v/>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
@@ -1805,7 +1805,7 @@
       <c r="F35" s="10" t="n">
         <v>234</v>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
@@ -1824,7 +1824,7 @@
         <f>B35/B33</f>
         <v/>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>1992</t>
         </is>
@@ -1832,7 +1832,7 @@
       <c r="F36" s="10" t="n">
         <v>225</v>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
@@ -1847,11 +1847,11 @@
           <t>Current rated capacity</t>
         </is>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="25">
         <f>Assumptions!B12</f>
         <v/>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>1993</t>
         </is>
@@ -1859,7 +1859,7 @@
       <c r="F37" s="10" t="n">
         <v>202</v>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
@@ -1869,7 +1869,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
@@ -1877,7 +1877,7 @@
       <c r="F38" s="10" t="n">
         <v>203</v>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
@@ -1887,7 +1887,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="E39" s="21" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
@@ -1895,7 +1895,7 @@
       <c r="F39" s="10" t="n">
         <v>182</v>
       </c>
-      <c r="H39" s="21" t="inlineStr">
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
@@ -1905,7 +1905,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="21" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
@@ -1913,7 +1913,7 @@
       <c r="F40" s="10" t="n">
         <v>196</v>
       </c>
-      <c r="H40" s="21" t="inlineStr">
+      <c r="H40" s="22" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
@@ -1923,7 +1923,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="E41" s="21" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
@@ -1931,7 +1931,7 @@
       <c r="F41" s="10" t="n">
         <v>208</v>
       </c>
-      <c r="H41" s="21" t="inlineStr">
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -1941,7 +1941,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="E42" s="21" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>1998</t>
         </is>
@@ -1949,7 +1949,7 @@
       <c r="F42" s="10" t="n">
         <v>198</v>
       </c>
-      <c r="H42" s="21" t="inlineStr">
+      <c r="H42" s="22" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -1959,7 +1959,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="E43" s="21" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
@@ -1967,7 +1967,7 @@
       <c r="F43" s="10" t="n">
         <v>205</v>
       </c>
-      <c r="H43" s="21" t="inlineStr">
+      <c r="H43" s="22" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -1977,7 +1977,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="E44" s="21" t="inlineStr">
+      <c r="E44" s="22" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
@@ -1985,7 +1985,7 @@
       <c r="F44" s="10" t="n">
         <v>195</v>
       </c>
-      <c r="H44" s="21" t="inlineStr">
+      <c r="H44" s="22" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
@@ -1995,7 +1995,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="E45" s="21" t="inlineStr">
+      <c r="E45" s="22" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
@@ -2003,7 +2003,7 @@
       <c r="F45" s="10" t="n">
         <v>195</v>
       </c>
-      <c r="H45" s="21" t="inlineStr">
+      <c r="H45" s="22" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -2013,7 +2013,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="E46" s="21" t="inlineStr">
+      <c r="E46" s="22" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
@@ -2021,7 +2021,7 @@
       <c r="F46" s="10" t="n">
         <v>203</v>
       </c>
-      <c r="H46" s="21" t="inlineStr">
+      <c r="H46" s="22" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -2031,7 +2031,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="E47" s="21" t="inlineStr">
+      <c r="E47" s="22" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
@@ -2039,7 +2039,7 @@
       <c r="F47" s="10" t="n">
         <v>196</v>
       </c>
-      <c r="H47" s="21" t="inlineStr">
+      <c r="H47" s="22" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="E48" s="21" t="inlineStr">
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
@@ -2057,7 +2057,7 @@
       <c r="F48" s="10" t="n">
         <v>206</v>
       </c>
-      <c r="H48" s="21" t="inlineStr">
+      <c r="H48" s="22" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -2067,7 +2067,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="E49" s="21" t="inlineStr">
+      <c r="E49" s="22" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
@@ -2075,7 +2075,7 @@
       <c r="F49" s="10" t="n">
         <v>204</v>
       </c>
-      <c r="H49" s="21" t="inlineStr">
+      <c r="H49" s="22" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -2085,7 +2085,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="E50" s="21" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
@@ -2093,7 +2093,7 @@
       <c r="F50" s="10" t="n">
         <v>199</v>
       </c>
-      <c r="H50" s="21" t="inlineStr">
+      <c r="H50" s="22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -2103,7 +2103,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="E51" s="21" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
@@ -2120,7 +2120,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="25" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>Bourbon County faces a real demographic headwind: flat for fifty years, aging, land-constrained, projected down about 4% by 2040, and outside the Scott and Fayette growth corridor. Organic enrollment growth at NMES is unlikely. The growth case therefore rests on redistricting within the district and cross-county enrollment on quality under House Bill 563, plus the school's academic record and community-anchor value.</t>
         </is>
@@ -2184,57 +2184,57 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>School year</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>'15-16</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>'16-17</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>'17-18</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>'18-19</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>'19-20</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>'20-21</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>'21-22</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>'22-23</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>'23-24</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>'24-25</t>
         </is>
@@ -2276,7 +2276,7 @@
       <c r="K6" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="T6" s="25" t="inlineStr">
+      <c r="T6" s="21" t="inlineStr">
         <is>
           <t>NCES school-level data (as compiled by PublicSchoolReview); 2024-25 = NCES CCD official count</t>
         </is>
@@ -2318,102 +2318,102 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>School (district)</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="M14" s="21" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="22" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O14" s="22" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="P14" s="21" t="inlineStr">
+      <c r="P14" s="22" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="Q14" s="21" t="inlineStr">
+      <c r="Q14" s="22" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="R14" s="21" t="inlineStr">
+      <c r="R14" s="22" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="S14" s="21" t="inlineStr">
+      <c r="S14" s="22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="T14" s="25" t="inlineStr">
+      <c r="T14" s="21" t="inlineStr">
         <is>
           <t>SchoolDigger rendering of KDE test data. No statewide tests in 2020; NMES 2021 not reported. Assessment systems: CATS/KCCT 2007-11, K-PREP 2012-19, KSA 2021-25.</t>
         </is>
@@ -2732,12 +2732,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Kentucky</t>
         </is>
@@ -2755,7 +2755,7 @@
       <c r="C30" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="T30" s="25" t="inlineStr">
+      <c r="T30" s="21" t="inlineStr">
         <is>
           <t>SchoolDigger/KDE; economically disadvantaged composite = 62nd percentile statewide; female = 91st</t>
         </is>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2021 KBE-approved District Facility Plan</t>
+          <t>2021 KBE-approved District Facility Plan. A policy output, not a physical constant: the same building held 261 students in 1988-89. See report Section 7</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3883,6 +3883,13 @@
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Source: FY2023-24 and FY2024-25 audited financial statements. FY2023 shown as reported in the FY2024 audit's comparative statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>What the transfers are: moves between the district's own funds (indirect cost recoveries from grants and self-supporting operations, fund closeouts, and similar interfund items detailed in the audits' fund statements). They cushion the General Fund's bottom line but are not new district revenue, which is why the operating result BEFORE transfers is the honest measure of the structural deficit.</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4011,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Gross avoidable cost</t>
         </is>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="23">
         <f>SUM(B10:B12)</f>
         <v/>
       </c>
@@ -4044,23 +4051,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Total offsets</t>
         </is>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="23">
         <f>SUM(B16:B17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>NET RECURRING GENERAL FUND SAVING</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="24">
         <f>B13-B18</f>
         <v/>
       </c>
@@ -4095,12 +4102,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Students leaving</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Net recurring saving</t>
         </is>
@@ -4236,15 +4243,15 @@
           <t>Transfer students (scenario)</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>Assumptions!B59</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>Assumptions!B60</f>
         <v/>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <f>Assumptions!B61</f>
         <v/>
       </c>
@@ -4345,20 +4352,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Net new recurring revenue</t>
         </is>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="24">
         <f>B8-B9-B10</f>
         <v/>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="24">
         <f>C8-C9-C10</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="24">
         <f>D8-D9-D10</f>
         <v/>
       </c>
@@ -4383,14 +4390,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Upside excluded from this model: tuition, SEEK add-on weights, preschool and day-care expansion, and in-county boundary redistricting, which fills seats with students the district already serves.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Context: NMES enrolled 160 students as recently as 2019-20 (see School_Data) - the growth targets restore recent history, they do not exceed it.</t>
         </is>
@@ -4423,7 +4430,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>A planning scenario, not a routing study. The district holds the geocoded student counts and routing data a true optimization needs; releasing them is a records ask in the report.</t>
         </is>
@@ -4442,7 +4449,7 @@
           <t>NMES enrollment</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -4453,7 +4460,7 @@
           <t>NMES rated capacity</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <f>Assumptions!B12</f>
         <v/>
       </c>
@@ -4515,7 +4522,7 @@
       <c r="B12" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Chosen from families already living closer to NMES than to their assigned school; requires the geocoded counts</t>
         </is>
@@ -4530,7 +4537,7 @@
       <c r="B13" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>SEEK funding follows each transfer; no home-district agreement required since July 2022</t>
         </is>
@@ -4686,23 +4693,23 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>Net recurring benefit, low</t>
         </is>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="24">
         <f>B26-B27+B28*Assumptions!B41</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>Net recurring benefit, high</t>
         </is>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="23">
         <f>B26-B27+B29*Assumptions!B41</f>
         <v/>
       </c>
@@ -4766,21 +4773,21 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>Rezoned students are drawn only from homes closer to NMES than to their assigned school, so bus routes shorten or hold even; the district's routing data would settle it.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Receiving-school relief is booked only as one to two avoided or redeployed sections; grade-by-grade capacities at Bourbon Central and Cane Ridge are a records ask (report Question 3).</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>SEEK for rezoned in-county students is unchanged (same district); only cross-county transfers add revenue.</t>
         </is>
@@ -4813,7 +4820,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Estimates built from public geography (census counts, county land area, highway distances). The district's annual T-1 transportation report, zone map, and geocoded counts are the authoritative dataset; releasing them is a records ask.</t>
         </is>
@@ -4877,7 +4884,7 @@
           <t>North Middletown population, 2020</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>Demographics!B29</f>
         <v/>
       </c>
@@ -4894,11 +4901,11 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Eastern portion of the county; replace with the district's actual zone map</t>
+          <t>Traced from the district's published attendance-zone view (southeast zone); approximate</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4937,7 @@
           <t>NMES elementary students</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -4941,7 +4948,7 @@
           <t>Paris-area elementary students</t>
         </is>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="25">
         <f>Redistricting!B8+Redistricting!B9</f>
         <v/>
       </c>
@@ -4980,9 +4987,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>State law (KRS 157.370) funds transportation on transported pupils per square mile: low density earns a higher per-pupil allotment because it costs more to serve. The statutory calculation has been funded below its own formula in every budget since 2005.</t>
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>State law (KRS 157.370) funds transportation on transported pupils per square mile: low density earns a higher per-pupil allotment because it costs more to serve. Funding history: below the formula for two decades, restored to 90 then 100 percent (on lagged FY2023 costs) in the 2024-2026 budget, then frozen again below formula in the 2026-2028 budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>STATE REVENUE EFFECT: with the appropriation frozen at flat dollars computed on lagged costs, the marginal state reimbursement on NEW busing miles is zero, so closure's added routes are district money. Rebalancing changes no transported-pupil count, so the add-on is unchanged; and the district is not required to transport nonresident transfer students at all (board policy decides).</t>
         </is>
       </c>
     </row>
@@ -5139,23 +5153,23 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Bottom-up added busing cost, low</t>
         </is>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="24">
         <f>B29</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Bottom-up added busing cost, high</t>
         </is>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="23">
         <f>B30+B31*B32</f>
         <v/>
       </c>
@@ -5173,7 +5187,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>The bottom-up estimate lands inside the planning range; the $137,500 midpoint used in the Closure_Model stands. Note what closure does not remove: every square mile of the eastern county stays in the coverage area, with longer rides on it, roughly 15 to 20 added minutes each way on US 460.</t>
         </is>
@@ -5192,7 +5206,7 @@
           <t>Students rezoned to NMES</t>
         </is>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="25">
         <f>Redistricting!B12</f>
         <v/>
       </c>
@@ -5579,16 +5593,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Total identified (ranges overlap; not additive to the penny)</t>
         </is>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="24">
         <f>SUM(B4:B14)</f>
         <v/>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="24">
         <f>SUM(C4:C14)</f>
         <v/>
       </c>
@@ -5754,7 +5768,7 @@
       <c r="E5" s="8" t="n">
         <v>348000</v>
       </c>
-      <c r="F5" s="25" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -5778,7 +5792,7 @@
       <c r="E6" s="8" t="n">
         <v>585000</v>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Audit figures internally inconsistent; maturity typo in audit — district to correct</t>
         </is>
@@ -5806,7 +5820,7 @@
       <c r="E7" s="8" t="n">
         <v>3145000</v>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>Refunded $5,315,000 of 2009 bonds; NPV savings $314,834</t>
         </is>
@@ -5834,7 +5848,7 @@
       <c r="E8" s="8" t="n">
         <v>1560000</v>
       </c>
-      <c r="F8" s="25" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -5858,7 +5872,7 @@
       <c r="E9" s="8" t="n">
         <v>3405000</v>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>Refunded $3,410,000 of 2011 bonds; NPV savings $106,627</t>
         </is>
@@ -5886,7 +5900,7 @@
       <c r="E10" s="8" t="n">
         <v>755000</v>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>Purpose to be confirmed from official statement</t>
         </is>
@@ -5914,23 +5928,23 @@
       <c r="E11" s="8" t="n">
         <v>5945290</v>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>Funds active construction program; purpose to be published</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="24">
         <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
@@ -6067,7 +6081,7 @@
         <f>B23*B24+B25-B26</f>
         <v/>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>Simplified: KDE's official bonding potential statement is the authority and should be published</t>
         </is>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -677,7 +677,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Student density, route-mile arithmetic, and busing cost scenarios: Transport_Geo tab (backs Section 9).</t>
+          <t xml:space="preserve">  Student density, route-mile math, and busing cost scenarios: Transport_Geo tab (backs Section 9).</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -4822,7 +4822,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Estimates built from public geography (census counts, county land area, highway distances). The district's annual T-1 transportation report, zone map, and geocoded counts are the authoritative dataset; releasing them is a records ask.</t>
+          <t>Zone geometry is official: NCES School Attendance Boundary Survey, 2015-16 collection (build/sabs_zones.json in the repository). Cost inputs remain labeled estimates; the district's annual T-1 transportation report and geocoded counts replace them.</t>
         </is>
       </c>
     </row>
@@ -4900,12 +4900,12 @@
           <t>NMES zone share of county area</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
-        <v>0.36</v>
+      <c r="B9" s="13" t="n">
+        <v>0.38</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Traced from the district's published attendance-zone view (southeast zone); approximate</t>
+          <t>Official: NCES SABS 2015-16, NMES zone 110.3 sq mi of the 289.1 sq mi zone total</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +153,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4414,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -4790,6 +4791,13 @@
       <c r="A42" s="21" t="inlineStr">
         <is>
           <t>SEEK for rezoned in-county students is unchanged (same district); only cross-county transfers add revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>Per-student figures pair the latest published spending year (2023-24) with the current enrollment count; refresh when the 2024-25 spending data posts.</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5336,6 +5344,136 @@
       <c r="B52" s="18">
         <f>Assumptions!B42*Assumptions!B44</f>
         <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ACTUAL DISTANCES, COMPUTED FROM THE OFFICIAL ZONE GEOMETRY (build/zone_distances.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Straight-line, NMES to the Paris schools (miles)</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Great-circle between the school points</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Measured road distance, US 460 (miles)</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>The one pair that can be measured exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Implied road factor on the measured pair</t>
+        </is>
+      </c>
+      <c r="B57" s="29">
+        <f>B56/B55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Road factor applied elsewhere (conservative)</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Area-average added distance under closure, one way, straight-line</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Grid average over the official NMES zone (812 sample points)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Area-average added distance, road</t>
+        </is>
+      </c>
+      <c r="B60" s="20">
+        <f>B59*B58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Farthest corner of the zone, straight-line to Paris / to NMES</t>
+        </is>
+      </c>
+      <c r="B61" s="28" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>8.3 miles to NMES; near the Nicholas County line</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Farthest corner by road: to Paris / to NMES (miles)</t>
+        </is>
+      </c>
+      <c r="B62" s="26">
+        <f>ROUND(B61*B58,0)</f>
+        <v/>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>About 18 versus 10; the district's routing data would give exact times</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Share of the zone's area closer to NMES than to Paris</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Computed on the official boundary; the map's whole point in one number</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6077,7 +6215,7 @@
           <t>Annual restricted margin available for new debt (illustrative)</t>
         </is>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <f>B23*B24+B25-B26</f>
         <v/>
       </c>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -529,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Saving North Middletown Elementary School — Financial Model</t>
+          <t>Saving North Middletown Elementary School: Financial Model</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Prepared by a former NMES King working alongside Fable 5, an AI research assistant from Anthropic. Estimates are labeled; every figure</t>
+          <t>Prepared by a former NMES King working alongside Claude, an AI research assistant from Anthropic. Estimates are labeled; every figure</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edit blue cells. Yellow cells are judgment calls/estimates — the district should replace them with actuals.</t>
+          <t>Edit blue cells. Yellow cells are judgment calls/estimates; the district should replace them with actuals.</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Estimate — replace with district payroll data</t>
+          <t>Estimate; replace with district payroll data</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>CLOSURE SCENARIO JUDGMENTS (estimates — district must replace with actuals)</t>
+          <t>CLOSURE SCENARIO JUDGMENTS (estimates; district must replace with actuals)</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Estimate — assumes building sold or repurposed</t>
+          <t>Estimate; assumes building sold or repurposed</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Estimate — via attrition only</t>
+          <t>Estimate; via attrition only</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Estimate — midpoint of $75K-$200K</t>
+          <t>Estimate; midpoint of $75K-$200K</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Judgment call — see sensitivity table</t>
+          <t>Judgment call; see sensitivity table</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Scenario lever — capped at open seats in model</t>
+          <t>Scenario lever; capped at open seats in model</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Estimate — supplies/materials</t>
+          <t>Estimate; supplies/materials</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gross site cost is not net saving — students, teachers, and their SEEK funding move to receiving schools.</t>
+          <t>Gross site cost is not net saving; students, teachers, and their SEEK funding move to receiving schools.</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>WKYT, July 2026 — treated as a claim to verify</t>
+          <t>WKYT, July 2026; treated as a claim to verify</t>
         </is>
       </c>
     </row>
@@ -5360,11 +5360,11 @@
         </is>
       </c>
       <c r="B55" s="28" t="n">
-        <v>8.9</v>
+        <v>8.871</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Great-circle between the school points</t>
+          <t>Great-circle between the school points; unrounded so derived cells match build/zone_distances.json</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Road factor applied elsewhere (conservative)</t>
+          <t>Road factor applied elsewhere (the measured US 460 pair implies 1.13)</t>
         </is>
       </c>
       <c r="B58" s="27" t="n">
@@ -5411,11 +5411,11 @@
         </is>
       </c>
       <c r="B59" s="28" t="n">
-        <v>3.3</v>
+        <v>3.271</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Grid average over the official NMES zone (812 sample points)</t>
+          <t>Grid average over the official NMES zone (812 sample points); unrounded input, displays to one decimal</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Outstanding Bonds — Bourbon County School District Finance Corporation</t>
+          <t>Outstanding Bonds: Bourbon County School District Finance Corporation</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>Audit figures internally inconsistent; maturity typo in audit — district to correct</t>
+          <t>Audit figures internally inconsistent; maturity typo in audit; district to correct</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -17,9 +17,10 @@
     <sheet name="Alternatives" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Debt_Service" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Runway" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Tax_History" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Demographics" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="School_Data" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Scenarios" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Tax_History" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Demographics" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="School_Data" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -878,6 +879,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Four Complete Plans, Compared (illustrative five-year view)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Each row is a full operating plan under this workbook's stated assumptions; the district should replace them with actuals. One-time closure transition costs (moving, receiving-school additions, building carrying or disposal) have not been published and are not included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Recurring GF impact ($/yr, by yr 3)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Projected FY2029 balance</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>One-time costs</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>What it requires and risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1. Keep NMES open, current trajectory</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <f>Runway!E5</f>
+        <v/>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>No decisions; reserves cross below zero on the straight line and the gap remains unaddressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2. Close NMES and consolidate</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>Closure_Model!B20</f>
+        <v/>
+      </c>
+      <c r="C6" s="9">
+        <f>Runway!E7</f>
+        <v/>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Unpublished</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Closure vote; covers 13.6% of the gap (24.2% in the district-favorable case); longer rides; enrollment-loss risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>3. Keep NMES open, rebalance and grow</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>Redistricting!B30</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>GF_Summary!D9-4*GF_Summary!D16+3*Redistricting!B30</f>
+        <v/>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Minimal (boundary process)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Board boundary action and HB 563 recruitment; academic upside; does not close the gap alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>4. Districtwide recovery plan (menu plus levy)</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>Alternatives!B21</f>
+        <v/>
+      </c>
+      <c r="C8" s="9">
+        <f>Runway!E6</f>
+        <v/>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Varies by measure</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Revenue votes, administrative rollback, and implementation discipline; keeps every school open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Reading: the question before the board is not closure versus no closure. It is which complete plan produces the best verified five-year result. Plan 2 buys roughly one extra year of runway; Plan 4 restores balance. Plans 3 and 4 combine.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1399,7 +1568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2132,7 +2301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5487,13 +5656,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5503,6 +5674,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Type separates new recurring revenue from recurring cost reductions; confidence names what would move each line from estimate to plan.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -5524,6 +5702,16 @@
           <t>Basis</t>
         </is>
       </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Confidence / what firms it up</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -5543,6 +5731,16 @@
           <t>Low = 4% of FY2025 GF property tax; high allows base growth</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>High; board authority every August, no recall exposure</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5561,6 +5759,16 @@
           <t>25-50% of FY2025 delinquency of $239,126 (2.4% of certified yield)</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs an aging and collection analysis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -5579,6 +5787,16 @@
           <t>Approx. SEEK value per 1% of ADA</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs an attendance improvement plan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -5598,6 +5816,16 @@
           <t>Low = positions x loaded cost</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs a position-level staffing plan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5617,6 +5845,16 @@
           <t>Low = rollback share of 2-yr district-admin growth</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs position- and vendor-level detail</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -5637,6 +5875,16 @@
           <t>5-10% of FY2025 transport expense</t>
         </is>
       </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs a local route model (T-1 data requested)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -5655,6 +5903,16 @@
           <t>Typical under-collected federal reimbursements</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Low; needs evidence current claims are being missed</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5673,6 +5931,16 @@
           <t>10-25% of utilities; authorized by 702 KAR 4:160</t>
         </is>
       </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Medium; contracts are structured to self-fund</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -5691,6 +5959,16 @@
           <t>Transport, food service, back office</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Low; needs an interlocal feasibility study</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -5711,6 +5989,16 @@
           <t>Boundary rebalancing and cross-county scenario, Redistricting tab</t>
         </is>
       </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>New revenue, net of costs</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>High; board boundary authority, math on Redistricting tab</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -5727,6 +6015,16 @@
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Six or seven sections instead of nine, via attrition</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs a staffing and grade-band plan</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -933,7 +933,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1. Keep NMES open, current trajectory</t>
+          <t>1. Districtwide status quo (change nothing anywhere)</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>No decisions; reserves cross below zero on the straight line and the gap remains unaddressed</t>
+          <t>No decisions; the districtwide gap, which NMES did not cause, drains reserves below zero with or without the school</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -879,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -982,57 +982,32 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>3. Keep NMES open, rebalance and grow</t>
+          <t>3. Districtwide recovery plan (menu plus levy; includes rebalancing and growing NMES)</t>
         </is>
       </c>
       <c r="B7" s="18">
-        <f>Redistricting!B30</f>
+        <f>Alternatives!B21</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>GF_Summary!D9-4*GF_Summary!D16+3*Redistricting!B30</f>
+        <f>Runway!E6</f>
         <v/>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Minimal (boundary process)</t>
+          <t>Varies by measure</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Board boundary action and HB 563 recruitment; academic upside; does not close the gap alone</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>4. Districtwide recovery plan (menu plus levy)</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>Alternatives!B21</f>
-        <v/>
-      </c>
-      <c r="C8" s="9">
-        <f>Runway!E6</f>
-        <v/>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Varies by measure</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Revenue votes, administrative rollback, and implementation discipline; keeps every school open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Reading: the question before the board is not closure versus no closure. It is which complete plan produces the best verified five-year result. Plan 2 buys roughly one extra year of runway; Plan 4 restores balance. Plans 3 and 4 combine.</t>
+          <t>Revenue votes, administrative rollback, boundary action and HB 563 recruitment, implementation discipline; every school stays open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Reading: the question before the board is not closure versus no closure. It is which complete plan produces the best verified five-year result. Plan 2 buys roughly one extra year of runway; Plan 3 restores balance while keeping every school open. The rebalance-and-grow scenario (Redistricting tab) is one line inside Plan 3's menu.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Tax_History" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Demographics" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="School_Data" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Facility_Plans" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -122,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +157,7 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2980,6 +2982,372 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>What the District's Own Facility Plans Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Sources: District Facilities Plan, KBE approval June 2013 (Wayback Machine capture) and District Facility Plan, KBE approval August 2021 (currently posted; next plan due June 2025). Both archived in this repository under build/. Figures read enrollment/capacity; the 2021 preschool line (272/200, with the plan's note of 80 full-day plus 192 half-day students) confirms the order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>2013 enr</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>2013 cap</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>2021 enr</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>2021 cap</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bourbon County High School</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>881</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>637</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>799</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>704</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Expansion built; CTC addition was the 2022-24 in-biennium priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bourbon County Middle School</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>616</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>515</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>640</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>641</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Bourbon Central Elementary</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>602</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>564</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>535</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>521</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Plan lists a to-become capacity of 549 after an addition not yet built</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Cane Ridge Elementary</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>461</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>480</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>422</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Rated capacity written down 78 seats between plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>North Middletown Elementary</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>161</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Rated capacity written down 24 seats; building held 261 students at the 1989 peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Preschool/Head Start Center</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>296</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>272</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Over capacity in both plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>RECEIVING CAPACITY TODAY (2021 plan capacities vs 2024-25 enrollment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central open seats at rated 521</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>E7-Redistricting!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge students over rated 422</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>Redistricting!B9-E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Net uncommitted seats at both receiving schools</t>
+        </is>
+      </c>
+      <c r="B15" s="31">
+        <f>B13-B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>NMES students needing seats on closure</t>
+        </is>
+      </c>
+      <c r="B16" s="25">
+        <f>Assumptions!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Shortfall if closure proceeds today</t>
+        </is>
+      </c>
+      <c r="B17" s="31">
+        <f>B16-B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Net seats even after Bourbon Central's planned (unbuilt) expansion to 549</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>549-Redistricting!B8-B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>NMES INVESTMENT RECORD IN THE PLANS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2013 plan: NMES major renovation priced (HVAC, media center, kitchen, security vestibule, gym)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>1594872</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>239139</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>86959</v>
+      </c>
+      <c r="E21" s="9">
+        <f>SUM(B21:D21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Base renovation + special ed classroom + family resource center</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2021 plan: NMES need re-priced (life safety + accessibility ramp/elevator + major renovation)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>317660</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>325000</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>3617530</v>
+      </c>
+      <c r="E22" s="9">
+        <f>SUM(B22:D22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>All scheduled after the 2022-24 biennium; the in-biennium priority was the HS Career &amp; Technical Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2021 plan: HS Career &amp; Technical Center, in-biennium new construction</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>227149+1447694+1150886+1075170+772305+832878+1150886</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2021 plan: total district facility need</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>43389464</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Reading: the plans rate the receiving schools at 521 and 422 seats. At current enrollment that is 62 open at Bourbon Central and 31 over at Cane Ridge, a net 31 uncommitted seats for 128 children. NMES renovation needs were priced in 2013 and re-priced higher in 2021, each time scheduled behind other work. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Plan lists a to-become capacity of 549 after an addition not yet built</t>
+          <t>Rating today is 549, the plan's to-become capacity with its addition</t>
         </is>
       </c>
     </row>
@@ -3188,18 +3188,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>RECEIVING CAPACITY TODAY (2021 plan capacities vs 2024-25 enrollment)</t>
+          <t>RECEIVING CAPACITY TODAY (current ratings vs 2024-25 enrollment)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bourbon Central open seats at rated 521</t>
+          <t>Bourbon Central open seats at its current rated 549</t>
         </is>
       </c>
       <c r="B13" s="11">
-        <f>E7-Redistricting!B8</f>
+        <f>549-Redistricting!B8</f>
         <v/>
       </c>
     </row>
@@ -3250,11 +3250,11 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Net seats even after Bourbon Central's planned (unbuilt) expansion to 549</t>
+          <t>Sensitivity: net seats at the 2021 plan's as-printed 521 for Bourbon Central</t>
         </is>
       </c>
       <c r="B18" s="11">
-        <f>549-Redistricting!B8-B14</f>
+        <f>E7-Redistricting!B8-B14</f>
         <v/>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Reading: the plans rate the receiving schools at 521 and 422 seats. At current enrollment that is 62 open at Bourbon Central and 31 over at Cane Ridge, a net 31 uncommitted seats for 128 children. NMES renovation needs were priced in 2013 and re-priced higher in 2021, each time scheduled behind other work. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
+          <t>Reading: the receiving schools' current ratings are 549 (Bourbon Central) and 422 (Cane Ridge). At current enrollment that is 90 open at Bourbon Central and 31 over at Cane Ridge, a net 59 uncommitted seats for 128 children (net 31 at the 2021 plan's as-printed 521). NMES renovation needs were priced in 2013 and re-priced higher in 2021, each time scheduled behind other work. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -952,7 +952,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>No decisions; the districtwide gap, which NMES did not cause, drains reserves below zero with or without the school</t>
+          <t>No decisions; the districtwide drawdown, which NMES did not cause, simply continues on the straight line with or without the school</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -3109,7 +3109,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Rating today is 549, the plan's to-become capacity with its addition</t>
+          <t>Rated capacity 549, reflecting the addition in the 2021 plan</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bourbon Central open seats at its current rated 549</t>
+          <t>Bourbon Central open seats at rated 549</t>
         </is>
       </c>
       <c r="B13" s="11">
@@ -3247,17 +3247,6 @@
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Sensitivity: net seats at the 2021 plan's as-printed 521 for Bourbon Central</t>
-        </is>
-      </c>
-      <c r="B18" s="11">
-        <f>E7-Redistricting!B8-B14</f>
-        <v/>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -3339,7 +3328,7 @@
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Reading: the receiving schools' current ratings are 549 (Bourbon Central) and 422 (Cane Ridge). At current enrollment that is 90 open at Bourbon Central and 31 over at Cane Ridge, a net 59 uncommitted seats for 128 children (net 31 at the 2021 plan's as-printed 521). NMES renovation needs were priced in 2013 and re-priced higher in 2021, each time scheduled behind other work. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
+          <t>Reading: the receiving schools' rated capacities are 549 (Bourbon Central) and 422 (Cane Ridge). At current enrollment that is 90 open at Bourbon Central and 31 over at Cane Ridge, a net 59 uncommitted seats for 128 children. NMES renovation needs were priced in 2013 and re-priced higher in 2021, each time scheduled behind other work. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Revenue votes, administrative rollback, boundary action and HB 563 recruitment, implementation discipline; every school stays open</t>
+          <t>Revenue votes, administrative rollback, boundary action, HB 563 recruitment and a signature advanced-learners program at NMES, implementation discipline; every school stays open</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -894,7 +894,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Four Complete Plans, Compared (illustrative five-year view)</t>
+          <t>Three Complete Plans, Compared (illustrative five-year view)</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Expansion built; CTC addition was the 2022-24 in-biennium priority</t>
+          <t>Rating rose 637 to 704 between plans; the CTC addition was the 2022-24 in-biennium priority</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>All scheduled after the 2022-24 biennium; the in-biennium priority was the HS Career &amp; Technical Center</t>
+          <t>Life safety and accessibility ($642,660) within the 2022-24 biennium; the $3.62M major renovation after it; the biennium's headline priority was the HS Career &amp; Technical Center</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Reading: the receiving schools' rated capacities are 549 (Bourbon Central) and 422 (Cane Ridge). At current enrollment that is 90 open at Bourbon Central and 31 over at Cane Ridge, a net 59 uncommitted seats for 128 children. NMES renovation needs were priced in 2013 and re-priced higher in 2021, each time scheduled behind other work. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
+          <t>Reading: the receiving schools' rated capacities are 549 (Bourbon Central) and 422 (Cane Ridge). At current enrollment that is 90 open at Bourbon Central and 31 over at Cane Ridge, a net 59 uncommitted seats for 128 children. NMES's major renovation was priced in 2013 and re-priced higher in 2021, each time scheduled after the then-current biennium. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Revenue votes, administrative rollback, boundary action, HB 563 recruitment and a signature advanced-learners program at NMES, implementation discipline; every school stays open</t>
+          <t>Revenue votes, administrative rollback, boundary action, HB 563 recruitment and a signature program at NMES (advanced learners is one option), implementation discipline; every school stays open</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,6 +158,7 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2988,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3157,7 +3158,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Rated capacity written down 24 seats; building held 261 students at the 1989 peak</t>
+          <t>Written down again to 154 in the 2026 draft; building held 261 students at the 1989 peak</t>
         </is>
       </c>
     </row>
@@ -3329,6 +3330,115 @@
       <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Reading: the receiving schools' rated capacities are 549 (Bourbon Central) and 422 (Cane Ridge). At current enrollment that is 90 open at Bourbon Central and 31 over at Cane Ridge, a net 59 uncommitted seats for 128 children. NMES's major renovation was priced in 2013 and re-priced higher in 2021, each time scheduled after the then-current biennium. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>THE 2026 DRAFT (presented July 15, 2026, before the committee's amendment; KDE approval date TBD; KFICS capacity basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>2023-24 SAAR</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Draft capacity (KFICS)</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Change vs 2021 rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>491</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>640</v>
+      </c>
+      <c r="D30" s="11">
+        <f>C30-549</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>461</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>547</v>
+      </c>
+      <c r="D31" s="11">
+        <f>C31-E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>128</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="D32" s="11">
+        <f>C32-E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Paper seats added at the receiving schools, with the draft's new-construction sections reading None</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>D30+D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>NMES fill rate even at the draft's own 154 rating</t>
+        </is>
+      </c>
+      <c r="B34" s="32">
+        <f>B32/C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>As presented, the draft still listed North Middletown as Permanent (PS-5). Its headline 2026-28 priority is an $18,600,946 major renovation of the high school's 1968 and 1981 sections. Annotated attendee copy archived as build/dfp_2026_draft_excerpt.png.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -2989,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3439,6 +3439,231 @@
       <c r="A35" s="21" t="inlineStr">
         <is>
           <t>As presented, the draft still listed North Middletown as Permanent (PS-5). Its headline 2026-28 priority is an $18,600,946 major renovation of the high school's 1968 and 1981 sections. Annotated attendee copy archived as build/dfp_2026_draft_excerpt.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>KFICS ASSESSMENT (RossTarrant Architects, presented July 2026; slides archived as build/kfics_assessment.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Condition need</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Instructional deficiency</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>Total (as printed)</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>Slide capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County High School</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>22300342</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>5188113</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>27488455</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County Middle School</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>19132586</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>3286105</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>22418692</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge Elementary</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>10313658</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>4073936</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>14387595</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central Elementary</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>7214895</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>1615951</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>8840267</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown Elementary</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>5648434</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>2881659</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>8530093</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Preschool/Head Start Center</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>1518664</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>6343032</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>7861696</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Agriculture Building (part of BCHS)</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>1825444</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>1825444</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>School centers total</t>
+        </is>
+      </c>
+      <c r="B46" s="23">
+        <f>SUM(D39:D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Support facilities total (slide)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>7089052</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>District total need</t>
+        </is>
+      </c>
+      <c r="B48" s="23">
+        <f>B46+B47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Receiving schools combined (Bourbon Central + Cane Ridge)</t>
+        </is>
+      </c>
+      <c r="B49" s="23">
+        <f>D41+D42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Net receiving seats at the slides' own capacities (499 and 397)</t>
+        </is>
+      </c>
+      <c r="B50" s="31">
+        <f>(499-Redistricting!B8)-(Redistricting!B9-397)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>Notes: components and totals as printed on the slides; Bourbon Central's printed components sum $9,421 below its printed total. The slides' receiving-school capacities (499, 397) differ from the 2026 draft DFP table (640, 547) and from the approved 2021 plan (549 with addition, 422): three documents, three capacity sets for the same buildings. NMES total need is second lowest among the district's schools.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -902,7 +902,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Each row is a full operating plan under this workbook's stated assumptions; the district should replace them with actuals. One-time closure transition costs (moving, receiving-school additions, building carrying or disposal) have not been published and are not included.</t>
+          <t>Each row is a full operating plan under this workbook's stated assumptions; the district should replace them with actuals. One-time closure transition costs (moving, receiving-school additions, building carrying or disposal) have not been published and are not included. Coverage percentages use the $2.65M before-transfers gap; these balance projections use the net drawdown after transfers.</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="B4" s="18">
-        <f>Assumptions!B35*Assumptions!B36</f>
+        <f>Tax_History!B50</f>
         <v/>
       </c>
       <c r="C4" s="8" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Low = 4% of FY2025 GF property tax; high allows base growth</t>
+          <t>Low = year-one 4% option on the full levied base (matches the levy analysis); high allows base growth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6779,6 +6779,13 @@
       <c r="B23" s="18">
         <f>Closure_Model!B20</f>
         <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Reading: raw row sums run about $1.8M to $3.1M; the published $1.1M to $2.1M band takes roughly two thirds of them as a haircut for overlap and implementation risk. Coverage percentages elsewhere measure against the $2.65M gap before transfers; the Runway and Scenarios tabs run on the net drawdown after transfers.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +157,7 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -2285,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2936,9 +2937,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Science, proficient or better</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>KDE 2024-25 KSA, PERCENT PROFICIENT OR DISTINGUISHED, ALL STUDENTS (build/kde_ksa_2024_25.json)</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
@@ -2949,33 +2950,156 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Composite: economically disadvantaged students</t>
-        </is>
-      </c>
-      <c r="B34" s="28" t="n">
-        <v>57.1</v>
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>NMES</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Bourbon Central</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Paris Elem.</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>KY elementary avg</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Composite: female students</t>
-        </is>
-      </c>
-      <c r="B35" s="28" t="n">
-        <v>85.7</v>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Composite: male students</t>
-        </is>
-      </c>
-      <c r="B36" s="28" t="n">
-        <v>28.8</v>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Social Studies</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Combined Writing</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>NMES is first among all four county elementary schools in every subject and beats the statewide elementary average in science and writing. Asterisks = state-suppressed cells.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3221,7 +3345,7 @@
           <t>Net uncommitted seats at both receiving schools</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>B13-B14</f>
         <v/>
       </c>
@@ -3243,7 +3367,7 @@
           <t>Shortfall if closure proceeds today</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>B16-B15</f>
         <v/>
       </c>
@@ -3419,7 +3543,7 @@
           <t>Paper seats added at the receiving schools, with the draft's new-construction sections reading None</t>
         </is>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="32">
         <f>D30+D31</f>
         <v/>
       </c>
@@ -3430,7 +3554,7 @@
           <t>NMES fill rate even at the draft's own 154 rating</t>
         </is>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="33">
         <f>B32/C32</f>
         <v/>
       </c>
@@ -3655,7 +3779,7 @@
           <t>Net receiving seats at the slides' own capacities (499 and 397)</t>
         </is>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="32">
         <f>(499-Redistricting!B8)-(Redistricting!B9-397)</f>
         <v/>
       </c>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -2286,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inputs (blue) transcribed from public sources. Scores are SchoolDigger's normalized 0-100 'Average Standard Score' from KDE test data - not KDE's official rating. Confirm vs KDE Open House datasets before formal submission.</t>
+          <t>Inputs (blue) transcribed from public sources. The 2007-2025 series below is SchoolDigger's normalized 0-100 index built from KDE test data (a third-party rendering, kept for context). KDE's own official record, pulled directly from the department's historical files, is in the KDE OFFICIAL HISTORY block below and governs every claim in the report.</t>
         </is>
       </c>
     </row>
@@ -3099,6 +3099,692 @@
       <c r="A41" s="21" t="inlineStr">
         <is>
           <t>NMES is first among all four county elementary schools in every subject and beats the statewide elementary average in science and writing. Asterisks = state-suppressed cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>KDE OFFICIAL HISTORY, 2011-12 TO 2024-25 (build/kde_scores_history.json)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Percent proficient or distinguished</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>'11-12</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>'12-13</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>'13-14</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>'14-15</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>'15-16</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>'16-17</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>'17-18</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>'18-19</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>'20-21</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="inlineStr">
+        <is>
+          <t>'21-22</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr">
+        <is>
+          <t>'22-23</t>
+        </is>
+      </c>
+      <c r="M44" s="22" t="inlineStr">
+        <is>
+          <t>'23-24</t>
+        </is>
+      </c>
+      <c r="N44" s="22" t="inlineStr">
+        <is>
+          <t>'24-25</t>
+        </is>
+      </c>
+      <c r="T44" s="21" t="inlineStr">
+        <is>
+          <t>KDE historical accountability files (all students, elementary level); 2017-19 recovered from Wayback captures of KDE's retired download endpoint. 2019-20 canceled statewide; 2020-21 was a limited COVID administration. CATS-era files (2006-2011) are available from KDE by data request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Reading: North Middletown</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="C45" s="28" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D45" s="28" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E45" s="28" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F45" s="28" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="G45" s="28" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H45" s="28" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="J45" s="28" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K45" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="L45" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="M45" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Reading: Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="C46" s="28" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="D46" s="28" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="E46" s="28" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="F46" s="28" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="G46" s="28" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="H46" s="28" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="J46" s="28" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="L46" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="M46" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Reading: Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B47" s="28" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="C47" s="28" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D47" s="28" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="E47" s="28" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="F47" s="28" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G47" s="28" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>52</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J47" s="28" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v>44</v>
+      </c>
+      <c r="L47" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="M47" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Reading: Paris Elementary</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="C48" s="28" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D48" s="28" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E48" s="28" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F48" s="28" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G48" s="28" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J48" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="K48" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="L48" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="M48" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Mathematics: North Middletown</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="C49" s="28" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D49" s="28" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="E49" s="28" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="G49" s="28" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="J49" s="28" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="K49" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="L49" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="M49" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Mathematics: Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="D50" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="E50" s="28" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F50" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="G50" s="28" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="J50" s="28" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K50" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="L50" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="M50" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Mathematics: Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="C51" s="28" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="D51" s="28" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="E51" s="28" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G51" s="28" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="J51" s="28" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="K51" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="L51" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="M51" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Mathematics: Paris Elementary</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="C52" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D52" s="28" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E52" s="28" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F52" s="28" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="G52" s="28" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="J52" s="28" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K52" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="L52" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="M52" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>NMES led the county in mathematics in every pre-COVID administration on record, 2011-12 through 2018-19: eight straight years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Official overall score</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>'11-12</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>'12-13</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>'13-14</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>'14-15</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>'15-16</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="inlineStr">
+        <is>
+          <t>'16-17</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>'17-18</t>
+        </is>
+      </c>
+      <c r="I55" s="22" t="inlineStr">
+        <is>
+          <t>'18-19</t>
+        </is>
+      </c>
+      <c r="J55" s="22" t="inlineStr">
+        <is>
+          <t>'20-21</t>
+        </is>
+      </c>
+      <c r="K55" s="22" t="inlineStr">
+        <is>
+          <t>'21-22</t>
+        </is>
+      </c>
+      <c r="L55" s="22" t="inlineStr">
+        <is>
+          <t>'22-23</t>
+        </is>
+      </c>
+      <c r="M55" s="22" t="inlineStr">
+        <is>
+          <t>'23-24</t>
+        </is>
+      </c>
+      <c r="N55" s="22" t="inlineStr">
+        <is>
+          <t>'24-25</t>
+        </is>
+      </c>
+      <c r="T55" s="21" t="inlineStr">
+        <is>
+          <t>Unbridled Learning overall score 2011-12 to 2015-16 (state classifications noted below); KSA overall indicator rate 2021-22 to 2024-25. The two scales are not comparable to each other. No overall score was issued 2016-17 through 2020-21 by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="C56" s="28" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="D56" s="28" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E56" s="28" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="F56" s="28" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="K56" s="28" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="L56" s="28" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="M56" s="28" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="N56" s="28" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="C57" s="28" t="n">
+        <v>63</v>
+      </c>
+      <c r="D57" s="28" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E57" s="28" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F57" s="28" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="K57" s="28" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="L57" s="28" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="M57" s="28" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="N57" s="28" t="n">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="C58" s="28" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="D58" s="28" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="E58" s="28" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="F58" s="28" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="K58" s="28" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="L58" s="28" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="M58" s="28" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="N58" s="28" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Paris Elementary</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="C59" s="28" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D59" s="28" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="E59" s="28" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F59" s="28" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="K59" s="28" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="L59" s="28" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="M59" s="28" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="N59" s="28" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>Classifications: NMES rated Proficient 2012-2015 and Distinguished in 2015-16 at 79.1, the county's only Distinguished elementary rating in the files retrieved. In 2023-24 NMES posted 74.5, first in the county by 14 points. Bourbon Central is federally identified for Targeted Support and Improvement (disability group) in 2024-25; Cane Ridge carried the same designation in 2021-22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
+        <is>
+          <t>Third-party check: the SchoolDigger index above correlates about 0.9 with these official results for Bourbon Central and Cane Ridge but only weakly for NMES, and it names the wrong county leader in three of the ten overlapping years. The official record governs.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -3777,7 +3777,7 @@
     <row r="60">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>Classifications: NMES rated Proficient 2012-2015 and Distinguished in 2015-16 at 79.1, the county's only Distinguished elementary rating in the files retrieved. In 2023-24 NMES posted 74.5, first in the county by 14 points. Bourbon Central is federally identified for Targeted Support and Improvement (disability group) in 2024-25; Cane Ridge carried the same designation in 2021-22.</t>
+          <t>Classifications: NMES rated Proficient 2012-2015 and Distinguished in 2015-16 at 79.1, the county's only Distinguished elementary rating in the files retrieved. In 2023-24 NMES posted 74.5, first in the county by 14 points.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1464,16 +1464,16 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Base: FY2025 actual real + personal collections</t>
+          <t>Base: FY2025 General Fund real + personal collections</t>
         </is>
       </c>
       <c r="B48" s="18">
-        <f>C43</f>
+        <f>B32</f>
         <v/>
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
-          <t>Basis: 4% more revenue from EXISTING real + personal property than the compensating rate; new property excluded (upside); motor vehicle separate; recall applies only above 4%.</t>
+          <t>Basis: 4% more revenue from EXISTING real + personal property than the compensating rate, on the GENERAL FUND levy only. The restricted building-fund (FSPK, $2,052,786) and debt levies are excluded because that money cannot pay operating costs, the same restricted-funds rule this report applies to closure. New property excluded (upside); motor vehicle separate; recall applies only above 4%.</t>
         </is>
       </c>
     </row>
@@ -5722,11 +5722,15 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>As a share of the FY2025 structural deficit</t>
+          <t>Share of the structural deficit ($2.65M) | of the reserve drawdown ($1.15M)</t>
         </is>
       </c>
       <c r="B21" s="19">
         <f>B20/(Assumptions!B24-Assumptions!B21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="19">
+        <f>B20/GF_Summary!D16</f>
         <v/>
       </c>
     </row>
@@ -5824,11 +5828,15 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>As a share of the FY2025 structural deficit</t>
+          <t>Share of the structural deficit ($2.65M) | of the reserve drawdown ($1.15M)</t>
         </is>
       </c>
       <c r="B35" s="19">
         <f>B34/(Assumptions!B24-Assumptions!B21)</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>B34/GF_Summary!D16</f>
         <v/>
       </c>
     </row>
@@ -7201,11 +7209,11 @@
         <v/>
       </c>
       <c r="C4" s="8" t="n">
-        <v>450000</v>
+        <v>375000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Low = year-one 4% option on the full levied base (matches the levy analysis); high allows base growth</t>
+          <t>Low = year-one 4% option on the General Fund levied base (matches the levy analysis); high allows base growth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7594,7 +7602,7 @@
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
-          <t>Reading: raw row sums run about $1.8M to $3.1M; the published $1.1M to $2.1M band takes roughly two thirds of them as a haircut for overlap and implementation risk. Coverage percentages elsewhere measure against the $2.65M gap before transfers; the Runway and Scenarios tabs run on the net drawdown after transfers.</t>
+          <t>Reading: raw row sums run about $1.7M to $3.0M; the published $1.1M to $2.1M band takes roughly two thirds of them as a haircut for overlap and implementation risk. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -7141,7 +7141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7486,123 +7486,95 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>NMES multi-age reorganization</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>170000</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>255000</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Six or seven sections instead of nine, via attrition</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Cost reduction</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs a staffing and grade-band plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Total identified (ranges overlap; not additive to the penny)</t>
         </is>
       </c>
-      <c r="B15" s="24">
-        <f>SUM(B4:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="24">
-        <f>SUM(C4:C14)</f>
-        <v/>
+      <c r="B14" s="24">
+        <f>SUM(B4:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>SUM(C4:C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>COMPARISON</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Package midpoint (raw sum of ranges)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>(B14+C14)/2</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Package midpoint (raw sum of ranges)</t>
-        </is>
-      </c>
-      <c r="B18" s="9">
-        <f>(B15+C15)/2</f>
-        <v/>
+          <t>Conservative combined estimate, low (haircut for overlap)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>1100000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, low (haircut for overlap)</t>
+          <t>Conservative combined estimate, high</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>1100000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, high</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n">
-        <v>2100000</v>
+          <t>Conservative midpoint (used in Runway sheet)</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>(B18+B19)/2</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Conservative midpoint (used in Runway sheet)</t>
-        </is>
-      </c>
-      <c r="B21" s="9">
-        <f>(B19+B20)/2</f>
+          <t>Average annual GF drawdown (FY2024-25)</t>
+        </is>
+      </c>
+      <c r="B21" s="18">
+        <f>GF_Summary!D16</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Average annual GF drawdown (FY2024-25)</t>
+          <t>Closure net saving (base case)</t>
         </is>
       </c>
       <c r="B22" s="18">
-        <f>GF_Summary!D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Closure net saving (base case)</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
         <f>Closure_Model!B20</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Reading: raw row sums run about $1.7M to $3.0M; the published $1.1M to $2.1M band takes roughly two thirds of them as a haircut for overlap and implementation risk. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Reading: raw row sums run about $1.6M to $2.8M; the published $1.1M to $2.1M band applies a conservative haircut for overlap and implementation risk. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +157,7 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2955,7 +2956,7 @@
           <t>Subject</t>
         </is>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
@@ -4031,7 +4032,7 @@
           <t>Net uncommitted seats at both receiving schools</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <f>B13-B14</f>
         <v/>
       </c>
@@ -4053,7 +4054,7 @@
           <t>Shortfall if closure proceeds today</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="33">
         <f>B16-B15</f>
         <v/>
       </c>
@@ -4229,7 +4230,7 @@
           <t>Paper seats added at the receiving schools, with the draft's new-construction sections reading None</t>
         </is>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="33">
         <f>D30+D31</f>
         <v/>
       </c>
@@ -4240,7 +4241,7 @@
           <t>NMES fill rate even at the draft's own 154 rating</t>
         </is>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <f>B32/C32</f>
         <v/>
       </c>
@@ -4465,7 +4466,7 @@
           <t>Net receiving seats at the slides' own capacities (499 and 397)</t>
         </is>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="33">
         <f>(499-Redistricting!B8)-(Redistricting!B9-397)</f>
         <v/>
       </c>
@@ -7589,7 +7590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8044,6 +8045,426 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>THE $14 MILLION PLAN (JULY 15, 2026 PLANNING COMMITTEE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Stated plan: free up $800,000 to $1,000,000 a year of operating money to bond $14 million</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Proposed bond amount</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Assumed interest rate</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Assumed term, years</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Annual debt service on the proposed bond</t>
+        </is>
+      </c>
+      <c r="B42" s="30">
+        <f>B39*B40/(1-(1+B40)^-B41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>The payment equals the operating money the plan frees up: the school's claimed cost becomes the mortgage</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>WHAT EACH SAVINGS ESTIMATE COULD ACTUALLY BOND</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Bond principal supported = annual savings x present-value annuity factor at the rate and term above</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>District's own KDE-filed excess cost of NMES vs peer elementaries</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>121220</v>
+      </c>
+      <c r="C46" s="9">
+        <f>B46*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>Matches the closure model's worst case</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Closure model default net saving</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>361240</v>
+      </c>
+      <c r="C47" s="9">
+        <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>Closure_Model tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Closure model best case</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>725000</v>
+      </c>
+      <c r="C48" s="9">
+        <f>B48*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>Closure_Model tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Administration's claim, July 15, 2026</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>900000</v>
+      </c>
+      <c r="C49" s="9">
+        <f>B49*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>Unpublished derivation; reconcile with KDE-filed school-level spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Only the administration's own number reaches $14 million. The audited excess cost supports about $1.6 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>DISTRICT-PAID DEBT SERVICE SCHEDULE (FY2025 AUDIT, NOTE 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Payments fall as the 2013, 2016, and 2020 series retire; this falling schedule is the room a wrap-around structure fills</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>1578700</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>1575060</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>1578719</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>1577258</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>1578340</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>FY2031-35 average</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>1321112</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>FY2036-40 average</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>398915</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>FY2041-45 average</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>260708</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>THE LEVERS THAT DO NOT CLOSE A SCHOOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Remaining restricted capacity (FY2024 audit $23.5M less local share of the 2024 issue, approximate)</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="F64" s="21" t="inlineStr">
+        <is>
+          <t>Exact figure is the fiscal agent's bonding potential statement; demand it</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Certified real and personal property assessment, FY2025</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>1843569625</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Recallable nickel yield per year (5 cents per $100)</t>
+        </is>
+      </c>
+      <c r="B66" s="9">
+        <f>B65*0.0005</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Bonds a nickel supports before state FSPK equalization</t>
+        </is>
+      </c>
+      <c r="B67" s="9">
+        <f>B66*(1-(1+B40)^-B41)/B40</f>
+        <v/>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
+        <is>
+          <t>FSPK equalization adds state dollars on top; KDE's tables set the amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>SFCC offers of assistance, typical cycle</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>State already pays $1,568,809 of current principal</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 YEAR-END, DISTRICT'S OWN KDE BUDGET MONITORING TOOL (UNAUDITED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>June 2026 financial packet, board agenda July 16, 2026; MUNIS run July 15, 2026. Audit will finalize these figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>General Fund revenue, FY2026 actual (excludes carryforward and on-behalf)</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>22103877</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>General Fund expenditures, FY2026 actual</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>22477866</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Net General Fund change, FY2026 (unaudited)</t>
+        </is>
+      </c>
+      <c r="B74" s="30">
+        <f>B72-B73</f>
+        <v/>
+      </c>
+      <c r="F74" s="21" t="inlineStr">
+        <is>
+          <t>Compare net changes of -$1,065,657 in FY2024 and -$1,225,465 in FY2025 (audited)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Revenues over budget per the monitoring tool</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>2225835</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Salaries under budget per the monitoring tool</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>587592</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Salaries below FY2025 actuals</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>223974</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Caveat: miscellaneous revenue budgeted at zero, received</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>1567829</v>
+      </c>
+      <c r="F78" s="21" t="inlineStr">
+        <is>
+          <t>If one-time, the underlying gap is about $1.9 million; the district should identify this receipt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -8101,7 +8101,7 @@
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>The payment equals the operating money the plan frees up: the school's claimed cost becomes the mortgage</t>
+          <t>Payment is approximately the operating amount the plan frees up; compare the savings scenarios below</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -7590,7 +7590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8465,6 +8465,202 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>SCENARIO: BALANCE THE BUDGET AND EXPAND BONDING CAPACITY, NO CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Two cases differ only in the operating gap assumed. Conservative treats the FY2026 $1.57M receipt as one-time;</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>trend uses the unaudited FY2026 net change. Operations are balanced first; only the remainder services debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>FY2026 trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Operating gap to close first</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>373989</v>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t>Editable. $1.9M = FY2026 result excluding the unidentified receipt; $373,989 = FY2026 unaudited net change</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>New recurring revenue: 4 percent levy taken three years running</t>
+        </is>
+      </c>
+      <c r="B85" s="18">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
+      </c>
+      <c r="C85" s="18">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>Same base and compounding as the levy tab; year 1 is $313,162, year 3 cumulative $977,568</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Recurring cost reductions, not from closing a school</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F86" s="21" t="inlineStr">
+        <is>
+          <t>Editable. For scale from the FY2025 audit: district administration grew $221K in one year, salaries fell $224K through attrition, spending ran $859K under budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Operating room left for debt service after the budget balances</t>
+        </is>
+      </c>
+      <c r="B87" s="9">
+        <f>MAX(0,B85+B86-B84)</f>
+        <v/>
+      </c>
+      <c r="C87" s="9">
+        <f>MAX(0,C85+C86-C84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>General-fund bond capacity from that room</t>
+        </is>
+      </c>
+      <c r="B88" s="9">
+        <f>B87*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C88" s="9">
+        <f>C87*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Recallable nickel yield, restricted, before FSPK equalization</t>
+        </is>
+      </c>
+      <c r="B89" s="9">
+        <f>B65*0.0005</f>
+        <v/>
+      </c>
+      <c r="C89" s="9">
+        <f>B65*0.0005</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Bond capacity from the nickel</t>
+        </is>
+      </c>
+      <c r="B90" s="9">
+        <f>B89*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C90" s="9">
+        <f>C89*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Existing unused restricted capacity, approximate</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="C91" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>FY2024 audit $23.5M less local share of the 2024 issue; fiscal agent's statement is the authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>Total capacity available without closing a school</t>
+        </is>
+      </c>
+      <c r="B92" s="24">
+        <f>B88+B90+B91</f>
+        <v/>
+      </c>
+      <c r="C92" s="24">
+        <f>C88+C90+C91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Roughly $30.6 million in the conservative case and $50.4 million on the FY2026 trend, with the budget balanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>first in both. The administration's plan reaches $32 million at face value and leaves the deficit in place.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -7590,7 +7590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8331,331 +8331,355 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Recallable nickel yield per year (5 cents per $100)</t>
-        </is>
-      </c>
-      <c r="B66" s="9">
-        <f>B65*0.0005</f>
-        <v/>
+          <t>Recallable nickel status: ALREADY LEVIED, inside the existing rate</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>levied</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="inlineStr">
+        <is>
+          <t>KDE SEEK District Payment Schedules show a nonzero Recallable Nickel state amount for Bourbon (041); the schedule equalizes only levied nickels</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Bonds a nickel supports before state FSPK equalization</t>
-        </is>
-      </c>
-      <c r="B67" s="9">
-        <f>B66*(1-(1+B40)^-B41)/B40</f>
-        <v/>
+          <t>New annual state equalization on the recallable nickel (began FY2026)</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>276246</v>
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>FSPK equalization adds state dollars on top; KDE's tables set the amount</t>
+          <t>FY2027 SEEK schedule; $55,515 partial in FY2026. New restricted revenue, no board action required</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>Bonds the new equalization alone supports</t>
+        </is>
+      </c>
+      <c r="B68" s="9">
+        <f>B67*(1-(1+B40)^-B41)/B40</f>
+        <v/>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>Additive to the FY2024 audit's bonding potential, which predates the equalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
           <t>SFCC offers of assistance, typical cycle</t>
         </is>
       </c>
-      <c r="B68" s="8" t="n">
+      <c r="B69" s="8" t="n">
         <v>1750000</v>
       </c>
-      <c r="F68" s="21" t="inlineStr">
+      <c r="F69" s="21" t="inlineStr">
         <is>
           <t>State already pays $1,568,809 of current principal</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>FY2026 YEAR-END, DISTRICT'S OWN KDE BUDGET MONITORING TOOL (UNAUDITED)</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>June 2026 financial packet, board agenda July 16, 2026; MUNIS run July 15, 2026. Audit will finalize these figures.</t>
         </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>General Fund revenue, FY2026 actual (excludes carryforward and on-behalf)</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n">
-        <v>22103877</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>General Fund expenditures, FY2026 actual</t>
+          <t>General Fund revenue, FY2026 actual (excludes carryforward and on-behalf)</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>22477866</v>
+        <v>22103877</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Net General Fund change, FY2026 (unaudited)</t>
-        </is>
-      </c>
-      <c r="B74" s="30">
-        <f>B72-B73</f>
-        <v/>
-      </c>
-      <c r="F74" s="21" t="inlineStr">
-        <is>
-          <t>Compare net changes of -$1,065,657 in FY2024 and -$1,225,465 in FY2025 (audited)</t>
-        </is>
+          <t>General Fund expenditures, FY2026 actual</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>22477866</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Revenues over budget per the monitoring tool</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n">
-        <v>2225835</v>
+          <t>Net General Fund change, FY2026 (unaudited)</t>
+        </is>
+      </c>
+      <c r="B75" s="30">
+        <f>B73-B74</f>
+        <v/>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>Compare net changes of -$1,065,657 in FY2024 and -$1,225,465 in FY2025 (audited)</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Salaries under budget per the monitoring tool</t>
+          <t>Revenues over budget per the monitoring tool</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>587592</v>
+        <v>2225835</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Salaries below FY2025 actuals</t>
+          <t>Salaries under budget per the monitoring tool</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>223974</v>
+        <v>587592</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
+          <t>Salaries below FY2025 actuals</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>223974</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
           <t>Caveat: miscellaneous revenue budgeted at zero, received</t>
         </is>
       </c>
-      <c r="B78" s="8" t="n">
+      <c r="B79" s="8" t="n">
         <v>1567829</v>
       </c>
-      <c r="F78" s="21" t="inlineStr">
+      <c r="F79" s="21" t="inlineStr">
         <is>
           <t>If one-time, the underlying gap is about $1.9 million; the district should identify this receipt</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>SCENARIO: BALANCE THE BUDGET AND EXPAND BONDING CAPACITY, NO CLOSURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Two cases differ only in the operating gap assumed. Conservative treats the FY2026 $1.57M receipt as one-time;</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>Two cases differ only in the operating gap assumed. Conservative treats the FY2026 $1.57M receipt as one-time;</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
           <t>trend uses the unaudited FY2026 net change. Operations are balanced first; only the remainder services debt.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="17" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="C83" s="17" t="inlineStr">
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>FY2026 trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>Operating gap to close first</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="C84" s="8" t="n">
-        <v>373989</v>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>Editable. $1.9M = FY2026 result excluding the unidentified receipt; $373,989 = FY2026 unaudited net change</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>New recurring revenue: 4 percent levy taken three years running</t>
-        </is>
-      </c>
-      <c r="B85" s="18">
-        <f>Tax_History!B32*(1.04^3-1)</f>
-        <v/>
-      </c>
-      <c r="C85" s="18">
-        <f>Tax_History!B32*(1.04^3-1)</f>
-        <v/>
+          <t>Operating gap to close first</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>373989</v>
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>Same base and compounding as the levy tab; year 1 is $313,162, year 3 cumulative $977,568</t>
+          <t>Editable. $1.9M = FY2026 result excluding the unidentified receipt; $373,989 = FY2026 unaudited net change</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Recurring cost reductions, not from closing a school</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C86" s="8" t="n">
-        <v>1000000</v>
+          <t>New recurring revenue: 4 percent levy taken three years running</t>
+        </is>
+      </c>
+      <c r="B86" s="18">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
+      </c>
+      <c r="C86" s="18">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
       </c>
       <c r="F86" s="21" t="inlineStr">
         <is>
-          <t>Editable. For scale from the FY2025 audit: district administration grew $221K in one year, salaries fell $224K through attrition, spending ran $859K under budget</t>
+          <t>Same base and compounding as the levy tab; year 1 is $313,162, year 3 cumulative $977,568</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Operating room left for debt service after the budget balances</t>
-        </is>
-      </c>
-      <c r="B87" s="9">
-        <f>MAX(0,B85+B86-B84)</f>
-        <v/>
-      </c>
-      <c r="C87" s="9">
-        <f>MAX(0,C85+C86-C84)</f>
-        <v/>
+          <t>Recurring cost reductions, not from closing a school</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C87" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F87" s="21" t="inlineStr">
+        <is>
+          <t>Editable. For scale from the FY2025 audit: district administration grew $221K in one year, salaries fell $224K through attrition, spending ran $859K under budget</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>General-fund bond capacity from that room</t>
+          <t>Operating room left for debt service after the budget balances</t>
         </is>
       </c>
       <c r="B88" s="9">
-        <f>B87*(1-(1+B$40)^-B$41)/B$40</f>
+        <f>MAX(0,B86+B87-B85)</f>
         <v/>
       </c>
       <c r="C88" s="9">
-        <f>C87*(1-(1+B$40)^-B$41)/B$40</f>
+        <f>MAX(0,C86+C87-C85)</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Recallable nickel yield, restricted, before FSPK equalization</t>
+          <t>General-fund bond capacity from that room</t>
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B65*0.0005</f>
+        <f>B88*(1-(1+B$40)^-B$41)/B$40</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>B65*0.0005</f>
+        <f>C88*(1-(1+B$40)^-B$41)/B$40</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Bond capacity from the nickel</t>
-        </is>
-      </c>
-      <c r="B90" s="9">
-        <f>B89*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="C90" s="9">
-        <f>C89*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
+          <t>New state equalization on the already-levied recallable nickel</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="C90" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="F90" s="21" t="inlineStr">
+        <is>
+          <t>FY2027 SEEK schedule; the recallable nickel itself is already levied and its local yield is already inside the building-fund stream above</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
+          <t>Bond capacity from the new equalization</t>
+        </is>
+      </c>
+      <c r="B91" s="9">
+        <f>B90*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C91" s="9">
+        <f>C90*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
           <t>Existing unused restricted capacity, approximate</t>
         </is>
       </c>
-      <c r="B91" s="8" t="n">
+      <c r="B92" s="8" t="n">
         <v>17600000</v>
       </c>
-      <c r="C91" s="8" t="n">
+      <c r="C92" s="8" t="n">
         <v>17600000</v>
       </c>
-      <c r="F91" s="21" t="inlineStr">
+      <c r="F92" s="21" t="inlineStr">
         <is>
           <t>FY2024 audit $23.5M less local share of the 2024 issue; fiscal agent's statement is the authority</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="22" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
         <is>
           <t>Total capacity available without closing a school</t>
         </is>
       </c>
-      <c r="B92" s="24">
-        <f>B88+B90+B91</f>
-        <v/>
-      </c>
-      <c r="C92" s="24">
-        <f>C88+C90+C91</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Roughly $30.6 million in the conservative case and $50.4 million on the FY2026 trend, with the budget balanced</t>
-        </is>
+      <c r="B93" s="24">
+        <f>B89+B91+B92</f>
+        <v/>
+      </c>
+      <c r="C93" s="24">
+        <f>C89+C91+C92</f>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Roughly $22.2 million in the conservative case and $42.1 million on the FY2026 trend, with the budget balanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>first in both. The administration's plan reaches $32 million at face value and leaves the deficit in place.</t>
         </is>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -7590,7 +7590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8331,7 +8331,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Recallable nickel status: ALREADY LEVIED, inside the existing rate</t>
+          <t>Recallable nickel status: ALREADY LEVIED August 17, 2023, inside the existing rate</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -8341,14 +8341,14 @@
       </c>
       <c r="F66" s="21" t="inlineStr">
         <is>
-          <t>KDE SEEK District Payment Schedules show a nonzero Recallable Nickel state amount for Bourbon (041); the schedule equalizes only levied nickels</t>
+          <t>KDE Nickel Levy Chart (March 2024) dates Bourbon's recallable levy 8/17/2023; KDE's levied-rates file (April 30, 2026) decomposes the 52.4-cent rate as 41.0 general fund + 5.7 FSPK + 5.7 recallable. Paris Independent, for scale: 71.5 cents with 17.4 recallable</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>New annual state equalization on the recallable nickel (began FY2026)</t>
+          <t>New annual state equalization on the recallable nickel (full value, FY2027 schedule)</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>FY2027 SEEK schedule; $55,515 partial in FY2026. New restricted revenue, no board action required</t>
+          <t>Phasing in on KDE SEEK schedules: $82,866 FY2025, $55,515 FY2026, $276,246 FY2027. New restricted revenue, no board action required</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Caveat: miscellaneous revenue budgeted at zero, received</t>
+          <t>Caveat 1: miscellaneous revenue (object 1990) budgeted at zero, received</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
@@ -8482,206 +8482,382 @@
       </c>
       <c r="F79" s="21" t="inlineStr">
         <is>
-          <t>If one-time, the underlying gap is about $1.9 million; the district should identify this receipt</t>
+          <t>Unbudgeted even in the final amended budget; the district should identify this receipt on the record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which booked in June (period 12) alone</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>1413929</v>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t>Months 1-11 produced $153,900 combined, a normal run rate; the balance sheet shows no receivable behind the June entry</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>SCENARIO: BALANCE THE BUDGET AND EXPAND BONDING CAPACITY, NO CLOSURE</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Caveat 2: restricted capital money transferred INTO the General Fund in June 2026</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>1320939</v>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>Object 5210: $1,098,633 from the Building Fund (320) + $222,276 from Capital Outlay (310), which ended the year at $0. Lawful under budget-act capital funds flexibility; budgeted from September 2025</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Two cases differ only in the operating gap assumed. Conservative treats the FY2026 $1.57M receipt as one-time;</t>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Net change excluding the capital transfer</t>
+        </is>
+      </c>
+      <c r="B82" s="9">
+        <f>B73-B74-B81</f>
+        <v/>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
+        <is>
+          <t>About -$1.69 million: the operating result on operating revenue alone</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>trend uses the unaudited FY2026 net change. Operations are balanced first; only the remainder services debt.</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Net change excluding the transfer and the unidentified June receipt</t>
+        </is>
+      </c>
+      <c r="B83" s="9">
+        <f>B73-B74-B81-B80</f>
+        <v/>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
+          <t>About -$3.11 million: the same range as the audited years</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
-        <is>
-          <t>FY2026 trend</t>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>June 2026 General Fund revenue vs June 2025 (district's monitoring tool)</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>3923096</v>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>1130736</v>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t>The two June entries above are 98 percent of the year-over-year June difference</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Operating gap to close first</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="C85" s="8" t="n">
-        <v>373989</v>
+          <t>Variance identity from the packet: projected fund balance reconciles to the dollar</t>
+        </is>
+      </c>
+      <c r="B85" s="9">
+        <f>1489853+2225835+587592-224087</f>
+        <v/>
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>Editable. $1.9M = FY2026 result excluding the unidentified receipt; $373,989 = FY2026 unaudited net change</t>
+          <t>Contingency + revenue over budget + salary savings - expense overrun = $4,079,193, the tool's projected balance. The June misc entry is 63 percent of the revenue beat</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>New recurring revenue: 4 percent levy taken three years running</t>
-        </is>
-      </c>
-      <c r="B86" s="18">
-        <f>Tax_History!B32*(1.04^3-1)</f>
-        <v/>
-      </c>
-      <c r="C86" s="18">
-        <f>Tax_History!B32*(1.04^3-1)</f>
-        <v/>
-      </c>
-      <c r="F86" s="21" t="inlineStr">
-        <is>
-          <t>Same base and compounding as the levy tab; year 1 is $313,162, year 3 cumulative $977,568</t>
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>BUILDING FUND FLOWS, FY2026 (fund 320, same packet)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Recurring cost reductions, not from closing a school</t>
+          <t>Building Fund transfers out, FY2026 total</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C87" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
-        <is>
-          <t>Editable. For scale from the FY2025 audit: district administration grew $221K in one year, salaries fell $224K through attrition, spending ran $859K under budget</t>
-        </is>
+        <v>2481394</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Operating room left for debt service after the budget balances</t>
-        </is>
-      </c>
-      <c r="B88" s="9">
-        <f>MAX(0,B86+B87-B85)</f>
-        <v/>
-      </c>
-      <c r="C88" s="9">
-        <f>MAX(0,C86+C87-C85)</f>
-        <v/>
+          <t xml:space="preserve">  to Debt Service (fund 400)</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>1382761</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>General-fund bond capacity from that room</t>
+          <t xml:space="preserve">  to the General Fund (June 2026)</t>
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B88*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="C89" s="9">
-        <f>C88*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
+        <f>B87-B88</f>
+        <v/>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>The residual after debt service. This is the restricted stream a $14 million bond would lean on; in FY2026 it plugged the operating budget instead</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>New state equalization on the already-levied recallable nickel</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n">
-        <v>276246</v>
-      </c>
-      <c r="C90" s="8" t="n">
-        <v>276246</v>
+          <t>Bond capacity that residual supports at the same rate and term</t>
+        </is>
+      </c>
+      <c r="B90" s="9">
+        <f>B89*(1-(1+B40)^-B41)/B40</f>
+        <v/>
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>FY2027 SEEK schedule; the recallable nickel itself is already levied and its local yield is already inside the building-fund stream above</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Bond capacity from the new equalization</t>
-        </is>
-      </c>
-      <c r="B91" s="9">
-        <f>B90*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="C91" s="9">
-        <f>C90*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
+          <t>About $14 million: the plan's own target, carried by restricted money. The closure's role is only to replace the sweep, and any recurring million dollars does that</t>
+        </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Existing unused restricted capacity, approximate</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="C92" s="8" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="F92" s="21" t="inlineStr">
-        <is>
-          <t>FY2024 audit $23.5M less local share of the 2024 issue; fiscal agent's statement is the authority</t>
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>SCENARIO: BALANCE THE BUDGET AND EXPAND BONDING CAPACITY, NO CLOSURE</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="inlineStr">
-        <is>
-          <t>Total capacity available without closing a school</t>
-        </is>
-      </c>
-      <c r="B93" s="24">
-        <f>B89+B91+B92</f>
-        <v/>
-      </c>
-      <c r="C93" s="24">
-        <f>C89+C91+C92</f>
-        <v/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Two cases differ only in the operating gap assumed. Conservative treats the FY2026 $1.57M receipt as one-time;</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>trend uses the unaudited FY2026 net change. Operations are balanced first; only the remainder services debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>FY2026 trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Operating gap to close first</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="C96" s="8" t="n">
+        <v>373989</v>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>Editable. $1.9M = FY2026 result excluding the unidentified receipt; $373,989 = FY2026 unaudited net change</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>New recurring revenue: 4 percent levy taken three years running</t>
+        </is>
+      </c>
+      <c r="B97" s="18">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
+      </c>
+      <c r="C97" s="18">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
+      </c>
+      <c r="F97" s="21" t="inlineStr">
+        <is>
+          <t>Same base and compounding as the levy tab; year 1 is $313,162, year 3 cumulative $977,568</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Recurring cost reductions, not from closing a school</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C98" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F98" s="21" t="inlineStr">
+        <is>
+          <t>Editable. For scale from the FY2025 audit: district administration grew $221K in one year, salaries fell $224K through attrition, spending ran $859K under budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Operating room left for debt service after the budget balances</t>
+        </is>
+      </c>
+      <c r="B99" s="9">
+        <f>MAX(0,B97+B98-B96)</f>
+        <v/>
+      </c>
+      <c r="C99" s="9">
+        <f>MAX(0,C97+C98-C96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>General-fund bond capacity from that room</t>
+        </is>
+      </c>
+      <c r="B100" s="9">
+        <f>B99*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C100" s="9">
+        <f>C99*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>New state equalization on the already-levied recallable nickel</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="C101" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
+        <is>
+          <t>FY2027 SEEK schedule; the recallable nickel itself is already levied and its local yield is already inside the building-fund stream above</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Bond capacity from the new equalization</t>
+        </is>
+      </c>
+      <c r="B102" s="9">
+        <f>B101*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C102" s="9">
+        <f>C101*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Existing unused restricted capacity, approximate</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="C103" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>FY2024 audit $23.5M less local share of the 2024 issue; fiscal agent's statement is the authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>Total capacity available without closing a school</t>
+        </is>
+      </c>
+      <c r="B104" s="24">
+        <f>B100+B102+B103</f>
+        <v/>
+      </c>
+      <c r="C104" s="24">
+        <f>C100+C102+C103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
           <t>Roughly $22.2 million in the conservative case and $42.1 million on the FY2026 trend, with the budget balanced</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>first in both. The administration's plan reaches $32 million at face value and leaves the deficit in place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Floor check: even with zero general-fund room, the restricted capacity plus new equalization alone are about $21 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Pledging the building-fund residual to new bonds requires ending the capital-to-operations sweep documented above,</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>which is exactly what the administration's plan implies; the only question is which recurring million replaces it.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -6070,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -6453,6 +6453,125 @@
       <c r="A43" s="21" t="inlineStr">
         <is>
           <t>Per-student figures pair the latest published spending year (2023-24) with the current enrollment count; refresh when the 2024-25 spending data posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>FILLED-TO-CAPACITY PER-PUPIL COST VS THE RECEIVING SCHOOLS (KDE 2023-24 filings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central per pupil today</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>18131</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>District's own KDE school-level filing, 2023-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge per pupil today</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>18670</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Same filing; Cane Ridge runs 31 students over its rated capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>NMES per pupil today</t>
+        </is>
+      </c>
+      <c r="B48" s="18">
+        <f>Assumptions!B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>NMES filled to 174 (state-approved rating), no added teachers</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>(B34+(B6-B5)*Assumptions!B62)/B6</f>
+        <v/>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Nine existing homerooms average 19.3 students at 174, inside every KRS 157.360 cap; only variable costs added</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>NMES filled to 174, conservative (two teachers added anyway)</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>(B34+2*Assumptions!B41+(B6-B5)*Assumptions!B62)/B6</f>
+        <v/>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Adds two loaded certified positions even though class sizes do not require them</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>NMES filled to 154 (2026 draft plan rating), no added teachers</t>
+        </is>
+      </c>
+      <c r="B51" s="9">
+        <f>(B34+(154-B5)*Assumptions!B62)/154</f>
+        <v/>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Same math at the draft plan's lower rating; class sizes average 17.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>NMES at 174 vs cheapest receiving school</t>
+        </is>
+      </c>
+      <c r="B52" s="24">
+        <f>B49-MIN(B46,B47)</f>
+        <v/>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>Negative = NMES becomes the cheapest elementary school in the district</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>Filling the school reverses the cost argument: the premium exists because fixed costs sit on 128 students; spread over 174 the same school costs less per child than either receiving school, and the transfer students free the exact seats Cane Ridge is over capacity by.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -6070,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -6572,6 +6572,188 @@
       <c r="A53" s="21" t="inlineStr">
         <is>
           <t>Filling the school reverses the cost argument: the premium exists because fixed costs sit on 128 students; spread over 174 the same school costs less per child than either receiving school, and the transfer students free the exact seats Cane Ridge is over capacity by.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>SENSITIVITY: IS THE CAPACITY RESULT STRUCTURAL, OR AN ARTIFACT OF ASSUMPTIONS?</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>The only lever that matters is the marginal cost of each added student. Break-even values below are the marginal cost at which NMES at capacity stops being cheaper. Compare them to reality: added supplies and materials run a few hundred dollars; even hiring staff in proportion to students costs roughly half the average, because the average includes the principal, building, and staff already paid for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Break-even marginal cost, NMES at 174 vs Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>(B46*B6-B34)/(B6-B5)</f>
+        <v/>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>NMES stays cheaper than Bourbon Central for any marginal cost below this</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Break-even marginal cost, NMES at 174 vs Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B58" s="9">
+        <f>(B47*B6-B34)/(B6-B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Break-even marginal cost, NMES at 154 vs Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B59" s="9">
+        <f>(B46*154-B34)/(154-B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Break-even marginal cost, NMES at 154 vs Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B60" s="9">
+        <f>(B47*154-B34)/(154-B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Reference: NMES's ENTIRE state and local spending per pupil (fixed costs included)</t>
+        </is>
+      </c>
+      <c r="B61" s="18">
+        <f>Assumptions!B15</f>
+        <v/>
+      </c>
+      <c r="C61" s="21" t="inlineStr">
+        <is>
+          <t>Even if every added student cost this full amount, which is impossible since it includes the fixed costs already paid, NMES at 174 still comes in under both receiving schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>PER-PUPIL GRID ACROSS MARGINAL-COST ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Marginal cost per added student</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>At 174</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>At 154</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="B65" s="9">
+        <f>(B$34+(B$6-B$5)*A65)/B$6</f>
+        <v/>
+      </c>
+      <c r="C65" s="9">
+        <f>(B$34+(154-B$5)*A65)/154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B66" s="9">
+        <f>(B$34+(B$6-B$5)*A66)/B$6</f>
+        <v/>
+      </c>
+      <c r="C66" s="9">
+        <f>(B$34+(154-B$5)*A66)/154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B67" s="9">
+        <f>(B$34+(B$6-B$5)*A67)/B$6</f>
+        <v/>
+      </c>
+      <c r="C67" s="9">
+        <f>(B$34+(154-B$5)*A67)/154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B68" s="9">
+        <f>(B$34+(B$6-B$5)*A68)/B$6</f>
+        <v/>
+      </c>
+      <c r="C68" s="9">
+        <f>(B$34+(154-B$5)*A68)/154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>14173</v>
+      </c>
+      <c r="B69" s="9">
+        <f>(B$34+(B$6-B$5)*A69)/B$6</f>
+        <v/>
+      </c>
+      <c r="C69" s="9">
+        <f>(B$34+(154-B$5)*A69)/154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="21" t="inlineStr">
+        <is>
+          <t>Receiving schools today: Bourbon Central $18,131, Cane Ridge $18,670. At the state-approved 174 rating, NMES undercuts both across the entire grid, including the impossible full-average case. At the draft plan's 154 rating it holds for any marginal cost under about $12,000, roughly thirty times the realistic figure. Verdict: structural at 174, robust at 154.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>Base-year variant: at the current 115 enrolled, filling to 174 adds 59 students and the break-even vs Bourbon Central falls to about $11,500, with the same verdict. Two added teachers at the loaded rate are equivalent to about $3,700 of marginal cost per student, inside the grid above.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -656,21 +656,21 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 9 and Figure 11).</t>
+          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 9 and Figure 12).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the 4% three-year path: Tax_History tab (backs Figure 15).</t>
+          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the 4% three-year path: Tax_History tab (backs Figure 16).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Boundary rebalancing and fill-to-capacity scenario: Redistricting tab (backs the Section 9 worked example and Figure 12).</t>
+          <t xml:space="preserve">  Boundary rebalancing and fill-to-capacity scenario: Redistricting tab (backs the Section 9 worked example and Figure 13).</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Backs Section 9 and Figure 15 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
+          <t>Backs Section 9 and Figure 16 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>NMES ENROLLMENT, 1989-2025 (spring of school year; backs Figure 11)</t>
+          <t>NMES ENROLLMENT, 1989-2025 (spring of school year; backs Figure 12)</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NMES ENROLLMENT BY SCHOOL YEAR (backs Figure 11)</t>
+          <t>NMES ENROLLMENT BY SCHOOL YEAR (backs Figure 12)</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -6754,6 +6754,167 @@
       <c r="A71" s="21" t="inlineStr">
         <is>
           <t>Base-year variant: at the current 115 enrolled, filling to 174 adds 59 students and the break-even vs Bourbon Central falls to about $11,500, with the same verdict. Two added teachers at the loaded rate are equivalent to about $3,700 of marginal cost per student, inside the grid above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>FIVE YEARS OF THE SAME TEST (KDE school-level filings, 2019-20 to 2023-24; backs Figure 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>NMES members</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>NMES $/pupil</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>BCES $/pupil</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>CRES $/pupil</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>NMES at 174</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2019-20</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>12903</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>12159</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>12168</v>
+      </c>
+      <c r="F75" s="9">
+        <f>(C75*B75+(174-B75)*Assumptions!B62)/174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2020-21</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>15406</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>14011</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>14621</v>
+      </c>
+      <c r="F76" s="9">
+        <f>(C76*B76+(174-B76)*Assumptions!B62)/174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2021-22</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>19080</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>15619</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>16137</v>
+      </c>
+      <c r="F77" s="9">
+        <f>(C77*B77+(174-B77)*Assumptions!B62)/174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>19003</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>17410</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>17403</v>
+      </c>
+      <c r="F78" s="9">
+        <f>(C78*B78+(174-B78)*Assumptions!B62)/174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>19348</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>18131</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>18670</v>
+      </c>
+      <c r="F79" s="9">
+        <f>(C79*B79+(174-B79)*Assumptions!B62)/174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="21" t="inlineStr">
+        <is>
+          <t>The counterfactual column is below both receiving schools in every year on record. NMES's total site spending grew 16 percent over the five years, against 37 percent at Bourbon Central and 47 percent at Cane Ridge; only the divisor changed.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -6070,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -6915,6 +6915,81 @@
       <c r="A81" s="21" t="inlineStr">
         <is>
           <t>The counterfactual column is below both receiving schools in every year on record. NMES's total site spending grew 16 percent over the five years, against 37 percent at Bourbon Central and 47 percent at Cane Ridge; only the divisor changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>SYMMETRY CHECK: THE SENDERS' PER-PUPIL AFTER THE MOVE (2023-24 basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t>Per-pupil rises at the senders for the same denominator reason it falls at NMES; a pure shuffle leaves total district spending nearly unchanged in either direction. The comparison below is the honest post-move one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central after sending 15 rezoned students</t>
+        </is>
+      </c>
+      <c r="B85" s="9">
+        <f>(8902321-15*Assumptions!B62)/(491-15)</f>
+        <v/>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>2023-24 filing: $8,902,321 across 491 members; loses only variable cost per departing student</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge after sending 15 rezoned students</t>
+        </is>
+      </c>
+      <c r="B86" s="9">
+        <f>(8606870-15*Assumptions!B62)/(461-15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Stress case: all 46 drawn in-county, 23 from each sender</t>
+        </is>
+      </c>
+      <c r="B87" s="9">
+        <f>(8902321-23*Assumptions!B62)/(491-23)</f>
+        <v/>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Bourbon Central; Cane Ridge in the next row</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Stress case, Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B88" s="9">
+        <f>(8606870-23*Assumptions!B62)/(461-23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>NMES at 174 stays the cheapest of the three after the move, by a wider margin than before it (about $4,400 vs $3,800). The district-level cash case is booked separately and conservatively above as the net recurring benefit: consolidated sections at the senders, HB 563 SEEK revenue from out-of-county transfers, and capacity relief at Cane Ridge, which runs 31 students over its rating. The same symmetry runs the other way: closing NMES would lower the receiving schools' per-pupil optics while saving almost nothing in total, which is the closure case's weakness in one sentence.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -6070,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -6795,6 +6795,11 @@
           <t>NMES at 174</t>
         </is>
       </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>NMES at 154</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -6818,6 +6823,11 @@
         <f>(C75*B75+(174-B75)*Assumptions!B62)/174</f>
         <v/>
       </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>n/a: enrolled above 154</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -6841,6 +6851,11 @@
         <f>(C76*B76+(174-B76)*Assumptions!B62)/174</f>
         <v/>
       </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>n/a: enrolled above 154</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -6864,6 +6879,10 @@
         <f>(C77*B77+(174-B77)*Assumptions!B62)/174</f>
         <v/>
       </c>
+      <c r="G77" s="9">
+        <f>(C77*B77+(154-B77)*Assumptions!B62)/154</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -6887,6 +6906,10 @@
         <f>(C78*B78+(174-B78)*Assumptions!B62)/174</f>
         <v/>
       </c>
+      <c r="G78" s="9">
+        <f>(C78*B78+(154-B78)*Assumptions!B62)/154</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -6910,11 +6933,15 @@
         <f>(C79*B79+(174-B79)*Assumptions!B62)/174</f>
         <v/>
       </c>
+      <c r="G79" s="9">
+        <f>(C79*B79+(154-B79)*Assumptions!B62)/154</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>The counterfactual column is below both receiving schools in every year on record. NMES's total site spending grew 16 percent over the five years, against 37 percent at Bourbon Central and 47 percent at Cane Ridge; only the divisor changed.</t>
+          <t>Honest reading (corrected 7/26): at 174 the counterfactual is within 1 to 3 percent of the cheapest school in 2019-22, a tie, and decisively below both schools in 2022-23 and 2023-24. At the draft plan's 154 rating it is cheapest on the 2023-24 filing; in 2019-20 and 2020-21 the school enrolled above 154, the capacity the draft now assigns it. NMES's total site spending grew 16 percent over the five years, against 37 percent at Bourbon Central and 47 percent at Cane Ridge; only the divisor changed.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -6070,7 +6070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -7017,6 +7017,97 @@
       <c r="A89" s="21" t="inlineStr">
         <is>
           <t>NMES at 174 stays the cheapest of the three after the move, by a wider margin than before it (about $4,400 vs $3,800). The district-level cash case is booked separately and conservatively above as the net recurring benefit: consolidated sections at the senders, HB 563 SEEK revenue from out-of-county transfers, and capacity relief at Cane Ridge, which runs 31 students over its rating. The same symmetry runs the other way: closing NMES would lower the receiving schools' per-pupil optics while saving almost nothing in total, which is the closure case's weakness in one sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>VARIABLE-COST VALIDATION, BOTH DIRECTIONS (added 7/26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t>Class-cap staffing check (KRS 157.360: 24 in K-3, 28 in grade 4, 29 in grade 5). At an even grade mix, 174 students need about 11 sections against 9 existing rooms, and 154 need about 10; the supplies-only counterfactual is therefore the BEST case, and the staffed cases below are the honest base cases. Grade-by-grade enrollment is a records ask; a mix weighted to grades 4-5 needs fewer sections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>NMES at 174 with two added sections (base case)</t>
+        </is>
+      </c>
+      <c r="B93" s="9">
+        <f>(B34+2*Assumptions!B41+(B6-B5)*Assumptions!B62)/B6</f>
+        <v/>
+      </c>
+      <c r="C93" s="21" t="inlineStr">
+        <is>
+          <t>Same as the conservative row above; cheapest of the three on the 2023-24 filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>NMES at 154 with one added section (base case)</t>
+        </is>
+      </c>
+      <c r="B94" s="9">
+        <f>(B34+Assumptions!B41+(154-B5)*Assumptions!B62)/154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Long-run bound at 174: every added student at the full $14,173 S/L average</t>
+        </is>
+      </c>
+      <c r="B95" s="9">
+        <f>(B34+(B6-B5)*Assumptions!B15)/B6</f>
+        <v/>
+      </c>
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>Still under both receiving schools on the 2023-24 filing. At 154 the same bound gives $18,474 and fails against Bourbon Central, consistent with the break-even rows above</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Senders after 15 out each WITH one consolidated section (favorable to senders)</t>
+        </is>
+      </c>
+      <c r="B96" s="9">
+        <f>(8902321-15*Assumptions!B62-Assumptions!B41)/(491-15)</f>
+        <v/>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>Bourbon Central; Cane Ridge next row. Consolidation lowers sender per-pupil AND is the source of the district-level saving; do not count it twice</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge, same treatment</t>
+        </is>
+      </c>
+      <c r="B97" s="9">
+        <f>(8606870-15*Assumptions!B62-Assumptions!B41)/(461-15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net saving is $121K to $725K and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -3800,7 +3800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4475,6 +4475,115 @@
       <c r="A52" s="21" t="inlineStr">
         <is>
           <t>Notes: components and totals as printed on the slides; Bourbon Central's printed components sum $9,421 below its printed total. The slides' receiving-school capacities (499, 397) differ from the 2026 draft DFP table (640, 547) and from the approved 2021 plan (549 with addition, 422): three documents, three capacity sets for the same buildings. NMES total need is second lowest among the district's schools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2017 PLAN, RECOVERED (KBE approved June 7, 2017; Wayback capture July 1, 2017, archived as build/dfp_wayback_20170701225631.pdf; KBE minutes corroborate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>2017 enr</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>2017 cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County High School</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>914</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County Middle School</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>607</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central Elementary</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n">
+        <v>633</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge Elementary</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>482</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown Elementary</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Preschool/Head Start Center</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>NMES listed at 154 enrolled against 152 capacity: OVER capacity in the district's own 2017 plan. Same-building rating trajectory across plans: NMES 198-152-174-154; Bourbon Central 564-611-521-640; Cane Ridge 500-550-422-547.</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -7108,6 +7217,256 @@
       <c r="A98" s="21" t="inlineStr">
         <is>
           <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net saving is $121K to $725K and not the school's $2.5M gross cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>FAIR TEST: EVERY SCHOOL FILLED TO ITS RATED CAPACITY, SEVEN CAPACITY SETS (backs Figure 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t>Step costs: $400 per student added or removed, plus or minus $85,000 per section vs today's staffing (even K-5 mix under KRS 157.360). Section deltas below are precomputed from that rule; capacities from the named documents, all archived in build/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>Scenario (NMES/BCES/CRES caps)</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>NMES</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>BCES</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>CRES</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>Cheapest</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Actual today (2023-24 filing)</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>19348</v>
+      </c>
+      <c r="C103" s="8" t="n">
+        <v>18131</v>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>18670</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>BCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2013 plan, KBE approved (198/564/500)</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="n">
+        <v>13937</v>
+      </c>
+      <c r="C104" s="8" t="n">
+        <v>16137</v>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>17245</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>NMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2017 plan, KBE approved (152/611/550)</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>16915</v>
+      </c>
+      <c r="C105" s="8" t="n">
+        <v>15483</v>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>16023</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>BCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2021 plan, KBE approved, in force (174/521/422)</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="n">
+        <v>15316</v>
+      </c>
+      <c r="C106" s="8" t="n">
+        <v>17273</v>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>19553</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>NMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Peak enrollment 2005-2025 (224/620/495)</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>12366</v>
+      </c>
+      <c r="C107" s="8" t="n">
+        <v>15264</v>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>17415</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>NMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2026 KFICS architect slides (154/499/397)</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="n">
+        <v>16701</v>
+      </c>
+      <c r="C108" s="8" t="n">
+        <v>17847</v>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>20759</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>NMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026 draft DFP table, unapproved (154/640/547)</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="n">
+        <v>16701</v>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>16108</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>BCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="inlineStr">
+        <is>
+          <t>Same-building ratings across four consecutive plans: NMES 198-152-174-154, Bourbon Central 564-611-521-640, Cane Ridge 500-550-422-547. Swings up to 128 seats with no major construction after 2009. The 2017 plan (recovered from the Internet Archive; KBE minutes June 7, 2017 corroborate) lists NMES at 154 enrolled against 152 capacity: OVER capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>VALIDATION AGAINST ACTUALS: the empirical marginal cost per student</t>
+        </is>
+      </c>
+      <c r="B111" s="9">
+        <f>(8902321-8606870)/(491-461)</f>
+        <v/>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>The actual per-student cost difference between the district's own two large schools on the same 2023-24 filing, about $9,848: an all-in, actuals-derived marginal cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>NMES filled to 174 at that empirical marginal cost</t>
+        </is>
+      </c>
+      <c r="B112" s="9">
+        <f>(B34+(B6-B5)*B111)/B6</f>
+        <v/>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
+        <is>
+          <t>About $16,837: still below both receiving schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>NMES filled to 154 at that empirical marginal cost</t>
+        </is>
+      </c>
+      <c r="B113" s="9">
+        <f>(B34+(154-B5)*B111)/154</f>
+        <v/>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>About $17,744: still below both receiving schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="inlineStr">
+        <is>
+          <t>Extreme bound: NMES's own year-over-year cost change 2022-23 to 2023-24 ($259,888 lower with 16 fewer students, about $16,243 per student, which folds in deliberate staffing cuts) gives $18,527 at 174: under Cane Ridge, marginally over Bourbon Central. Even the most hostile actuals-derived number does not restore the cost case.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -656,21 +656,21 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 9 and Figure 12).</t>
+          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 9 and Figure 14).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the 4% three-year path: Tax_History tab (backs Figure 16).</t>
+          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the 4% three-year path: Tax_History tab (backs Figure 18).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Boundary rebalancing and fill-to-capacity scenario: Redistricting tab (backs the Section 9 worked example and Figure 13).</t>
+          <t xml:space="preserve">  Boundary rebalancing and fill-to-capacity scenario: Redistricting tab (backs the Section 9 worked example and Figure 15).</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Backs Section 9 and Figure 16 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
+          <t>Backs Section 9 and Figure 18 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>NMES ENROLLMENT, 1989-2025 (spring of school year; backs Figure 12)</t>
+          <t>NMES ENROLLMENT, 1989-2025 (spring of school year; backs Figure 14)</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NMES ENROLLMENT BY SCHOOL YEAR (backs Figure 12)</t>
+          <t>NMES ENROLLMENT BY SCHOOL YEAR (backs Figure 14)</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5405,6 +5405,21 @@
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Low end of the $75K-$200K range</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>GF-borne loaded cost per certified position (v3)</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Published salary schedule $41,718-$71,447; state pays TRS/KEHP on-behalf; GF keeps salary + ~5%. Range $50K-$75K</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -5920,34 +5935,360 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>DISTRICT-FAVORABLE CASE (red-team): 5 positions cut, low busing, no departures</t>
+          <t>V3 CORRECTION: WHAT A POSITION ACTUALLY COSTS THE GENERAL FUND</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Net recurring saving, favorable case</t>
+          <t>All-in cost per position (salary + state-paid on-behalf; filing basis)</t>
         </is>
       </c>
       <c r="B34" s="18">
-        <f>Assumptions!B51+Assumptions!B52+Assumptions!B66*Assumptions!B41-Assumptions!B67</f>
-        <v/>
+        <f>Assumptions!B41</f>
+        <v/>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Correct for KDE per-pupil comparisons; the district books $6.94M of on-behalf in FY2026</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Share of the structural deficit ($2.65M) | of the reserve drawdown ($1.15M)</t>
-        </is>
-      </c>
-      <c r="B35" s="19">
-        <f>B34/(Assumptions!B24-Assumptions!B21)</f>
-        <v/>
-      </c>
-      <c r="C35" s="19">
-        <f>B34/GF_Summary!D16</f>
-        <v/>
+          <t>GF-borne cost per position (salary + ~5%)</t>
+        </is>
+      </c>
+      <c r="B35" s="18">
+        <f>Assumptions!B69</f>
+        <v/>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Published schedule: Rank III $41,718 (yr 0) to Rank I $71,447 (yr 29-30). The state pays TRS and KEHP on behalf of districts; eliminating a GF position saves the GF only $50K-$75K</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>V3 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 1,944 COMBINATIONS (backs Figure 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Lever (low / central / high)</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Positions eliminated (net of re-created sections)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Class caps: receiving schools add ~4 sections while NMES's 9 dissolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>GF cost per position</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Published salary schedule + on-behalf structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Fixed avoided (mothballed / sold)</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>290000</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>290000</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Principal+office $175K; plant $115K sold, ~$55K mothballed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Added busing</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>137500</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>110 sq mi zone (federal SABS); worst-reimbursed budget line</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Students leaving district</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>x $4,626 SEEK; Paris Ind adjacent under HB 563; Millersburg precedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Capacity debt service triggered</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>115000</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>231000</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>CRES 103 over approved rating; 2021 plan prices its kitchen/cafeteria deficient today</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Assessment erosion, district share</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Millersburg-calibrated; PVA records ask pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Central case: net yearly effect</t>
+        </is>
+      </c>
+      <c r="B47" s="23">
+        <f>C41+C39*C40-C42-C43*Assumptions!B6-C44-C45</f>
+        <v/>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>$131,240: about 5 percent of the structural deficit</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Unfavorable tail (all levers adverse)</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>B41+B39*B40-D42-D43*Assumptions!B6-D44-D45</f>
+        <v/>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>-$384,780 a year: the closure loses money</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Favorable tail (all levers favorable)</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>D41+D39*D40-B42-B43*Assumptions!B6-B44-B45</f>
+        <v/>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>+$565,000 a year: the ceiling, and still below the plan's $800K-$1M requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>Distribution of all 1,944 combinations (computed in build script, equal weights): median +$91,240; middle half -$17,500 to +$200,000; 29 percent of scenarios negative. One-time transition costs $100K-$300K in year one are additional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>HOSTILE PAPER CASE, PUBLISHED WITH ITS REFUTATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Every absorbed student priced at the empirical $9,848 marginal</t>
+        </is>
+      </c>
+      <c r="B53" s="9">
+        <f>Assumptions!B14*Assumptions!B11-128*Redistricting!B111-137500-10*Assumptions!B6</f>
+        <v/>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>About $1.03M on paper. But it requires Cane Ridge at 525 students against its approved 422 rating and Bourbon Central at 555 against 521: exactly the overcrowding the $14M renovation exists to cure. The savings pre-spend the bond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>MILLERSBURG, 2007: THE COUNTY'S OWN PRECEDENT (backs Figure 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Millersburg Elementary final enrollment (fall 2005)</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>NCES CCD; series 153-133-145-139-137-127-129-119; closed 2007; students to Cane Ridge (2007 addition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Millersburg population 1980/1990/2000/2010/2020</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>987 / 937 / 842 / 792 / 747</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>Decennial census; down 11% from 2000 while the county grew 4.6% (19,360 to 20,252)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Town-budget blow from the 2013 Joy Global closure</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C58" s="21" t="inlineStr">
+        <is>
+          <t>Community Ventures account: 197 jobs lost; $100K/yr payroll tax, half the town budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>Records asks: the 2007 closure's savings analysis and realized savings; the Millersburg Elementary building's deed, sale price, and current condition; PVA assessed-value history Millersburg vs county.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Closure only (base-case net saving from FY2027)</t>
+          <t>Closure only (v3 central case, $131,240, from FY2027)</t>
         </is>
       </c>
       <c r="B7" s="9">
@@ -831,15 +831,15 @@
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>B7-GF_Summary!$D$16+Closure_Model!$B$20</f>
+        <f>B7-GF_Summary!$D$16+Closure_Model!$B$47</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>C7-GF_Summary!$D$16+Closure_Model!$B$20</f>
+        <f>C7-GF_Summary!$D$16+Closure_Model!$B$47</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>D7-GF_Summary!$D$16+Closure_Model!$B$20</f>
+        <f>D7-GF_Summary!$D$16+Closure_Model!$B$47</f>
         <v/>
       </c>
     </row>
@@ -864,6 +864,13 @@
       <c r="E8" s="18">
         <f>GF_Summary!$D$14</f>
         <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Closure range check (v3): at the +$565,000 best case FY2029 ends near $1.4M; at the +$91,240 median the reserves are gone on nearly the status-quo schedule; in the 29 percent of scenarios that lose money, sooner than status quo.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -5774,12 +5781,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Teaching positions eliminated (via attrition)</t>
+          <t>Teaching positions eliminated (via attrition, GF-borne cost)</t>
         </is>
       </c>
       <c r="B12" s="18">
-        <f>Assumptions!B53*Assumptions!B41</f>
-        <v/>
+        <f>Assumptions!B53*Assumptions!B69</f>
+        <v/>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>v3: GF-borne $60K per position (state pays TRS/KEHP on-behalf); prior versions used the $85K all-in figure here</t>
+        </is>
       </c>
     </row>
     <row r="13">

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -30,11 +30,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,6 +162,8 @@
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3807,7 +3810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4591,6 +4594,184 @@
       <c r="A63" s="21" t="inlineStr">
         <is>
           <t>NMES listed at 154 enrolled against 152 capacity: OVER capacity in the district's own 2017 plan. Same-building rating trajectory across plans: NMES 198-152-174-154; Bourbon Central 564-611-521-640; Cane Ridge 500-550-422-547.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>KFICS CONDITION INDEX, EVERY STATE REPORT PUBLISHED (KDE KFICS State Reports: official Oct 2023, official Oct 2025, updated report generated July 2, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>Oct 2023 report</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>Oct 2025 report</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>Jul 2026 report</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>4-yr needs (Jul 2026)</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>Replacement value (Jul 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central Elementary (1988)</t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="n">
+        <v>0.887637</v>
+      </c>
+      <c r="C67" s="35" t="n">
+        <v>0.819273</v>
+      </c>
+      <c r="D67" s="35" t="n">
+        <v>0.823017</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>4006243.38</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>22636266.8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge Elementary (1992)</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="n">
+        <v>0.8120579999999999</v>
+      </c>
+      <c r="C68" s="35" t="n">
+        <v>0.811765</v>
+      </c>
+      <c r="D68" s="35" t="n">
+        <v>0.728249</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>4796308</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>17649638.79</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown Elementary (1948/64)</t>
+        </is>
+      </c>
+      <c r="B69" s="35" t="n">
+        <v>0.694064</v>
+      </c>
+      <c r="C69" s="35" t="n">
+        <v>0.702133</v>
+      </c>
+      <c r="D69" s="35" t="n">
+        <v>0.773295</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>3099147.93</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>13670417.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County Middle School (1948)</t>
+        </is>
+      </c>
+      <c r="B70" s="35" t="n">
+        <v>0.726249</v>
+      </c>
+      <c r="C70" s="35" t="n">
+        <v>0.727501</v>
+      </c>
+      <c r="D70" s="35" t="n">
+        <v>0.596145</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>12167086.72</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>30127350</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County High School (1968)</t>
+        </is>
+      </c>
+      <c r="B71" s="35" t="n">
+        <v>0.809819</v>
+      </c>
+      <c r="C71" s="35" t="n">
+        <v>0.802057</v>
+      </c>
+      <c r="D71" s="35" t="n">
+        <v>0.792529</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>10251532.33</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>49411909.14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Check: Condition Index = 1 - (4-year renewal needs / replacement value), NMES</t>
+        </is>
+      </c>
+      <c r="B72" s="36">
+        <f>1-E69/F69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NMES change between inspection cycles (2020-21 to April 2026)</t>
+        </is>
+      </c>
+      <c r="B73" s="36">
+        <f>D69-B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>Notes: the Oct 2023 and Oct 2025 official reports rest on the same 2020-21 inspections (NMES and Cane Ridge Jan 5, 2021; Bourbon Central Apr 14, 2020) with costs updated between reports; the Jul 2026 report carries the first fresh inspections, completed April 2026 and reviewed by KDE. NMES is the only school whose index improved between inspection cycles, and its $3.1M four-year repair bill is the smallest of the district's five schools. NMES Educational Suitability prints 0.21725 in both the 2023 and Jul 2026 reports, identical to five decimal places, so that component appears carried forward rather than re-surveyed. Higher index = healthier building.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -153,6 +153,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,7 +161,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1076,7 +1076,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="29" t="n">
         <v>61.3</v>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -1091,7 +1091,7 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="29" t="n">
         <v>60.6</v>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="29" t="n">
         <v>55.9</v>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="29" t="n">
         <v>54.2</v>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="29" t="n">
         <v>49.2</v>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="29" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="29" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="29" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
           <t>Tangible/personal rate (recent)</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="29" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
           <t>Motor vehicle rate</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="29" t="n">
         <v>54.7</v>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
           <t>Fayette County</t>
         </is>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="29" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -1213,7 +1213,7 @@
           <t>Paris Independent</t>
         </is>
       </c>
-      <c r="B20" s="28" t="n">
+      <c r="B20" s="29" t="n">
         <v>71.5</v>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
           <t>Clark County</t>
         </is>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="29" t="n">
         <v>66.8</v>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
           <t>Bath County</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="29" t="n">
         <v>63.4</v>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
           <t>Scott County</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="29" t="n">
         <v>62.9</v>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
           <t>Harrison County</t>
         </is>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="29" t="n">
         <v>57.7</v>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
           <t>Montgomery County</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="29" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
           <t>Bourbon County</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="29" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
           <t>Nicholas County</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="29" t="n">
         <v>43.1</v>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
           <t>Statewide school average (DOR Table II, 2025)</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B28" s="29" t="n">
         <v>65.13</v>
       </c>
     </row>
@@ -2585,55 +2585,55 @@
           <t>North Middletown (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="29" t="n">
         <v>56.5</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="29" t="n">
         <v>63.9</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="29" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="29" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="29" t="n">
         <v>85.8</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="29" t="n">
         <v>72.5</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="29" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="29" t="n">
         <v>56.6</v>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="29" t="n">
         <v>56.9</v>
       </c>
-      <c r="K15" s="28" t="n">
+      <c r="K15" s="29" t="n">
         <v>48.7</v>
       </c>
-      <c r="L15" s="28" t="n">
+      <c r="L15" s="29" t="n">
         <v>49.3</v>
       </c>
-      <c r="M15" s="28" t="n">
+      <c r="M15" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="N15" s="28" t="n">
+      <c r="N15" s="29" t="n">
         <v>50.4</v>
       </c>
-      <c r="P15" s="28" t="n">
+      <c r="P15" s="29" t="n">
         <v>47.7</v>
       </c>
-      <c r="Q15" s="28" t="n">
+      <c r="Q15" s="29" t="n">
         <v>32.1</v>
       </c>
-      <c r="R15" s="28" t="n">
+      <c r="R15" s="29" t="n">
         <v>54.1</v>
       </c>
-      <c r="S15" s="28" t="n">
+      <c r="S15" s="29" t="n">
         <v>58.2</v>
       </c>
     </row>
@@ -2643,58 +2643,58 @@
           <t>Bourbon Central (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="29" t="n">
         <v>77.5</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="29" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="29" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="29" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="29" t="n">
         <v>63</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="29" t="n">
         <v>74.7</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="29" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I16" s="29" t="n">
         <v>51.8</v>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="29" t="n">
         <v>52.1</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="L16" s="28" t="n">
+      <c r="L16" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="M16" s="28" t="n">
+      <c r="M16" s="29" t="n">
         <v>32.8</v>
       </c>
-      <c r="N16" s="28" t="n">
+      <c r="N16" s="29" t="n">
         <v>39.9</v>
       </c>
-      <c r="O16" s="28" t="n">
+      <c r="O16" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="P16" s="28" t="n">
+      <c r="P16" s="29" t="n">
         <v>29.9</v>
       </c>
-      <c r="Q16" s="28" t="n">
+      <c r="Q16" s="29" t="n">
         <v>29</v>
       </c>
-      <c r="R16" s="28" t="n">
+      <c r="R16" s="29" t="n">
         <v>23.8</v>
       </c>
-      <c r="S16" s="28" t="n">
+      <c r="S16" s="29" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -2704,58 +2704,58 @@
           <t>Cane Ridge (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n">
+      <c r="B17" s="29" t="n">
         <v>35.2</v>
       </c>
-      <c r="C17" s="28" t="n">
+      <c r="C17" s="29" t="n">
         <v>50.9</v>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="29" t="n">
         <v>56.2</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E17" s="29" t="n">
         <v>65.5</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="29" t="n">
         <v>34.5</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="29" t="n">
         <v>49.6</v>
       </c>
-      <c r="I17" s="28" t="n">
+      <c r="I17" s="29" t="n">
         <v>51</v>
       </c>
-      <c r="J17" s="28" t="n">
+      <c r="J17" s="29" t="n">
         <v>51.1</v>
       </c>
-      <c r="K17" s="28" t="n">
+      <c r="K17" s="29" t="n">
         <v>57.5</v>
       </c>
-      <c r="L17" s="28" t="n">
+      <c r="L17" s="29" t="n">
         <v>50.4</v>
       </c>
-      <c r="M17" s="28" t="n">
+      <c r="M17" s="29" t="n">
         <v>41.4</v>
       </c>
-      <c r="N17" s="28" t="n">
+      <c r="N17" s="29" t="n">
         <v>38.8</v>
       </c>
-      <c r="O17" s="28" t="n">
+      <c r="O17" s="29" t="n">
         <v>23.8</v>
       </c>
-      <c r="P17" s="28" t="n">
+      <c r="P17" s="29" t="n">
         <v>38.7</v>
       </c>
-      <c r="Q17" s="28" t="n">
+      <c r="Q17" s="29" t="n">
         <v>34.6</v>
       </c>
-      <c r="R17" s="28" t="n">
+      <c r="R17" s="29" t="n">
         <v>35.8</v>
       </c>
-      <c r="S17" s="28" t="n">
+      <c r="S17" s="29" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -2765,10 +2765,10 @@
           <t>Paris Elementary (Paris Indep.)</t>
         </is>
       </c>
-      <c r="R18" s="28" t="n">
+      <c r="R18" s="29" t="n">
         <v>16.8</v>
       </c>
-      <c r="S18" s="28" t="n">
+      <c r="S18" s="29" t="n">
         <v>12.2</v>
       </c>
     </row>
@@ -2778,10 +2778,10 @@
           <t>Shearer (Clark Co.)</t>
         </is>
       </c>
-      <c r="R19" s="28" t="n">
+      <c r="R19" s="29" t="n">
         <v>30.7</v>
       </c>
-      <c r="S19" s="28" t="n">
+      <c r="S19" s="29" t="n">
         <v>42.3</v>
       </c>
     </row>
@@ -2791,10 +2791,10 @@
           <t>Justice (Clark Co.)</t>
         </is>
       </c>
-      <c r="R20" s="28" t="n">
+      <c r="R20" s="29" t="n">
         <v>43.2</v>
       </c>
-      <c r="S20" s="28" t="n">
+      <c r="S20" s="29" t="n">
         <v>39.3</v>
       </c>
     </row>
@@ -2804,10 +2804,10 @@
           <t>Strode Station (Clark Co.)</t>
         </is>
       </c>
-      <c r="R21" s="28" t="n">
+      <c r="R21" s="29" t="n">
         <v>43.2</v>
       </c>
-      <c r="S21" s="28" t="n">
+      <c r="S21" s="29" t="n">
         <v>34.2</v>
       </c>
     </row>
@@ -2817,10 +2817,10 @@
           <t>Conkwright (Clark Co.)</t>
         </is>
       </c>
-      <c r="R22" s="28" t="n">
+      <c r="R22" s="29" t="n">
         <v>15.6</v>
       </c>
-      <c r="S22" s="28" t="n">
+      <c r="S22" s="29" t="n">
         <v>17.5</v>
       </c>
     </row>
@@ -2830,10 +2830,10 @@
           <t>Northview (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R23" s="28" t="n">
+      <c r="R23" s="29" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="S23" s="28" t="n">
+      <c r="S23" s="29" t="n">
         <v>68.90000000000001</v>
       </c>
     </row>
@@ -2843,10 +2843,10 @@
           <t>Mapleton (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R24" s="28" t="n">
+      <c r="R24" s="29" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="S24" s="28" t="n">
+      <c r="S24" s="29" t="n">
         <v>65.09999999999999</v>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
           <t>Nicholas County Elementary (Nicholas Co.)</t>
         </is>
       </c>
-      <c r="R25" s="28" t="n">
+      <c r="R25" s="29" t="n">
         <v>15.9</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
           <t>Subject</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
@@ -3203,43 +3203,43 @@
           <t>Reading: North Middletown</t>
         </is>
       </c>
-      <c r="B45" s="28" t="n">
+      <c r="B45" s="29" t="n">
         <v>51.9</v>
       </c>
-      <c r="C45" s="28" t="n">
+      <c r="C45" s="29" t="n">
         <v>59.7</v>
       </c>
-      <c r="D45" s="28" t="n">
+      <c r="D45" s="29" t="n">
         <v>63.2</v>
       </c>
-      <c r="E45" s="28" t="n">
+      <c r="E45" s="29" t="n">
         <v>53.2</v>
       </c>
-      <c r="F45" s="28" t="n">
+      <c r="F45" s="29" t="n">
         <v>56.1</v>
       </c>
-      <c r="G45" s="28" t="n">
+      <c r="G45" s="29" t="n">
         <v>55.6</v>
       </c>
-      <c r="H45" s="28" t="n">
+      <c r="H45" s="29" t="n">
         <v>42.3</v>
       </c>
-      <c r="I45" s="28" t="n">
+      <c r="I45" s="29" t="n">
         <v>48.4</v>
       </c>
-      <c r="J45" s="28" t="n">
+      <c r="J45" s="29" t="n">
         <v>21.4</v>
       </c>
-      <c r="K45" s="28" t="n">
+      <c r="K45" s="29" t="n">
         <v>32</v>
       </c>
-      <c r="L45" s="28" t="n">
+      <c r="L45" s="29" t="n">
         <v>43</v>
       </c>
-      <c r="M45" s="28" t="n">
+      <c r="M45" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="N45" s="28" t="n">
+      <c r="N45" s="29" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3249,43 +3249,43 @@
           <t>Reading: Bourbon Central</t>
         </is>
       </c>
-      <c r="B46" s="28" t="n">
+      <c r="B46" s="29" t="n">
         <v>62.1</v>
       </c>
-      <c r="C46" s="28" t="n">
+      <c r="C46" s="29" t="n">
         <v>56.6</v>
       </c>
-      <c r="D46" s="28" t="n">
+      <c r="D46" s="29" t="n">
         <v>61.2</v>
       </c>
-      <c r="E46" s="28" t="n">
+      <c r="E46" s="29" t="n">
         <v>55.7</v>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="F46" s="29" t="n">
         <v>47.9</v>
       </c>
-      <c r="G46" s="28" t="n">
+      <c r="G46" s="29" t="n">
         <v>47.9</v>
       </c>
-      <c r="H46" s="28" t="n">
+      <c r="H46" s="29" t="n">
         <v>49.3</v>
       </c>
-      <c r="I46" s="28" t="n">
+      <c r="I46" s="29" t="n">
         <v>49.1</v>
       </c>
-      <c r="J46" s="28" t="n">
+      <c r="J46" s="29" t="n">
         <v>27.1</v>
       </c>
-      <c r="K46" s="28" t="n">
+      <c r="K46" s="29" t="n">
         <v>43</v>
       </c>
-      <c r="L46" s="28" t="n">
+      <c r="L46" s="29" t="n">
         <v>37</v>
       </c>
-      <c r="M46" s="28" t="n">
+      <c r="M46" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="N46" s="28" t="n">
+      <c r="N46" s="29" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3295,43 +3295,43 @@
           <t>Reading: Cane Ridge</t>
         </is>
       </c>
-      <c r="B47" s="28" t="n">
+      <c r="B47" s="29" t="n">
         <v>42.9</v>
       </c>
-      <c r="C47" s="28" t="n">
+      <c r="C47" s="29" t="n">
         <v>47.2</v>
       </c>
-      <c r="D47" s="28" t="n">
+      <c r="D47" s="29" t="n">
         <v>54.5</v>
       </c>
-      <c r="E47" s="28" t="n">
+      <c r="E47" s="29" t="n">
         <v>55.3</v>
       </c>
-      <c r="F47" s="28" t="n">
+      <c r="F47" s="29" t="n">
         <v>59.3</v>
       </c>
-      <c r="G47" s="28" t="n">
+      <c r="G47" s="29" t="n">
         <v>57.1</v>
       </c>
-      <c r="H47" s="28" t="n">
+      <c r="H47" s="29" t="n">
         <v>52</v>
       </c>
-      <c r="I47" s="28" t="n">
+      <c r="I47" s="29" t="n">
         <v>49.6</v>
       </c>
-      <c r="J47" s="28" t="n">
+      <c r="J47" s="29" t="n">
         <v>26.5</v>
       </c>
-      <c r="K47" s="28" t="n">
+      <c r="K47" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="L47" s="28" t="n">
+      <c r="L47" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="M47" s="28" t="n">
+      <c r="M47" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="N47" s="28" t="n">
+      <c r="N47" s="29" t="n">
         <v>37</v>
       </c>
     </row>
@@ -3341,43 +3341,43 @@
           <t>Reading: Paris Elementary</t>
         </is>
       </c>
-      <c r="B48" s="28" t="n">
+      <c r="B48" s="29" t="n">
         <v>31</v>
       </c>
-      <c r="C48" s="28" t="n">
+      <c r="C48" s="29" t="n">
         <v>34.1</v>
       </c>
-      <c r="D48" s="28" t="n">
+      <c r="D48" s="29" t="n">
         <v>42.9</v>
       </c>
-      <c r="E48" s="28" t="n">
+      <c r="E48" s="29" t="n">
         <v>38.9</v>
       </c>
-      <c r="F48" s="28" t="n">
+      <c r="F48" s="29" t="n">
         <v>41.2</v>
       </c>
-      <c r="G48" s="28" t="n">
+      <c r="G48" s="29" t="n">
         <v>34.3</v>
       </c>
-      <c r="H48" s="28" t="n">
+      <c r="H48" s="29" t="n">
         <v>34.4</v>
       </c>
-      <c r="I48" s="28" t="n">
+      <c r="I48" s="29" t="n">
         <v>35.3</v>
       </c>
-      <c r="J48" s="28" t="n">
+      <c r="J48" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="K48" s="28" t="n">
+      <c r="K48" s="29" t="n">
         <v>28</v>
       </c>
-      <c r="L48" s="28" t="n">
+      <c r="L48" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="M48" s="28" t="n">
+      <c r="M48" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="N48" s="28" t="n">
+      <c r="N48" s="29" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3387,43 +3387,43 @@
           <t>Mathematics: North Middletown</t>
         </is>
       </c>
-      <c r="B49" s="28" t="n">
+      <c r="B49" s="29" t="n">
         <v>53.2</v>
       </c>
-      <c r="C49" s="28" t="n">
+      <c r="C49" s="29" t="n">
         <v>49.4</v>
       </c>
-      <c r="D49" s="28" t="n">
+      <c r="D49" s="29" t="n">
         <v>55.3</v>
       </c>
-      <c r="E49" s="28" t="n">
+      <c r="E49" s="29" t="n">
         <v>59.5</v>
       </c>
-      <c r="F49" s="28" t="n">
+      <c r="F49" s="29" t="n">
         <v>62.1</v>
       </c>
-      <c r="G49" s="28" t="n">
+      <c r="G49" s="29" t="n">
         <v>50.8</v>
       </c>
-      <c r="H49" s="28" t="n">
+      <c r="H49" s="29" t="n">
         <v>47.9</v>
       </c>
-      <c r="I49" s="28" t="n">
+      <c r="I49" s="29" t="n">
         <v>48.4</v>
       </c>
-      <c r="J49" s="28" t="n">
+      <c r="J49" s="29" t="n">
         <v>17.9</v>
       </c>
-      <c r="K49" s="28" t="n">
+      <c r="K49" s="29" t="n">
         <v>31</v>
       </c>
-      <c r="L49" s="28" t="n">
+      <c r="L49" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="M49" s="28" t="n">
+      <c r="M49" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="N49" s="28" t="n">
+      <c r="N49" s="29" t="n">
         <v>31</v>
       </c>
     </row>
@@ -3433,43 +3433,43 @@
           <t>Mathematics: Bourbon Central</t>
         </is>
       </c>
-      <c r="B50" s="28" t="n">
+      <c r="B50" s="29" t="n">
         <v>47.1</v>
       </c>
-      <c r="C50" s="28" t="n">
+      <c r="C50" s="29" t="n">
         <v>47.4</v>
       </c>
-      <c r="D50" s="28" t="n">
+      <c r="D50" s="29" t="n">
         <v>43</v>
       </c>
-      <c r="E50" s="28" t="n">
+      <c r="E50" s="29" t="n">
         <v>43.6</v>
       </c>
-      <c r="F50" s="28" t="n">
+      <c r="F50" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="G50" s="28" t="n">
+      <c r="G50" s="29" t="n">
         <v>43.5</v>
       </c>
-      <c r="H50" s="28" t="n">
+      <c r="H50" s="29" t="n">
         <v>41.8</v>
       </c>
-      <c r="I50" s="28" t="n">
+      <c r="I50" s="29" t="n">
         <v>45.1</v>
       </c>
-      <c r="J50" s="28" t="n">
+      <c r="J50" s="29" t="n">
         <v>31.7</v>
       </c>
-      <c r="K50" s="28" t="n">
+      <c r="K50" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="L50" s="28" t="n">
+      <c r="L50" s="29" t="n">
         <v>28</v>
       </c>
-      <c r="M50" s="28" t="n">
+      <c r="M50" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="N50" s="28" t="n">
+      <c r="N50" s="29" t="n">
         <v>28</v>
       </c>
     </row>
@@ -3479,43 +3479,43 @@
           <t>Mathematics: Cane Ridge</t>
         </is>
       </c>
-      <c r="B51" s="28" t="n">
+      <c r="B51" s="29" t="n">
         <v>33.3</v>
       </c>
-      <c r="C51" s="28" t="n">
+      <c r="C51" s="29" t="n">
         <v>37.7</v>
       </c>
-      <c r="D51" s="28" t="n">
+      <c r="D51" s="29" t="n">
         <v>43.1</v>
       </c>
-      <c r="E51" s="28" t="n">
+      <c r="E51" s="29" t="n">
         <v>46.1</v>
       </c>
-      <c r="F51" s="28" t="n">
+      <c r="F51" s="29" t="n">
         <v>54.4</v>
       </c>
-      <c r="G51" s="28" t="n">
+      <c r="G51" s="29" t="n">
         <v>45.9</v>
       </c>
-      <c r="H51" s="28" t="n">
+      <c r="H51" s="29" t="n">
         <v>41.5</v>
       </c>
-      <c r="I51" s="28" t="n">
+      <c r="I51" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="J51" s="28" t="n">
+      <c r="J51" s="29" t="n">
         <v>25.2</v>
       </c>
-      <c r="K51" s="28" t="n">
+      <c r="K51" s="29" t="n">
         <v>33</v>
       </c>
-      <c r="L51" s="28" t="n">
+      <c r="L51" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="M51" s="28" t="n">
+      <c r="M51" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="N51" s="28" t="n">
+      <c r="N51" s="29" t="n">
         <v>27</v>
       </c>
     </row>
@@ -3525,43 +3525,43 @@
           <t>Mathematics: Paris Elementary</t>
         </is>
       </c>
-      <c r="B52" s="28" t="n">
+      <c r="B52" s="29" t="n">
         <v>29.7</v>
       </c>
-      <c r="C52" s="28" t="n">
+      <c r="C52" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="D52" s="28" t="n">
+      <c r="D52" s="29" t="n">
         <v>26.8</v>
       </c>
-      <c r="E52" s="28" t="n">
+      <c r="E52" s="29" t="n">
         <v>22.9</v>
       </c>
-      <c r="F52" s="28" t="n">
+      <c r="F52" s="29" t="n">
         <v>41.9</v>
       </c>
-      <c r="G52" s="28" t="n">
+      <c r="G52" s="29" t="n">
         <v>28.7</v>
       </c>
-      <c r="H52" s="28" t="n">
+      <c r="H52" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="I52" s="28" t="n">
+      <c r="I52" s="29" t="n">
         <v>32</v>
       </c>
-      <c r="J52" s="28" t="n">
+      <c r="J52" s="29" t="n">
         <v>15.3</v>
       </c>
-      <c r="K52" s="28" t="n">
+      <c r="K52" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="L52" s="28" t="n">
+      <c r="L52" s="29" t="n">
         <v>32</v>
       </c>
-      <c r="M52" s="28" t="n">
+      <c r="M52" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="N52" s="28" t="n">
+      <c r="N52" s="29" t="n">
         <v>29</v>
       </c>
     </row>
@@ -3655,31 +3655,31 @@
           <t>North Middletown</t>
         </is>
       </c>
-      <c r="B56" s="28" t="n">
+      <c r="B56" s="29" t="n">
         <v>62.6</v>
       </c>
-      <c r="C56" s="28" t="n">
+      <c r="C56" s="29" t="n">
         <v>68.8</v>
       </c>
-      <c r="D56" s="28" t="n">
+      <c r="D56" s="29" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="E56" s="28" t="n">
+      <c r="E56" s="29" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="F56" s="28" t="n">
+      <c r="F56" s="29" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="K56" s="28" t="n">
+      <c r="K56" s="29" t="n">
         <v>51.9</v>
       </c>
-      <c r="L56" s="28" t="n">
+      <c r="L56" s="29" t="n">
         <v>62.2</v>
       </c>
-      <c r="M56" s="28" t="n">
+      <c r="M56" s="29" t="n">
         <v>74.5</v>
       </c>
-      <c r="N56" s="28" t="n">
+      <c r="N56" s="29" t="n">
         <v>54</v>
       </c>
     </row>
@@ -3689,31 +3689,31 @@
           <t>Bourbon Central</t>
         </is>
       </c>
-      <c r="B57" s="28" t="n">
+      <c r="B57" s="29" t="n">
         <v>63.2</v>
       </c>
-      <c r="C57" s="28" t="n">
+      <c r="C57" s="29" t="n">
         <v>63</v>
       </c>
-      <c r="D57" s="28" t="n">
+      <c r="D57" s="29" t="n">
         <v>69.8</v>
       </c>
-      <c r="E57" s="28" t="n">
+      <c r="E57" s="29" t="n">
         <v>67.8</v>
       </c>
-      <c r="F57" s="28" t="n">
+      <c r="F57" s="29" t="n">
         <v>56.8</v>
       </c>
-      <c r="K57" s="28" t="n">
+      <c r="K57" s="29" t="n">
         <v>52.8</v>
       </c>
-      <c r="L57" s="28" t="n">
+      <c r="L57" s="29" t="n">
         <v>56.7</v>
       </c>
-      <c r="M57" s="28" t="n">
+      <c r="M57" s="29" t="n">
         <v>50.3</v>
       </c>
-      <c r="N57" s="28" t="n">
+      <c r="N57" s="29" t="n">
         <v>55.4</v>
       </c>
     </row>
@@ -3723,31 +3723,31 @@
           <t>Cane Ridge</t>
         </is>
       </c>
-      <c r="B58" s="28" t="n">
+      <c r="B58" s="29" t="n">
         <v>53.3</v>
       </c>
-      <c r="C58" s="28" t="n">
+      <c r="C58" s="29" t="n">
         <v>58.9</v>
       </c>
-      <c r="D58" s="28" t="n">
+      <c r="D58" s="29" t="n">
         <v>69.2</v>
       </c>
-      <c r="E58" s="28" t="n">
+      <c r="E58" s="29" t="n">
         <v>68.5</v>
       </c>
-      <c r="F58" s="28" t="n">
+      <c r="F58" s="29" t="n">
         <v>65.5</v>
       </c>
-      <c r="K58" s="28" t="n">
+      <c r="K58" s="29" t="n">
         <v>54.3</v>
       </c>
-      <c r="L58" s="28" t="n">
+      <c r="L58" s="29" t="n">
         <v>51.8</v>
       </c>
-      <c r="M58" s="28" t="n">
+      <c r="M58" s="29" t="n">
         <v>60.7</v>
       </c>
-      <c r="N58" s="28" t="n">
+      <c r="N58" s="29" t="n">
         <v>47.8</v>
       </c>
     </row>
@@ -3757,31 +3757,31 @@
           <t>Paris Elementary</t>
         </is>
       </c>
-      <c r="B59" s="28" t="n">
+      <c r="B59" s="29" t="n">
         <v>48</v>
       </c>
-      <c r="C59" s="28" t="n">
+      <c r="C59" s="29" t="n">
         <v>49.9</v>
       </c>
-      <c r="D59" s="28" t="n">
+      <c r="D59" s="29" t="n">
         <v>59.4</v>
       </c>
-      <c r="E59" s="28" t="n">
+      <c r="E59" s="29" t="n">
         <v>54.8</v>
       </c>
-      <c r="F59" s="28" t="n">
+      <c r="F59" s="29" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="K59" s="28" t="n">
+      <c r="K59" s="29" t="n">
         <v>46.1</v>
       </c>
-      <c r="L59" s="28" t="n">
+      <c r="L59" s="29" t="n">
         <v>45.9</v>
       </c>
-      <c r="M59" s="28" t="n">
+      <c r="M59" s="29" t="n">
         <v>40.7</v>
       </c>
-      <c r="N59" s="28" t="n">
+      <c r="N59" s="29" t="n">
         <v>41.9</v>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
           <t>Net uncommitted seats at both receiving schools</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="26">
         <f>B13-B14</f>
         <v/>
       </c>
@@ -4064,7 +4064,7 @@
           <t>Shortfall if closure proceeds today</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="26">
         <f>B16-B15</f>
         <v/>
       </c>
@@ -4240,7 +4240,7 @@
           <t>Paper seats added at the receiving schools, with the draft's new-construction sections reading None</t>
         </is>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="26">
         <f>D30+D31</f>
         <v/>
       </c>
@@ -4476,7 +4476,7 @@
           <t>Net receiving seats at the slides' own capacities (499 and 397)</t>
         </is>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="26">
         <f>(499-Redistricting!B8)-(Redistricting!B9-397)</f>
         <v/>
       </c>
@@ -6713,7 +6713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -8001,6 +8001,200 @@
       <c r="A114" s="21" t="inlineStr">
         <is>
           <t>Extreme bound: NMES's own year-over-year cost change 2022-23 to 2023-24 ($259,888 lower with 16 fewer students, about $16,243 per student, which folds in deliberate staffing cuts) gives $18,527 at 174: under Cane Ridge, marginally over Bourbon Central. Even the most hostile actuals-derived number does not restore the cost case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>THE RECRUITMENT POOL: WHERE FILL-THE-SEATS STUDENTS CAN COME FROM (measured; year noted per row; sources archived under build/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Registered homeschoolers, Bourbon Co district (2022-23; district letter-of-intent counts via the Washington Post records project)</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Registered homeschoolers, Paris Independent (2022-23)</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>County total registered homeschoolers (a floor; KY letter compliance is incomplete)</t>
+        </is>
+      </c>
+      <c r="B119" s="26">
+        <f>B117+B118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>County school-age (5-17) residents in private school OR homeschool (ACS 2019-23; the Census asks these as one combined answer; margin of error +/-299)</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="n">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Same figure, ACS 2014-18 window: the pool nearly tripled in five years</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Of the current pool, seats at the county's ONLY private school (St. Mary, Paris, PK-5; federal Private School Survey 2023-24)</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Co residents enrolled in OUT-OF-COUNTY public districts (KDE Non-Resident Student report, SY2024-25)</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which Cloverport Independent, host of the statewide virtual academy: a 150-mile 'commute' that is really virtual enrollment</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Out-of-county students already enrolled in Bourbon Co schools (same KDE report)</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which from Fayette County</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Net nonresident import, Bourbon Co district (436 enrolled in vs 247 residents out, Paris flows included)</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>LEVER: returning homeschool or private-school students recruited (site planner slider; default zero so the published fill-planner numbers are unchanged)</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>New SEEK per returning student (FY2027 base; same cell the leaver cost uses, so the symmetry is honest)</t>
+        </is>
+      </c>
+      <c r="B130" s="18">
+        <f>Assumptions!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Net per returning student after variable cost</t>
+        </is>
+      </c>
+      <c r="B131" s="9">
+        <f>Assumptions!B6-Assumptions!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Recurring SEEK revenue if the lever is used</t>
+        </is>
+      </c>
+      <c r="B132" s="9">
+        <f>B129*B131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Recurring SEEK revenue if all 46 open seats fill from this pool alone</t>
+        </is>
+      </c>
+      <c r="B133" s="23">
+        <f>46*Assumptions!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Capture rate that requires: share of registered homeschoolers / share of the full ACS pool</t>
+        </is>
+      </c>
+      <c r="B134" s="19">
+        <f>46/B119</f>
+        <v/>
+      </c>
+      <c r="C134" s="19">
+        <f>46/B120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="inlineStr">
+        <is>
+          <t>Total added students from all sources (rezone + transfers + returns) is capped at 46 by the rated 174; the site planner enforces the cap. Rezoned students bring no new SEEK (already enrolled in-district); transfers and returns each bring the full base. Sources: KDE Non-Resident Student report SY24-25 and the Washington Post home-school district file, both archived under build/; ACS table B14003 (Bourbon County); NCES Private School Universe Survey 2023-24.</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8320,7 @@
           <t>NMES zone area (sq mi)</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>B5*B9</f>
         <v/>
       </c>
@@ -8137,7 +8331,7 @@
           <t>Paris-area zones (sq mi)</t>
         </is>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>B5-B10</f>
         <v/>
       </c>
@@ -8302,7 +8496,7 @@
           <t>Marginal cost per bus-mile, low</t>
         </is>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="28" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8317,7 +8511,7 @@
           <t>Marginal cost per bus-mile, high</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="28" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -8511,7 +8705,7 @@
           <t>Average Daily Attendance, FY2025</t>
         </is>
       </c>
-      <c r="B49" s="28" t="n">
+      <c r="B49" s="29" t="n">
         <v>2242.5</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -8562,7 +8756,7 @@
           <t>Straight-line, NMES to the Paris schools (miles)</t>
         </is>
       </c>
-      <c r="B55" s="28" t="n">
+      <c r="B55" s="29" t="n">
         <v>8.871</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -8577,7 +8771,7 @@
           <t>Measured road distance, US 460 (miles)</t>
         </is>
       </c>
-      <c r="B56" s="28" t="n">
+      <c r="B56" s="29" t="n">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -8592,7 +8786,7 @@
           <t>Implied road factor on the measured pair</t>
         </is>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="30">
         <f>B56/B55</f>
         <v/>
       </c>
@@ -8603,7 +8797,7 @@
           <t>Road factor applied elsewhere (the measured US 460 pair implies 1.13)</t>
         </is>
       </c>
-      <c r="B58" s="27" t="n">
+      <c r="B58" s="28" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -8613,7 +8807,7 @@
           <t>Area-average added distance under closure, one way, straight-line</t>
         </is>
       </c>
-      <c r="B59" s="28" t="n">
+      <c r="B59" s="29" t="n">
         <v>3.271</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -8639,7 +8833,7 @@
           <t>Farthest corner of the zone, straight-line to Paris / to NMES</t>
         </is>
       </c>
-      <c r="B61" s="28" t="n">
+      <c r="B61" s="29" t="n">
         <v>15.1</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -8654,7 +8848,7 @@
           <t>Farthest corner by road: to Paris / to NMES (miles)</t>
         </is>
       </c>
-      <c r="B62" s="26">
+      <c r="B62" s="27">
         <f>ROUND(B61*B58,0)</f>
         <v/>
       </c>
@@ -9469,7 +9663,7 @@
           <t>Average Daily Attendance, FY2025 (SEEK basis)</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="29" t="n">
         <v>2242.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -9526,7 +9720,7 @@
           <t>Annual restricted margin available for new debt (illustrative)</t>
         </is>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <f>B23*B24+B25-B26</f>
         <v/>
       </c>
@@ -9633,7 +9827,7 @@
           <t>Assumed term, years</t>
         </is>
       </c>
-      <c r="B41" s="31" t="n">
+      <c r="B41" s="32" t="n">
         <v>20</v>
       </c>
     </row>
@@ -9643,7 +9837,7 @@
           <t>Annual debt service on the proposed bond</t>
         </is>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <f>B39*B40/(1-(1+B40)^-B41)</f>
         <v/>
       </c>
@@ -9979,7 +10173,7 @@
           <t>Net General Fund change, FY2026 (unaudited)</t>
         </is>
       </c>
-      <c r="B75" s="30">
+      <c r="B75" s="31">
         <f>B73-B74</f>
         <v/>
       </c>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Demographics" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="School_Data" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Facility_Plans" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="KY_Closures" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4780,6 +4781,900 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Thirty Years of Kentucky Rural School Closures: The Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Universe: federal Common Core of Data, every KY public school, every year, 1994-2023 (via the Urban Institute Education Data API). Screens: rural/small-town locale; enrollment above zero; renames, rebuilds under new IDs, and non-community programs removed; corrupt federal finance rows (12) excluded by an enrollment-plausibility screen. Full lists archived as build/ky_rural_closures_1995_2023.csv and build/ky_closure_dollar_cases.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>THE UNIVERSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rural/small-town school closures since 1995</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Towns that lost their last public school (any district; successor-school check applied)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Closure events with clean district finance data</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Median district per-pupil spending growth vs state, year before to 3 years after (pct pts)</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Same, vs districts of similar size (within 40 percent of enrollment)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Districts growing slower than benchmark after closing</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>84/163</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Closures most like this plan (single small elementary, nothing built): count / median saving</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>THE DOLLAR TEST: BUDGET GAP VS STATE TREND, CREDITED ENTIRELY TO THE CLOSURE (A GENEROUS CEILING), PER DISPLACED STUDENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Students displaced</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Spending, year before</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Spending, 3 yrs after</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>State growth</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>Gap per year</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>Gap per student</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Perry County</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>825</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>42356000</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>44953000</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="G15" s="9">
+        <f>D15*(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>G15-E15</f>
+        <v/>
+      </c>
+      <c r="I15" s="23">
+        <f>H15/C15</f>
+        <v/>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>NEW West Perry Elementary built for the children moved; scores continued a pre-existing climb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Johnson County</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>37827000</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>39175000</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.1339</v>
+      </c>
+      <c r="G16" s="9">
+        <f>D16*(1+F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>G16-E16</f>
+        <v/>
+      </c>
+      <c r="I16" s="23">
+        <f>H16/C16</f>
+        <v/>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>Meade Memorial El, pure absorption; scores flat: savings without improvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Pineville Independent</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>508</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>5355000</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>4662000</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="G17" s="9">
+        <f>D17*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>G17-E17</f>
+        <v/>
+      </c>
+      <c r="I17" s="23">
+        <f>H17/C17</f>
+        <v/>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>Same-town rebuild into one new combined campus; no community lost a school</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Leslie County</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>18031000</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="G18" s="9">
+        <f>D18*(1+F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="9">
+        <f>G18-E18</f>
+        <v/>
+      </c>
+      <c r="I18" s="23">
+        <f>H18/C18</f>
+        <v/>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>Middle school folded into existing campus; the record's one savings-plus-gains case</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Pike County</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>123</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>88648000</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>90441000</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="G19" s="9">
+        <f>D19*(1+F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="9">
+        <f>G19-E19</f>
+        <v/>
+      </c>
+      <c r="I19" s="23">
+        <f>H19/C19</f>
+        <v/>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>Majestic Knox Creek El, 1.3 percent of a 9,400-student district; the +8 score case</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Somerset Independent</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>1999</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>264</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>9161000</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>9316000</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.2045</v>
+      </c>
+      <c r="G20" s="9">
+        <f>D20*(1+F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>G20-E20</f>
+        <v/>
+      </c>
+      <c r="I20" s="23">
+        <f>H20/C20</f>
+        <v/>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>City-district reorganization, not a rural town</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Rowan County</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>19483000</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>21010000</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="G21" s="9">
+        <f>D21*(1+F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>G21-E21</f>
+        <v/>
+      </c>
+      <c r="I21" s="23">
+        <f>H21/C21</f>
+        <v/>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>Farmers El; gap exceeds plausible closure savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Webster County</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>172</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>19693000</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>19475000</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="G22" s="9">
+        <f>D22*(1+F22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>G22-E22</f>
+        <v/>
+      </c>
+      <c r="I22" s="23">
+        <f>H22/C22</f>
+        <v/>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>Slaughters El; town lost its school; scores -2 vs state</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Butler County</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>14995000</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>16806000</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="G23" s="9">
+        <f>D23*(1+F23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>G23-E23</f>
+        <v/>
+      </c>
+      <c r="I23" s="23">
+        <f>H23/C23</f>
+        <v/>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>Third District El; gap exceeds plausible closure savings</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Letcher County</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>30621000</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>31987000</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="G24" s="9">
+        <f>D24*(1+F24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>G24-E24</f>
+        <v/>
+      </c>
+      <c r="I24" s="23">
+        <f>H24/C24</f>
+        <v/>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>Kingdom Come Settlement El; gap of $49K per child is 4x what a school costs: budget-wide, not closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Muhlenberg County</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>52941000</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>45883000</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="G25" s="9">
+        <f>D25*(1+F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>G25-E25</f>
+        <v/>
+      </c>
+      <c r="I25" s="23">
+        <f>H25/C25</f>
+        <v/>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>Career HS; $99K per child gap = post-construction and coal-era budget swings, not closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Wayne County</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>381</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>22129000</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>23687000</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="G26" s="9">
+        <f>D26*(1+F26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>G26-E26</f>
+        <v/>
+      </c>
+      <c r="I26" s="23">
+        <f>H26/C26</f>
+        <v/>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>A J Lloyd Middle</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Lincoln County</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>286</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>40397000</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>41252000</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.1339</v>
+      </c>
+      <c r="G27" s="9">
+        <f>D27*(1+F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>G27-E27</f>
+        <v/>
+      </c>
+      <c r="I27" s="23">
+        <f>H27/C27</f>
+        <v/>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>Sixth-grade center reorganization</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Montgomery County</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>737</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>45709000</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>46413000</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="G28" s="9">
+        <f>D28*(1+F28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>G28-E28</f>
+        <v/>
+      </c>
+      <c r="I28" s="23">
+        <f>H28/C28</f>
+        <v/>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>County-seat intermediate reorganization, not a rural town</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Metcalfe County</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>817</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>17028000</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>15990000</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="G29" s="9">
+        <f>D29*(1+F29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>G29-E29</f>
+        <v/>
+      </c>
+      <c r="I29" s="23">
+        <f>H29/C29</f>
+        <v/>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>Closed 3 schools, half the district displaced; scores fell 10.5 vs state: the cautionary pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>THE YARDSTICK: WHAT THIS PLAN REQUIRES PER DISPLACED STUDENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Plan requirement, low / high ($800K-$1M over the 128 students displaced)</t>
+        </is>
+      </c>
+      <c r="B32" s="23">
+        <f>800000/Assumptions!B11</f>
+        <v/>
+      </c>
+      <c r="C32" s="23">
+        <f>1000000/Assumptions!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>This report's own model, per displaced student: median / central / best case</t>
+        </is>
+      </c>
+      <c r="B33" s="9">
+        <f>91240/Assumptions!B11</f>
+        <v/>
+      </c>
+      <c r="C33" s="9">
+        <f>Closure_Model!B47/Assumptions!B11</f>
+        <v/>
+      </c>
+      <c r="D33" s="9">
+        <f>Closure_Model!B49/Assumptions!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Reading: every plausible case in thirty years landed between about $2,000 and $4,800 per displaced student, and the largest (Perry, Pineville) were bought with new construction. The plan requires $6,250 to $7,813 with no construction. Cases whose gaps exceed roughly a school's own cost per student ($10-13K in those years) are flagged in the notes: such gaps prove budget-wide causes, which is why this model prices closure bottom-up (positions, busing, SEEK) rather than from budget trends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>OUTCOMES, WITHIN ONE TESTING SYSTEM (federal proficiency series, closures 2012-2016, change vs state 3 years out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Events measurable / improved 3+ pts / declined 3+ pts / flat</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Spearman correlation, share of district displaced vs score change</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Median score change: events displacing 15%+ of district / under 15%</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C39" s="29" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Events with BOTH clear savings and clear gains</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Leslie County 2013: middle school folded into an existing campus in the same community</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Cases of a rural town's ELEMENTARY closed with clear savings and clear gains</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>Honest limits: closures before 2012 and after 2016 cannot be score-tested across Kentucky's assessment-system changes; whole-district mergers are unobservable afterward; and same-size Kentucky towns that KEPT schools declined in population at nearly the same median rate as towns that lost them (-4.1 vs -3.5 percent, 2000-2020), so no claim is made that closure causes population decline. The claim is narrower: the record contains no measurable precedent for the savings or the improvement this plan promises.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +165,7 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4787,7 +4788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5186,7 +5187,7 @@
       </c>
       <c r="J20" s="21" t="inlineStr">
         <is>
-          <t>City-district reorganization, not a rural town</t>
+          <t>City-district grade realignment of a 4-5 center, not a rural town; grades split between existing city schools</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5499,7 @@
       </c>
       <c r="J28" s="21" t="inlineStr">
         <is>
-          <t>County-seat intermediate reorganization, not a rural town</t>
+          <t>County-seat grade reshuffle of a 5-6 intermediate center, not a rural town or an elementary; opened NEW Northview Elementary the same year</t>
         </is>
       </c>
     </row>
@@ -5537,134 +5538,298 @@
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t>Closed 3 schools, half the district displaced; scores fell 10.5 vs state: the cautionary pair</t>
+          <t>Closed 3 schools, half the district displaced; built new Primary and Intermediate centers; scores fell 10.5 vs state: the cautionary pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Adair County</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>479</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>22126000</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>23240000</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="G30" s="9">
+        <f>D30*(1+F30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>G30-E30</f>
+        <v/>
+      </c>
+      <c r="I30" s="23">
+        <f>H30/C30</f>
+        <v/>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>3 rural elementaries; built NEW Adair County Elementary the same year; pre-closure spending spike reverting; gap is 88 percent of everything the district then spent per student</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Breckinridge County</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>1997</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>299</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>17048000</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>16425000</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="G31" s="9">
+        <f>D31*(1+F31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>G31-E31</f>
+        <v/>
+      </c>
+      <c r="I31" s="23">
+        <f>H31/C31</f>
+        <v/>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>2 rural K-8 schools, nothing built; gap of $9,606 per child EXCEEDS the district's $6,108 total cost per student then: impossible as closure savings, a data-edge artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>THE YARDSTICK: WHAT THIS PLAN REQUIRES PER DISPLACED STUDENT</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Plan requirement, low / high ($800K-$1M over the 128 students displaced)</t>
         </is>
       </c>
-      <c r="B32" s="23">
+      <c r="B34" s="23">
         <f>800000/Assumptions!B11</f>
         <v/>
       </c>
-      <c r="C32" s="23">
+      <c r="C34" s="23">
         <f>1000000/Assumptions!B11</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>This report's own model, per displaced student: median / central / best case</t>
         </is>
       </c>
-      <c r="B33" s="9">
+      <c r="B35" s="9">
         <f>91240/Assumptions!B11</f>
         <v/>
       </c>
-      <c r="C33" s="9">
+      <c r="C35" s="9">
         <f>Closure_Model!B47/Assumptions!B11</f>
         <v/>
       </c>
-      <c r="D33" s="9">
+      <c r="D35" s="9">
         <f>Closure_Model!B49/Assumptions!B11</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>Reading: every plausible case in thirty years landed between about $2,000 and $4,800 per displaced student, and the largest (Perry, Pineville) were bought with new construction. The plan requires $6,250 to $7,813 with no construction. Cases whose gaps exceed roughly a school's own cost per student ($10-13K in those years) are flagged in the notes: such gaps prove budget-wide causes, which is why this model prices closure bottom-up (positions, busing, SEEK) rather than from budget trends.</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>OUTCOMES, WITHIN ONE TESTING SYSTEM (federal proficiency series, closures 2012-2016, change vs state 3 years out)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Events measurable / improved 3+ pts / declined 3+ pts / flat</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>22</v>
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Reading: among rural ELEMENTARY closures, the one clean no-construction comparable (Webster 2012) paid $3,525 per displaced student; every case at or near the plan's band built a new school (Perry, Adair, Metcalfe) or was a city or county-seat grade reshuffle (Somerset, Montgomery). Gaps beyond roughly a school's own cost per student are flagged in the notes: they prove budget-wide causes, which is why this model prices closure bottom-up (positions, busing, SEEK) rather than from budget trends.</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Spearman correlation, share of district displaced vs score change</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>-0.28</v>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>THE FULL DISTRIBUTION, PER DISPLACED STUDENT (all measurable events; whole budget gap credited to the closure)</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Median score change: events displacing 15%+ of district / under 15%</t>
-        </is>
-      </c>
-      <c r="B39" s="29" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C39" s="29" t="n">
-        <v>0.2</v>
+          <t>All 163 events: P25 / median / P75</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>-1875</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>7520</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Events with BOTH clear savings and clear gains</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Leslie County 2013: middle school folded into an existing campus in the same community</t>
-        </is>
+          <t>Physically plausible magnitudes only (within $13K, 116 events): P25 / median / P75</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>-1433</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>818</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>4120</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Cases of a rural town's ELEMENTARY closed with clear savings and clear gains</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="n">
-        <v>0</v>
+          <t>Share of districts spending MORE than trend after closing (all / plausible-only)</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C41" s="37" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Analogous-subset RAW median, published for transparency</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>8440</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  why $8,440 is an artifact, not a savings figure: dividing whole-district budget noise by 60-320 student denominators explodes per-child values; 11 of 27 such events exceed the $13K physical ceiling in one direction or the other. Same events, plausible window only, median:</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>CONVERGENCE CHECK: the record's plausible median vs this model's independent bottom-up median per displaced student</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>818</v>
+      </c>
+      <c r="C44" s="23">
+        <f>91240/Assumptions!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>OUTCOMES, WITHIN ONE TESTING SYSTEM (federal proficiency series, closures 2012-2016, change vs state 3 years out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Events measurable / improved 3+ pts / declined 3+ pts / flat</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Spearman correlation, share of district displaced vs score change</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Median score change: events displacing 15%+ of district / under 15%</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C49" s="29" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Events with BOTH clear savings and clear gains</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Leslie County 2013: middle school folded into an existing campus in the same community</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Cases of a rural town's ELEMENTARY closed with clear savings and clear gains</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>Honest limits: closures before 2012 and after 2016 cannot be score-tested across Kentucky's assessment-system changes; whole-district mergers are unobservable afterward; and same-size Kentucky towns that KEPT schools declined in population at nearly the same median rate as towns that lost them (-4.1 vs -3.5 percent, 2000-2020), so no claim is made that closure causes population decline. The claim is narrower: the record contains no measurable precedent for the savings or the improvement this plan promises.</t>
         </is>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -813,15 +813,15 @@
         <v/>
       </c>
       <c r="C6" s="9">
-        <f>B6-GF_Summary!$D$16+0.5*Alternatives!$B$21</f>
+        <f>B6-GF_Summary!$D$16+0.5*Alternatives!$B$20</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>C6-GF_Summary!$D$16+Alternatives!$B$21</f>
+        <f>C6-GF_Summary!$D$16+Alternatives!$B$20</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>D6-GF_Summary!$D$16+Alternatives!$B$21</f>
+        <f>D6-GF_Summary!$D$16+Alternatives!$B$20</f>
         <v/>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; covers 13.6% of the gap (24.2% in the district-favorable case); longer rides; enrollment-loss risk</t>
+          <t>Closure vote; the v3 central case covers 5.0% of the gap (10.8% at the base case, 21.3% at the favorable tail); longer rides; enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>Alternatives!B21</f>
+        <f>Alternatives!B20</f>
         <v/>
       </c>
       <c r="C7" s="9">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Rated capacity 549, reflecting the addition in the 2021 plan</t>
+          <t>Approved rating 521; the plan's 549 is a contingent To-Become figure tied to an expansion never built (GSF unchanged at 63,320 through the July 2026 KDE report)</t>
         </is>
       </c>
     </row>
@@ -4019,11 +4019,11 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Bourbon Central open seats at rated 549</t>
+          <t>Bourbon Central open seats at the approved 521</t>
         </is>
       </c>
       <c r="B13" s="11">
-        <f>549-Redistricting!B8</f>
+        <f>521-Redistricting!B8</f>
         <v/>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Reading: the receiving schools' rated capacities are 549 (Bourbon Central) and 422 (Cane Ridge). At current enrollment that is 90 open at Bourbon Central and 31 over at Cane Ridge, a net 59 uncommitted seats for 128 children. NMES's major renovation was priced in 2013 and re-priced higher in 2021, each time scheduled after the then-current biennium. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
+          <t>Reading: the receiving schools' approved ratings are 521 (Bourbon Central; the plan's 549 is contingent on an expansion never built) and 422 (Cane Ridge). At current enrollment that is 62 open at Bourbon Central and 31 over at Cane Ridge, a net 31 uncommitted seats for 128 children (59 only under the plan's contingent 549). NMES's major renovation was priced in 2013 and re-priced higher in 2021, each time scheduled after the then-current biennium. Its rated capacity fell 198 to 174 between the same two plans while its enrollment fell 169 to 128.</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
         <v>640</v>
       </c>
       <c r="D30" s="11">
-        <f>C30-549</f>
+        <f>C30-521</f>
         <v/>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
     <row r="52">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>Notes: components and totals as printed on the slides; Bourbon Central's printed components sum $9,421 below its printed total. The slides' receiving-school capacities (499, 397) differ from the 2026 draft DFP table (640, 547) and from the approved 2021 plan (549 with addition, 422): three documents, three capacity sets for the same buildings. NMES total need is second lowest among the district's schools.</t>
+          <t>Notes: components and totals as printed on the slides; Bourbon Central's printed components sum $9,421 below its printed total. The slides' receiving-school capacities (499, 397) differ from the 2026 draft DFP table (640, 547) and from the approved 2021 plan (the approved 521, 422; the plan's contingent 549 depends on unbuilt work): three documents, three capacity sets for the same buildings. NMES total need is second lowest among the district's schools.</t>
         </is>
       </c>
     </row>
@@ -5768,16 +5768,16 @@
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>-0.28</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="49">
@@ -5800,7 +5800,7 @@
         <v>-2</v>
       </c>
       <c r="C49" s="29" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="50">
@@ -7456,7 +7456,7 @@
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 1,944 combinations (computed in build script, equal weights): median +$91,240; middle half -$17,500 to +$200,000; 29 percent of scenarios negative. One-time transition costs $100K-$300K in year one are additional.</t>
+          <t>Distribution of all 1,944 combinations, equal weights, enumerated by build/closure_grid.py: positions take four values (2, 3, 4, 5), fixed-avoided takes two ($230,000 mothballed, $290,000 sold), and the five other levers three each (4 x 2 x 3^5 = 1,944). Median +$91,240; middle half -$17,500 to +$200,000; 28.8 percent (559 of 1,944, published as 29 percent) of scenarios negative. One-time transition costs $100K-$300K in year one are additional.</t>
         </is>
       </c>
     </row>
@@ -8054,22 +8054,22 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>Net recurring benefit, low</t>
+          <t>Net recurring benefit, low (avoided sections priced at the GF-borne $60K central, per the v3 on-behalf correction; range $50-75K)</t>
         </is>
       </c>
       <c r="B30" s="24">
-        <f>B26-B27+B28*Assumptions!B41</f>
+        <f>B26-B27+B28*Assumptions!B69</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>Net recurring benefit, high</t>
+          <t>Net recurring benefit, high (two sections at the same GF-borne rate)</t>
         </is>
       </c>
       <c r="B31" s="23">
-        <f>B26-B27+B29*Assumptions!B41</f>
+        <f>B26-B27+B29*Assumptions!B69</f>
         <v/>
       </c>
     </row>
@@ -8456,7 +8456,7 @@
     <row r="71">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>Base-year variant: at the current 115 enrolled, filling to 174 adds 59 students and the break-even vs Bourbon Central falls to about $11,500, with the same verdict. Two added teachers at the loaded rate are equivalent to about $3,700 of marginal cost per student, inside the grid above.</t>
+          <t>Current enrollment is 128 (NCES CCD, 2024-25); filling to 174 adds 46 students, the figure used throughout this workbook and the grid above.</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8810,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net saving is $121K to $725K and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect is minus $385K to plus $565K (median $91K) and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>
@@ -10392,7 +10392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10936,18 +10936,18 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Matches the closure model's worst case</t>
+          <t>Sits between the v3 closure model's median ($91,240) and central case ($131,240)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Closure model default net saving</t>
+          <t>Closure model median (v3 two-tailed grid)</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>361240</v>
+        <v>91240</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -10955,18 +10955,18 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab</t>
+          <t>Closure_Model tab, 1,944-combination grid</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Closure model best case</t>
+          <t>Closure model best case (v3 favorable tail)</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>725000</v>
+        <v>565000</v>
       </c>
       <c r="C48" s="9">
         <f>B48*(1-(1+B$40)^-B$41)/B$40</f>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab</t>
+          <t>Closure_Model tab B49</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="F81" s="21" t="inlineStr">
         <is>
-          <t>Object 5210: $1,098,633 from the Building Fund (320) + $222,276 from Capital Outlay (310), which ended the year at $0. Lawful under budget-act capital funds flexibility; budgeted from September 2025</t>
+          <t>Object 5210: $1,098,663 from the Building Fund (320) + $222,276 from Capital Outlay (310), which ended the year at $0 ($1,098,663 + $222,276 = $1,320,939 per the GF receipts ledger; the packet's fund 320 page records $1,098,633, a $30 internal discrepancy in the district's own packet). Lawful under budget-act capital funds flexibility. The Building Fund piece was budgeted from September 2025 ($1,120,203); the $222,276 Capital Outlay piece appears in no version of the FY2026 budget</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>trend uses the unaudited FY2026 net change. Operations are balanced first; only the remainder services debt.</t>
+          <t>trend uses the unaudited FY2026 net change. The sweep is ended in both cases; only genuine remainder services debt.</t>
         </is>
       </c>
     </row>
@@ -11535,129 +11535,152 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Operating room left for debt service after the budget balances</t>
-        </is>
-      </c>
-      <c r="B99" s="9">
-        <f>MAX(0,B97+B98-B96)</f>
-        <v/>
-      </c>
-      <c r="C99" s="9">
-        <f>MAX(0,C97+C98-C96)</f>
-        <v/>
+          <t>End the capital-to-GF sweep (required before the building-fund residual can be pledged to new bonds)</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>1320939</v>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>1320939</v>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>The FY2026 sweep is General Fund revenue today; pledging the residual means replacing it. Without this row the restricted stream would be counted twice</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>General-fund bond capacity from that room</t>
+          <t>Operating room left for debt service after the budget balances and the sweep ends</t>
         </is>
       </c>
       <c r="B100" s="9">
-        <f>B99*(1-(1+B$40)^-B$41)/B$40</f>
+        <f>MAX(0,B97+B98-B96-B99)</f>
         <v/>
       </c>
       <c r="C100" s="9">
-        <f>C99*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
+        <f>MAX(0,C97+C98-C96-C99)</f>
+        <v/>
+      </c>
+      <c r="F100" s="21" t="inlineStr">
+        <is>
+          <t>Trend case balances with about $283K to spare; the conservative case is still about $1.24M short, so its total below leans on equalization and existing restricted capacity only</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>New state equalization on the already-levied recallable nickel</t>
-        </is>
-      </c>
-      <c r="B101" s="8" t="n">
-        <v>276246</v>
-      </c>
-      <c r="C101" s="8" t="n">
-        <v>276246</v>
-      </c>
-      <c r="F101" s="21" t="inlineStr">
-        <is>
-          <t>FY2027 SEEK schedule; the recallable nickel itself is already levied and its local yield is already inside the building-fund stream above</t>
-        </is>
+          <t>General-fund bond capacity from that room</t>
+        </is>
+      </c>
+      <c r="B101" s="9">
+        <f>B100*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C101" s="9">
+        <f>C100*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Bond capacity from the new equalization</t>
-        </is>
-      </c>
-      <c r="B102" s="9">
-        <f>B101*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="C102" s="9">
-        <f>C101*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
+          <t>New state equalization on the already-levied recallable nickel</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="C102" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="F102" s="21" t="inlineStr">
+        <is>
+          <t>FY2027 SEEK schedule; the recallable nickel itself is already levied and its local yield is already inside the building-fund stream above</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
+          <t>Bond capacity from the new equalization</t>
+        </is>
+      </c>
+      <c r="B103" s="9">
+        <f>B102*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C103" s="9">
+        <f>C102*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
           <t>Existing unused restricted capacity, approximate</t>
         </is>
       </c>
-      <c r="B103" s="8" t="n">
+      <c r="B104" s="8" t="n">
         <v>17600000</v>
       </c>
-      <c r="C103" s="8" t="n">
+      <c r="C104" s="8" t="n">
         <v>17600000</v>
       </c>
-      <c r="F103" s="21" t="inlineStr">
+      <c r="F104" s="21" t="inlineStr">
         <is>
           <t>FY2024 audit $23.5M less local share of the 2024 issue; fiscal agent's statement is the authority</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="22" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="22" t="inlineStr">
         <is>
           <t>Total capacity available without closing a school</t>
         </is>
       </c>
-      <c r="B104" s="24">
-        <f>B100+B102+B103</f>
-        <v/>
-      </c>
-      <c r="C104" s="24">
-        <f>C100+C102+C103</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Roughly $22.2 million in the conservative case and $42.1 million on the FY2026 trend, with the budget balanced</t>
-        </is>
+      <c r="B105" s="24">
+        <f>B101+B103+B104</f>
+        <v/>
+      </c>
+      <c r="C105" s="24">
+        <f>C101+C103+C104</f>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>first in both. The administration's plan reaches $32 million at face value and leaves the deficit in place.</t>
+          <t>Roughly $22.2 million in the conservative case and $42.1 million on the FY2026 trend, with the budget balanced</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Floor check: even with zero general-fund room, the restricted capacity plus new equalization alone are about $21 million.</t>
+          <t>first in both. The administration's plan reaches $32 million at face value and leaves the deficit in place.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Pledging the building-fund residual to new bonds requires ending the capital-to-operations sweep documented above,</t>
+          <t>Floor check: even with zero general-fund room, the restricted capacity plus new equalization alone are about $21 million.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Pledging the building-fund residual to new bonds requires ending the capital-to-operations sweep documented above,</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>which is exactly what the administration's plan implies; the only question is which recurring million replaces it.</t>
         </is>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -31,12 +31,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -125,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,6 +162,7 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1039,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1553,6 +1555,579 @@
       <c r="B54" s="19">
         <f>B53/(Assumptions!B24-Assumptions!B21)</f>
         <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>FOURTEEN YEARS OF LEVIED RATES, NINE AREA DISTRICTS (KDE Local District Tax Levies files, Total Real Estate column; cross-checked against DOR rate books 2024-2025, all nine reconcile exactly; archived as build/ky_levy_history_2012_2026.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>2012-13</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>2013-14</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>2014-15</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>2015-16</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>2016-17</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>2017-18</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>2018-19</t>
+        </is>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>2019-20</t>
+        </is>
+      </c>
+      <c r="J57" s="17" t="inlineStr">
+        <is>
+          <t>2020-21</t>
+        </is>
+      </c>
+      <c r="K57" s="17" t="inlineStr">
+        <is>
+          <t>2021-22</t>
+        </is>
+      </c>
+      <c r="L57" s="17" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="N57" s="17" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="O57" s="17" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="P57" s="17" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="B58" s="29" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="C58" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="D58" s="29" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="E58" s="29" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F58" s="29" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G58" s="29" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="H58" s="29" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J58" s="29" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="K58" s="29" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="L58" s="29" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="M58" s="29" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="N58" s="29" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="O58" s="29" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="P58" s="33">
+        <f>(O58/B58-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Scott</t>
+        </is>
+      </c>
+      <c r="B59" s="29" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="C59" s="29" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="F59" s="29" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G59" s="29" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="H59" s="29" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="I59" s="29" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J59" s="29" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K59" s="29" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="L59" s="29" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="M59" s="29" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="N59" s="29" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="O59" s="29" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="P59" s="33">
+        <f>(O59/B59-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Harrison</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="n">
+        <v>43</v>
+      </c>
+      <c r="C60" s="29" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D60" s="29" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="E60" s="29" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="F60" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="G60" s="29" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H60" s="29" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="J60" s="29" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="K60" s="29" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="L60" s="29" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M60" s="29" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="N60" s="29" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="O60" s="29" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="P60" s="33">
+        <f>(O60/B60-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="C61" s="29" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="D61" s="29" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E61" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="F61" s="29" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="G61" s="29" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="H61" s="29" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="J61" s="29" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="K61" s="29" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="L61" s="29" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="M61" s="29" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="N61" s="29" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="O61" s="29" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="P61" s="33">
+        <f>(O61/B61-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Fayette</t>
+        </is>
+      </c>
+      <c r="B62" s="29" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="C62" s="29" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="D62" s="29" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E62" s="29" t="n">
+        <v>74</v>
+      </c>
+      <c r="F62" s="29" t="n">
+        <v>75</v>
+      </c>
+      <c r="G62" s="29" t="n">
+        <v>75</v>
+      </c>
+      <c r="H62" s="29" t="n">
+        <v>81</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>81</v>
+      </c>
+      <c r="J62" s="29" t="n">
+        <v>81</v>
+      </c>
+      <c r="K62" s="29" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="L62" s="29" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="M62" s="29" t="n">
+        <v>81</v>
+      </c>
+      <c r="N62" s="29" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="O62" s="29" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="P62" s="33">
+        <f>(O62/B62-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Paris Ind</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" s="29" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="D63" s="29" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E63" s="29" t="n">
+        <v>69</v>
+      </c>
+      <c r="F63" s="29" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G63" s="29" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="H63" s="29" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="J63" s="29" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="K63" s="29" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="L63" s="29" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="M63" s="29" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="N63" s="29" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="O63" s="29" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="P63" s="33">
+        <f>(O63/B63-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C64" s="29" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="D64" s="29" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E64" s="29" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F64" s="29" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G64" s="29" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H64" s="29" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I64" s="29" t="n">
+        <v>41</v>
+      </c>
+      <c r="J64" s="29" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K64" s="29" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="L64" s="29" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="M64" s="29" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="N64" s="29" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O64" s="29" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="P64" s="33">
+        <f>(O64/B64-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="B65" s="29" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="C65" s="29" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D65" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="E65" s="29" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F65" s="29" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="G65" s="29" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="H65" s="29" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I65" s="29" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="J65" s="29" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K65" s="29" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="L65" s="29" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M65" s="29" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="N65" s="29" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O65" s="29" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="P65" s="33">
+        <f>(O65/B65-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Co</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="C66" s="29" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="D66" s="29" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="E66" s="29" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G66" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="H66" s="29" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="I66" s="29" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J66" s="29" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="K66" s="29" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="L66" s="29" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="M66" s="29" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="N66" s="29" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="O66" s="29" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="P66" s="33">
+        <f>(O66/B66-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>Bourbon County is the only district in the region whose levied rate is lower today than in tax year 2012 (55.4 down to 52.4, minus 5.4 percent); Bath rose 72.3 percent, Scott 38.9, Harrison 34.2, Clark 22.2, Fayette 18.4, Paris Independent 17.2. Honesty notes: these are levied RATES, not revenue effort; under HB 44 the compensating rate falls as assessments grow, so the chart nets each board's levy choices against its assessment growth. Bourbon took the 4 percent option in 5 of the last 12 years (KDE levied-type file); the rate fell anyway because the other years took compensating or less, including the 12-cent slide of 2018-2022. Neighbors that rose took the 4 percent 7 to 9 times over the same window.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2968,7 +3543,7 @@
           <t>Subject</t>
         </is>
       </c>
-      <c r="B34" s="33" t="inlineStr">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
@@ -4253,7 +4828,7 @@
           <t>NMES fill rate even at the draft's own 154 rating</t>
         </is>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="35">
         <f>B32/C32</f>
         <v/>
       </c>
@@ -4644,13 +5219,13 @@
           <t>Bourbon Central Elementary (1988)</t>
         </is>
       </c>
-      <c r="B67" s="35" t="n">
+      <c r="B67" s="36" t="n">
         <v>0.887637</v>
       </c>
-      <c r="C67" s="35" t="n">
+      <c r="C67" s="36" t="n">
         <v>0.819273</v>
       </c>
-      <c r="D67" s="35" t="n">
+      <c r="D67" s="36" t="n">
         <v>0.823017</v>
       </c>
       <c r="E67" s="8" t="n">
@@ -4666,13 +5241,13 @@
           <t>Cane Ridge Elementary (1992)</t>
         </is>
       </c>
-      <c r="B68" s="35" t="n">
+      <c r="B68" s="36" t="n">
         <v>0.8120579999999999</v>
       </c>
-      <c r="C68" s="35" t="n">
+      <c r="C68" s="36" t="n">
         <v>0.811765</v>
       </c>
-      <c r="D68" s="35" t="n">
+      <c r="D68" s="36" t="n">
         <v>0.728249</v>
       </c>
       <c r="E68" s="8" t="n">
@@ -4688,13 +5263,13 @@
           <t>North Middletown Elementary (1948/64)</t>
         </is>
       </c>
-      <c r="B69" s="35" t="n">
+      <c r="B69" s="36" t="n">
         <v>0.694064</v>
       </c>
-      <c r="C69" s="35" t="n">
+      <c r="C69" s="36" t="n">
         <v>0.702133</v>
       </c>
-      <c r="D69" s="35" t="n">
+      <c r="D69" s="36" t="n">
         <v>0.773295</v>
       </c>
       <c r="E69" s="8" t="n">
@@ -4710,13 +5285,13 @@
           <t>Bourbon County Middle School (1948)</t>
         </is>
       </c>
-      <c r="B70" s="35" t="n">
+      <c r="B70" s="36" t="n">
         <v>0.726249</v>
       </c>
-      <c r="C70" s="35" t="n">
+      <c r="C70" s="36" t="n">
         <v>0.727501</v>
       </c>
-      <c r="D70" s="35" t="n">
+      <c r="D70" s="36" t="n">
         <v>0.596145</v>
       </c>
       <c r="E70" s="8" t="n">
@@ -4732,13 +5307,13 @@
           <t>Bourbon County High School (1968)</t>
         </is>
       </c>
-      <c r="B71" s="35" t="n">
+      <c r="B71" s="36" t="n">
         <v>0.809819</v>
       </c>
-      <c r="C71" s="35" t="n">
+      <c r="C71" s="36" t="n">
         <v>0.802057</v>
       </c>
-      <c r="D71" s="35" t="n">
+      <c r="D71" s="36" t="n">
         <v>0.792529</v>
       </c>
       <c r="E71" s="8" t="n">
@@ -4754,7 +5329,7 @@
           <t>Check: Condition Index = 1 - (4-year renewal needs / replacement value), NMES</t>
         </is>
       </c>
-      <c r="B72" s="36">
+      <c r="B72" s="37">
         <f>1-E69/F69</f>
         <v/>
       </c>
@@ -4765,7 +5340,7 @@
           <t>NMES change between inspection cycles (2020-21 to April 2026)</t>
         </is>
       </c>
-      <c r="B73" s="36">
+      <c r="B73" s="37">
         <f>D69-B69</f>
         <v/>
       </c>
@@ -5713,10 +6288,10 @@
           <t>Share of districts spending MORE than trend after closing (all / plausible-only)</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="38" t="n">
         <v>0.4</v>
       </c>
-      <c r="C41" s="37" t="n">
+      <c r="C41" s="38" t="n">
         <v>0.41</v>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -8068,7 +8068,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Millersburg Elementary final enrollment (fall 2005)</t>
+          <t>Millersburg Elementary final enrollment (fall 2005; last operated SY 2005-06, closed status in the 2006-07 federal CCD file; distinct from the private military institute, which closed permanently July 2006)</t>
         </is>
       </c>
       <c r="B56" s="10" t="n">
@@ -8115,7 +8115,7 @@
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>Records asks: the 2007 closure's savings analysis and realized savings; the Millersburg Elementary building's deed, sale price, and current condition; PVA assessed-value history Millersburg vs county.</t>
+          <t>Records asks: the 2006 closure's savings analysis and realized savings; the Millersburg Elementary building's deed, sale price, and current condition; PVA assessed-value history Millersburg vs county.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -31,13 +31,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="+0.0;-0.0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -126,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +165,8 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1041,14 +1045,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2127,6 +2131,316 @@
       <c r="A68" s="21" t="inlineStr">
         <is>
           <t>Bourbon County is the only district in the region whose levied rate is lower today than in tax year 2012 (55.4 down to 52.4, minus 5.4 percent); Bath rose 72.3 percent, Scott 38.9, Harrison 34.2, Clark 22.2, Fayette 18.4, Paris Independent 17.2. Honesty notes: these are levied RATES, not revenue effort; under HB 44 the compensating rate falls as assessments grow, so the chart nets each board's levy choices against its assessment growth. Bourbon took the 4 percent option in 5 of the last 12 years (KDE levied-type file); the rate fell anyway because the other years took compensating or less, including the 12-cent slide of 2018-2022. Neighbors that rose took the 4 percent 7 to 9 times over the same window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>BEYOND THE 4 PERCENT: THE RECALLABLE LEVY OPTIONS (KRS 160.470; backs the levy card and Section 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>General Fund share of the levied 52.4 cents (KDE levied-rates file: 41.0 GF + 5.7 FSPK + 5.7 recallable)</t>
+        </is>
+      </c>
+      <c r="B71" s="29" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Yield per cent of General Fund rate, per year</t>
+        </is>
+      </c>
+      <c r="B72" s="9">
+        <f>B32/B71</f>
+        <v/>
+      </c>
+      <c r="G72" s="21" t="inlineStr">
+        <is>
+          <t>FY2025 GF collections divided by the 41.0 GF cents: about $191,000 per cent. Real and personal property only; tangible and motor vehicle rates untouched, so every figure below is conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Median owner-occupied home value, Bourbon County (Census ACS 2019-2023, table B25077)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>211600</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Cost per added cent to that household, per year</t>
+        </is>
+      </c>
+      <c r="B74" s="34">
+        <f>B73*0.01/100</f>
+        <v/>
+      </c>
+      <c r="G74" s="21" t="inlineStr">
+        <is>
+          <t>$21.16 a year, $1.76 a month, per added cent. Homestead exemption shields about $46,000 of a senior homeowner's value; farmland is assessed at agricultural use value, not market; renters pay only what landlords pass through</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>New rate</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>Added cents</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Revenue per year</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>Median-home cost/yr</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>Direct bond capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Match Harrison County (2025-26 levied rate)</t>
+        </is>
+      </c>
+      <c r="B77" s="20">
+        <f>B24</f>
+        <v/>
+      </c>
+      <c r="C77" s="35">
+        <f>B77-B12</f>
+        <v/>
+      </c>
+      <c r="D77" s="9">
+        <f>C77*$B$72</f>
+        <v/>
+      </c>
+      <c r="E77" s="9">
+        <f>C77*$B$74</f>
+        <v/>
+      </c>
+      <c r="F77" s="9">
+        <f>D77*(1-(1+Debt_Service!B40)^-Debt_Service!B41)/Debt_Service!B40</f>
+        <v/>
+      </c>
+      <c r="G77" s="21" t="inlineStr">
+        <is>
+          <t>Rates pulled live from this tab: Harrison row 24, the 2025-26 columns of the levy table, and Bourbon's own 2018 row. Direct bond capacity uses the Debt_Service tab's 4.5 percent, 20-year assumption, the same one that prices the $14 million nickel-residual bond</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Match the regional median (eight area districts, Fayette excluded)</t>
+        </is>
+      </c>
+      <c r="B78" s="20">
+        <f>MEDIAN(O58,O59,O60,O61,O63,O64,O65,O66)</f>
+        <v/>
+      </c>
+      <c r="C78" s="35">
+        <f>B78-B12</f>
+        <v/>
+      </c>
+      <c r="D78" s="9">
+        <f>C78*$B$72</f>
+        <v/>
+      </c>
+      <c r="E78" s="9">
+        <f>C78*$B$74</f>
+        <v/>
+      </c>
+      <c r="F78" s="9">
+        <f>D78*(1-(1+Debt_Service!B40)^-Debt_Service!B41)/Debt_Service!B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Restore Bourbon's own 2018 rate</t>
+        </is>
+      </c>
+      <c r="B79" s="20">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C79" s="35">
+        <f>B79-B12</f>
+        <v/>
+      </c>
+      <c r="D79" s="9">
+        <f>C79*$B$72</f>
+        <v/>
+      </c>
+      <c r="E79" s="9">
+        <f>C79*$B$74</f>
+        <v/>
+      </c>
+      <c r="F79" s="9">
+        <f>D79*(1-(1+Debt_Service!B40)^-Debt_Service!B41)/Debt_Service!B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Match Clark County (2025-26 levied rate)</t>
+        </is>
+      </c>
+      <c r="B80" s="20">
+        <f>O61</f>
+        <v/>
+      </c>
+      <c r="C80" s="35">
+        <f>B80-B12</f>
+        <v/>
+      </c>
+      <c r="D80" s="9">
+        <f>C80*$B$72</f>
+        <v/>
+      </c>
+      <c r="E80" s="9">
+        <f>C80*$B$74</f>
+        <v/>
+      </c>
+      <c r="F80" s="9">
+        <f>D80*(1-(1+Debt_Service!B40)^-Debt_Service!B41)/Debt_Service!B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>THE SEQUENCE: BALANCE THE BUDGET FIRST, THEN BOND</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>First call on new recurring money: operating gap (FY2026 trend) plus ending the capital-to-GF sweep</t>
+        </is>
+      </c>
+      <c r="B83" s="9">
+        <f>Debt_Service!C96+Debt_Service!B99</f>
+        <v/>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
+        <is>
+          <t>$373,989 gap plus the $1,320,939 sweep = $1,694,928. Ending the sweep is what frees the building-fund residual to service new bonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Revenue from restoring the 2018 rate</t>
+        </is>
+      </c>
+      <c r="B84" s="9">
+        <f>D79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Margin after the gap is closed and the sweep ended</t>
+        </is>
+      </c>
+      <c r="B85" s="23">
+        <f>B84-B83</f>
+        <v/>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
+        <is>
+          <t>About $4,551. The rate this board itself levied in 2018 is, almost to the dollar, the make-the-General-Fund-stand-alone rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Capacity unlocked once the sweep ends: nickel-residual bond</t>
+        </is>
+      </c>
+      <c r="B86" s="9">
+        <f>Debt_Service!B90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  plus remaining restricted capacity (FY2024 audit less the 2024 issue)</t>
+        </is>
+      </c>
+      <c r="B87" s="9">
+        <f>Debt_Service!B64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  plus bonds the new nickel equalization supports</t>
+        </is>
+      </c>
+      <c r="B88" s="9">
+        <f>Debt_Service!B68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Construction capacity unlocked without pledging a cent of the new levy</t>
+        </is>
+      </c>
+      <c r="B89" s="23">
+        <f>B86+B87+B88</f>
+        <v/>
+      </c>
+      <c r="G89" s="21" t="inlineStr">
+        <is>
+          <t>Roughly $35 million, for $15.69 a month on the median home, with nothing closed. The Harrison and median options are honest partial steps, leaving about $680,000 and $190,000 a year to find from the alternatives menu before the sweep can end; the Clark option adds about $10.5 million more direct capacity from its surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>None of these is a recommendation of a particular number, and none is counted in the alternatives package total. The point is narrower: a menu of options exists between cut nothing and close a school, every one prices out larger than the most generous closure estimate, and every one carries a built-in democratic check. A levy above 4 percent can be recalled by the voters it taxes. A closed school cannot be recalled by the children it displaces. This community was offered that veto twice on the facilities nickels and twice declined to use it; it has never been offered the same vote on the operating levy that pays teachers.</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3857,7 @@
           <t>Subject</t>
         </is>
       </c>
-      <c r="B34" s="34" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
@@ -4828,7 +5142,7 @@
           <t>NMES fill rate even at the draft's own 154 rating</t>
         </is>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="37">
         <f>B32/C32</f>
         <v/>
       </c>
@@ -5219,13 +5533,13 @@
           <t>Bourbon Central Elementary (1988)</t>
         </is>
       </c>
-      <c r="B67" s="36" t="n">
+      <c r="B67" s="38" t="n">
         <v>0.887637</v>
       </c>
-      <c r="C67" s="36" t="n">
+      <c r="C67" s="38" t="n">
         <v>0.819273</v>
       </c>
-      <c r="D67" s="36" t="n">
+      <c r="D67" s="38" t="n">
         <v>0.823017</v>
       </c>
       <c r="E67" s="8" t="n">
@@ -5241,13 +5555,13 @@
           <t>Cane Ridge Elementary (1992)</t>
         </is>
       </c>
-      <c r="B68" s="36" t="n">
+      <c r="B68" s="38" t="n">
         <v>0.8120579999999999</v>
       </c>
-      <c r="C68" s="36" t="n">
+      <c r="C68" s="38" t="n">
         <v>0.811765</v>
       </c>
-      <c r="D68" s="36" t="n">
+      <c r="D68" s="38" t="n">
         <v>0.728249</v>
       </c>
       <c r="E68" s="8" t="n">
@@ -5263,13 +5577,13 @@
           <t>North Middletown Elementary (1948/64)</t>
         </is>
       </c>
-      <c r="B69" s="36" t="n">
+      <c r="B69" s="38" t="n">
         <v>0.694064</v>
       </c>
-      <c r="C69" s="36" t="n">
+      <c r="C69" s="38" t="n">
         <v>0.702133</v>
       </c>
-      <c r="D69" s="36" t="n">
+      <c r="D69" s="38" t="n">
         <v>0.773295</v>
       </c>
       <c r="E69" s="8" t="n">
@@ -5285,13 +5599,13 @@
           <t>Bourbon County Middle School (1948)</t>
         </is>
       </c>
-      <c r="B70" s="36" t="n">
+      <c r="B70" s="38" t="n">
         <v>0.726249</v>
       </c>
-      <c r="C70" s="36" t="n">
+      <c r="C70" s="38" t="n">
         <v>0.727501</v>
       </c>
-      <c r="D70" s="36" t="n">
+      <c r="D70" s="38" t="n">
         <v>0.596145</v>
       </c>
       <c r="E70" s="8" t="n">
@@ -5307,13 +5621,13 @@
           <t>Bourbon County High School (1968)</t>
         </is>
       </c>
-      <c r="B71" s="36" t="n">
+      <c r="B71" s="38" t="n">
         <v>0.809819</v>
       </c>
-      <c r="C71" s="36" t="n">
+      <c r="C71" s="38" t="n">
         <v>0.802057</v>
       </c>
-      <c r="D71" s="36" t="n">
+      <c r="D71" s="38" t="n">
         <v>0.792529</v>
       </c>
       <c r="E71" s="8" t="n">
@@ -5329,7 +5643,7 @@
           <t>Check: Condition Index = 1 - (4-year renewal needs / replacement value), NMES</t>
         </is>
       </c>
-      <c r="B72" s="37">
+      <c r="B72" s="39">
         <f>1-E69/F69</f>
         <v/>
       </c>
@@ -5340,7 +5654,7 @@
           <t>NMES change between inspection cycles (2020-21 to April 2026)</t>
         </is>
       </c>
-      <c r="B73" s="37">
+      <c r="B73" s="39">
         <f>D69-B69</f>
         <v/>
       </c>
@@ -6288,10 +6602,10 @@
           <t>Share of districts spending MORE than trend after closing (all / plausible-only)</t>
         </is>
       </c>
-      <c r="B41" s="38" t="n">
+      <c r="B41" s="40" t="n">
         <v>0.4</v>
       </c>
-      <c r="C41" s="38" t="n">
+      <c r="C41" s="40" t="n">
         <v>0.41</v>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -23,6 +23,7 @@
     <sheet name="School_Data" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Facility_Plans" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="KY_Closures" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="School_Costs" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -40,6 +41,8 @@
     <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="171" formatCode="+0.0;-0.0"/>
+    <numFmt numFmtId="172" formatCode="+0%;-0%"/>
+    <numFmt numFmtId="173" formatCode="0.00000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -128,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +175,10 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6729,6 +6736,950 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>School-Level Costs Across Every Reporting System, and Every Breakeven Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Backs the two v3.8 site cards and the Section 4 additions. Three reporting systems with different definitions; compare within a system and a year, never across.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DISTRICT REVENUE BY SOURCE, PER MEMBER (KDE funding files; archived build/bourbon_revenue_by_source_2020_2024.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Total/member</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2019-20</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>2620</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>9427594</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>18087210</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>5573373</v>
+      </c>
+      <c r="F6" s="9">
+        <f>(C6+D6+E6)/B6</f>
+        <v/>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>State column includes on-behalf pension and insurance payments that never pass through the district's accounts; net SEEK cash is $7.8M-$9.4M of it. Federal 2020-21 to 2022-23 carries ESSER.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2020-21</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>2561</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>9934020</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>17692714</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>7900643</v>
+      </c>
+      <c r="F7" s="9">
+        <f>(C7+D7+E7)/B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2021-22</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>2483</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>10662819</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>18079609</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>9985007</v>
+      </c>
+      <c r="F8" s="9">
+        <f>(C8+D8+E8)/B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>2454</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>11808998</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>20381341</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>9550068</v>
+      </c>
+      <c r="F9" s="9">
+        <f>(C9+D9+E9)/B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2406</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>13172314</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>17149768</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>8132977</v>
+      </c>
+      <c r="F10" s="9">
+        <f>(C10+D10+E10)/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>THE 300-STUDENT BREAKEVEN, RECONSTRUCTED (cited at the committee meeting; no worksheet published)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Cost side: NMES 2023-24 report-card total per student</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>19348</v>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>KYRC24_FT_Spending_per_Student.csv; includes federal spending and embedded on-behalf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Times 128 students</t>
+        </is>
+      </c>
+      <c r="B15" s="23">
+        <f>B14*128</f>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>Equals $2,476,544 exactly, zero-dollar difference from the figure the 300 implies</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Implied revenue denominator for a 300 breakeven</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>B15/300</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>State-only revenue per member, 2022-23</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>D9/B9</f>
+        <v/>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>$8,305: the only revenue definition in the state's files that lands near the implied $8,255</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Breakeven N at state-only revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="41">
+        <f>B15/B17</f>
+        <v/>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>298 students. Per SEEK AADA (2,490) instead of members: 303. The 300 sits between the two bases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Same fraction with matching definitions: all-in cost / total revenue per member (2023-24)</t>
+        </is>
+      </c>
+      <c r="B19" s="20">
+        <f>B15/F10</f>
+        <v/>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>155 students, not 300. The 300 construction counts local and federal dollars on the cost side and skips them on the revenue side; those two sources bring $8,855 per student, more than the state share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>THE CORRECTED TEST, APPLIED TO EVERY SCHOOL (all-in cost per pupil / total revenue per member, 2023-24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Cost/pupil</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Breakeven N</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Short by</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>19348</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="D23" s="27">
+        <f>B23*C23/F$10</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>D23-C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>18131</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>459</v>
+      </c>
+      <c r="D24" s="27">
+        <f>B24*C24/F$10</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>D24-C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>18670</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>453</v>
+      </c>
+      <c r="D25" s="27">
+        <f>B25*C25/F$10</f>
+        <v/>
+      </c>
+      <c r="E25" s="27">
+        <f>D25-C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Co Middle</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>16673</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>590</v>
+      </c>
+      <c r="D26" s="27">
+        <f>B26*C26/F$10</f>
+        <v/>
+      </c>
+      <c r="E26" s="27">
+        <f>D26-C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Co High</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>17404</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>766</v>
+      </c>
+      <c r="D27" s="27">
+        <f>B27*C27/F$10</f>
+        <v/>
+      </c>
+      <c r="E27" s="27">
+        <f>D27-C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Every school in the district fails, including both receiving schools; Cane Ridge falls short by 76 students and about $1.2 million on this test, nearly three times NMES. Statewide, 1,146 of 1,151 A1 schools with reported data (99.6 percent) spend more per student all-in than $8,255. An average-cost breakeven in a drawdown year is a district-budget thermometer, not a school test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>THE REAL BREAKEVEN: FIXED SITE BASE VS THE FUNDING A STUDENT CARRIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fixed base</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>N (SEEK only)</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>N (SEEK+federal)</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown</t>
+        </is>
+      </c>
+      <c r="B32" s="18">
+        <f>Assumptions!B51+Assumptions!B52</f>
+        <v/>
+      </c>
+      <c r="C32" s="27">
+        <f>B32/(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>B32/(Assumptions!B6+3380-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>Plant scaled by KFICS replacement value; office and principal equal across schools. Marginal federal $3,380 = measured 2023-24 federal per member. Local carries zero at the margin: the levy does not change with enrollment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B33" s="9">
+        <f>Assumptions!B51+Assumptions!B52*Facility_Plans!F68/Facility_Plans!F69</f>
+        <v/>
+      </c>
+      <c r="C33" s="27">
+        <f>B33/(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>B33/(Assumptions!B6+3380-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B34" s="9">
+        <f>Assumptions!B51+Assumptions!B52*Facility_Plans!F67/Facility_Plans!F69</f>
+        <v/>
+      </c>
+      <c r="C34" s="27">
+        <f>B34/(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>B34/(Assumptions!B6+3380-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>NMES clears its bar at roughly double to triple enrollment; the receiving schools at 6 to 10 times. The full grid version with position, busing, and leaver effects brackets NMES at 20 to 122 (KY_Closures yardstick rows). Every construction except all-source-cost-over-state-only-revenue says every school pays its way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SCHOOL-LEVEL SPENDING PER STUDENT, OLD SRC SYSTEM 2011-12 TO 2016-17 (KDE Learning Environment files; archived CSV in build/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>NMES</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>NMES members</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>BCES</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>NMES vs BCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>9715</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>177</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>7351</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>7740</v>
+      </c>
+      <c r="F39" s="42">
+        <f>B39/D39-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2012-13</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>19635</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>158</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>10281</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>11383</v>
+      </c>
+      <c r="F40" s="42">
+        <f>B40/D40-1</f>
+        <v/>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>2012-13 NMES prints $19,635, off both neighbors' trend by a factor of two in a renovation year: a capital charge booked to the site. Excluded from operating comparisons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2013-14</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>9948</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>7123</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>7718</v>
+      </c>
+      <c r="F41" s="42">
+        <f>B41/D41-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2014-15</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>10999</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>153</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>8651</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>9222</v>
+      </c>
+      <c r="F42" s="42">
+        <f>B42/D42-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2015-16</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>11521</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>8705</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>9655</v>
+      </c>
+      <c r="F43" s="42">
+        <f>B43/D43-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2016-17</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>13260</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>9197</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>9815</v>
+      </c>
+      <c r="F44" s="42">
+        <f>B44/D44-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>These are the deep-emptiness years (133-177 students): the premium is widest exactly when the building is emptiest. Two federal collections confirm the pattern independently: CRDC school-level salaries (archived) and the NCES school-level finance survey FY16-FY17 (archived).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>THE 2000-01 REPORT CARDS: FOUR SCHOOLS, ONE SCALE CURVE (recovered from the Internet Archive; archive copies being added)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>Reported $/student</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>Curve prediction</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n">
+        <v>595</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>3360</v>
+      </c>
+      <c r="D49" s="9">
+        <f>B$55+B$54*E49</f>
+        <v/>
+      </c>
+      <c r="E49" s="43">
+        <f>1/B49</f>
+        <v/>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>One formula, about $2,851 per student plus about $332,000 per building over the zone-assigned enrollment, predicts all four schools within 4 percent. No school on this table was mismanaged; the ranking is enrollment. Cane Ridge itself cost 21 percent more than Bourbon Central at 312 students. CATS-era cards may report prior-year spending; the within-year comparison is unaffected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>312</v>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>4053</v>
+      </c>
+      <c r="D50" s="9">
+        <f>B$55+B$54*E50</f>
+        <v/>
+      </c>
+      <c r="E50" s="43">
+        <f>1/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>193</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>4414</v>
+      </c>
+      <c r="D51" s="9">
+        <f>B$55+B$54*E51</f>
+        <v/>
+      </c>
+      <c r="E51" s="43">
+        <f>1/B51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Millersburg</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D52" s="9">
+        <f>B$55+B$54*E52</f>
+        <v/>
+      </c>
+      <c r="E52" s="43">
+        <f>1/B52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Fixed base per building (least-squares slope on 1/N)</t>
+        </is>
+      </c>
+      <c r="B54" s="23">
+        <f>SLOPE(C49:C52,E49:E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Variable cost per student (intercept)</t>
+        </is>
+      </c>
+      <c r="B55" s="23">
+        <f>INTERCEPT(C49:C52,E49:E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Fit quality (R-squared)</t>
+        </is>
+      </c>
+      <c r="B56" s="44">
+        <f>RSQ(C49:C52,E49:E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>THE MILLERSBURG SYMMETRY: THE DISTRICT HAS RUN THIS EXPERIMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Millersburg premium over its receiving school, 2000-01 (per student x students)</t>
+        </is>
+      </c>
+      <c r="B59" s="23">
+        <f>(C52-C50)*B52</f>
+        <v/>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>$166,315 in FY2001 dollars. Closed 2006; the 30-year record (KY_Closures tab) shows no measurable district budget bend afterward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>NMES premium over the cheaper receiving school, 2023-24 (same computation)</t>
+        </is>
+      </c>
+      <c r="B60" s="23">
+        <f>(B14-18131)*128</f>
+        <v/>
+      </c>
+      <c r="G60" s="21" t="inlineStr">
+        <is>
+          <t>$155,776. The same experiment at almost the same number, twenty-three years apart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>STAFFING RECORD (federal CCD, 1996-2019; archived build/bourbon_staffing_ratios_ccd.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>NMES students per teacher at its 2007-09 enrollment peak (224 and 217 students): 16.0 and 15.5, vs 16.1-16.3 at Bourbon Central and Cane Ridge: parity. The ratio falls to 11.8 by 2012-13 as enrollment falls; the dollar premium peaks in the same years. 1998-2000 CCD teacher counts are corrupt for small Kentucky schools and excluded; single-year integer FTE wobbles about one student per teacher.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8885,10 +9836,20 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Statutory caps (KRS 157.360): 24 in K-3, 28 in grade 4, 29 in grades 5-6. The scenario adds no NMES teachers.</t>
-        </is>
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Statutory caps (KRS 157.360): 24 in K-3, 28 in grade 4, 29 in grades 5-6. At an even mix, 174 students exceed the single-section caps in most grades, so the lever below prices new NMES sections honestly (v3.8 correction; earlier versions omitted this charge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>New sections needed at NMES under the caps (0 if the rezone is drawn grade-by-grade; 2 at a fully even mix)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -8943,23 +9904,30 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>Net recurring benefit, low (avoided sections priced at the GF-borne $60K central, per the v3 on-behalf correction; range $50-75K)</t>
+          <t>Net recurring benefit, low (avoided and added sections both priced at the GF-borne $60K central; v3.8 subtracts the NMES additions)</t>
         </is>
       </c>
       <c r="B30" s="24">
-        <f>B26-B27+B28*Assumptions!B69</f>
+        <f>B26-B27+(B28-B24)*Assumptions!B69</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>Net recurring benefit, high (two sections at the same GF-borne rate)</t>
+          <t>Net recurring benefit, high (two avoided sections, same NMES debit)</t>
         </is>
       </c>
       <c r="B31" s="23">
-        <f>B26-B27+B29*Assumptions!B69</f>
-        <v/>
+        <f>B26-B27+(B29-B24)*Assumptions!B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Corner cases for the record: two added and none avoided gives about -$64,000; none added and two avoided gives about +$176,000. The published range uses the levers above.</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -10833,7 +11801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -11178,95 +12146,199 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>25*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="C14" s="18">
+        <f>50*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (259 registered homeschoolers, ACS pool ~1,135, net import already 189); 62 open seats exist at Bourbon Central's approved rating</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs an enrollment marketing plan and incentive design</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Total identified (ranges overlap; not additive to the penny)</t>
         </is>
       </c>
-      <c r="B14" s="24">
-        <f>SUM(B4:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="24">
-        <f>SUM(C4:C13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B15" s="24">
+        <f>SUM(B4:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
+        <f>SUM(C4:C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>COMPARISON</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Package midpoint (raw sum of ranges)</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>(B14+C14)/2</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, low (haircut for overlap)</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>1100000</v>
+          <t>Package midpoint (raw sum of ranges)</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>(B15+C15)/2</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, high</t>
+          <t>Conservative combined estimate, low (haircut for overlap)</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>2100000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Conservative midpoint (used in Runway sheet)</t>
-        </is>
-      </c>
-      <c r="B20" s="9">
-        <f>(B18+B19)/2</f>
-        <v/>
+          <t>Conservative combined estimate, high</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>2100000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Average annual GF drawdown (FY2024-25)</t>
-        </is>
-      </c>
-      <c r="B21" s="18">
-        <f>GF_Summary!D16</f>
+          <t>Conservative midpoint (used in Runway sheet)</t>
+        </is>
+      </c>
+      <c r="B21" s="9">
+        <f>(B19+B20)/2</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Average annual GF drawdown (FY2024-25)</t>
+        </is>
+      </c>
+      <c r="B22" s="18">
+        <f>GF_Summary!D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Closure net saving (base case)</t>
         </is>
       </c>
-      <c r="B22" s="18">
+      <c r="B23" s="18">
         <f>Closure_Model!B20</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Reading: raw row sums run about $1.6M to $2.8M; the published $1.1M to $2.1M band applies a conservative haircut for overlap and implementation risk. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Reading: raw row sums run about $1.6M to $2.9M; the published $1.1M to $2.1M band applies a conservative haircut for overlap and implementation risk. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>THE GROWTH PATH: THE SAME MENU AS A DISTRICT-WIDE RECOVERY PLAN (v3.8; backs the site card and Section 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Move 1: inspect fixed costs, starting with administration (attrition, admin restraint, transport, reimbursements, energy, shared services)</t>
+        </is>
+      </c>
+      <c r="B28" s="23">
+        <f>SUM(B7:B12)</f>
+        <v/>
+      </c>
+      <c r="C28" s="23">
+        <f>SUM(C7:C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
+        </is>
+      </c>
+      <c r="B29" s="23">
+        <f>B6+B13+B14</f>
+        <v/>
+      </c>
+      <c r="C29" s="23">
+        <f>C6+C13+C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Move 3: the honest revenue conversation, year one (4 percent option plus delinquency; compounds by year three; recallable menu beyond it on Tax_History rows 70-91)</t>
+        </is>
+      </c>
+      <c r="B30" s="23">
+        <f>B4+B5</f>
+        <v/>
+      </c>
+      <c r="C30" s="23">
+        <f>C4+C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>B28+B29+B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="23">
+        <f>C28+C29+C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GF_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Closure_Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Growth_Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Redistricting" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Transport_Geo" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Alternatives" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Debt_Service" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Runway" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Scenarios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Tax_History" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Demographics" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="School_Data" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Facility_Plans" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="KY_Closures" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="School_Costs" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GF_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closure_Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redistricting" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport_Geo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt_Service" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runway" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_History" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demographics" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Data" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Plans" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY_Closures" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Costs" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>N (SEEK+federal)</t>
+          <t>N if fed counted</t>
         </is>
       </c>
       <c r="E31" s="17" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>Plant scaled by KFICS replacement value; office and principal equal across schools. Marginal federal $3,380 = measured 2023-24 federal per member. Local carries zero at the margin: the levy does not change with enrollment.</t>
+          <t>Office and principal are estimates held equal across schools and plant is scaled by KFICS replacement value. The district's FY2026 working budget now measures North Middletown's own General Fund lines, excluding state-paid on-behalf, at school administration $132,744, plant operations $96,107 (the General Fund portion of function 2600; $119,909 across all funds) and instructional staff support, the school's library and media line, $49,097. Administration plus plant measure $228,851 against the $290,000 this model assumes for the same two components. Local carries zero at the margin, because the levy does not change with enrollment, and federal carries zero as well, because Title I is a district allocation driven by resident poverty and reappears at whichever school the child attends. Column D keeps the federal case only to show how far the answer moves when you count it.</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
         <is>
-          <t>NMES clears its bar at roughly double to triple enrollment; the receiving schools at 6 to 10 times. The full grid version with position, busing, and leaver effects brackets NMES at 20 to 122 (KY_Closures yardstick rows). Every construction except all-source-cost-over-state-only-revenue says every school pays its way.</t>
+          <t>NMES clears its bar at roughly two to two and a half times its enrollment; the receiving schools at roughly 5 to 6 times. The full grid version with position, busing, and leaver effects brackets NMES at 20 to 122 (KY_Closures yardstick rows). Every construction except all-source-cost-over-state-only-revenue says every school pays its way.</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Principal+office $175K; plant $115K sold, ~$55K mothballed</t>
+          <t>Principal+office $175K; plant $115K sold, ~$55K mothballed. CORROBORATED v3.9 from the district FY2026 working budget, location 090, General Fund, excl on-behalf: school admin (2400) $132,744 + plant (2600) $96,107 = $228,851 vs the $230,000 mothballed lever, a 0.5% miss; adding the library/media line $49,097 gives $277,948 vs the $290,000 sold lever. NOTE: $230,000 is this grid FLOOR and assumes principal, secretary, custodian and utilities are all eliminated rather than reassigned; a redeployment case (utilities only, $58,774) is not in the grid.</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>110 sq mi zone (federal SABS); worst-reimbursed budget line</t>
+          <t>110 sq mi zone (federal SABS); worst-reimbursed budget line. Treated as net new cost with nothing in the school's own code to offset it: student transportation coded to location 090 in the FY2026 working budget is $2,000, while location 901 is 100 percent function 2700 at $2,688,247, the only material transportation coding in the district.</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
     <row r="70">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>Receiving schools today: Bourbon Central $18,131, Cane Ridge $18,670. At the state-approved 174 rating, NMES undercuts both across the entire grid, including the impossible full-average case. At the draft plan's 154 rating it holds for any marginal cost under about $12,000, roughly thirty times the realistic figure. Verdict: structural at 174, robust at 154.</t>
+          <t>Receiving schools today: Bourbon Central $18,131, Cane Ridge $18,670. At the state-approved 174 rating, NMES undercuts both across the entire grid, including the impossible full-average case. At the draft plan's 154 rating it holds for any marginal cost under about $12,140, roughly three times the class-cap marginal this workbook prices (about $3,670). Verdict: structural at 174, robust at 154.</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
     <row r="81">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>Honest reading (corrected 7/26): at 174 the counterfactual is within 1 to 3 percent of the cheapest school in 2019-22, a tie, and decisively below both schools in 2022-23 and 2023-24. At the draft plan's 154 rating it is cheapest on the 2023-24 filing; in 2019-20 and 2020-21 the school enrolled above 154, the capacity the draft now assigns it. NMES's total site spending grew 16 percent over the five years, against 37 percent at Bourbon Central and 47 percent at Cane Ridge; only the divisor changed.</t>
+          <t>Honest reading (corrected 7/26): at 174 the counterfactual is within 1 to 3 percent of the cheapest school in 2019-22, a tie, and decisively below both schools in 2022-23 and 2023-24. At the draft plan's 154 rating it is cheapest on the 2023-24 filing; in 2019-20 and 2020-21 the school enrolled above 154, the capacity the draft now assigns it. NMES's total site spending grew about 16 percent over the five years, against 35 to 37 percent at Bourbon Central and 46 to 47 percent at Cane Ridge, on the state's per-student filings times each school's reported enrollment; the bands carry the two base-year counts the record offers, the district's 2021 facility plan enrollment and the federal fall 2019 count. Decomposed, NMES's per-student rise is roughly one third spending and two thirds divisor (total up about 16 percent over membership down about 23 percent); at Bourbon Central the same decomposition is mostly spending. That is the finding: at this school the divisor did most of the work.</t>
         </is>
       </c>
     </row>
@@ -10867,50 +10867,9 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>VALIDATION AGAINST ACTUALS: the empirical marginal cost per student</t>
-        </is>
-      </c>
-      <c r="B111" s="9">
-        <f>(8902321-8606870)/(491-461)</f>
-        <v/>
-      </c>
-      <c r="F111" s="21" t="inlineStr">
-        <is>
-          <t>The actual per-student cost difference between the district's own two large schools on the same 2023-24 filing, about $9,848: an all-in, actuals-derived marginal cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>NMES filled to 174 at that empirical marginal cost</t>
-        </is>
-      </c>
-      <c r="B112" s="9">
-        <f>(B34+(B6-B5)*B111)/B6</f>
-        <v/>
-      </c>
-      <c r="F112" s="21" t="inlineStr">
-        <is>
-          <t>About $16,837: still below both receiving schools</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>NMES filled to 154 at that empirical marginal cost</t>
-        </is>
-      </c>
-      <c r="B113" s="9">
-        <f>(B34+(154-B5)*B111)/154</f>
-        <v/>
-      </c>
-      <c r="F113" s="21" t="inlineStr">
-        <is>
-          <t>About $17,744: still below both receiving schools</t>
+      <c r="A111" s="21" t="inlineStr">
+        <is>
+          <t>VALIDATION AGAINST ACTUALS: withdrawn in v3.9. The two-school cost slope used here depended on memberships (491 and 461) that appear in no archived source file and that contradict B8 and B9 above, and its sign flips from plus $9,848 to minus $941 to minus $22,564 across the three plausible membership pairs. The honest bound is the break-even marginal cost already computed live in rows 57 to 60.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -841,7 +841,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Closure only (v3 central case, $131,240, from FY2027)</t>
+          <t>Closure only (v3.9 central case, $69,071, from FY2027)</t>
         </is>
       </c>
       <c r="B7" s="9">
@@ -887,7 +887,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v3): at the +$565,000 best case FY2029 ends near $1.4M; at the +$91,240 median the reserves are gone on nearly the status-quo schedule; in the 29 percent of scenarios that lose money, sooner than status quo.</t>
+          <t>Closure range check (v3.9): at the +$551,928 best case FY2029 ends near $1.4M; at the +$21,571 median the reserves are gone on essentially the status-quo schedule; in the 45 percent of scenarios that lose money, sooner than status quo.</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>91240/Assumptions!B11</f>
+        <f>21571/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -6639,14 +6639,14 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CONVERGENCE CHECK: the record's plausible median vs this model's independent bottom-up median per displaced student</t>
+          <t>BRACKET CHECK (v3.9): the record's plausible median vs this model's independent bottom-up median per displaced student. These bracket rather than coincide and measure different things: the record credits a district's whole budget change to its closure (an upper bound by construction), the model prices only the levers a closure moves. Before the v3.9 fixed-cost rebuild the model read $713 and the two nearly coincided. Both remain far below the plan's $6,250-$7,813 requirement.</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
         <v>818</v>
       </c>
       <c r="C44" s="23">
-        <f>91240/Assumptions!B11</f>
+        <f>Closure_Model!B47/Assumptions!B11</f>
         <v/>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>Office and principal are estimates held equal across schools and plant is scaled by KFICS replacement value. The district's FY2026 working budget now measures North Middletown's own General Fund lines, excluding state-paid on-behalf, at school administration $132,744, plant operations $96,107 (the General Fund portion of function 2600; $119,909 across all funds) and instructional staff support, the school's library and media line, $49,097. Administration plus plant measure $228,851 against the $290,000 this model assumes for the same two components. Local carries zero at the margin, because the levy does not change with enrollment, and federal carries zero as well, because Title I is a district allocation driven by resident poverty and reappears at whichever school the child attends. Column D keeps the federal case only to show how far the answer moves when you count it.</t>
+          <t>B51 and B52 are now the measured lines themselves and plant is scaled by KFICS replacement value for the other two schools. The district's FY2026 working budget measures North Middletown's own General Fund lines, excluding state-paid on-behalf, at school administration $132,744, plant operations $96,107 (the General Fund portion of function 2600; $119,909 across all funds) and instructional staff support, the school's library and media line, $49,097. Administration plus plant measure $227,831 on the program view used by B51 and B52, or $228,851 on the function view, against the $290,000 this model assumed for the same two components through v3.8. Local carries zero at the margin, because the levy does not change with enrollment, and federal carries zero as well, because Title I is a district allocation driven by resident poverty and reappears at whichever school the child attends. Column D keeps the federal case only to show how far the answer moves when you count it.</t>
         </is>
       </c>
     </row>
@@ -8290,30 +8290,30 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Principal &amp; office costs avoided</t>
+          <t>School administration avoided (principal, secretary, extended day)</t>
         </is>
       </c>
       <c r="B51" s="14" t="n">
-        <v>175000</v>
+        <v>131724</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>MEASURED v3.9: district FY2026 working budget, location 090, General Fund program 077, excl on-behalf. Was a $175,000 estimate through v3.8.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Plant/utilities/insurance avoided, net of carrying cost</t>
+          <t>Plant operations avoided (custodial + utilities, sanitation, water)</t>
         </is>
       </c>
       <c r="B52" s="14" t="n">
-        <v>115000</v>
+        <v>96107</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Estimate; assumes building sold or repurposed</t>
+          <t>MEASURED v3.9: same source, custodial program 087 $37,333 + plant program 987 $58,774. B51+B52 = $227,831, the grid's mothballed case. Was a $115,000 estimate through v3.8.</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V3 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 1,944 COMBINATIONS (backs Figure 7)</t>
+          <t>V3.9 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 2,916 COMBINATIONS (backs Figure 7)</t>
         </is>
       </c>
     </row>
@@ -9143,21 +9143,21 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Fixed avoided (mothballed / sold)</t>
+          <t>Fixed avoided (reassigned / mothballed / sold)</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>230000</v>
+        <v>58774</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>290000</v>
+        <v>227831</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>290000</v>
+        <v>276928</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Principal+office $175K; plant $115K sold, ~$55K mothballed. CORROBORATED v3.9 from the district FY2026 working budget, location 090, General Fund, excl on-behalf: school admin (2400) $132,744 + plant (2600) $96,107 = $228,851 vs the $230,000 mothballed lever, a 0.5% miss; adding the library/media line $49,097 gives $277,948 vs the $290,000 sold lever. NOTE: $230,000 is this grid FLOOR and assumes principal, secretary, custodian and utilities are all eliminated rather than reassigned; a redeployment case (utilities only, $58,774) is not in the grid.</t>
+          <t>MEASURED v3.9 from the district FY2026 working budget, location 090, General Fund, excl on-behalf: school admin (2400) $132,744 + plant (2600) $96,107 = $228,851 vs the $230,000 mothballed lever, a 0.5% miss; adding the library/media line $49,097 gives $277,948 vs the $290,000 sold lever. NOTE: $230,000 is this grid FLOOR and assumes principal, secretary, custodian and utilities are all eliminated rather than reassigned; a redeployment case (utilities only, $58,774) is not in the grid.</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>$131,240: about 5 percent of the structural deficit</t>
+          <t>$69,071: about 2.6 percent of the structural deficit</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$384,780 a year: the closure loses money</t>
+          <t>-$556,006 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -9289,14 +9289,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$565,000 a year: the ceiling, and still below the plan's $800K-$1M requirement</t>
+          <t>+$551,928 a year: the ceiling, and still below the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 1,944 combinations, equal weights, enumerated by build/closure_grid.py: positions take four values (2, 3, 4, 5), fixed-avoided takes two ($230,000 mothballed, $290,000 sold), and the five other levers three each (4 x 2 x 3^5 = 1,944). Median +$91,240; middle half -$17,500 to +$200,000; 28.8 percent (559 of 1,944, published as 29 percent) of scenarios negative. One-time transition costs $100K-$300K in year one are additional.</t>
+          <t>Distribution of all 2,916 combinations, equal weights, enumerated by build/closure_grid.py: positions take four values (2, 3, 4, 5) and the six other levers three each (4 x 3^6 = 2,916). Median +$21,571; middle half -$104,726 to +$146,274; 45.06 percent (1,314 of 2,916, published as 45 percent) of scenarios negative. One-time transition costs $100K-$300K in year one are additional. REBUILT IN v3.9: the fixed-avoided lever previously took two estimated values ($230,000 mothballed, $290,000 sold), both of which assumed every fixed position at the school is eliminated. It now takes three measured values from the district FY2026 working budget, location 090, General Fund, excl on-behalf: $58,774 (staff reassigned to other buildings, utilities only), $227,831 (mothballed: school admin $131,724 + custodial $37,333 + plant $58,774) and $276,928 (sold: the above plus library and media $49,097). Adding the reassignment case moved the median from +$91,240 to +$21,571 and the negative share from 28.8 to 45.1 percent.</t>
         </is>
       </c>
     </row>
@@ -12856,18 +12856,18 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Sits between the v3 closure model's median ($91,240) and central case ($131,240)</t>
+          <t>Above the v3.9 closure model's median ($21,571) and central case ($69,071)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Closure model median (v3 two-tailed grid)</t>
+          <t>Closure model median (v3.9 two-tailed grid)</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>91240</v>
+        <v>21571</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -12875,18 +12875,18 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab, 1,944-combination grid</t>
+          <t>Closure_Model tab, 2,916-combination grid</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Closure model best case (v3 favorable tail)</t>
+          <t>Closure model best case (v3.9 favorable tail)</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>565000</v>
+        <v>551928</v>
       </c>
       <c r="C48" s="9">
         <f>B48*(1-(1+B$40)^-B$41)/B$40</f>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,11 +170,12 @@
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1052,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2448,6 +2449,292 @@
       <c r="A91" s="21" t="inlineStr">
         <is>
           <t>None of these is a recommendation of a particular number, and none is counted in the alternatives package total. The point is narrower: a menu of options exists between cut nothing and close a school, every one prices out larger than the most generous closure estimate, and every one carries a built-in democratic check. A levy above 4 percent can be recalled by the voters it taxes. A closed school cannot be recalled by the children it displaces. This community was offered that veto twice on the facilities nickels and twice declined to use it; it has never been offered the same vote on the operating levy that pays teachers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>HOUSE BILL 44: THE 4 PERCENT IS A LIMIT ON REVENUE, NOT ON THE RATE (backs Section 11 and Question 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Certified real and personal property assessment, FY2025 (audit)</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>1843569625</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>General Fund rate levied, cents per $100</t>
+        </is>
+      </c>
+      <c r="B95" s="30">
+        <f>B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>General Fund revenue at that rate on that assessment</t>
+        </is>
+      </c>
+      <c r="B96" s="9">
+        <f>B94*B95/100/100</f>
+        <v/>
+      </c>
+      <c r="G96" s="21" t="inlineStr">
+        <is>
+          <t>$7,558,635 on the certified assessment. Actual FY2025 GF tax collections were $7,829,060; the gap is motor vehicle and other classes plus collection timing, and it does not move any percentage below</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>Assessment growth</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Compensating rate</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>4 percent option</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>Rate raised 4 percent</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>Revenue at 4 percent option</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>Revenue at rate x 1.04</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>Above the ceiling, recallable</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B99" s="30">
+        <f>$B$95/(1+A99)</f>
+        <v/>
+      </c>
+      <c r="C99" s="30">
+        <f>B99*1.04</f>
+        <v/>
+      </c>
+      <c r="D99" s="30">
+        <f>$B$95*1.04</f>
+        <v/>
+      </c>
+      <c r="E99" s="9">
+        <f>$B$94*(1+A99)*C99/100/100</f>
+        <v/>
+      </c>
+      <c r="F99" s="9">
+        <f>$B$94*(1+A99)*D99/100/100</f>
+        <v/>
+      </c>
+      <c r="G99" s="23">
+        <f>F99-E99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B100" s="30">
+        <f>$B$95/(1+A100)</f>
+        <v/>
+      </c>
+      <c r="C100" s="30">
+        <f>B100*1.04</f>
+        <v/>
+      </c>
+      <c r="D100" s="30">
+        <f>$B$95*1.04</f>
+        <v/>
+      </c>
+      <c r="E100" s="9">
+        <f>$B$94*(1+A100)*C100/100/100</f>
+        <v/>
+      </c>
+      <c r="F100" s="9">
+        <f>$B$94*(1+A100)*D100/100/100</f>
+        <v/>
+      </c>
+      <c r="G100" s="23">
+        <f>F100-E100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B101" s="30">
+        <f>$B$95/(1+A101)</f>
+        <v/>
+      </c>
+      <c r="C101" s="30">
+        <f>B101*1.04</f>
+        <v/>
+      </c>
+      <c r="D101" s="30">
+        <f>$B$95*1.04</f>
+        <v/>
+      </c>
+      <c r="E101" s="9">
+        <f>$B$94*(1+A101)*C101/100/100</f>
+        <v/>
+      </c>
+      <c r="F101" s="9">
+        <f>$B$94*(1+A101)*D101/100/100</f>
+        <v/>
+      </c>
+      <c r="G101" s="23">
+        <f>F101-E101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B102" s="30">
+        <f>$B$95/(1+A102)</f>
+        <v/>
+      </c>
+      <c r="C102" s="30">
+        <f>B102*1.04</f>
+        <v/>
+      </c>
+      <c r="D102" s="30">
+        <f>$B$95*1.04</f>
+        <v/>
+      </c>
+      <c r="E102" s="9">
+        <f>$B$94*(1+A102)*C102/100/100</f>
+        <v/>
+      </c>
+      <c r="F102" s="9">
+        <f>$B$94*(1+A102)*D102/100/100</f>
+        <v/>
+      </c>
+      <c r="G102" s="23">
+        <f>F102-E102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>Read row 101, five percent growth: the largest rate the board can levy with no recall exposure is 40.61 cents, BELOW the 41.0 it levies now, and it still collects four percent more revenue. Column E is flat at every growth rate because the four percent is a revenue limit; column D is flat because it is a rate rule. The naive rate overshoots the protected rate by exactly the assessment growth rate, so the two coincide only at zero growth. New-construction revenue sits outside the cap and is additional; any rate above the compensating rate requires a public hearing; the two facilities nickels are separate from this General Fund table. KRS 132.010, KRS 132.017, KRS 160.470, read as a layperson, not as legal advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>What this settles, and what it does not: a flat or falling levied rate is not evidence either way about whether the four percent option was taken, because taking it in a county with rising assessments produces a falling rate. KDE's levied-type file shows Bourbon took the option in five of the last twelve years against seven, eight and nine for the neighbors that rose. The document that closes the question is the certified compensating rate against the rate actually levied, each year, and it is on the records list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>THE 2023 RATE MOVEMENT: 3.2 CENTS NET, 5.7 CENTS RESTRICTED IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Total levied rate, tax year 2022</t>
+        </is>
+      </c>
+      <c r="B109" s="29" t="n">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Total levied rate, tax year 2023 (held at 52.4 for three years since)</t>
+        </is>
+      </c>
+      <c r="B110" s="29" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Net change</t>
+        </is>
+      </c>
+      <c r="B111" s="35">
+        <f>B110-B109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Recallable facilities nickel levied 8/17/2023 (KDE levied-rates file, current year)</t>
+        </is>
+      </c>
+      <c r="B112" s="29" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Implied change in the rest of the rate</t>
+        </is>
+      </c>
+      <c r="B113" s="37">
+        <f>B111-B112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Implied annual change in unrestricted revenue</t>
+        </is>
+      </c>
+      <c r="B114" s="23">
+        <f>B113*B72</f>
+        <v/>
+      </c>
+      <c r="G114" s="21" t="inlineStr">
+        <is>
+          <t>About -2.5 cents, roughly -$477,000 a year. INFERENCE, NOT A DOCUMENT: KDE does not publish the year-by-year rate-type split, and a facilities nickel is an equivalent rate restated annually against the whole property base, so it drifts. The certified split by year is requested in Appendix B. What is not in doubt: the levy that rose in 2023 was restricted building money that cannot lawfully pay a teacher</t>
         </is>
       </c>
     </row>
@@ -3864,7 +4151,7 @@
           <t>Subject</t>
         </is>
       </c>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
@@ -5149,7 +5436,7 @@
           <t>NMES fill rate even at the draft's own 154 rating</t>
         </is>
       </c>
-      <c r="B34" s="37">
+      <c r="B34" s="39">
         <f>B32/C32</f>
         <v/>
       </c>
@@ -5540,13 +5827,13 @@
           <t>Bourbon Central Elementary (1988)</t>
         </is>
       </c>
-      <c r="B67" s="38" t="n">
+      <c r="B67" s="40" t="n">
         <v>0.887637</v>
       </c>
-      <c r="C67" s="38" t="n">
+      <c r="C67" s="40" t="n">
         <v>0.819273</v>
       </c>
-      <c r="D67" s="38" t="n">
+      <c r="D67" s="40" t="n">
         <v>0.823017</v>
       </c>
       <c r="E67" s="8" t="n">
@@ -5562,13 +5849,13 @@
           <t>Cane Ridge Elementary (1992)</t>
         </is>
       </c>
-      <c r="B68" s="38" t="n">
+      <c r="B68" s="40" t="n">
         <v>0.8120579999999999</v>
       </c>
-      <c r="C68" s="38" t="n">
+      <c r="C68" s="40" t="n">
         <v>0.811765</v>
       </c>
-      <c r="D68" s="38" t="n">
+      <c r="D68" s="40" t="n">
         <v>0.728249</v>
       </c>
       <c r="E68" s="8" t="n">
@@ -5584,13 +5871,13 @@
           <t>North Middletown Elementary (1948/64)</t>
         </is>
       </c>
-      <c r="B69" s="38" t="n">
+      <c r="B69" s="40" t="n">
         <v>0.694064</v>
       </c>
-      <c r="C69" s="38" t="n">
+      <c r="C69" s="40" t="n">
         <v>0.702133</v>
       </c>
-      <c r="D69" s="38" t="n">
+      <c r="D69" s="40" t="n">
         <v>0.773295</v>
       </c>
       <c r="E69" s="8" t="n">
@@ -5606,13 +5893,13 @@
           <t>Bourbon County Middle School (1948)</t>
         </is>
       </c>
-      <c r="B70" s="38" t="n">
+      <c r="B70" s="40" t="n">
         <v>0.726249</v>
       </c>
-      <c r="C70" s="38" t="n">
+      <c r="C70" s="40" t="n">
         <v>0.727501</v>
       </c>
-      <c r="D70" s="38" t="n">
+      <c r="D70" s="40" t="n">
         <v>0.596145</v>
       </c>
       <c r="E70" s="8" t="n">
@@ -5628,13 +5915,13 @@
           <t>Bourbon County High School (1968)</t>
         </is>
       </c>
-      <c r="B71" s="38" t="n">
+      <c r="B71" s="40" t="n">
         <v>0.809819</v>
       </c>
-      <c r="C71" s="38" t="n">
+      <c r="C71" s="40" t="n">
         <v>0.802057</v>
       </c>
-      <c r="D71" s="38" t="n">
+      <c r="D71" s="40" t="n">
         <v>0.792529</v>
       </c>
       <c r="E71" s="8" t="n">
@@ -5650,7 +5937,7 @@
           <t>Check: Condition Index = 1 - (4-year renewal needs / replacement value), NMES</t>
         </is>
       </c>
-      <c r="B72" s="39">
+      <c r="B72" s="41">
         <f>1-E69/F69</f>
         <v/>
       </c>
@@ -5661,7 +5948,7 @@
           <t>NMES change between inspection cycles (2020-21 to April 2026)</t>
         </is>
       </c>
-      <c r="B73" s="39">
+      <c r="B73" s="41">
         <f>D69-B69</f>
         <v/>
       </c>
@@ -6609,10 +6896,10 @@
           <t>Share of districts spending MORE than trend after closing (all / plausible-only)</t>
         </is>
       </c>
-      <c r="B41" s="40" t="n">
+      <c r="B41" s="36" t="n">
         <v>0.4</v>
       </c>
-      <c r="C41" s="40" t="n">
+      <c r="C41" s="36" t="n">
         <v>0.41</v>
       </c>
     </row>
@@ -6998,7 +7285,7 @@
           <t>Breakeven N at state-only revenue</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="42">
         <f>B15/B17</f>
         <v/>
       </c>
@@ -7339,7 +7626,7 @@
       <c r="E39" s="8" t="n">
         <v>7740</v>
       </c>
-      <c r="F39" s="42">
+      <c r="F39" s="43">
         <f>B39/D39-1</f>
         <v/>
       </c>
@@ -7362,7 +7649,7 @@
       <c r="E40" s="8" t="n">
         <v>11383</v>
       </c>
-      <c r="F40" s="42">
+      <c r="F40" s="43">
         <f>B40/D40-1</f>
         <v/>
       </c>
@@ -7390,7 +7677,7 @@
       <c r="E41" s="8" t="n">
         <v>7718</v>
       </c>
-      <c r="F41" s="42">
+      <c r="F41" s="43">
         <f>B41/D41-1</f>
         <v/>
       </c>
@@ -7413,7 +7700,7 @@
       <c r="E42" s="8" t="n">
         <v>9222</v>
       </c>
-      <c r="F42" s="42">
+      <c r="F42" s="43">
         <f>B42/D42-1</f>
         <v/>
       </c>
@@ -7436,7 +7723,7 @@
       <c r="E43" s="8" t="n">
         <v>9655</v>
       </c>
-      <c r="F43" s="42">
+      <c r="F43" s="43">
         <f>B43/D43-1</f>
         <v/>
       </c>
@@ -7459,7 +7746,7 @@
       <c r="E44" s="8" t="n">
         <v>9815</v>
       </c>
-      <c r="F44" s="42">
+      <c r="F44" s="43">
         <f>B44/D44-1</f>
         <v/>
       </c>
@@ -7516,7 +7803,7 @@
         <f>B$55+B$54*E49</f>
         <v/>
       </c>
-      <c r="E49" s="43">
+      <c r="E49" s="44">
         <f>1/B49</f>
         <v/>
       </c>
@@ -7542,7 +7829,7 @@
         <f>B$55+B$54*E50</f>
         <v/>
       </c>
-      <c r="E50" s="43">
+      <c r="E50" s="44">
         <f>1/B50</f>
         <v/>
       </c>
@@ -7563,7 +7850,7 @@
         <f>B$55+B$54*E51</f>
         <v/>
       </c>
-      <c r="E51" s="43">
+      <c r="E51" s="44">
         <f>1/B51</f>
         <v/>
       </c>
@@ -7584,7 +7871,7 @@
         <f>B$55+B$54*E52</f>
         <v/>
       </c>
-      <c r="E52" s="43">
+      <c r="E52" s="44">
         <f>1/B52</f>
         <v/>
       </c>
@@ -7617,7 +7904,7 @@
           <t>Fit quality (R-squared)</t>
         </is>
       </c>
-      <c r="B56" s="44">
+      <c r="B56" s="45">
         <f>RSQ(C49:C52,E49:E52)</f>
         <v/>
       </c>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -9486,7 +9486,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>x $4,626 SEEK; Paris Ind adjacent under HB 563; Millersburg precedent</t>
+          <t>x $4,626 SEEK; scenario values; exits free and funded under HB 563, homeschool and statewide virtual academy growing</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -842,7 +842,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Closure only (v3.9 central case, $69,071, from FY2027)</t>
+          <t>Closure only (v4.2 central case, $54,539, from FY2027)</t>
         </is>
       </c>
       <c r="B7" s="9">
@@ -888,7 +888,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v3.9): at the +$551,928 best case FY2029 ends near $1.4M; at the +$21,571 median the reserves are gone on essentially the status-quo schedule; in the 45 percent of scenarios that lose money, sooner than status quo.</t>
+          <t>Closure range check (v4.2): at the +$488,631 best case FY2029 ends near $1.2M; at the -$21,971 median the reserves go slightly FASTER than status quo; 55 percent of scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>21571/Assumptions!B11</f>
+        <f>-21971/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -9354,7 +9354,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V3.9 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 2,916 COMBINATIONS (backs Figure 7)</t>
+          <t>V4.2 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 5,832 COMBINATIONS (backs Figure 7)</t>
         </is>
       </c>
     </row>
@@ -9388,63 +9388,63 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Positions eliminated (net of re-created sections)</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>5</v>
+          <t>Non-salary capture (their worksheet, + insurance at the full stop)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>53519</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>80279</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>127039</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Class caps: receiving schools add ~4 sections while NMES's 9 dissolve</t>
+          <t>District Response Appendix A: $107,039 of building-bound lines (utilities, telecom, maintenance, custodial supplies) captured at 50/75/100 percent, plus its ~$20,000 insurance figure at the full stop. The worksheet's other $40,693 (supplies, books, field trips, printing = $318/student vs our measured $331) travels with the students.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>GF cost per position</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="n">
-        <v>50000</v>
+          <t>Fixed positions cut over time (school admin + custodial + library)</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>60000</v>
+        <v>109077</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>75000</v>
+        <v>218154</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Published salary schedule + on-behalf structure</t>
+          <t>Measured lines: $131,724 + $37,333 + $49,097 = $218,154 (the district's own A.1 prices the same four roles at $209,700, within 4 percent, and states all current staff are retained in year one; the full-cut leg is an attrition end state)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Fixed avoided (reassigned / mothballed / sold)</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="n">
-        <v>58774</v>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>227831</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>276928</v>
+          <t>Teachers cut (grid legs 0/1/2/3) x $54,479.40 each</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>MEASURED v3.9 from the district FY2026 working budget, location 090, General Fund, excl on-behalf: school admin (2400) $132,744 + plant (2600) $96,107 = $228,851 vs the $230,000 mothballed lever, a 0.5% miss; adding the library/media line $49,097 gives $277,948 vs the $290,000 sold lever. NOTE: $230,000 is this grid FLOOR and assumes principal, secretary, custodian and utilities are all eliminated rather than reassigned; a redeployment case (utilities only, $58,774) is not in the grid.</t>
+          <t>Priced at the district's OWN fully loaded 0-years-experience figure, $54,479.40 (Response Appendix A.1: 'Elementary Teachers: 2, $108,958.80'). The top leg credits 3 because Appendix B's own classroom count eliminates three homerooms net.</t>
         </is>
       </c>
     </row>
@@ -9455,80 +9455,80 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="C42" s="8" t="n">
-        <v>137500</v>
+        <v>63000</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>250000</v>
+        <v>190000</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>110 sq mi zone (federal SABS); worst-reimbursed budget line. Treated as net new cost with nothing in the school's own code to offset it: student transportation coded to location 090 in the FY2026 working budget is $2,000, while location 901 is 100 percent function 2700 at $2,688,247, the only material transportation coding in the district.</t>
+          <t>Derived bottom-up with uncertainty: 2-4 zone buses terminating in Paris (~9-11 road miles farther one-way), 2 loaded + 0-2 deadhead legs daily, 175 days, $3.25-$4.75/mile (KDE/NAPT band), high stop adds one $45,000 route split. Per zone student $160/$492/$1,495 vs the $1,032 district average. The district's routing data was requested and answered N/A.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students leaving district</t>
+          <t>Students leaving district (grid legs 0/13/26/38/51/64)</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>x $4,626 SEEK; scenario values; exits free and funded under HB 563, homeschool and statewide virtual academy growing</t>
+          <t>0 to 50 percent of 128, x ($4,626 SEEK base + the add-ons lever); exits free and funded under HB 563, homeschool and statewide virtual academy growing</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Capacity debt service triggered</t>
+          <t>SEEK add-ons lost per leaver</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="8" t="n">
-        <v>115000</v>
+        <v>500</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>231000</v>
+        <v>1000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CRES 103 over approved rating; 2021 plan prices its kitchen/cafeteria deficient today</t>
+          <t>At-risk weight (15% of base on a ~72% FRL school), exceptional-child weights, transportation component, $100 capital outlay</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Assessment erosion, district share</t>
+          <t>Property-value loss (zone tax base)</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>40000</v>
+        <v>47500</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>95000</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Millersburg-calibrated; PVA records ask pending</t>
+          <t>Roughly 0-10 percent of an estimated zone base; kept as foregone revenue because the board's rate practice does not raise rates to recapture zone valuation losses; PVA records ask pending</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
         </is>
       </c>
       <c r="B47" s="23">
-        <f>C41+C39*C40-C42-C43*Assumptions!B6-C44-C45</f>
+        <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44)-C45</f>
         <v/>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>$69,071: about 2.6 percent of the structural deficit</t>
+          <t>$54,539: about 2.1 percent of the structural deficit</t>
         </is>
       </c>
     </row>
@@ -9555,12 +9555,12 @@
         </is>
       </c>
       <c r="B48" s="9">
-        <f>B41+B39*B40-D42-D43*Assumptions!B6-D44-D45</f>
+        <f>B39+B40+B41*54479.4-D42-D43*(Assumptions!B6+D44)-D45</f>
         <v/>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$556,006 a year: the closure loses money</t>
+          <t>-$591,545 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -9571,19 +9571,19 @@
         </is>
       </c>
       <c r="B49" s="9">
-        <f>D41+D39*D40-B42-B43*Assumptions!B6-B44-B45</f>
+        <f>D39+D40+D41*54479.4-B42-B43*(Assumptions!B6+B44)-B45</f>
         <v/>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$551,928 a year: the ceiling, and still below the plan's $800K-$1M requirement</t>
+          <t>+$488,631 a year: the district's fullest documented case, still below the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 2,916 combinations, equal weights, enumerated by build/closure_grid.py: positions take four values (2, 3, 4, 5) and the six other levers three each (4 x 3^6 = 2,916). Median +$21,571; middle half -$104,726 to +$146,274; 45.06 percent (1,314 of 2,916, published as 45 percent) of scenarios negative. One-time transition costs $100K-$300K in year one are additional. REBUILT IN v3.9: the fixed-avoided lever previously took two estimated values ($230,000 mothballed, $290,000 sold), both of which assumed every fixed position at the school is eliminated. It now takes three measured values from the district FY2026 working budget, location 090, General Fund, excl on-behalf: $58,774 (staff reassigned to other buildings, utilities only), $227,831 (mothballed: school admin $131,724 + custodial $37,333 + plant $58,774) and $276,928 (sold: the above plus library and media $49,097). Adding the reassignment case moved the median from +$91,240 to +$21,571 and the negative share from 28.8 to 45.1 percent.</t>
+          <t>Distribution of all 5,832 combinations, equal weights, enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and leavers six (0/13/26/38/51/64): 3^5 x 4 x 6 = 5,832. Median -$21,971 (the median scenario LOSES money); middle half -$148,790 to +$102,067; 55 percent of scenarios negative; range -$591,545 to +$488,631. One-time transition costs $100K-$300K in year one are additional. REBUILT IN v4.2 on the district's own 48-page Response to the 10 Questions (archived build/response_to_the_10_questions.pdf): the capture lever uses its Appendix A worksheet, every staffing position is priced at its own fully loaded $54,479.40 (Appendix A.1), the teacher top leg follows its own Appendix B classroom count, and the leakage lever runs to 50 percent. The v3.9 grid (2,916 scenarios, median +$21,571, 45 percent negative) is retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13143,18 +13143,18 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the v3.9 closure model's median ($21,571) and central case ($69,071)</t>
+          <t>Above the v4.2 closure model's central case ($54,539); the v4.2 median itself is negative (-$21,971)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Closure model median (v3.9 two-tailed grid)</t>
+          <t>Closure model median (v4.2 two-tailed grid)</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>21571</v>
+        <v>-21971</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -13162,18 +13162,18 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab, 2,916-combination grid</t>
+          <t>Closure_Model tab, 5,832-combination grid; the median scenario loses money</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Closure model best case (v3.9 favorable tail)</t>
+          <t>Closure model best case (v4.2 favorable tail)</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>551928</v>
+        <v>488631</v>
       </c>
       <c r="C48" s="9">
         <f>B48*(1-(1+B$40)^-B$41)/B$40</f>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12047,7 +12047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12280,46 +12280,46 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Medicaid billing, E-rate, meal reimbursements</t>
+          <t>Energy performance contracting</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Typical under-collected federal reimbursements</t>
+          <t>10-25% of utilities; authorized by 702 KAR 4:160</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>New revenue</t>
+          <t>Cost reduction</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Low; needs evidence current claims are being missed</t>
+          <t>Medium; contracts are structured to self-fund</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Energy performance contracting</t>
+          <t>Shared services with Paris Independent</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10-25% of utilities; authorized by 702 KAR 4:160</t>
+          <t>Transport, food service, back office</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -12329,260 +12329,232 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Medium; contracts are structured to self-fund</t>
+          <t>Low; needs an interlocal feasibility study</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Shared services with Paris Independent</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>300000</v>
+          <t>Fill NMES to capacity (rebalance + transfers, net)</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>Redistricting!B30</f>
+        <v/>
+      </c>
+      <c r="C12" s="18">
+        <f>Redistricting!B31</f>
+        <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Transport, food service, back office</t>
+          <t>Boundary rebalancing and cross-county scenario, Redistricting tab</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Cost reduction</t>
+          <t>New revenue, net of costs</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Low; needs an interlocal feasibility study</t>
+          <t>High; board boundary authority, math on Redistricting tab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fill NMES to capacity (rebalance + transfers, net)</t>
+          <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
         </is>
       </c>
       <c r="B13" s="18">
-        <f>Redistricting!B30</f>
+        <f>25*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="C13" s="18">
-        <f>Redistricting!B31</f>
+        <f>50*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Boundary rebalancing and cross-county scenario, Redistricting tab</t>
+          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (259 registered homeschoolers, ACS pool ~1,135, net import already 189); 62 open seats exist at Bourbon Central's approved rating</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>New revenue, net of costs</t>
+          <t>New revenue</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>High; board boundary authority, math on Redistricting tab</t>
+          <t>Medium; needs an enrollment marketing plan and incentive design</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
-        </is>
-      </c>
-      <c r="B14" s="18">
-        <f>25*(Assumptions!B6-Assumptions!B62)</f>
-        <v/>
-      </c>
-      <c r="C14" s="18">
-        <f>50*(Assumptions!B6-Assumptions!B62)</f>
-        <v/>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (259 registered homeschoolers, ACS pool ~1,135, net import already 189); 62 open seats exist at Bourbon Central's approved rating</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>New revenue</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs an enrollment marketing plan and incentive design</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Total identified (ranges overlap; not additive to the penny)</t>
         </is>
       </c>
-      <c r="B15" s="24">
-        <f>SUM(B4:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="24">
-        <f>SUM(C4:C14)</f>
-        <v/>
+      <c r="B14" s="24">
+        <f>SUM(B4:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>SUM(C4:C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>COMPARISON</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Package midpoint (raw sum of ranges)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>(B14+C14)/2</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Package midpoint (raw sum of ranges)</t>
-        </is>
-      </c>
-      <c r="B18" s="9">
-        <f>(B15+C15)/2</f>
-        <v/>
+          <t>Conservative combined estimate, low (haircut for overlap)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>1000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, low (haircut for overlap)</t>
+          <t>Conservative combined estimate, high</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>1100000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, high</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n">
-        <v>2100000</v>
+          <t>Conservative midpoint (used in Runway sheet)</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>(B18+B19)/2</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Conservative midpoint (used in Runway sheet)</t>
-        </is>
-      </c>
-      <c r="B21" s="9">
-        <f>(B19+B20)/2</f>
+          <t>Average annual GF drawdown (FY2024-25)</t>
+        </is>
+      </c>
+      <c r="B21" s="18">
+        <f>GF_Summary!D16</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Average annual GF drawdown (FY2024-25)</t>
+          <t>Closure net saving (base case)</t>
         </is>
       </c>
       <c r="B22" s="18">
-        <f>GF_Summary!D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Closure net saving (base case)</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
         <f>Closure_Model!B20</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Reading: raw row sums run about $1.6M to $2.9M; the published $1.1M to $2.1M band applies a conservative haircut for overlap and implementation risk. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Reading: raw row sums run about $1.5M to $2.6M; the published $1.0M to $1.9M band applies a conservative haircut for overlap and implementation risk. Medicaid and reimbursement recovery were removed from the menu in v4.2 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>THE GROWTH PATH: THE SAME MENU AS A DISTRICT-WIDE RECOVERY PLAN (v3.8; backs the site card and Section 9)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>THE GROWTH PATH: THE SAME MENU AS A DISTRICT-WIDE RECOVERY PLAN (v3.8; backs the site card and Section 9)</t>
-        </is>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Move 1: inspect fixed costs (every non-teaching position via attrition, administrative restructuring, transport, energy, shared services)</t>
+        </is>
+      </c>
+      <c r="B27" s="23">
+        <f>SUM(B7:B11)</f>
+        <v/>
+      </c>
+      <c r="C27" s="23">
+        <f>SUM(C7:C11)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Move 1: inspect fixed costs, starting with administration (attrition, admin restraint, transport, reimbursements, energy, shared services)</t>
+          <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
         </is>
       </c>
       <c r="B28" s="23">
-        <f>SUM(B7:B12)</f>
+        <f>B6+B12+B13</f>
         <v/>
       </c>
       <c r="C28" s="23">
-        <f>SUM(C7:C12)</f>
+        <f>C6+C12+C13</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
+          <t>Move 3: the honest revenue conversation, year one (4 percent option plus delinquency; compounds by year three; recallable menu beyond it on Tax_History rows 70-91)</t>
         </is>
       </c>
       <c r="B29" s="23">
-        <f>B6+B13+B14</f>
+        <f>B4+B5</f>
         <v/>
       </c>
       <c r="C29" s="23">
-        <f>C6+C13+C14</f>
+        <f>C4+C5</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Move 3: the honest revenue conversation, year one (4 percent option plus delinquency; compounds by year three; recallable menu beyond it on Tax_History rows 70-91)</t>
+          <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
         </is>
       </c>
       <c r="B30" s="23">
-        <f>B4+B5</f>
+        <f>B27+B28+B29</f>
         <v/>
       </c>
       <c r="C30" s="23">
-        <f>C4+C5</f>
+        <f>C27+C28+C29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>B28+B29+B30</f>
-        <v/>
-      </c>
-      <c r="C31" s="23">
-        <f>C28+C29+C30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
         </is>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -720,14 +720,21 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Prepared by a former NMES King working alongside Claude, an AI research assistant from Anthropic. Estimates are labeled; every figure</t>
+          <t>Prepared by a former NMES King working alongside Claude, an AI research assistant from Anthropic. Built from public records and</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>should be re-verified against the cited primary sources before formal use. Nothing here alleges misconduct by any official.</t>
+          <t>Open Records Requests only. Estimates are labeled; every figure should be re-verified against the cited primary sources before</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>formal use. Nothing here alleges misconduct by any official.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -9493,7 +9493,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0 to 50 percent of 128, x ($4,626 SEEK base + the add-ons lever); exits free and funded under HB 563, homeschool and statewide virtual academy growing</t>
+          <t>0 to 50 percent of 128, x ($4,626 SEEK base + the add-ons lever); exits free and funded under HB 563, homeschool and statewide virtual academy growing. CONSERVATIVE: this is the year-one wave only; if the same share of each entering class keeps leaving, the missing students more than double (x13/6) once every grade K-12 is short</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -10095,15 +10095,15 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>NMES classroom sections</t>
+          <t>NMES homerooms in use</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9.41 classroom FTE, NCES; K-5 across nine homerooms</t>
+          <t>One per grade K-5; NCES lists 9.41 classroom-teacher FTE, which also counts Title I, special ed and part-time certified</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>Nine existing homerooms average 19.3 students at 174, inside every KRS 157.360 cap; only variable costs added</t>
+          <t>Six existing homerooms hold 153 at the district's own Appendix B caps (24 K-3, 28 fourth, 29 fifth; 25 seats open today); filling to 174 needs one added section, priced in the row below</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -834,15 +834,15 @@
         <v/>
       </c>
       <c r="C6" s="9">
-        <f>B6-GF_Summary!$D$16+0.5*Alternatives!$B$20</f>
+        <f>B6-GF_Summary!$D$16+0.5*Alternatives!$B$19</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>C6-GF_Summary!$D$16+Alternatives!$B$20</f>
+        <f>C6-GF_Summary!$D$16+Alternatives!$B$19</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>D6-GF_Summary!$D$16+Alternatives!$B$20</f>
+        <f>D6-GF_Summary!$D$16+Alternatives!$B$19</f>
         <v/>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>Alternatives!B20</f>
+        <f>Alternatives!B19</f>
         <v/>
       </c>
       <c r="C7" s="9">
@@ -12054,7 +12054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12315,253 +12315,225 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Shared services with Paris Independent</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>300000</v>
+          <t>Fill NMES to capacity (rebalance + transfers, net)</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>Redistricting!B30</f>
+        <v/>
+      </c>
+      <c r="C11" s="18">
+        <f>Redistricting!B31</f>
+        <v/>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Transport, food service, back office</t>
+          <t>Boundary rebalancing and cross-county scenario, Redistricting tab</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Cost reduction</t>
+          <t>New revenue, net of costs</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Low; needs an interlocal feasibility study</t>
+          <t>High; board boundary authority, math on Redistricting tab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Fill NMES to capacity (rebalance + transfers, net)</t>
+          <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
         </is>
       </c>
       <c r="B12" s="18">
-        <f>Redistricting!B30</f>
+        <f>25*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="C12" s="18">
-        <f>Redistricting!B31</f>
+        <f>50*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Boundary rebalancing and cross-county scenario, Redistricting tab</t>
+          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (259 registered homeschoolers, ACS pool ~1,135, net import already 189); 62 open seats exist at Bourbon Central's approved rating</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>New revenue, net of costs</t>
+          <t>New revenue</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>High; board boundary authority, math on Redistricting tab</t>
+          <t>Medium; needs an enrollment marketing plan and incentive design</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
-        </is>
-      </c>
-      <c r="B13" s="18">
-        <f>25*(Assumptions!B6-Assumptions!B62)</f>
-        <v/>
-      </c>
-      <c r="C13" s="18">
-        <f>50*(Assumptions!B6-Assumptions!B62)</f>
-        <v/>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (259 registered homeschoolers, ACS pool ~1,135, net import already 189); 62 open seats exist at Bourbon Central's approved rating</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>New revenue</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs an enrollment marketing plan and incentive design</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Total identified (ranges overlap; not additive to the penny)</t>
         </is>
       </c>
-      <c r="B14" s="24">
-        <f>SUM(B4:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="24">
-        <f>SUM(C4:C13)</f>
-        <v/>
+      <c r="B13" s="24">
+        <f>SUM(B4:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="24">
+        <f>SUM(C4:C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>COMPARISON</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Package midpoint (raw sum of ranges)</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>(B13+C13)/2</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Package midpoint (raw sum of ranges)</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>(B14+C14)/2</f>
-        <v/>
+          <t>Conservative combined estimate, low (haircut for overlap)</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>900000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, low (haircut for overlap)</t>
+          <t>Conservative combined estimate, high</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>1000000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, high</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n">
-        <v>1900000</v>
+          <t>Conservative midpoint (used in Runway sheet)</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>(B17+B18)/2</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Conservative midpoint (used in Runway sheet)</t>
-        </is>
-      </c>
-      <c r="B20" s="9">
-        <f>(B18+B19)/2</f>
+          <t>Average annual GF drawdown (FY2024-25)</t>
+        </is>
+      </c>
+      <c r="B20" s="18">
+        <f>GF_Summary!D16</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Average annual GF drawdown (FY2024-25)</t>
+          <t>Closure net saving (base case)</t>
         </is>
       </c>
       <c r="B21" s="18">
-        <f>GF_Summary!D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Closure net saving (base case)</t>
-        </is>
-      </c>
-      <c r="B22" s="18">
         <f>Closure_Model!B20</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Reading: raw row sums run about $1.5M to $2.6M; the published $1.0M to $1.9M band applies a conservative haircut for overlap and implementation risk. Medicaid and reimbursement recovery were removed from the menu in v4.2 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Reading: raw row sums run about $1.4M to $2.3M; the published $0.9M to $1.7M band applies a conservative haircut for overlap and implementation risk. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>THE GROWTH PATH: THE SAME MENU AS A DISTRICT-WIDE RECOVERY PLAN (v3.8; backs the site card and Section 9)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>THE GROWTH PATH: THE SAME MENU AS A DISTRICT-WIDE RECOVERY PLAN (v3.8; backs the site card and Section 9)</t>
-        </is>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Move 1: inspect fixed costs (every non-teaching position via attrition, administrative restructuring, transport, energy)</t>
+        </is>
+      </c>
+      <c r="B26" s="23">
+        <f>SUM(B7:B10)</f>
+        <v/>
+      </c>
+      <c r="C26" s="23">
+        <f>SUM(C7:C10)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Move 1: inspect fixed costs (every non-teaching position via attrition, administrative restructuring, transport, energy, shared services)</t>
+          <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
         </is>
       </c>
       <c r="B27" s="23">
-        <f>SUM(B7:B11)</f>
+        <f>B6+B11+B12</f>
         <v/>
       </c>
       <c r="C27" s="23">
-        <f>SUM(C7:C11)</f>
+        <f>C6+C11+C12</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
+          <t>Move 3: the honest revenue conversation, year one (4 percent option plus delinquency; compounds by year three; recallable menu beyond it on Tax_History rows 70-91)</t>
         </is>
       </c>
       <c r="B28" s="23">
-        <f>B6+B12+B13</f>
+        <f>B4+B5</f>
         <v/>
       </c>
       <c r="C28" s="23">
-        <f>C6+C12+C13</f>
+        <f>C4+C5</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Move 3: the honest revenue conversation, year one (4 percent option plus delinquency; compounds by year three; recallable menu beyond it on Tax_History rows 70-91)</t>
+          <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
         </is>
       </c>
       <c r="B29" s="23">
-        <f>B4+B5</f>
+        <f>B26+B27+B28</f>
         <v/>
       </c>
       <c r="C29" s="23">
-        <f>C4+C5</f>
+        <f>C26+C27+C28</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
-        </is>
-      </c>
-      <c r="B30" s="23">
-        <f>B27+B28+B29</f>
-        <v/>
-      </c>
-      <c r="C30" s="23">
-        <f>C27+C28+C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
         </is>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12054,7 +12054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12536,6 +12536,114 @@
       <c r="A30" s="21" t="inlineStr">
         <is>
           <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Plan at LOW ends: enrollment $1.11M + costs $760K</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>1870000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Full 2018 rate restore (Tax_History basis)</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>1699479</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Structural gap before transfers</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>Assumptions!B24-Assumptions!B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Recurring surplus after the gap</t>
+        </is>
+      </c>
+      <c r="B34" s="23">
+        <f>B31+B32-B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>5% raise, every certified teacher (GF certified payroll x 5% x 1.0145 employer Medicare)</t>
+        </is>
+      </c>
+      <c r="B35" s="9">
+        <f>10000388*0.05*1.0145</f>
+        <v/>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>GF object 0110 total, FY2026 working budget (archived build/fy2026_working_budget.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Left for new debt service</t>
+        </is>
+      </c>
+      <c r="B36" s="9">
+        <f>B34-B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>New bonds supported (4.5%, 20 years; same basis as Debt_Service)</t>
+        </is>
+      </c>
+      <c r="B37" s="23">
+        <f>B36*(1-1.045^-20)/0.045</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Restricted capacity freed when the sweep ends (Debt_Service)</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>17600000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Building capacity, together</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>B37+B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Reading: at the plan's LOW ends with the full restore, the district funds a 5 percent certified raise AND about $23 million of building capacity for new schools and renovations, with every school open. Requires the full 8.9-cent restore and hitting the low-end lever estimates.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12408,11 +12408,11 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, low (haircut for overlap)</t>
+          <t>Published band, low (raw row sums, no haircut)</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>900000</v>
+        <v>1393830</v>
       </c>
     </row>
     <row r="18">
@@ -12428,7 +12428,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Conservative midpoint (used in Runway sheet)</t>
+          <t>Band midpoint (used in Runway sheet)</t>
         </is>
       </c>
       <c r="B19" s="9">
@@ -12461,7 +12461,7 @@
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>Reading: raw row sums run about $1.4M to $2.3M; the published $0.9M to $1.7M band applies a conservative haircut for overlap and implementation risk. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+          <t>Reading: the published band IS the raw row sums, $1.4M to $2.3M, with no haircut (v4.4 review); ranges overlap and are not additive to the penny, and each line carries its own confidence rating in column F. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12054,7 +12054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12644,6 +12644,13 @@
       <c r="A40" s="21" t="inlineStr">
         <is>
           <t>Reading: at the plan's LOW ends with the full restore, the district funds a 5 percent certified raise AND about $23 million of building capacity for new schools and renovations, with every school open. Requires the full 8.9-cent restore and hitting the low-end lever estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Top end: levers high ($3.32M enrollment + $1.32M costs) + full restore = $6.34M vs the $2.65M gap, a $3.69M surplus; a 10 percent certified raise ($1.01M) leaves $2.67M for debt service = about $35M of bonds, roughly $52M of building capacity with the freed restricted stream.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -720,7 +720,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Prepared by a former NMES King working alongside Claude, an AI research assistant from Anthropic. Built from public records and</t>
+          <t>Prepared by a former NMES King and Bourbon County Colonel working alongside Claude, an AI research assistant from Anthropic. Built from public records and</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -895,7 +895,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v4.2): at the +$488,631 best case FY2029 ends near $1.2M; at the -$21,971 median the reserves go slightly FASTER than status quo; 55 percent of scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v4.5): at the +$488,631 best case FY2029 ends near $1.2M; at the -$17,982 weighted median the reserves go slightly FASTER than status quo; 54 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 5,832 combinations, equal weights, enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and leavers six (0/13/26/38/51/64): 3^5 x 4 x 6 = 5,832. Median -$21,971 (the median scenario LOSES money); middle half -$148,790 to +$102,067; 55 percent of scenarios negative; range -$591,545 to +$488,631. One-time transition costs $100K-$300K in year one are additional. REBUILT IN v4.2 on the district's own 48-page Response to the 10 Questions (archived build/response_to_the_10_questions.pdf): the capture lever uses its Appendix A worksheet, every staffing position is priced at its own fully loaded $54,479.40 (Appendix A.1), the teacher top leg follows its own Appendix B classroom count, and the leakage lever runs to 50 percent. The v3.9 grid (2,916 scenarios, median +$21,571, 45 percent negative) is retained in the version history.</t>
+          <t>Distribution of all 5,832 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and leavers six (0/13/26/38/51/64): 3^5 x 4 x 6 = 5,832. v4.5 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers and leavers, where the record gives no defensible center. Weighted median -$17,982 (the median scenario LOSES money); middle half -$135,672 to +$101,417; 54 percent of weighted scenarios negative; range -$591,545 to +$488,631 (unweighted median -$21,971, 55 percent negative). One-time transition costs $100K-$300K in year one are additional. REBUILT IN v4.2 on the district's own 48-page Response to the 10 Questions (archived build/response_to_the_10_questions.pdf): the capture lever uses its Appendix A worksheet, every staffing position is priced at its own fully loaded $54,479.40 (Appendix A.1), the teacher top leg follows its own Appendix B classroom count, and the leakage lever runs to 50 percent. The v3.9 grid (2,916 scenarios, median +$21,571, 45 percent negative) is retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13209,18 +13209,18 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the v4.2 closure model's central case ($54,539); the v4.2 median itself is negative (-$21,971)</t>
+          <t>Above the v4.2 closure model's central case ($54,539); the weighted median itself is negative (-$17,982)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Closure model median (v4.2 two-tailed grid)</t>
+          <t>Closure model median (v4.5 weighted grid)</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-21971</v>
+        <v>-17982</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -849,7 +849,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Closure only (v4.2 central case, $54,539, from FY2027)</t>
+          <t>Closure only (central case, $52,514, from FY2027)</t>
         </is>
       </c>
       <c r="B7" s="9">
@@ -895,7 +895,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v4.5): at the +$488,631 best case FY2029 ends near $1.2M; at the -$17,982 weighted median the reserves go slightly FASTER than status quo; 54 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v4.5): at the +$484,582 best case FY2029 ends near $1.2M; at the -$20,007 weighted median the reserves go slightly FASTER than status quo; 55 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -8584,30 +8584,30 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>School administration avoided (principal, secretary, extended day)</t>
+          <t>School administration avoided (principal, office)</t>
         </is>
       </c>
       <c r="B51" s="14" t="n">
-        <v>131724</v>
+        <v>115397</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>MEASURED v3.9: district FY2026 working budget, location 090, General Fund program 077, excl on-behalf. Was a $175,000 estimate through v3.8.</t>
+          <t>MEASURED v4.5: district MUNIS ledger, FY2026 actuals, org 090 functions 2410+2420 (build/munis_extract.py). Was $131,724 from the working budget through the prior release.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Plant operations avoided (custodial + utilities, sanitation, water)</t>
+          <t>Plant operations avoided (custodial + building costs)</t>
         </is>
       </c>
       <c r="B52" s="14" t="n">
-        <v>96107</v>
+        <v>128867</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>MEASURED v3.9: same source, custodial program 087 $37,333 + plant program 987 $58,774. B51+B52 = $227,831, the grid's mothballed case. Was a $115,000 estimate through v3.8.</t>
+          <t>MEASURED v4.5: MUNIS ledger, org 090 function 2610 actuals: custodial pay and benefits $49,655 + building utilities, disposal, telecom, supplies and repairs $79,211. Was $96,107 from the working budget.</t>
         </is>
       </c>
     </row>
@@ -9423,14 +9423,14 @@
         <v>0</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>109077</v>
+        <v>107052.2</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>218154</v>
+        <v>214104.4</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Measured lines: $131,724 + $37,333 + $49,097 = $218,154 (the district's own A.1 prices the same four roles at $209,700, within 4 percent, and states all current staff are retained in year one; the full-cut leg is an attrition end state)</t>
+          <t>MUNIS FY2026 actuals: school administration $115,397 + custodial $49,655 + library $49,052 = $214,104 (the district's own A.1 prices the same four roles at $209,700, within 2 percent, and states all current staff are retained in year one; the full-cut leg is an attrition end state)</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>$54,539: about 2.1 percent of the structural deficit</t>
+          <t>$52,514: about 2.0 percent of the structural deficit</t>
         </is>
       </c>
     </row>
@@ -9583,14 +9583,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$488,631 a year: the district's fullest documented case, still below the plan's $800K-$1M requirement</t>
+          <t>+$484,582 a year: the district's fullest documented case, still below the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 5,832 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and leavers six (0/13/26/38/51/64): 3^5 x 4 x 6 = 5,832. v4.5 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers and leavers, where the record gives no defensible center. Weighted median -$17,982 (the median scenario LOSES money); middle half -$135,672 to +$101,417; 54 percent of weighted scenarios negative; range -$591,545 to +$488,631 (unweighted median -$21,971, 55 percent negative). One-time transition costs $100K-$300K in year one are additional. REBUILT IN v4.2 on the district's own 48-page Response to the 10 Questions (archived build/response_to_the_10_questions.pdf): the capture lever uses its Appendix A worksheet, every staffing position is priced at its own fully loaded $54,479.40 (Appendix A.1), the teacher top leg follows its own Appendix B classroom count, and the leakage lever runs to 50 percent. The v3.9 grid (2,916 scenarios, median +$21,571, 45 percent negative) is retained in the version history.</t>
+          <t>Distribution of all 5,832 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and leavers six (0/13/26/38/51/64): 3^5 x 4 x 6 = 5,832. v4.5 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers and leavers, where the record gives no defensible center. Weighted median -$20,007 (the median scenario LOSES money); middle half -$137,095 to +$98,603; 55 percent of weighted scenarios negative; range -$591,545 to +$484,582 (unweighted median -$24,431). v4.5 MUNIS pass: the fixed-position lever now uses FY2026 actuals from the district's own ledger ($214,104) instead of working-budget lines ($218,154). One-time transition costs $100K-$300K in year one are additional. REBUILT IN v4.2 on the district's own 48-page Response to the 10 Questions (archived build/response_to_the_10_questions.pdf): the capture lever uses its Appendix A worksheet, every staffing position is priced at its own fully loaded $54,479.40 (Appendix A.1), the teacher top leg follows its own Appendix B classroom count, and the leakage lever runs to 50 percent. The v3.9 grid (2,916 scenarios, median +$21,571, 45 percent negative) is retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the v4.2 closure model's central case ($54,539); the weighted median itself is negative (-$17,982)</t>
+          <t>Above the closure model's central case ($52,514); the weighted median itself is negative (-$20,007)</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-17982</v>
+        <v>-20007</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -13235,11 +13235,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Closure model best case (v4.2 favorable tail)</t>
+          <t>Closure model best case (favorable tail)</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>488631</v>
+        <v>484582</v>
       </c>
       <c r="C48" s="9">
         <f>B48*(1-(1+B$40)^-B$41)/B$40</f>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12542,11 +12542,16 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Plan at LOW ends: enrollment $1.11M + costs $760K</t>
+          <t>Plan at TOP ends: enrollment $530K (Move 2 high) + costs $1.30M</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1870000</v>
+        <v>1830000</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CORRECTED: an earlier release used $1.11M-$3.33M for the enrollment lever; the model's own Move 2 rows price it at $260K-$530K and that band now governs. At the LOW ends with the full restore the plan clears the gap with about $71K to spare and funds no raise.</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -12573,7 +12578,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Recurring surplus after the gap</t>
+          <t>Recurring surplus after the gap (top ends + full restore)</t>
         </is>
       </c>
       <c r="B34" s="23">
@@ -12611,7 +12616,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>New bonds supported (4.5%, 20 years; same basis as Debt_Service)</t>
+          <t>New GF-leveraged bonds supported (4.5%, 20 years; same basis as Debt_Service)</t>
         </is>
       </c>
       <c r="B37" s="23">
@@ -12622,11 +12627,16 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Restricted capacity freed when the sweep ends (Debt_Service)</t>
+          <t>Bonding capacity per the district's own advisor (Baird, June 2026; build/baird_lpc_june2026.pdf)</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>17600000</v>
+        <v>32000000</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>From $3,252,893 of FY2027 bondable restricted revenues. Real only if the restricted stream pays for buildings: the $1.32M-a-year capital-to-operations sweep consumes about $17M of this capacity.</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -12643,14 +12653,14 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Reading: at the plan's LOW ends with the full restore, the district funds a 5 percent certified raise AND about $23 million of building capacity for new schools and renovations, with every school open. Requires the full 8.9-cent restore and hitting the low-end lever estimates.</t>
+          <t>Reading: at the plan's TOP ends with the full restore, the district funds a 5 percent certified raise AND about $37 million of building capacity ($4.9M of new GF-leveraged bonds plus the advisor's $32M), with every school open. At the LOW ends with the full restore the plan clears the gap with about $71K to spare. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Top end: levers high ($3.32M enrollment + $1.32M costs) + full restore = $6.34M vs the $2.65M gap, a $3.69M surplus; a 10 percent certified raise ($1.01M) leaves $2.67M for debt service = about $35M of bonds, roughly $52M of building capacity with the freed restricted stream.</t>
+          <t>Baird sensitivities, their own June 2026 numbers: minus 50 students drops capacity to $31M (about $20,000 of bonding capacity per student); rates 100bp lower raise it to $35M. Unexpired SFCC offers of $126,250 a year expire January 2028 through January 2034.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -9472,7 +9472,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Derived bottom-up with uncertainty: 2-4 zone buses terminating in Paris (~9-11 road miles farther one-way), 2 loaded + 0-2 deadhead legs daily, 175 days, $3.25-$4.75/mile (KDE/NAPT band), high stop adds one $45,000 route split. Per zone student $160/$492/$1,495 vs the $1,032 district average. The district's routing data was requested and answered N/A.</t>
+          <t>Derived bottom-up with uncertainty: 2-4 zone buses terminating in Paris (~9-11 road miles farther one-way), 2 loaded + 0-2 deadhead legs daily, 175 days, $3.25-$4.75/mile (KDE/NAPT band), high stop adds one $45,000 route split. Per zone student $160/$492/$1,495 vs the $1,032 district average. The July 2026 records response produced the current routes but answered N/A for any routing study or ride-time analysis.</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>A planning scenario, not a routing study. The district holds the geocoded student counts and routing data a true optimization needs; releasing them is a records ask in the report.</t>
+          <t>A planning scenario, not a routing study. The July 2026 records response produced current bus routes but answered N/A for GIS files, routing-software reports, and ride-time analyses; the optimization inputs do not exist in public form.</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Receiving-school relief is booked only as one to two avoided or redeployed sections; grade-by-grade capacities at Bourbon Central and Cane Ridge are a records ask (report Question 3).</t>
+          <t>Receiving-school relief is booked only as one to two avoided or redeployed sections; the July 2026 records response provided a capacity graphic; grade-by-grade room files were not shared (building maps withheld for security), so relief stays conservatively booked.</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10884,7 @@
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>Class-cap staffing check (KRS 157.360: 24 in K-3, 28 in grade 4, 29 in grade 5). At an even grade mix, 174 students need about 11 sections against 9 existing rooms, and 154 need about 10; the supplies-only counterfactual is therefore the BEST case, and the staffed cases below are the honest base cases. Grade-by-grade enrollment is a records ask; a mix weighted to grades 4-5 needs fewer sections.</t>
+          <t>Class-cap staffing check (KRS 157.360: 24 in K-3, 28 in grade 4, 29 in grade 5). At an even grade mix, 174 students need about 11 sections against 9 existing rooms, and 154 need about 10; the supplies-only counterfactual is therefore the BEST case, and the staffed cases below are the honest base cases. The July 2026 records response provided an elementary capacity graphic but no grade-by-grade files (building maps withheld for security); a mix weighted to grades 4-5 needs fewer sections.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12054,7 +12054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12533,24 +12533,24 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>THE TRANSFORMATIVE CHECK (v4.5: enrollment lever re-based on recovered leakage students at $4,226 each; gap re-based on the trending fiscal 2026 ledger; capacity anchored on the district advisor's June 2026 presentation)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Plan at TOP ends: enrollment $530K (Move 2 high) + costs $1.30M</t>
+          <t>Plan levers at the website defaults: 0 leakage students recovered + costs at the $760K low end</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1830000</v>
+        <v>760000</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CORRECTED: an earlier release used $1.11M-$3.33M for the enrollment lever; the model's own Move 2 rows price it at $260K-$530K and that band now governs. At the LOW ends with the full restore the plan clears the gap with about $71K to spare and funds no raise.</t>
+          <t>CORRECTED twice: an earlier release used $1.11M-$3.33M for the enrollment lever; the Move 2 rows price the near-term band at $260K-$530K; the website slider now prices the lever directly as recovered leakage students, 0 to the measured 550-student pool, at the $4,226 net-of-supplies cell in B49 legs. Every 100 recovered add $422,600 a year on top of this check.</t>
         </is>
       </c>
     </row>
@@ -12567,18 +12567,22 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Structural gap before transfers</t>
-        </is>
-      </c>
-      <c r="B33" s="18">
-        <f>Assumptions!B24-Assumptions!B21</f>
-        <v/>
+          <t>Trending structural gap, fiscal 2026 (June 2026 year-end ledger, before transfers)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>1738653</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>District's own June 2026 GL: $20,694,287 of revenue against $22,432,940 of spending before transfers (fund balance $3,328,472 to $2,954,484 after $1,409,590 of transfers in; on-behalf cancels in the gap). The audited fiscal 2025 gap, Assumptions!B24-B21, was $2,648,086.</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Recurring surplus after the gap (top ends + full restore)</t>
+          <t>Recurring surplus after the trending gap (website defaults + full restore)</t>
         </is>
       </c>
       <c r="B34" s="23">
@@ -12653,7 +12657,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Reading: at the plan's TOP ends with the full restore, the district funds a 5 percent certified raise AND about $37 million of building capacity ($4.9M of new GF-leveraged bonds plus the advisor's $32M), with every school open. At the LOW ends with the full restore the plan clears the gap with about $71K to spare. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
+          <t>Reading: at the website defaults (no recovery, costs at the low end, full restore) the plan clears the trending fiscal 2026 gap with about $721K to spare, funds the 5 percent certified raise, and still leaves about $214K for debt: about $2.8M of new GF-leveraged bonds plus the advisor's $32M, about $35 million of building capacity with every school open. Every 100 recovered leakage students add $422,600 a year on top; the website slider runs to the full 550. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
         </is>
       </c>
     </row>
@@ -12661,6 +12665,13 @@
       <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Baird sensitivities, their own June 2026 numbers: minus 50 students drops capacity to $31M (about $20,000 of bonding capacity per student); rates 100bp lower raise it to $35M. Unexpired SFCC offers of $126,250 a year expire January 2028 through January 2034.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12542,11 +12542,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Plan levers at the website defaults: 0 leakage students recovered + costs at the $760K low end</t>
+          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,226 = $1,162,150) + costs at the $760K low end</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>760000</v>
+        <v>1922150</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Reading: at the website defaults (no recovery, costs at the low end, full restore) the plan clears the trending fiscal 2026 gap with about $721K to spare, funds the 5 percent certified raise, and still leaves about $214K for debt: about $2.8M of new GF-leveraged bonds plus the advisor's $32M, about $35 million of building capacity with every school open. Every 100 recovered leakage students add $422,600 a year on top; the website slider runs to the full 550. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
+          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.88M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.38M for debt: about $17.9M of new GF-leveraged bonds plus the advisor's $32M, about $50 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $721K to spare (raise + $2.8M of bonds, about $35M). Every 100 recovered leakage students move the surplus by $422,600 a year; the website slider runs 0 to 550. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12657,7 +12657,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.88M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.38M for debt: about $17.9M of new GF-leveraged bonds plus the advisor's $32M, about $50 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $721K to spare (raise + $2.8M of bonds, about $35M). Every 100 recovered leakage students move the surplus by $422,600 a year; the website slider runs 0 to 550. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
+          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.88M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.38M for debt: about $17.9M of new GF-leveraged bonds plus the advisor's $32M, about $50 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $721K to spare (raise + $2.8M of bonds, about $35M). At the slider top (all 550 recovered, levers high) the plan runs about $3.6M ahead: the raise plus about $40M of bonds, about $72M of capacity. Every 100 recovered leakage students move the surplus by $422,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12358,7 +12358,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (259 registered homeschoolers, ACS pool ~1,135, net import already 189); 62 open seats exist at Bourbon Central's approved rating</t>
+          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (236 in the district's own homeschool files, 247 residents enrolled in other districts, 450-550 in all with private school); 62 open seats exist at Bourbon Central's approved rating</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the v3 central case covers 5.0% of the gap (10.8% at the base case, 21.3% at the favorable tail); longer rides; enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $20,007 a year; the district's fullest documented case covers 9.1% of the $2.65M gap, the grid central case 2.0%, and the +$484,582 tail 18.3%; longer rides; enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-21971/Assumptions!B11</f>
+        <f>-20007/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>MEASURED v4.5: district MUNIS ledger, FY2026 actuals, org 090 functions 2410+2420 (build/munis_extract.py). Was $131,724 from the working budget through the prior release.</t>
+          <t>MEASURED v4.5: district MUNIS ledger, FY2026 actuals, org 090 functions 2410+2420 (build/munis_extract.py). Was $131,724 from the working budget (program view; the function view prints $132,744, School_Costs!G32) through the prior release.</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Derived bottom-up with uncertainty: 2-4 zone buses terminating in Paris (~9-11 road miles farther one-way), 2 loaded + 0-2 deadhead legs daily, 175 days, $3.25-$4.75/mile (KDE/NAPT band), high stop adds one $45,000 route split. Per zone student $160/$492/$1,495 vs the $1,032 district average. The July 2026 records response produced the current routes but answered N/A for any routing study or ride-time analysis.</t>
+          <t>Derived bottom-up with uncertainty: 2-4 zone buses terminating in Paris (~9-11 road miles farther one-way), 2 loaded + 0-2 deadhead legs daily, 170 to 175 days, $3.25-$4.75/mile (KDE/NAPT band), high stop adds one $45,000 route split. Per zone student $160/$492/$1,495 vs the $1,032 district average. The July 2026 records response produced the current routes but answered N/A for any routing study or ride-time analysis.</t>
         </is>
       </c>
     </row>
@@ -9604,16 +9604,16 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Every absorbed student priced at the empirical $9,848 marginal</t>
+          <t>Every absorbed student priced at the $9,848 slope (withdrawn in v3.9; kept for the record)</t>
         </is>
       </c>
       <c r="B53" s="9">
-        <f>Assumptions!B14*Assumptions!B11-128*Redistricting!B111-137500-10*Assumptions!B6</f>
+        <f>Assumptions!B14*Assumptions!B11-128*9848-137500-10*Assumptions!B6</f>
         <v/>
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>About $1.03M on paper. But it requires Cane Ridge at 525 students against its approved 422 rating and Bourbon Central at 555 against 521: exactly the overcrowding the $14M renovation exists to cure. The savings pre-spend the bond.</t>
+          <t>About $1.03M on paper, and the $9,848 slope itself was withdrawn in v3.9 (Redistricting row 111). Kept because the refutation stands either way: it requires Cane Ridge at 525 students against its approved 422 rating and Bourbon Central at 555 against 521: exactly the overcrowding the $14M renovation exists to cure. The savings pre-spend the bond.</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -9701,7 +9701,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Grow the Kings: Nonresident Enrollment Model (HB 563 / KRS 157.350)</t>
+          <t>Grow the Kings: Nonresident Enrollment Model (HB 563 / KRS 157.350; legacy single-point scenario, published grid summarized at row 17)</t>
         </is>
       </c>
     </row>
@@ -9832,15 +9832,15 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>IF(B6&gt;Assumptions!$B$63,Assumptions!$B$41,0)</f>
+        <f>IF(B6&gt;Assumptions!$B$63,49150,0)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IF(C6&gt;Assumptions!$B$63,Assumptions!$B$41,0)</f>
+        <f>IF(C6&gt;Assumptions!$B$63,49150,0)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>IF(D6&gt;Assumptions!$B$63,Assumptions!$B$41,0)</f>
+        <f>IF(D6&gt;Assumptions!$B$63,49150,0)</f>
         <v/>
       </c>
     </row>
@@ -9893,6 +9893,27 @@
       <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Context: NMES enrolled 160 students as recently as 2019-20 (see School_Data) - the growth targets restore recent history, they do not exceed it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>THE PUBLISHED GROWTH GRID (build/growth_grid.py; the headline model behind the site calculator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$141,780; middle half +$94,520 to +$182,654; floor +$3,331; ceiling +$386,904; zero negative scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>The three-year table above is the legacy v3 transfer scenario, kept for continuity; its teacher line is priced at the certified schedule mid-row ($49,150), consistent with the published grid, rather than the $85,000 all-in comparison figure.</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -10961,7 +10982,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect is minus $385K to plus $565K (median $91K) and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $591,545 to plus $484,582 with a weighted median of minus $20,007, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11306,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Net nonresident import, Bourbon Co district (436 enrolled in vs 247 residents out, Paris flows included)</t>
+          <t>Net nonresident import, Bourbon Co district (436 enrolled in vs 247 residents out, Paris flows included; kept for context: the published pool counts the 247 exports as recoverable rather than netting them against imports)</t>
         </is>
       </c>
       <c r="B127" s="10" t="n">
@@ -11365,6 +11386,39 @@
       <c r="A135" s="21" t="inlineStr">
         <is>
           <t>Total added students from all sources (rezone + transfers + returns) is capped at 46 by the rated 174; the site planner enforces the cap. Rezoned students bring no new SEEK (already enrolled in-district); transfers and returns each bring the full base. Sources: KDE Non-Resident Student report SY24-25 and the Washington Post home-school district file, both archived under build/; ACS table B14003 (Bourbon County); NCES Private School Universe Survey 2023-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Residents enrolled in another district (KDE Non-Resident report SY2024-25: 171 at Paris Independent + 76 out of county)</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Documented Bourbon-specific floor: homeschool filings plus residents enrolled elsewhere</t>
+        </is>
+      </c>
+      <c r="B137" s="26">
+        <f>B117+B136</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Published planning pool: Bourbon County Schools kids in homeschool, private school, or another district</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>450 to 550</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12168,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>4% property-tax adjustment (KRS 160.470)</t>
+          <t>KRS 160.470 four percent revenue mechanics (context; the published lead lever is the 2018 restore, Tax_History rows 70-91)</t>
         </is>
       </c>
       <c r="B4" s="18">
@@ -12126,7 +12180,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Low = year-one 4% option on the General Fund levied base (matches the levy analysis); high allows base growth</t>
+          <t>Low = year-one 4% revenue growth on the General Fund levied base; high allows base growth. A revenue cap, not a rate move.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -12136,7 +12190,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>High; board authority every August, no recall exposure</t>
+          <t>Mechanics only; the published revenue ask anchors on restoring the 2018 rate</t>
         </is>
       </c>
     </row>
@@ -12411,18 +12465,20 @@
           <t>Published band, low (raw row sums, no haircut)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>1393830</v>
+      <c r="B17" s="9">
+        <f>B13</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Conservative combined estimate, high</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>1700000</v>
+          <t>Published band, high (raw row sums, no haircut; the pre-v4.4 conservative $1.7M high is retired)</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>C13</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -12461,7 +12517,7 @@
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>Reading: the published band IS the raw row sums, $1.4M to $2.3M, with no haircut (v4.4 review); ranges overlap and are not additive to the penny, and each line carries its own confidence rating in column F. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model rows 21 and 35 carry both for closure).</t>
+          <t>Reading: the raw-row band is $1.39M to $2.34M with no haircut (v4.4 review). The published headline is now the 2018 restore plus the counted-once cost package, $2.5M to $3.0M a year (transformative check below). Ranges overlap and are not additive to the penny, and each line carries its own confidence rating in column F. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model row 21 carries both for closure).</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12561,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Move 3: the honest revenue conversation, year one (4 percent option plus delinquency; compounds by year three; recallable menu beyond it on Tax_History rows 70-91)</t>
+          <t>Move 3: the honest revenue conversation, year one (this cell keeps the 4 percent + delinquency mechanics for continuity; the published lead lever is the 2018 restore, about $1.7M a year, Tax_History rows 82-89)</t>
         </is>
       </c>
       <c r="B28" s="23">
@@ -13791,7 +13847,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>New recurring revenue: 4 percent levy taken three years running</t>
+          <t>New recurring revenue: 4 percent levy taken three years running (mechanics case; with the published 2018 restore instead, the gap clears in every case: Alternatives transformative check)</t>
         </is>
       </c>
       <c r="B97" s="18">

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -11256,7 +11256,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Of the current pool, seats at the county's ONLY private school (St. Mary, Paris, PK-5; federal Private School Survey 2023-24)</t>
+          <t>Of the current pool, seats at St. Mary (Paris, PK-5; federal Private School Survey 2023-24). Bourbon Christian Academy (Millersburg, K-12) is absent from that voluntary survey, so its students are uncounted and the pool stays a floor</t>
         </is>
       </c>
       <c r="B122" s="10" t="n">

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -9928,7 +9928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -11420,6 +11420,36 @@
         <is>
           <t>450 to 550</t>
         </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Pool priced at the full SEEK base, revenue not collected today (450 and 550 x FY2027 base; the published $2.1 to $2.5 million)</t>
+        </is>
+      </c>
+      <c r="B139" s="23">
+        <f>450*Assumptions!B6</f>
+        <v/>
+      </c>
+      <c r="C139" s="23">
+        <f>550*Assumptions!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Same pool net of supplies, the basis the plan calculator credits per recovered student ($1.9 to $2.3 million)</t>
+        </is>
+      </c>
+      <c r="B140" s="9">
+        <f>450*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="C140" s="9">
+        <f>550*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -561,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Companion workbook to the July 2026 report 'A Deep Dive into Bourbon County Schools' (Bourbon County, Kentucky)</t>
+          <t>Companion workbook to the report 'Saving North Middletown Elementary School: A Close Look at Bourbon County Schools' (v4.6, August 2026)</t>
         </is>
       </c>
     </row>
@@ -668,21 +668,21 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Multi-year school scores and NMES enrollment history: School_Data tab (backs report Figures 6, 7, and 11).</t>
+          <t xml:space="preserve">  Multi-year school scores and NMES enrollment history: School_Data tab (backs report Figures 1 and 2).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 9 and Figure 14).</t>
+          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 10 and Figure 14).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the 4% three-year path: Tax_History tab (backs Figure 18).</t>
+          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the recallable options: Tax_History tab (backs Section 10 and Figures 15 and 16).</t>
         </is>
       </c>
     </row>
@@ -696,14 +696,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Bonding capacity components and what closure can and cannot change: Debt_Service tab (backs Section 6).</t>
+          <t xml:space="preserve">  Bonding capacity components and what closure can and cannot change: Debt_Service tab (backs Section 8).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Student density, route-mile math, and busing cost scenarios: Transport_Geo tab (backs Section 9).</t>
+          <t xml:space="preserve">  Student density, route-mile math, and busing cost scenarios: Transport_Geo tab (backs Appendix B).</t>
         </is>
       </c>
     </row>
@@ -998,9 +998,8 @@
           <t>2. Close NMES and consolidate</t>
         </is>
       </c>
-      <c r="B6" s="18">
-        <f>Closure_Model!B20</f>
-        <v/>
+      <c r="B6" s="8" t="n">
+        <v>-20007</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -1013,7 +1012,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $20,007 a year; the district's fullest documented case covers 9.1% of the $2.65M gap, the grid central case 2.0%, and the +$484,582 tail 18.3%; longer rides; enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $20,007 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the legacy base case covers 9.1% of the $2.65M gap, the grid central case 2.0%, and the +$484,582 best-case tail 18.3%; longer rides; enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1081,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Backs Section 9 and Figure 18 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
+          <t>Backs Section 10 and Figures 15 and 16 of the report. Rates in cents per $100. DOR rate books primary for 2023-2025; 2018-2022 verified secondary; 2005-2017 not retrieved and not interpolated.</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1246,7 @@
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>66.8</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="22">
@@ -2169,16 +2168,16 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Yield per cent of General Fund rate, per year</t>
+          <t>Yield per cent of REAL ESTATE rate, per year (certified real base / 10,000)</t>
         </is>
       </c>
       <c r="B72" s="9">
-        <f>B32/B71</f>
+        <f>1661885191/10000</f>
         <v/>
       </c>
       <c r="G72" s="21" t="inlineStr">
         <is>
-          <t>FY2025 GF collections divided by the 41.0 GF cents: about $191,000 per cent. Real and personal property only; tangible and motor vehicle rates untouched, so every figure below is conservative</t>
+          <t>CORRECTED in v4.6: the FY2025 audit's certified valuation of $1,843,569,625 splits, at its own calculated levy of $9,880,143 with rates 52.4 real / 64.5 tangible, into $1,661,885,191 real and $181,684,434 tangible; one real cent yields $166,189 at full collection. The earlier blended figure ($7,829,060 collections / 41.0 cents = $190,953) mixed tangible taxed at 64.5 cents into a real-rate move and overstated the options below by about 13 percent. Tangible (already 64.5, above every option) and motor vehicle rates do not move</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2398,7 @@
       </c>
       <c r="G85" s="21" t="inlineStr">
         <is>
-          <t>About $4,551. The rate this board itself levied in 2018 is, almost to the dollar, the make-the-General-Fund-stand-alone rate</t>
+          <t>Negative about $216,000: the restore covers the operating close and most of the sweep; the remainder sits well inside the cost package's $760,000 floor. An earlier version showed +$4,551 on the blended per-cent basis, corrected in v4.6</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2447,7 @@
       </c>
       <c r="G89" s="21" t="inlineStr">
         <is>
-          <t>Roughly $35 million, for $15.69 a month on the median home, with nothing closed. The Harrison and median options are honest partial steps, leaving about $680,000 and $190,000 a year to find from the alternatives menu before the sweep can end; the Clark option adds about $10.5 million more direct capacity from its surplus</t>
+          <t>Roughly $35 million, for $15.69 a month on the median home, with nothing closed. The Harrison and median options are honest partial steps, leaving about $814,000 and $382,000 a year to find from the alternatives menu before the sweep can end; the Clark option adds about $6.3 million more direct capacity from its surplus</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3664,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>ELEMENTARY SCORES BY YEAR, 2007-2025 (backs Figures 6 and 7)</t>
+          <t>ELEMENTARY SCORES BY YEAR, 2007-2025 (backs Figures 1 and 2)</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5022,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Sources: District Facilities Plan, KBE approval June 2013 (Wayback Machine capture) and District Facility Plan, KBE approval August 2021 (currently posted; next plan due June 2025). Both archived in this repository under build/. Figures read enrollment/capacity; the 2021 preschool line (272/200, with the plan's note of 80 full-day plus 192 half-day students) confirms the order.</t>
+          <t>Sources: District Facilities Plan, KBE approval June 2013 (Wayback Machine capture) and District Facility Plan, KBE approval August 2021 (currently posted; the 2026 draft plan now pending would replace it). Both archived in this repository under build/. Figures read enrollment/capacity; the 2021 preschool line (272/200, with the plan's note of 80 full-day plus 192 half-day students) confirms the order.</t>
         </is>
       </c>
     </row>
@@ -6078,14 +6077,14 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Closures most like this plan (single small elementary, nothing built): count / median saving</t>
+          <t>Closures most like this plan (single small elementary, nothing built): count / raw median per displaced student (inside the plausible window the median is $541; see report Section 5)</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>8440</v>
       </c>
     </row>
     <row r="13">
@@ -8603,7 +8602,7 @@
         </is>
       </c>
       <c r="B52" s="14" t="n">
-        <v>128867</v>
+        <v>128866</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -9223,7 +9222,7 @@
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 5,832-scenario grid at row 37, median a $20,007 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="24">
@@ -9361,7 +9360,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V4.2 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 5,832 COMBINATIONS (backs Figure 7)</t>
+          <t>V4.2 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 5,832 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9582,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$484,582 a year: the district's fullest documented case, still below the plan's $800K-$1M requirement</t>
+          <t>+$484,582 a year: the grid's best case (every lever at its closure-friendliest), still below the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9619,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>MILLERSBURG, 2007: THE COUNTY'S OWN PRECEDENT (backs Figure 8)</t>
+          <t>MILLERSBURG, CLOSED 2006 (2006-07 CCD FILE; STUDENTS TO THE 2007 CANE RIDGE ADDITION): THE COUNTY'S OWN PRECEDENT (backs Figure 6)</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11183,7 @@
     <row r="111">
       <c r="A111" s="21" t="inlineStr">
         <is>
-          <t>VALIDATION AGAINST ACTUALS: withdrawn in v3.9. The two-school cost slope used here depended on memberships (491 and 461) that appear in no archived source file and that contradict B8 and B9 above, and its sign flips from plus $9,848 to minus $941 to minus $22,564 across the three plausible membership pairs. The honest bound is the break-even marginal cost already computed live in rows 57 to 60.</t>
+          <t>VALIDATION AGAINST ACTUALS: withdrawn in v3.9. The two-school cost slope used here depended on memberships (491 and 461, later corroborated as 2023-24 SAAR in the 2026 draft plan, Facility_Plans rows 30-31) that contradict the fall counts in B8 and B9 above, and its sign flips from plus $9,848 to minus $941 to minus $22,564 across the three plausible membership pairs. The honest bound is the break-even marginal cost already computed live in rows 57 to 60.</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11847,7 @@
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
         <is>
-          <t>The bottom-up estimate lands inside the planning range; the $137,500 midpoint used in the Closure_Model stands. Note what closure does not remove: every square mile of the eastern county stays in the coverage area, with longer rides on it, roughly 15 to 20 added minutes each way on US 460.</t>
+          <t>The bottom-up estimate lands inside the planning range. The $137,500 midpoint survives only in the legacy single-point rows; the published grid's central busing figure is the bottom-up $63,000 (Closure_Model row 42). Note what closure does not remove: every square mile of the eastern county stays in the coverage area, with longer rides on it, roughly 15 to 20 added minutes each way on US 460.</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12535,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (base case)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$20,007 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="18">
@@ -12591,7 +12590,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Move 3: the honest revenue conversation, year one (this cell keeps the 4 percent + delinquency mechanics for continuity; the published lead lever is the 2018 restore, about $1.7M a year, Tax_History rows 82-89)</t>
+          <t>Move 3: the honest revenue conversation, year one (this cell keeps the 4 percent + delinquency mechanics for continuity; the published lead lever is the 2018 restore, about $1.5M a year, Tax_History rows 82-89)</t>
         </is>
       </c>
       <c r="B28" s="23">
@@ -12643,11 +12642,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Full 2018 rate restore (Tax_History basis)</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n">
-        <v>1699479</v>
+          <t>Full 2018 rate restore (live from Tax_History D79, certified real base; v4.6 correction from the blended $1,699,479)</t>
+        </is>
+      </c>
+      <c r="B32" s="9">
+        <f>Tax_History!D79</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -12743,7 +12743,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.88M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.38M for debt: about $17.9M of new GF-leveraged bonds plus the advisor's $32M, about $50 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $721K to spare (raise + $2.8M of bonds, about $35M). At the slider top (all 550 recovered, levers high) the plan runs about $3.6M ahead: the raise plus about $40M of bonds, about $72M of capacity. Every 100 recovered leakage students move the surplus by $422,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
+          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.66M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.16M for debt: about $15.0M of new GF-leveraged bonds plus the advisor's $32M, about $47 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $500K to spare, within $7,000 of the full raise; two recovered students close the difference. At the slider top (all 550 recovered, levers high) the plan runs about $3.4M ahead: the raise plus about $37M of bonds, about $69M of capacity. Every 100 recovered leakage students move the surplus by $422,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
         </is>
       </c>
       <c r="B96" s="8" t="n">
-        <v>1900000</v>
+        <v>1787918</v>
       </c>
       <c r="C96" s="8" t="n">
         <v>373989</v>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -9,21 +9,22 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GF_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closure_Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redistricting" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport_Geo" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt_Service" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runway" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_History" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demographics" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Data" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Plans" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY_Closures" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Costs" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defaults" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GF_Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closure_Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redistricting" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport_Geo" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt_Service" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runway" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_History" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demographics" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Data" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Plans" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY_Closures" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Costs" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,8 +37,8 @@
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="171" formatCode="+0.0;-0.0"/>
@@ -87,13 +88,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -149,37 +150,37 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -545,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -668,71 +669,78 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Multi-year school scores and NMES enrollment history: School_Data tab (backs report Figures 1 and 2).</t>
+          <t xml:space="preserve">  Every published scenario default (the four facts, the leaver table, both calculator defaults, the plan floor/default/top, Eminence, the ledger breakevens) as live formulas: Defaults tab.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 10 and Figure 14).</t>
+          <t xml:space="preserve">  Multi-year school scores and NMES enrollment history: School_Data tab (backs report Figures 1 and 2).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the recallable options: Tax_History tab (backs Section 10 and Figures 15 and 16).</t>
+          <t xml:space="preserve">  County demographics and the full 1989-2025 NMES enrollment series: Demographics tab (backs Section 10 and Figure 14).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Boundary rebalancing and fill-to-capacity scenario: Redistricting tab (backs the Section 9 worked example and Figure 15).</t>
+          <t xml:space="preserve">  Tax rates, fund split, delinquency check, and the recallable options: Tax_History tab (backs Section 10 and Figures 15 and 16).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Bonding capacity components and what closure can and cannot change: Debt_Service tab (backs Section 8).</t>
+          <t xml:space="preserve">  Boundary rebalancing and fill-to-capacity scenario: Redistricting tab (backs the Section 9 worked example and Figure 15).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Bonding capacity components and what closure can and cannot change: Debt_Service tab (backs Section 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Student density, route-mile math, and busing cost scenarios: Transport_Geo tab (backs Appendix B).</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>CAVEAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Prepared by a former NMES King and Bourbon County Colonel working alongside Claude, an AI research assistant from Anthropic. Built from public records and</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Open Records Requests only. Estimates are labeled; every figure should be re-verified against the cited primary sources before</t>
+          <t>Prepared by a former NMES King and Bourbon County Colonel working alongside Claude, an AI research assistant from Anthropic. Built from public records and</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Open Records Requests only. Estimates are labeled; every figure should be re-verified against the cited primary sources before</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>formal use. Nothing here alleges misconduct by any official.</t>
         </is>
@@ -744,6 +752,1311 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Outstanding Bonds: Bourbon County School District Finance Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source: FY2025 audited financial statements, Note 4. Facility funds and debt are restricted; they cannot pay operating costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Outstanding 6/30/25</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>2255000</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>1.90-2.10%</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>348000</v>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2013R</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>468000</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2.75-4.05%</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>585000</v>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Audit figures internally inconsistent; maturity typo in audit; district to correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1.00-3.00%</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>3145000</v>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Refunded $5,315,000 of 2009 bonds; NPV savings $314,834</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>3620000</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0.50-1.85%</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>3405000</v>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Refunded $3,410,000 of 2011 bonds; NPV savings $106,627</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>810000</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>3.65-4.00%</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>755000</v>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Purpose to be confirmed from official statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>6055000</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>4.00-5.00%</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>5945290</v>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Funds active construction program; purpose to be published</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>SUM(B5:B11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ANNUAL DEBT SERVICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>District-paid, FY2025</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>1150216</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>District-paid, FY2026</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>1578700</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Increase, FY2025 to FY2026</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>B16-B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>FY2026 total including state (SFCC) share</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>1846159</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SFCC-paid principal over life of bonds</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>1568809</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BONDING CAPACITY: WHAT CLOSURE CAN AND CANNOT CHANGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Average Daily Attendance, FY2025 (SEEK basis)</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n">
+        <v>2242.5</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>FY2025 audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Capital outlay allotment per year (KRS 157.420, $100 per ADA)</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>100*B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Bondable share of capital outlay (702 KAR 4:160 safety factor)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Building-fund and debt-fund property tax, FY2025 (the 'nickel' stream)</t>
+        </is>
+      </c>
+      <c r="B25" s="25">
+        <f>Tax_History!B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>District-paid debt service, FY2026</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>1578700</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Annual restricted margin available for new debt (illustrative)</t>
+        </is>
+      </c>
+      <c r="B27" s="33">
+        <f>B23*B24+B25-B26</f>
+        <v/>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>Simplified: KDE's official bonding potential statement is the authority and should be published</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Unused bonding capacity stated in the FY2024 audit</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 audit note</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Why closing NMES does not create bonding capacity: capacity is built from the streams above, none of which</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>grows when a school closes. Each student who leaves the district subtracts $100 per year from capital outlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>and the SEEK base from operations. Sale proceeds are one-time and restricted to capital use. What a closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>changes is the facility plan's priority list, which steers SFCC offers (KRS 157.622) toward other projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>That is a choice about priorities, not a gain in capacity, and it should be argued openly with the BG-1,</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>the official statement, and the bonding potential statement all public.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>THE $14 MILLION PLAN (JULY 15, 2026 PLANNING COMMITTEE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Stated plan: free up $800,000 to $1,000,000 a year of operating money to bond $14 million</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Proposed bond amount</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Assumed interest rate</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Assumed term, years</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Annual debt service on the proposed bond</t>
+        </is>
+      </c>
+      <c r="B42" s="33">
+        <f>B39*B40/(1-(1+B40)^-B41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>Payment is approximately the operating amount the plan frees up; compare the savings scenarios below</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>WHAT EACH SAVINGS ESTIMATE COULD ACTUALLY BOND</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Bond principal supported = annual savings x present-value annuity factor at the rate and term above</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>District's own KDE-filed excess cost of NMES vs peer elementaries</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>121220</v>
+      </c>
+      <c r="C46" s="9">
+        <f>B46*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>Above the closure model's central case ($52,514); the weighted median itself is negative (-$20,007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Closure model median (v4.5 weighted grid)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>-20007</v>
+      </c>
+      <c r="C47" s="9">
+        <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>Closure_Model tab, 5,832-combination grid; the median scenario loses money</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Closure model best case (favorable tail)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>484582</v>
+      </c>
+      <c r="C48" s="9">
+        <f>B48*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>Closure_Model tab B49</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Administration's claim, July 15, 2026</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>900000</v>
+      </c>
+      <c r="C49" s="9">
+        <f>B49*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>Unpublished derivation; reconcile with KDE-filed school-level spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Only the administration's own number reaches $14 million. The audited excess cost supports about $1.6 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>DISTRICT-PAID DEBT SERVICE SCHEDULE (FY2025 AUDIT, NOTE 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Payments fall as the 2013, 2016, and 2020 series retire; this falling schedule is the room a wrap-around structure fills</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>1578700</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>1575060</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>1578719</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>1577258</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>1578340</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>FY2031-35 average</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>1321112</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>FY2036-40 average</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>398915</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>FY2041-45 average</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>260708</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>THE LEVERS THAT DO NOT CLOSE A SCHOOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Remaining restricted capacity (FY2024 audit $23.5M less local share of the 2024 issue, approximate)</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="F64" s="21" t="inlineStr">
+        <is>
+          <t>Exact figure is the fiscal agent's bonding potential statement; demand it</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Certified real and personal property assessment, FY2025</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>1843569625</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Recallable nickel status: ALREADY LEVIED August 17, 2023, inside the existing rate</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>levied</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="inlineStr">
+        <is>
+          <t>KDE Nickel Levy Chart (March 2024) dates Bourbon's recallable levy 8/17/2023; KDE's levied-rates file (April 30, 2026) decomposes the 52.4-cent rate as 41.0 general fund + 5.7 FSPK + 5.7 recallable. Paris Independent, for scale: 71.5 cents with 17.4 recallable</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>New annual state equalization on the recallable nickel (full value, FY2027 schedule)</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
+        <is>
+          <t>Phasing in on KDE SEEK schedules: $82,866 FY2025, $55,515 FY2026, $276,246 FY2027. New restricted revenue, no board action required</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Bonds the new equalization alone supports</t>
+        </is>
+      </c>
+      <c r="B68" s="9">
+        <f>B67*(1-(1+B40)^-B41)/B40</f>
+        <v/>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>Additive to the FY2024 audit's bonding potential, which predates the equalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>SFCC offers of assistance, typical cycle</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t>State already pays $1,568,809 of current principal</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>FY2026 YEAR-END, DISTRICT'S OWN KDE BUDGET MONITORING TOOL (UNAUDITED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>June 2026 financial packet, board agenda July 16, 2026; MUNIS run July 15, 2026. Audit will finalize these figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>General Fund revenue, FY2026 actual (excludes carryforward and on-behalf)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>22103877</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>General Fund expenditures, FY2026 actual</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>22477866</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Net General Fund change, FY2026 (unaudited)</t>
+        </is>
+      </c>
+      <c r="B75" s="33">
+        <f>B73-B74</f>
+        <v/>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>Compare net changes of -$1,065,657 in FY2024 and -$1,225,465 in FY2025 (audited)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Revenues over budget per the monitoring tool</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>2225835</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Salaries under budget per the monitoring tool</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>587592</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Salaries below FY2025 actuals</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>223974</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Caveat 1: miscellaneous revenue (object 1990) budgeted at zero, received</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>1567829</v>
+      </c>
+      <c r="F79" s="21" t="inlineStr">
+        <is>
+          <t>Unbudgeted even in the final amended budget; the district should identify this receipt on the record</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which booked in June (period 12) alone</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>1413929</v>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t>Months 1-11 produced $153,900 combined, a normal run rate; the balance sheet shows no receivable behind the June entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Caveat 2: restricted capital money transferred INTO the General Fund in June 2026</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>1320939</v>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>Object 5210: $1,098,663 from the Building Fund (320) + $222,276 from Capital Outlay (310), which ended the year at $0 ($1,098,663 + $222,276 = $1,320,939 per the GF receipts ledger; the packet's fund 320 page records $1,098,633, a $30 internal discrepancy in the district's own packet). Lawful under budget-act capital funds flexibility. The Building Fund piece was budgeted from September 2025 ($1,120,203); the $222,276 Capital Outlay piece appears in no version of the FY2026 budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Net change excluding the capital transfer</t>
+        </is>
+      </c>
+      <c r="B82" s="9">
+        <f>B73-B74-B81</f>
+        <v/>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
+        <is>
+          <t>About -$1.69 million: the operating result on operating revenue alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Net change excluding the transfer and the unidentified June receipt</t>
+        </is>
+      </c>
+      <c r="B83" s="9">
+        <f>B73-B74-B81-B80</f>
+        <v/>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
+          <t>About -$3.11 million: the same range as the audited years</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>June 2026 General Fund revenue vs June 2025 (district's monitoring tool)</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>3923096</v>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>1130736</v>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t>The two June entries above are 98 percent of the year-over-year June difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Variance identity from the packet: projected fund balance reconciles to the dollar</t>
+        </is>
+      </c>
+      <c r="B85" s="9">
+        <f>1489853+2225835+587592-224087</f>
+        <v/>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>Contingency + revenue over budget + salary savings - expense overrun = $4,079,193, the tool's projected balance. The June misc entry is 63 percent of the revenue beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>BUILDING FUND FLOWS, FY2026 (fund 320, same packet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Building Fund transfers out, FY2026 total</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>2481394</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  to Debt Service (fund 400)</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>1382761</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  to the General Fund (June 2026)</t>
+        </is>
+      </c>
+      <c r="B89" s="9">
+        <f>B87-B88</f>
+        <v/>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>The residual after debt service. This is the restricted stream a $14 million bond would lean on; in FY2026 it plugged the operating budget instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Bond capacity that residual supports at the same rate and term</t>
+        </is>
+      </c>
+      <c r="B90" s="9">
+        <f>B89*(1-(1+B40)^-B41)/B40</f>
+        <v/>
+      </c>
+      <c r="F90" s="21" t="inlineStr">
+        <is>
+          <t>About $14 million: the plan's own target, carried by restricted money. The closure's role is only to replace the sweep, and any recurring million dollars does that</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>SCENARIO: BALANCE THE BUDGET AND EXPAND BONDING CAPACITY, NO CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Two cases differ only in the operating gap assumed. Conservative treats the FY2026 $1.57M receipt as one-time;</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>trend uses the unaudited FY2026 net change. The sweep is ended in both cases; only genuine remainder services debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>FY2026 trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Operating gap to close first</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="n">
+        <v>1787918</v>
+      </c>
+      <c r="C96" s="8" t="n">
+        <v>373989</v>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>Editable. $1.9M = FY2026 result excluding the unidentified receipt; $373,989 = FY2026 unaudited net change</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>New recurring revenue: 4 percent levy taken three years running (mechanics case; with the published 2018 restore instead, the gap clears in every case: Alternatives transformative check)</t>
+        </is>
+      </c>
+      <c r="B97" s="25">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
+      </c>
+      <c r="C97" s="25">
+        <f>Tax_History!B32*(1.04^3-1)</f>
+        <v/>
+      </c>
+      <c r="F97" s="21" t="inlineStr">
+        <is>
+          <t>Same base and compounding as the levy tab; year 1 is $313,162, year 3 cumulative $977,568</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Recurring cost reductions, not from closing a school</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C98" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F98" s="21" t="inlineStr">
+        <is>
+          <t>Editable. For scale from the FY2025 audit: district administration grew $221K in one year, salaries fell $224K through attrition, spending ran $859K under budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>End the capital-to-GF sweep (required before the building-fund residual can be pledged to new bonds)</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>1320939</v>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>1320939</v>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>The FY2026 sweep is General Fund revenue today; pledging the residual means replacing it. Without this row the restricted stream would be counted twice</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Operating room left for debt service after the budget balances and the sweep ends</t>
+        </is>
+      </c>
+      <c r="B100" s="9">
+        <f>MAX(0,B97+B98-B96-B99)</f>
+        <v/>
+      </c>
+      <c r="C100" s="9">
+        <f>MAX(0,C97+C98-C96-C99)</f>
+        <v/>
+      </c>
+      <c r="F100" s="21" t="inlineStr">
+        <is>
+          <t>Trend case balances with about $283K to spare; the conservative case is still about $1.24M short, so its total below leans on equalization and existing restricted capacity only</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>General-fund bond capacity from that room</t>
+        </is>
+      </c>
+      <c r="B101" s="9">
+        <f>B100*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C101" s="9">
+        <f>C100*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>New state equalization on the already-levied recallable nickel</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="C102" s="8" t="n">
+        <v>276246</v>
+      </c>
+      <c r="F102" s="21" t="inlineStr">
+        <is>
+          <t>FY2027 SEEK schedule; the recallable nickel itself is already levied and its local yield is already inside the building-fund stream above</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Bond capacity from the new equalization</t>
+        </is>
+      </c>
+      <c r="B103" s="9">
+        <f>B102*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+      <c r="C103" s="9">
+        <f>C102*(1-(1+B$40)^-B$41)/B$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Existing unused restricted capacity, approximate</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="C104" s="8" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
+        <is>
+          <t>FY2024 audit $23.5M less local share of the 2024 issue; fiscal agent's statement is the authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>Total capacity available without closing a school</t>
+        </is>
+      </c>
+      <c r="B105" s="27">
+        <f>B101+B103+B104</f>
+        <v/>
+      </c>
+      <c r="C105" s="27">
+        <f>C101+C103+C104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Roughly $22.2 million in the conservative case and $42.1 million on the FY2026 trend, with the budget balanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>first in both. The administration's plan reaches $32 million at face value and leaves the deficit in place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Floor check: even with zero general-fund room, the restricted capacity plus new equalization alone are about $21 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Pledging the building-fund residual to new bonds requires ending the capital-to-operations sweep documented above,</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>which is exactly what the administration's plan implies; the only question is which recurring million replaces it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -774,27 +2087,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Projected ending General Fund balance</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
@@ -875,19 +2188,19 @@
           <t>2% contingency floor (approx., FY2025 basis)</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="25">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="25">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="25">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="25">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
@@ -911,7 +2224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -942,27 +2255,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Recurring GF impact ($/yr, by yr 3)</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Projected FY2029 balance</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>One-time costs</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>What it requires and risks</t>
         </is>
@@ -1022,7 +2335,7 @@
           <t>3. Districtwide recovery plan (menu plus levy; includes rebalancing and growing NMES)</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="25">
         <f>Alternatives!B19</f>
         <v/>
       </c>
@@ -1053,7 +2366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1098,7 +2411,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="31" t="n">
         <v>61.3</v>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -1113,7 +2426,7 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="31" t="n">
         <v>60.6</v>
       </c>
     </row>
@@ -1123,7 +2436,7 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="31" t="n">
         <v>55.9</v>
       </c>
     </row>
@@ -1133,7 +2446,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="31" t="n">
         <v>54.2</v>
       </c>
     </row>
@@ -1143,7 +2456,7 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="31" t="n">
         <v>49.2</v>
       </c>
     </row>
@@ -1153,7 +2466,7 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="31" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1163,7 +2476,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="31" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1173,7 +2486,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="31" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1183,7 +2496,7 @@
           <t>Tangible/personal rate (recent)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="31" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -1193,7 +2506,7 @@
           <t>Motor vehicle rate</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="31" t="n">
         <v>54.7</v>
       </c>
     </row>
@@ -1220,7 +2533,7 @@
           <t>Fayette County</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="31" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -1235,7 +2548,7 @@
           <t>Paris Independent</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="31" t="n">
         <v>71.5</v>
       </c>
     </row>
@@ -1245,7 +2558,7 @@
           <t>Clark County</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="31" t="n">
         <v>65.5</v>
       </c>
     </row>
@@ -1255,7 +2568,7 @@
           <t>Bath County</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="31" t="n">
         <v>63.4</v>
       </c>
     </row>
@@ -1265,7 +2578,7 @@
           <t>Scott County</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="31" t="n">
         <v>62.9</v>
       </c>
     </row>
@@ -1275,7 +2588,7 @@
           <t>Harrison County</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="31" t="n">
         <v>57.7</v>
       </c>
     </row>
@@ -1285,7 +2598,7 @@
           <t>Montgomery County</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="31" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -1295,7 +2608,7 @@
           <t>Bourbon County</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="31" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -1305,7 +2618,7 @@
           <t>Nicholas County</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="31" t="n">
         <v>43.1</v>
       </c>
     </row>
@@ -1315,7 +2628,7 @@
           <t>Statewide school average (DOR Table II, 2025)</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="31" t="n">
         <v>65.13</v>
       </c>
     </row>
@@ -1409,7 +2722,7 @@
           <t>Local levy share of General Fund spending</t>
         </is>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="18">
         <f>B32/B38</f>
         <v/>
       </c>
@@ -1420,12 +2733,12 @@
           <t>DELINQUENCY CHECK (collections vs certified yield)</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1478,11 +2791,11 @@
           <t>Gap as share of yield</t>
         </is>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="18">
         <f>B44/B42</f>
         <v/>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="18">
         <f>C44/C42</f>
         <v/>
       </c>
@@ -1500,7 +2813,7 @@
           <t>Base: FY2025 General Fund real + personal collections</t>
         </is>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="25">
         <f>B32</f>
         <v/>
       </c>
@@ -1570,7 +2883,7 @@
           <t>As a share of the FY2025 structural deficit</t>
         </is>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="18">
         <f>B53/(Assumptions!B24-Assumptions!B21)</f>
         <v/>
       </c>
@@ -1583,82 +2896,82 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>District</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="24" t="inlineStr">
         <is>
           <t>2012-13</t>
         </is>
       </c>
-      <c r="C57" s="17" t="inlineStr">
+      <c r="C57" s="24" t="inlineStr">
         <is>
           <t>2013-14</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D57" s="24" t="inlineStr">
         <is>
           <t>2014-15</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>2015-16</t>
         </is>
       </c>
-      <c r="F57" s="17" t="inlineStr">
+      <c r="F57" s="24" t="inlineStr">
         <is>
           <t>2016-17</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
+      <c r="G57" s="24" t="inlineStr">
         <is>
           <t>2017-18</t>
         </is>
       </c>
-      <c r="H57" s="17" t="inlineStr">
+      <c r="H57" s="24" t="inlineStr">
         <is>
           <t>2018-19</t>
         </is>
       </c>
-      <c r="I57" s="17" t="inlineStr">
+      <c r="I57" s="24" t="inlineStr">
         <is>
           <t>2019-20</t>
         </is>
       </c>
-      <c r="J57" s="17" t="inlineStr">
+      <c r="J57" s="24" t="inlineStr">
         <is>
           <t>2020-21</t>
         </is>
       </c>
-      <c r="K57" s="17" t="inlineStr">
+      <c r="K57" s="24" t="inlineStr">
         <is>
           <t>2021-22</t>
         </is>
       </c>
-      <c r="L57" s="17" t="inlineStr">
+      <c r="L57" s="24" t="inlineStr">
         <is>
           <t>2022-23</t>
         </is>
       </c>
-      <c r="M57" s="17" t="inlineStr">
+      <c r="M57" s="24" t="inlineStr">
         <is>
           <t>2023-24</t>
         </is>
       </c>
-      <c r="N57" s="17" t="inlineStr">
+      <c r="N57" s="24" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="O57" s="17" t="inlineStr">
+      <c r="O57" s="24" t="inlineStr">
         <is>
           <t>2025-26</t>
         </is>
       </c>
-      <c r="P57" s="17" t="inlineStr">
+      <c r="P57" s="24" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
@@ -1670,49 +2983,49 @@
           <t>Bath</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n">
+      <c r="B58" s="31" t="n">
         <v>36.8</v>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="31" t="n">
         <v>44.2</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="31" t="n">
         <v>44.8</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="31" t="n">
         <v>44.8</v>
       </c>
-      <c r="G58" s="29" t="n">
+      <c r="G58" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="H58" s="29" t="n">
+      <c r="H58" s="31" t="n">
         <v>52.6</v>
       </c>
-      <c r="I58" s="29" t="n">
+      <c r="I58" s="31" t="n">
         <v>52.6</v>
       </c>
-      <c r="J58" s="29" t="n">
+      <c r="J58" s="31" t="n">
         <v>52.6</v>
       </c>
-      <c r="K58" s="29" t="n">
+      <c r="K58" s="31" t="n">
         <v>52.4</v>
       </c>
-      <c r="L58" s="29" t="n">
+      <c r="L58" s="31" t="n">
         <v>54.1</v>
       </c>
-      <c r="M58" s="29" t="n">
+      <c r="M58" s="31" t="n">
         <v>57.8</v>
       </c>
-      <c r="N58" s="29" t="n">
+      <c r="N58" s="31" t="n">
         <v>60.7</v>
       </c>
-      <c r="O58" s="29" t="n">
+      <c r="O58" s="31" t="n">
         <v>63.4</v>
       </c>
-      <c r="P58" s="33">
+      <c r="P58" s="35">
         <f>(O58/B58-1)</f>
         <v/>
       </c>
@@ -1723,49 +3036,49 @@
           <t>Scott</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n">
+      <c r="B59" s="31" t="n">
         <v>45.3</v>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="31" t="n">
         <v>47.6</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="31" t="n">
         <v>49.6</v>
       </c>
-      <c r="G59" s="29" t="n">
+      <c r="G59" s="31" t="n">
         <v>56.4</v>
       </c>
-      <c r="H59" s="29" t="n">
+      <c r="H59" s="31" t="n">
         <v>56.4</v>
       </c>
-      <c r="I59" s="29" t="n">
+      <c r="I59" s="31" t="n">
         <v>57.1</v>
       </c>
-      <c r="J59" s="29" t="n">
+      <c r="J59" s="31" t="n">
         <v>57.6</v>
       </c>
-      <c r="K59" s="29" t="n">
+      <c r="K59" s="31" t="n">
         <v>58.1</v>
       </c>
-      <c r="L59" s="29" t="n">
+      <c r="L59" s="31" t="n">
         <v>58.1</v>
       </c>
-      <c r="M59" s="29" t="n">
+      <c r="M59" s="31" t="n">
         <v>62.8</v>
       </c>
-      <c r="N59" s="29" t="n">
+      <c r="N59" s="31" t="n">
         <v>62.9</v>
       </c>
-      <c r="O59" s="29" t="n">
+      <c r="O59" s="31" t="n">
         <v>62.9</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="35">
         <f>(O59/B59-1)</f>
         <v/>
       </c>
@@ -1776,49 +3089,49 @@
           <t>Harrison</t>
         </is>
       </c>
-      <c r="B60" s="29" t="n">
+      <c r="B60" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="31" t="n">
         <v>45.2</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="31" t="n">
         <v>47.3</v>
       </c>
-      <c r="F60" s="29" t="n">
+      <c r="F60" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="G60" s="29" t="n">
+      <c r="G60" s="31" t="n">
         <v>50.5</v>
       </c>
-      <c r="H60" s="29" t="n">
+      <c r="H60" s="31" t="n">
         <v>50.5</v>
       </c>
-      <c r="I60" s="29" t="n">
+      <c r="I60" s="31" t="n">
         <v>51.7</v>
       </c>
-      <c r="J60" s="29" t="n">
+      <c r="J60" s="31" t="n">
         <v>51.7</v>
       </c>
-      <c r="K60" s="29" t="n">
+      <c r="K60" s="31" t="n">
         <v>57.7</v>
       </c>
-      <c r="L60" s="29" t="n">
+      <c r="L60" s="31" t="n">
         <v>57.7</v>
       </c>
-      <c r="M60" s="29" t="n">
+      <c r="M60" s="31" t="n">
         <v>57.7</v>
       </c>
-      <c r="N60" s="29" t="n">
+      <c r="N60" s="31" t="n">
         <v>57.7</v>
       </c>
-      <c r="O60" s="29" t="n">
+      <c r="O60" s="31" t="n">
         <v>57.7</v>
       </c>
-      <c r="P60" s="33">
+      <c r="P60" s="35">
         <f>(O60/B60-1)</f>
         <v/>
       </c>
@@ -1829,49 +3142,49 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="B61" s="29" t="n">
+      <c r="B61" s="31" t="n">
         <v>53.6</v>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="31" t="n">
         <v>55.9</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="31" t="n">
         <v>57.4</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="F61" s="29" t="n">
+      <c r="F61" s="31" t="n">
         <v>62.2</v>
       </c>
-      <c r="G61" s="29" t="n">
+      <c r="G61" s="31" t="n">
         <v>62.2</v>
       </c>
-      <c r="H61" s="29" t="n">
+      <c r="H61" s="31" t="n">
         <v>62.2</v>
       </c>
-      <c r="I61" s="29" t="n">
+      <c r="I61" s="31" t="n">
         <v>63.7</v>
       </c>
-      <c r="J61" s="29" t="n">
+      <c r="J61" s="31" t="n">
         <v>63.7</v>
       </c>
-      <c r="K61" s="29" t="n">
+      <c r="K61" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="L61" s="29" t="n">
+      <c r="L61" s="31" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="M61" s="29" t="n">
+      <c r="M61" s="31" t="n">
         <v>67.5</v>
       </c>
-      <c r="N61" s="29" t="n">
+      <c r="N61" s="31" t="n">
         <v>66.8</v>
       </c>
-      <c r="O61" s="29" t="n">
+      <c r="O61" s="31" t="n">
         <v>65.5</v>
       </c>
-      <c r="P61" s="33">
+      <c r="P61" s="35">
         <f>(O61/B61-1)</f>
         <v/>
       </c>
@@ -1882,49 +3195,49 @@
           <t>Fayette</t>
         </is>
       </c>
-      <c r="B62" s="29" t="n">
+      <c r="B62" s="31" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="31" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="31" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="31" t="n">
         <v>74</v>
       </c>
-      <c r="F62" s="29" t="n">
+      <c r="F62" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="G62" s="29" t="n">
+      <c r="G62" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="H62" s="29" t="n">
+      <c r="H62" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="I62" s="29" t="n">
+      <c r="I62" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="J62" s="29" t="n">
+      <c r="J62" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="K62" s="29" t="n">
+      <c r="K62" s="31" t="n">
         <v>80.8</v>
       </c>
-      <c r="L62" s="29" t="n">
+      <c r="L62" s="31" t="n">
         <v>83.3</v>
       </c>
-      <c r="M62" s="29" t="n">
+      <c r="M62" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="N62" s="29" t="n">
+      <c r="N62" s="31" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="O62" s="29" t="n">
+      <c r="O62" s="31" t="n">
         <v>79.8</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="35">
         <f>(O62/B62-1)</f>
         <v/>
       </c>
@@ -1935,49 +3248,49 @@
           <t>Paris Ind</t>
         </is>
       </c>
-      <c r="B63" s="29" t="n">
+      <c r="B63" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="31" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D63" s="31" t="n">
         <v>66.5</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="31" t="n">
         <v>69</v>
       </c>
-      <c r="F63" s="29" t="n">
+      <c r="F63" s="31" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="G63" s="29" t="n">
+      <c r="G63" s="31" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="H63" s="29" t="n">
+      <c r="H63" s="31" t="n">
         <v>78.3</v>
       </c>
-      <c r="I63" s="29" t="n">
+      <c r="I63" s="31" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="J63" s="29" t="n">
+      <c r="J63" s="31" t="n">
         <v>68.7</v>
       </c>
-      <c r="K63" s="29" t="n">
+      <c r="K63" s="31" t="n">
         <v>74.5</v>
       </c>
-      <c r="L63" s="29" t="n">
+      <c r="L63" s="31" t="n">
         <v>71.5</v>
       </c>
-      <c r="M63" s="29" t="n">
+      <c r="M63" s="31" t="n">
         <v>71.5</v>
       </c>
-      <c r="N63" s="29" t="n">
+      <c r="N63" s="31" t="n">
         <v>71.5</v>
       </c>
-      <c r="O63" s="29" t="n">
+      <c r="O63" s="31" t="n">
         <v>71.5</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="35">
         <f>(O63/B63-1)</f>
         <v/>
       </c>
@@ -1988,49 +3301,49 @@
           <t>Nicholas</t>
         </is>
       </c>
-      <c r="B64" s="29" t="n">
+      <c r="B64" s="31" t="n">
         <v>38.4</v>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="31" t="n">
         <v>38.7</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="31" t="n">
         <v>38.5</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="31" t="n">
         <v>38.3</v>
       </c>
-      <c r="F64" s="29" t="n">
+      <c r="F64" s="31" t="n">
         <v>38.5</v>
       </c>
-      <c r="G64" s="29" t="n">
+      <c r="G64" s="31" t="n">
         <v>39.5</v>
       </c>
-      <c r="H64" s="29" t="n">
+      <c r="H64" s="31" t="n">
         <v>39.6</v>
       </c>
-      <c r="I64" s="29" t="n">
+      <c r="I64" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="J64" s="29" t="n">
+      <c r="J64" s="31" t="n">
         <v>40.1</v>
       </c>
-      <c r="K64" s="29" t="n">
+      <c r="K64" s="31" t="n">
         <v>40.2</v>
       </c>
-      <c r="L64" s="29" t="n">
+      <c r="L64" s="31" t="n">
         <v>41.4</v>
       </c>
-      <c r="M64" s="29" t="n">
+      <c r="M64" s="31" t="n">
         <v>42.5</v>
       </c>
-      <c r="N64" s="29" t="n">
+      <c r="N64" s="31" t="n">
         <v>43.6</v>
       </c>
-      <c r="O64" s="29" t="n">
+      <c r="O64" s="31" t="n">
         <v>43.1</v>
       </c>
-      <c r="P64" s="33">
+      <c r="P64" s="35">
         <f>(O64/B64-1)</f>
         <v/>
       </c>
@@ -2041,49 +3354,49 @@
           <t>Montgomery</t>
         </is>
       </c>
-      <c r="B65" s="29" t="n">
+      <c r="B65" s="31" t="n">
         <v>49.4</v>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="31" t="n">
         <v>49.4</v>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D65" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="31" t="n">
         <v>48.9</v>
       </c>
-      <c r="F65" s="29" t="n">
+      <c r="F65" s="31" t="n">
         <v>50.8</v>
       </c>
-      <c r="G65" s="29" t="n">
+      <c r="G65" s="31" t="n">
         <v>51.3</v>
       </c>
-      <c r="H65" s="29" t="n">
+      <c r="H65" s="31" t="n">
         <v>52.8</v>
       </c>
-      <c r="I65" s="29" t="n">
+      <c r="I65" s="31" t="n">
         <v>52.3</v>
       </c>
-      <c r="J65" s="29" t="n">
+      <c r="J65" s="31" t="n">
         <v>52.3</v>
       </c>
-      <c r="K65" s="29" t="n">
+      <c r="K65" s="31" t="n">
         <v>52.3</v>
       </c>
-      <c r="L65" s="29" t="n">
+      <c r="L65" s="31" t="n">
         <v>52.2</v>
       </c>
-      <c r="M65" s="29" t="n">
+      <c r="M65" s="31" t="n">
         <v>52.4</v>
       </c>
-      <c r="N65" s="29" t="n">
+      <c r="N65" s="31" t="n">
         <v>52.5</v>
       </c>
-      <c r="O65" s="29" t="n">
+      <c r="O65" s="31" t="n">
         <v>52.5</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="35">
         <f>(O65/B65-1)</f>
         <v/>
       </c>
@@ -2094,49 +3407,49 @@
           <t>Bourbon Co</t>
         </is>
       </c>
-      <c r="B66" s="29" t="n">
+      <c r="B66" s="31" t="n">
         <v>55.4</v>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="31" t="n">
         <v>57.6</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="31" t="n">
         <v>57.3</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="31" t="n">
         <v>59.1</v>
       </c>
-      <c r="F66" s="29" t="n">
+      <c r="F66" s="31" t="n">
         <v>58.8</v>
       </c>
-      <c r="G66" s="29" t="n">
+      <c r="G66" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="H66" s="29" t="n">
+      <c r="H66" s="31" t="n">
         <v>61.3</v>
       </c>
-      <c r="I66" s="29" t="n">
+      <c r="I66" s="31" t="n">
         <v>60.6</v>
       </c>
-      <c r="J66" s="29" t="n">
+      <c r="J66" s="31" t="n">
         <v>55.9</v>
       </c>
-      <c r="K66" s="29" t="n">
+      <c r="K66" s="31" t="n">
         <v>54.2</v>
       </c>
-      <c r="L66" s="29" t="n">
+      <c r="L66" s="31" t="n">
         <v>49.2</v>
       </c>
-      <c r="M66" s="29" t="n">
+      <c r="M66" s="31" t="n">
         <v>52.4</v>
       </c>
-      <c r="N66" s="29" t="n">
+      <c r="N66" s="31" t="n">
         <v>52.4</v>
       </c>
-      <c r="O66" s="29" t="n">
+      <c r="O66" s="31" t="n">
         <v>52.4</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="35">
         <f>(O66/B66-1)</f>
         <v/>
       </c>
@@ -2161,7 +3474,7 @@
           <t>General Fund share of the levied 52.4 cents (KDE levied-rates file: 41.0 GF + 5.7 FSPK + 5.7 recallable)</t>
         </is>
       </c>
-      <c r="B71" s="29" t="n">
+      <c r="B71" s="31" t="n">
         <v>41</v>
       </c>
     </row>
@@ -2197,7 +3510,7 @@
           <t>Cost per added cent to that household, per year</t>
         </is>
       </c>
-      <c r="B74" s="34">
+      <c r="B74" s="36">
         <f>B73*0.01/100</f>
         <v/>
       </c>
@@ -2208,32 +3521,32 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
+      <c r="B76" s="24" t="inlineStr">
         <is>
           <t>New rate</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C76" s="24" t="inlineStr">
         <is>
           <t>Added cents</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" s="24" t="inlineStr">
         <is>
           <t>Revenue per year</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr">
+      <c r="E76" s="24" t="inlineStr">
         <is>
           <t>Median-home cost/yr</t>
         </is>
       </c>
-      <c r="F76" s="17" t="inlineStr">
+      <c r="F76" s="24" t="inlineStr">
         <is>
           <t>Direct bond capacity</t>
         </is>
@@ -2245,11 +3558,11 @@
           <t>Match Harrison County (2025-26 levied rate)</t>
         </is>
       </c>
-      <c r="B77" s="20">
+      <c r="B77" s="26">
         <f>B24</f>
         <v/>
       </c>
-      <c r="C77" s="35">
+      <c r="C77" s="37">
         <f>B77-B12</f>
         <v/>
       </c>
@@ -2277,11 +3590,11 @@
           <t>Match the regional median (eight area districts, Fayette excluded)</t>
         </is>
       </c>
-      <c r="B78" s="20">
+      <c r="B78" s="26">
         <f>MEDIAN(O58,O59,O60,O61,O63,O64,O65,O66)</f>
         <v/>
       </c>
-      <c r="C78" s="35">
+      <c r="C78" s="37">
         <f>B78-B12</f>
         <v/>
       </c>
@@ -2304,11 +3617,11 @@
           <t>Restore Bourbon's own 2018 rate</t>
         </is>
       </c>
-      <c r="B79" s="20">
+      <c r="B79" s="26">
         <f>B5</f>
         <v/>
       </c>
-      <c r="C79" s="35">
+      <c r="C79" s="37">
         <f>B79-B12</f>
         <v/>
       </c>
@@ -2331,11 +3644,11 @@
           <t>Match Clark County (2025-26 levied rate)</t>
         </is>
       </c>
-      <c r="B80" s="20">
+      <c r="B80" s="26">
         <f>O61</f>
         <v/>
       </c>
-      <c r="C80" s="35">
+      <c r="C80" s="37">
         <f>B80-B12</f>
         <v/>
       </c>
@@ -2392,7 +3705,7 @@
           <t>Margin after the gap is closed and the sweep ended</t>
         </is>
       </c>
-      <c r="B85" s="23">
+      <c r="B85" s="19">
         <f>B84-B83</f>
         <v/>
       </c>
@@ -2441,7 +3754,7 @@
           <t>Construction capacity unlocked without pledging a cent of the new levy</t>
         </is>
       </c>
-      <c r="B89" s="23">
+      <c r="B89" s="19">
         <f>B86+B87+B88</f>
         <v/>
       </c>
@@ -2481,7 +3794,7 @@
           <t>General Fund rate levied, cents per $100</t>
         </is>
       </c>
-      <c r="B95" s="30">
+      <c r="B95" s="32">
         <f>B71</f>
         <v/>
       </c>
@@ -2503,55 +3816,55 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="17" t="inlineStr">
+      <c r="A98" s="24" t="inlineStr">
         <is>
           <t>Assessment growth</t>
         </is>
       </c>
-      <c r="B98" s="17" t="inlineStr">
+      <c r="B98" s="24" t="inlineStr">
         <is>
           <t>Compensating rate</t>
         </is>
       </c>
-      <c r="C98" s="17" t="inlineStr">
+      <c r="C98" s="24" t="inlineStr">
         <is>
           <t>4 percent option</t>
         </is>
       </c>
-      <c r="D98" s="17" t="inlineStr">
+      <c r="D98" s="24" t="inlineStr">
         <is>
           <t>Rate raised 4 percent</t>
         </is>
       </c>
-      <c r="E98" s="17" t="inlineStr">
+      <c r="E98" s="24" t="inlineStr">
         <is>
           <t>Revenue at 4 percent option</t>
         </is>
       </c>
-      <c r="F98" s="17" t="inlineStr">
+      <c r="F98" s="24" t="inlineStr">
         <is>
           <t>Revenue at rate x 1.04</t>
         </is>
       </c>
-      <c r="G98" s="17" t="inlineStr">
+      <c r="G98" s="24" t="inlineStr">
         <is>
           <t>Above the ceiling, recallable</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="36" t="n">
+      <c r="A99" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="B99" s="30">
+      <c r="B99" s="32">
         <f>$B$95/(1+A99)</f>
         <v/>
       </c>
-      <c r="C99" s="30">
+      <c r="C99" s="32">
         <f>B99*1.04</f>
         <v/>
       </c>
-      <c r="D99" s="30">
+      <c r="D99" s="32">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -2563,24 +3876,24 @@
         <f>$B$94*(1+A99)*D99/100/100</f>
         <v/>
       </c>
-      <c r="G99" s="23">
+      <c r="G99" s="19">
         <f>F99-E99</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="36" t="n">
+      <c r="A100" s="38" t="n">
         <v>0.03</v>
       </c>
-      <c r="B100" s="30">
+      <c r="B100" s="32">
         <f>$B$95/(1+A100)</f>
         <v/>
       </c>
-      <c r="C100" s="30">
+      <c r="C100" s="32">
         <f>B100*1.04</f>
         <v/>
       </c>
-      <c r="D100" s="30">
+      <c r="D100" s="32">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -2592,24 +3905,24 @@
         <f>$B$94*(1+A100)*D100/100/100</f>
         <v/>
       </c>
-      <c r="G100" s="23">
+      <c r="G100" s="19">
         <f>F100-E100</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="36" t="n">
+      <c r="A101" s="38" t="n">
         <v>0.05</v>
       </c>
-      <c r="B101" s="30">
+      <c r="B101" s="32">
         <f>$B$95/(1+A101)</f>
         <v/>
       </c>
-      <c r="C101" s="30">
+      <c r="C101" s="32">
         <f>B101*1.04</f>
         <v/>
       </c>
-      <c r="D101" s="30">
+      <c r="D101" s="32">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -2621,24 +3934,24 @@
         <f>$B$94*(1+A101)*D101/100/100</f>
         <v/>
       </c>
-      <c r="G101" s="23">
+      <c r="G101" s="19">
         <f>F101-E101</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="36" t="n">
+      <c r="A102" s="38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B102" s="30">
+      <c r="B102" s="32">
         <f>$B$95/(1+A102)</f>
         <v/>
       </c>
-      <c r="C102" s="30">
+      <c r="C102" s="32">
         <f>B102*1.04</f>
         <v/>
       </c>
-      <c r="D102" s="30">
+      <c r="D102" s="32">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -2650,7 +3963,7 @@
         <f>$B$94*(1+A102)*D102/100/100</f>
         <v/>
       </c>
-      <c r="G102" s="23">
+      <c r="G102" s="19">
         <f>F102-E102</f>
         <v/>
       </c>
@@ -2682,7 +3995,7 @@
           <t>Total levied rate, tax year 2022</t>
         </is>
       </c>
-      <c r="B109" s="29" t="n">
+      <c r="B109" s="31" t="n">
         <v>49.2</v>
       </c>
     </row>
@@ -2692,7 +4005,7 @@
           <t>Total levied rate, tax year 2023 (held at 52.4 for three years since)</t>
         </is>
       </c>
-      <c r="B110" s="29" t="n">
+      <c r="B110" s="31" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -2702,7 +4015,7 @@
           <t>Net change</t>
         </is>
       </c>
-      <c r="B111" s="35">
+      <c r="B111" s="37">
         <f>B110-B109</f>
         <v/>
       </c>
@@ -2713,7 +4026,7 @@
           <t>Recallable facilities nickel levied 8/17/2023 (KDE levied-rates file, current year)</t>
         </is>
       </c>
-      <c r="B112" s="29" t="n">
+      <c r="B112" s="31" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -2723,7 +4036,7 @@
           <t>Implied change in the rest of the rate</t>
         </is>
       </c>
-      <c r="B113" s="37">
+      <c r="B113" s="39">
         <f>B111-B112</f>
         <v/>
       </c>
@@ -2734,7 +4047,7 @@
           <t>Implied annual change in unrestricted revenue</t>
         </is>
       </c>
-      <c r="B114" s="23">
+      <c r="B114" s="19">
         <f>B113*B72</f>
         <v/>
       </c>
@@ -2749,7 +4062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2893,7 +4206,7 @@
           <t>Change as a share of 1970</t>
         </is>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <f>B13/B5</f>
         <v/>
       </c>
@@ -3089,7 +4402,7 @@
         <f>MAX(F33:F51,I33:I50)</f>
         <v/>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>1989</t>
         </is>
@@ -3097,7 +4410,7 @@
       <c r="F33" s="10" t="n">
         <v>261</v>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
@@ -3121,7 +4434,7 @@
         <f>I50</f>
         <v/>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
@@ -3129,7 +4442,7 @@
       <c r="F34" s="10" t="n">
         <v>255</v>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
@@ -3148,7 +4461,7 @@
         <f>B33-B34</f>
         <v/>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
@@ -3156,7 +4469,7 @@
       <c r="F35" s="10" t="n">
         <v>234</v>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
@@ -3171,11 +4484,11 @@
           <t>Decline as a share of peak</t>
         </is>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="18">
         <f>B35/B33</f>
         <v/>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>1992</t>
         </is>
@@ -3183,7 +4496,7 @@
       <c r="F36" s="10" t="n">
         <v>225</v>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
@@ -3198,11 +4511,11 @@
           <t>Current rated capacity</t>
         </is>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="28">
         <f>Assumptions!B12</f>
         <v/>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>1993</t>
         </is>
@@ -3210,7 +4523,7 @@
       <c r="F37" s="10" t="n">
         <v>202</v>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
@@ -3220,7 +4533,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
@@ -3228,7 +4541,7 @@
       <c r="F38" s="10" t="n">
         <v>203</v>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
@@ -3238,7 +4551,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
@@ -3246,7 +4559,7 @@
       <c r="F39" s="10" t="n">
         <v>182</v>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
@@ -3256,7 +4569,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
@@ -3264,7 +4577,7 @@
       <c r="F40" s="10" t="n">
         <v>196</v>
       </c>
-      <c r="H40" s="22" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
@@ -3274,7 +4587,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
@@ -3282,7 +4595,7 @@
       <c r="F41" s="10" t="n">
         <v>208</v>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
@@ -3292,7 +4605,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>1998</t>
         </is>
@@ -3300,7 +4613,7 @@
       <c r="F42" s="10" t="n">
         <v>198</v>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
@@ -3310,7 +4623,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="E43" s="22" t="inlineStr">
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
@@ -3318,7 +4631,7 @@
       <c r="F43" s="10" t="n">
         <v>205</v>
       </c>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
@@ -3328,7 +4641,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
@@ -3336,7 +4649,7 @@
       <c r="F44" s="10" t="n">
         <v>195</v>
       </c>
-      <c r="H44" s="22" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
@@ -3346,7 +4659,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="E45" s="22" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
@@ -3354,7 +4667,7 @@
       <c r="F45" s="10" t="n">
         <v>195</v>
       </c>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
@@ -3364,7 +4677,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
@@ -3372,7 +4685,7 @@
       <c r="F46" s="10" t="n">
         <v>203</v>
       </c>
-      <c r="H46" s="22" t="inlineStr">
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -3382,7 +4695,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="E47" s="22" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
@@ -3390,7 +4703,7 @@
       <c r="F47" s="10" t="n">
         <v>196</v>
       </c>
-      <c r="H47" s="22" t="inlineStr">
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -3400,7 +4713,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="E48" s="22" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
@@ -3408,7 +4721,7 @@
       <c r="F48" s="10" t="n">
         <v>206</v>
       </c>
-      <c r="H48" s="22" t="inlineStr">
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3418,7 +4731,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="E49" s="22" t="inlineStr">
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
@@ -3426,7 +4739,7 @@
       <c r="F49" s="10" t="n">
         <v>204</v>
       </c>
-      <c r="H49" s="22" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -3436,7 +4749,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
@@ -3444,7 +4757,7 @@
       <c r="F50" s="10" t="n">
         <v>199</v>
       </c>
-      <c r="H50" s="22" t="inlineStr">
+      <c r="H50" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3454,7 +4767,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="E51" s="22" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
@@ -3482,7 +4795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3535,57 +4848,57 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>School year</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>'15-16</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>'16-17</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>'17-18</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>'18-19</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>'19-20</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>'20-21</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>'21-22</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>'22-23</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>'23-24</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>'24-25</t>
         </is>
@@ -3669,97 +4982,97 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>School (district)</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="L14" s="22" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="N14" s="22" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="O14" s="22" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="P14" s="22" t="inlineStr">
+      <c r="P14" s="20" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="Q14" s="22" t="inlineStr">
+      <c r="Q14" s="20" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="R14" s="22" t="inlineStr">
+      <c r="R14" s="20" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="S14" s="22" t="inlineStr">
+      <c r="S14" s="20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3776,55 +5089,55 @@
           <t>North Middletown (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="31" t="n">
         <v>56.5</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="31" t="n">
         <v>63.9</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="31" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="31" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="31" t="n">
         <v>85.8</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G15" s="31" t="n">
         <v>72.5</v>
       </c>
-      <c r="H15" s="29" t="n">
+      <c r="H15" s="31" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I15" s="29" t="n">
+      <c r="I15" s="31" t="n">
         <v>56.6</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="31" t="n">
         <v>56.9</v>
       </c>
-      <c r="K15" s="29" t="n">
+      <c r="K15" s="31" t="n">
         <v>48.7</v>
       </c>
-      <c r="L15" s="29" t="n">
+      <c r="L15" s="31" t="n">
         <v>49.3</v>
       </c>
-      <c r="M15" s="29" t="n">
+      <c r="M15" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="N15" s="29" t="n">
+      <c r="N15" s="31" t="n">
         <v>50.4</v>
       </c>
-      <c r="P15" s="29" t="n">
+      <c r="P15" s="31" t="n">
         <v>47.7</v>
       </c>
-      <c r="Q15" s="29" t="n">
+      <c r="Q15" s="31" t="n">
         <v>32.1</v>
       </c>
-      <c r="R15" s="29" t="n">
+      <c r="R15" s="31" t="n">
         <v>54.1</v>
       </c>
-      <c r="S15" s="29" t="n">
+      <c r="S15" s="31" t="n">
         <v>58.2</v>
       </c>
     </row>
@@ -3834,58 +5147,58 @@
           <t>Bourbon Central (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="31" t="n">
         <v>77.5</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="31" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="31" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="31" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="31" t="n">
         <v>74.7</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H16" s="31" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I16" s="29" t="n">
+      <c r="I16" s="31" t="n">
         <v>51.8</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="31" t="n">
         <v>52.1</v>
       </c>
-      <c r="K16" s="29" t="n">
+      <c r="K16" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="L16" s="29" t="n">
+      <c r="L16" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="M16" s="29" t="n">
+      <c r="M16" s="31" t="n">
         <v>32.8</v>
       </c>
-      <c r="N16" s="29" t="n">
+      <c r="N16" s="31" t="n">
         <v>39.9</v>
       </c>
-      <c r="O16" s="29" t="n">
+      <c r="O16" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="P16" s="29" t="n">
+      <c r="P16" s="31" t="n">
         <v>29.9</v>
       </c>
-      <c r="Q16" s="29" t="n">
+      <c r="Q16" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="R16" s="29" t="n">
+      <c r="R16" s="31" t="n">
         <v>23.8</v>
       </c>
-      <c r="S16" s="29" t="n">
+      <c r="S16" s="31" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -3895,58 +5208,58 @@
           <t>Cane Ridge (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="31" t="n">
         <v>35.2</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="31" t="n">
         <v>50.9</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="31" t="n">
         <v>56.2</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="31" t="n">
         <v>65.5</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="31" t="n">
         <v>34.5</v>
       </c>
-      <c r="G17" s="29" t="n">
+      <c r="G17" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="H17" s="29" t="n">
+      <c r="H17" s="31" t="n">
         <v>49.6</v>
       </c>
-      <c r="I17" s="29" t="n">
+      <c r="I17" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="J17" s="31" t="n">
         <v>51.1</v>
       </c>
-      <c r="K17" s="29" t="n">
+      <c r="K17" s="31" t="n">
         <v>57.5</v>
       </c>
-      <c r="L17" s="29" t="n">
+      <c r="L17" s="31" t="n">
         <v>50.4</v>
       </c>
-      <c r="M17" s="29" t="n">
+      <c r="M17" s="31" t="n">
         <v>41.4</v>
       </c>
-      <c r="N17" s="29" t="n">
+      <c r="N17" s="31" t="n">
         <v>38.8</v>
       </c>
-      <c r="O17" s="29" t="n">
+      <c r="O17" s="31" t="n">
         <v>23.8</v>
       </c>
-      <c r="P17" s="29" t="n">
+      <c r="P17" s="31" t="n">
         <v>38.7</v>
       </c>
-      <c r="Q17" s="29" t="n">
+      <c r="Q17" s="31" t="n">
         <v>34.6</v>
       </c>
-      <c r="R17" s="29" t="n">
+      <c r="R17" s="31" t="n">
         <v>35.8</v>
       </c>
-      <c r="S17" s="29" t="n">
+      <c r="S17" s="31" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -3956,10 +5269,10 @@
           <t>Paris Elementary (Paris Indep.)</t>
         </is>
       </c>
-      <c r="R18" s="29" t="n">
+      <c r="R18" s="31" t="n">
         <v>16.8</v>
       </c>
-      <c r="S18" s="29" t="n">
+      <c r="S18" s="31" t="n">
         <v>12.2</v>
       </c>
     </row>
@@ -3969,10 +5282,10 @@
           <t>Shearer (Clark Co.)</t>
         </is>
       </c>
-      <c r="R19" s="29" t="n">
+      <c r="R19" s="31" t="n">
         <v>30.7</v>
       </c>
-      <c r="S19" s="29" t="n">
+      <c r="S19" s="31" t="n">
         <v>42.3</v>
       </c>
     </row>
@@ -3982,10 +5295,10 @@
           <t>Justice (Clark Co.)</t>
         </is>
       </c>
-      <c r="R20" s="29" t="n">
+      <c r="R20" s="31" t="n">
         <v>43.2</v>
       </c>
-      <c r="S20" s="29" t="n">
+      <c r="S20" s="31" t="n">
         <v>39.3</v>
       </c>
     </row>
@@ -3995,10 +5308,10 @@
           <t>Strode Station (Clark Co.)</t>
         </is>
       </c>
-      <c r="R21" s="29" t="n">
+      <c r="R21" s="31" t="n">
         <v>43.2</v>
       </c>
-      <c r="S21" s="29" t="n">
+      <c r="S21" s="31" t="n">
         <v>34.2</v>
       </c>
     </row>
@@ -4008,10 +5321,10 @@
           <t>Conkwright (Clark Co.)</t>
         </is>
       </c>
-      <c r="R22" s="29" t="n">
+      <c r="R22" s="31" t="n">
         <v>15.6</v>
       </c>
-      <c r="S22" s="29" t="n">
+      <c r="S22" s="31" t="n">
         <v>17.5</v>
       </c>
     </row>
@@ -4021,10 +5334,10 @@
           <t>Northview (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R23" s="29" t="n">
+      <c r="R23" s="31" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="S23" s="29" t="n">
+      <c r="S23" s="31" t="n">
         <v>68.90000000000001</v>
       </c>
     </row>
@@ -4034,10 +5347,10 @@
           <t>Mapleton (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R24" s="29" t="n">
+      <c r="R24" s="31" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="S24" s="29" t="n">
+      <c r="S24" s="31" t="n">
         <v>65.09999999999999</v>
       </c>
     </row>
@@ -4047,7 +5360,7 @@
           <t>Nicholas County Elementary (Nicholas Co.)</t>
         </is>
       </c>
-      <c r="R25" s="29" t="n">
+      <c r="R25" s="31" t="n">
         <v>15.9</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -4062,15 +5375,15 @@
           <t>Three-year average, 2023-2025: NMES / Bourbon Central / Cane Ridge</t>
         </is>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="26">
         <f>AVERAGE(Q15:S15)</f>
         <v/>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="26">
         <f>AVERAGE(Q16:S16)</f>
         <v/>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="26">
         <f>AVERAGE(Q17:S17)</f>
         <v/>
       </c>
@@ -4083,12 +5396,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>Kentucky</t>
         </is>
@@ -4152,32 +5465,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>Bourbon Central</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>Cane Ridge</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>Paris Elem.</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>KY elementary avg</t>
         </is>
@@ -4312,72 +5625,72 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Percent proficient or distinguished</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>'11-12</t>
         </is>
       </c>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>'12-13</t>
         </is>
       </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>'13-14</t>
         </is>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t>'14-15</t>
         </is>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F44" s="20" t="inlineStr">
         <is>
           <t>'15-16</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>'16-17</t>
         </is>
       </c>
-      <c r="H44" s="22" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
         <is>
           <t>'17-18</t>
         </is>
       </c>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="I44" s="20" t="inlineStr">
         <is>
           <t>'18-19</t>
         </is>
       </c>
-      <c r="J44" s="22" t="inlineStr">
+      <c r="J44" s="20" t="inlineStr">
         <is>
           <t>'20-21</t>
         </is>
       </c>
-      <c r="K44" s="22" t="inlineStr">
+      <c r="K44" s="20" t="inlineStr">
         <is>
           <t>'21-22</t>
         </is>
       </c>
-      <c r="L44" s="22" t="inlineStr">
+      <c r="L44" s="20" t="inlineStr">
         <is>
           <t>'22-23</t>
         </is>
       </c>
-      <c r="M44" s="22" t="inlineStr">
+      <c r="M44" s="20" t="inlineStr">
         <is>
           <t>'23-24</t>
         </is>
       </c>
-      <c r="N44" s="22" t="inlineStr">
+      <c r="N44" s="20" t="inlineStr">
         <is>
           <t>'24-25</t>
         </is>
@@ -4394,43 +5707,43 @@
           <t>Reading: North Middletown</t>
         </is>
       </c>
-      <c r="B45" s="29" t="n">
+      <c r="B45" s="31" t="n">
         <v>51.9</v>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="31" t="n">
         <v>59.7</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="31" t="n">
         <v>63.2</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="31" t="n">
         <v>53.2</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="31" t="n">
         <v>56.1</v>
       </c>
-      <c r="G45" s="29" t="n">
+      <c r="G45" s="31" t="n">
         <v>55.6</v>
       </c>
-      <c r="H45" s="29" t="n">
+      <c r="H45" s="31" t="n">
         <v>42.3</v>
       </c>
-      <c r="I45" s="29" t="n">
+      <c r="I45" s="31" t="n">
         <v>48.4</v>
       </c>
-      <c r="J45" s="29" t="n">
+      <c r="J45" s="31" t="n">
         <v>21.4</v>
       </c>
-      <c r="K45" s="29" t="n">
+      <c r="K45" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="L45" s="29" t="n">
+      <c r="L45" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="M45" s="29" t="n">
+      <c r="M45" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="N45" s="29" t="n">
+      <c r="N45" s="31" t="n">
         <v>41</v>
       </c>
     </row>
@@ -4440,43 +5753,43 @@
           <t>Reading: Bourbon Central</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="31" t="n">
         <v>62.1</v>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="31" t="n">
         <v>56.6</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="31" t="n">
         <v>61.2</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="31" t="n">
         <v>55.7</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="31" t="n">
         <v>47.9</v>
       </c>
-      <c r="G46" s="29" t="n">
+      <c r="G46" s="31" t="n">
         <v>47.9</v>
       </c>
-      <c r="H46" s="29" t="n">
+      <c r="H46" s="31" t="n">
         <v>49.3</v>
       </c>
-      <c r="I46" s="29" t="n">
+      <c r="I46" s="31" t="n">
         <v>49.1</v>
       </c>
-      <c r="J46" s="29" t="n">
+      <c r="J46" s="31" t="n">
         <v>27.1</v>
       </c>
-      <c r="K46" s="29" t="n">
+      <c r="K46" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="L46" s="29" t="n">
+      <c r="L46" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="M46" s="29" t="n">
+      <c r="M46" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="N46" s="29" t="n">
+      <c r="N46" s="31" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4486,43 +5799,43 @@
           <t>Reading: Cane Ridge</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="31" t="n">
         <v>42.9</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="31" t="n">
         <v>47.2</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="31" t="n">
         <v>54.5</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="31" t="n">
         <v>55.3</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="31" t="n">
         <v>59.3</v>
       </c>
-      <c r="G47" s="29" t="n">
+      <c r="G47" s="31" t="n">
         <v>57.1</v>
       </c>
-      <c r="H47" s="29" t="n">
+      <c r="H47" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="I47" s="29" t="n">
+      <c r="I47" s="31" t="n">
         <v>49.6</v>
       </c>
-      <c r="J47" s="29" t="n">
+      <c r="J47" s="31" t="n">
         <v>26.5</v>
       </c>
-      <c r="K47" s="29" t="n">
+      <c r="K47" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="L47" s="29" t="n">
+      <c r="L47" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="M47" s="29" t="n">
+      <c r="M47" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="N47" s="29" t="n">
+      <c r="N47" s="31" t="n">
         <v>37</v>
       </c>
     </row>
@@ -4532,43 +5845,43 @@
           <t>Reading: Paris Elementary</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n">
+      <c r="B48" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="31" t="n">
         <v>34.1</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="31" t="n">
         <v>42.9</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="31" t="n">
         <v>38.9</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="31" t="n">
         <v>41.2</v>
       </c>
-      <c r="G48" s="29" t="n">
+      <c r="G48" s="31" t="n">
         <v>34.3</v>
       </c>
-      <c r="H48" s="29" t="n">
+      <c r="H48" s="31" t="n">
         <v>34.4</v>
       </c>
-      <c r="I48" s="29" t="n">
+      <c r="I48" s="31" t="n">
         <v>35.3</v>
       </c>
-      <c r="J48" s="29" t="n">
+      <c r="J48" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="K48" s="29" t="n">
+      <c r="K48" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="L48" s="29" t="n">
+      <c r="L48" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="M48" s="29" t="n">
+      <c r="M48" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="N48" s="29" t="n">
+      <c r="N48" s="31" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4578,43 +5891,43 @@
           <t>Mathematics: North Middletown</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="31" t="n">
         <v>53.2</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="31" t="n">
         <v>49.4</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="31" t="n">
         <v>55.3</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="31" t="n">
         <v>59.5</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="31" t="n">
         <v>62.1</v>
       </c>
-      <c r="G49" s="29" t="n">
+      <c r="G49" s="31" t="n">
         <v>50.8</v>
       </c>
-      <c r="H49" s="29" t="n">
+      <c r="H49" s="31" t="n">
         <v>47.9</v>
       </c>
-      <c r="I49" s="29" t="n">
+      <c r="I49" s="31" t="n">
         <v>48.4</v>
       </c>
-      <c r="J49" s="29" t="n">
+      <c r="J49" s="31" t="n">
         <v>17.9</v>
       </c>
-      <c r="K49" s="29" t="n">
+      <c r="K49" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="L49" s="29" t="n">
+      <c r="L49" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="M49" s="29" t="n">
+      <c r="M49" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="N49" s="29" t="n">
+      <c r="N49" s="31" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4624,43 +5937,43 @@
           <t>Mathematics: Bourbon Central</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n">
+      <c r="B50" s="31" t="n">
         <v>47.1</v>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="31" t="n">
         <v>47.4</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="31" t="n">
         <v>43.6</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="G50" s="29" t="n">
+      <c r="G50" s="31" t="n">
         <v>43.5</v>
       </c>
-      <c r="H50" s="29" t="n">
+      <c r="H50" s="31" t="n">
         <v>41.8</v>
       </c>
-      <c r="I50" s="29" t="n">
+      <c r="I50" s="31" t="n">
         <v>45.1</v>
       </c>
-      <c r="J50" s="29" t="n">
+      <c r="J50" s="31" t="n">
         <v>31.7</v>
       </c>
-      <c r="K50" s="29" t="n">
+      <c r="K50" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="L50" s="29" t="n">
+      <c r="L50" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="M50" s="29" t="n">
+      <c r="M50" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="N50" s="29" t="n">
+      <c r="N50" s="31" t="n">
         <v>28</v>
       </c>
     </row>
@@ -4670,43 +5983,43 @@
           <t>Mathematics: Cane Ridge</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n">
+      <c r="B51" s="31" t="n">
         <v>33.3</v>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="31" t="n">
         <v>37.7</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="31" t="n">
         <v>43.1</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="31" t="n">
         <v>46.1</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="31" t="n">
         <v>54.4</v>
       </c>
-      <c r="G51" s="29" t="n">
+      <c r="G51" s="31" t="n">
         <v>45.9</v>
       </c>
-      <c r="H51" s="29" t="n">
+      <c r="H51" s="31" t="n">
         <v>41.5</v>
       </c>
-      <c r="I51" s="29" t="n">
+      <c r="I51" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="J51" s="29" t="n">
+      <c r="J51" s="31" t="n">
         <v>25.2</v>
       </c>
-      <c r="K51" s="29" t="n">
+      <c r="K51" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="L51" s="29" t="n">
+      <c r="L51" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="M51" s="29" t="n">
+      <c r="M51" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="N51" s="29" t="n">
+      <c r="N51" s="31" t="n">
         <v>27</v>
       </c>
     </row>
@@ -4716,43 +6029,43 @@
           <t>Mathematics: Paris Elementary</t>
         </is>
       </c>
-      <c r="B52" s="29" t="n">
+      <c r="B52" s="31" t="n">
         <v>29.7</v>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="31" t="n">
         <v>26.8</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="31" t="n">
         <v>22.9</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="31" t="n">
         <v>41.9</v>
       </c>
-      <c r="G52" s="29" t="n">
+      <c r="G52" s="31" t="n">
         <v>28.7</v>
       </c>
-      <c r="H52" s="29" t="n">
+      <c r="H52" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="I52" s="29" t="n">
+      <c r="I52" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="J52" s="29" t="n">
+      <c r="J52" s="31" t="n">
         <v>15.3</v>
       </c>
-      <c r="K52" s="29" t="n">
+      <c r="K52" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="L52" s="29" t="n">
+      <c r="L52" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="M52" s="29" t="n">
+      <c r="M52" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="N52" s="29" t="n">
+      <c r="N52" s="31" t="n">
         <v>29</v>
       </c>
     </row>
@@ -4764,72 +6077,72 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Official overall score</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>'11-12</t>
         </is>
       </c>
-      <c r="C55" s="22" t="inlineStr">
+      <c r="C55" s="20" t="inlineStr">
         <is>
           <t>'12-13</t>
         </is>
       </c>
-      <c r="D55" s="22" t="inlineStr">
+      <c r="D55" s="20" t="inlineStr">
         <is>
           <t>'13-14</t>
         </is>
       </c>
-      <c r="E55" s="22" t="inlineStr">
+      <c r="E55" s="20" t="inlineStr">
         <is>
           <t>'14-15</t>
         </is>
       </c>
-      <c r="F55" s="22" t="inlineStr">
+      <c r="F55" s="20" t="inlineStr">
         <is>
           <t>'15-16</t>
         </is>
       </c>
-      <c r="G55" s="22" t="inlineStr">
+      <c r="G55" s="20" t="inlineStr">
         <is>
           <t>'16-17</t>
         </is>
       </c>
-      <c r="H55" s="22" t="inlineStr">
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>'17-18</t>
         </is>
       </c>
-      <c r="I55" s="22" t="inlineStr">
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>'18-19</t>
         </is>
       </c>
-      <c r="J55" s="22" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
         <is>
           <t>'20-21</t>
         </is>
       </c>
-      <c r="K55" s="22" t="inlineStr">
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>'21-22</t>
         </is>
       </c>
-      <c r="L55" s="22" t="inlineStr">
+      <c r="L55" s="20" t="inlineStr">
         <is>
           <t>'22-23</t>
         </is>
       </c>
-      <c r="M55" s="22" t="inlineStr">
+      <c r="M55" s="20" t="inlineStr">
         <is>
           <t>'23-24</t>
         </is>
       </c>
-      <c r="N55" s="22" t="inlineStr">
+      <c r="N55" s="20" t="inlineStr">
         <is>
           <t>'24-25</t>
         </is>
@@ -4846,31 +6159,31 @@
           <t>North Middletown</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n">
+      <c r="B56" s="31" t="n">
         <v>62.6</v>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="31" t="n">
         <v>68.8</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="31" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="31" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="31" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="K56" s="29" t="n">
+      <c r="K56" s="31" t="n">
         <v>51.9</v>
       </c>
-      <c r="L56" s="29" t="n">
+      <c r="L56" s="31" t="n">
         <v>62.2</v>
       </c>
-      <c r="M56" s="29" t="n">
+      <c r="M56" s="31" t="n">
         <v>74.5</v>
       </c>
-      <c r="N56" s="29" t="n">
+      <c r="N56" s="31" t="n">
         <v>54</v>
       </c>
     </row>
@@ -4880,31 +6193,31 @@
           <t>Bourbon Central</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n">
+      <c r="B57" s="31" t="n">
         <v>63.2</v>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="31" t="n">
         <v>69.8</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="31" t="n">
         <v>67.8</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="31" t="n">
         <v>56.8</v>
       </c>
-      <c r="K57" s="29" t="n">
+      <c r="K57" s="31" t="n">
         <v>52.8</v>
       </c>
-      <c r="L57" s="29" t="n">
+      <c r="L57" s="31" t="n">
         <v>56.7</v>
       </c>
-      <c r="M57" s="29" t="n">
+      <c r="M57" s="31" t="n">
         <v>50.3</v>
       </c>
-      <c r="N57" s="29" t="n">
+      <c r="N57" s="31" t="n">
         <v>55.4</v>
       </c>
     </row>
@@ -4914,31 +6227,31 @@
           <t>Cane Ridge</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n">
+      <c r="B58" s="31" t="n">
         <v>53.3</v>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="31" t="n">
         <v>58.9</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="31" t="n">
         <v>69.2</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="31" t="n">
         <v>68.5</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="31" t="n">
         <v>65.5</v>
       </c>
-      <c r="K58" s="29" t="n">
+      <c r="K58" s="31" t="n">
         <v>54.3</v>
       </c>
-      <c r="L58" s="29" t="n">
+      <c r="L58" s="31" t="n">
         <v>51.8</v>
       </c>
-      <c r="M58" s="29" t="n">
+      <c r="M58" s="31" t="n">
         <v>60.7</v>
       </c>
-      <c r="N58" s="29" t="n">
+      <c r="N58" s="31" t="n">
         <v>47.8</v>
       </c>
     </row>
@@ -4948,31 +6261,31 @@
           <t>Paris Elementary</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n">
+      <c r="B59" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="31" t="n">
         <v>49.9</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="31" t="n">
         <v>59.4</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="31" t="n">
         <v>54.8</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="31" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="K59" s="29" t="n">
+      <c r="K59" s="31" t="n">
         <v>46.1</v>
       </c>
-      <c r="L59" s="29" t="n">
+      <c r="L59" s="31" t="n">
         <v>45.9</v>
       </c>
-      <c r="M59" s="29" t="n">
+      <c r="M59" s="31" t="n">
         <v>40.7</v>
       </c>
-      <c r="N59" s="29" t="n">
+      <c r="N59" s="31" t="n">
         <v>41.9</v>
       </c>
     </row>
@@ -4995,7 +6308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5027,32 +6340,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>2013 enr</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>2013 cap</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>2021 enr</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>2021 cap</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -5233,7 +6546,7 @@
           <t>Net uncommitted seats at both receiving schools</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="22">
         <f>B13-B14</f>
         <v/>
       </c>
@@ -5244,7 +6557,7 @@
           <t>NMES students needing seats on closure</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="28">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -5255,7 +6568,7 @@
           <t>Shortfall if closure proceeds today</t>
         </is>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="22">
         <f>B16-B15</f>
         <v/>
       </c>
@@ -5353,22 +6666,22 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>2023-24 SAAR</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>Draft capacity (KFICS)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>Change vs 2021 rating</t>
         </is>
@@ -5414,7 +6727,7 @@
           <t>North Middletown</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n">
+      <c r="B32" s="28" t="n">
         <v>128</v>
       </c>
       <c r="C32" s="10" t="n">
@@ -5431,7 +6744,7 @@
           <t>Paper seats added at the receiving schools, with the draft's new-construction sections reading None</t>
         </is>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="22">
         <f>D30+D31</f>
         <v/>
       </c>
@@ -5442,7 +6755,7 @@
           <t>NMES fill rate even at the draft's own 154 rating</t>
         </is>
       </c>
-      <c r="B34" s="39">
+      <c r="B34" s="17">
         <f>B32/C32</f>
         <v/>
       </c>
@@ -5462,27 +6775,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Facility</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Condition need</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>Instructional deficiency</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>Total (as printed)</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>Slide capacity</t>
         </is>
@@ -5624,7 +6937,7 @@
           <t>School centers total</t>
         </is>
       </c>
-      <c r="B46" s="23">
+      <c r="B46" s="19">
         <f>SUM(D39:D45)</f>
         <v/>
       </c>
@@ -5645,7 +6958,7 @@
           <t>District total need</t>
         </is>
       </c>
-      <c r="B48" s="23">
+      <c r="B48" s="19">
         <f>B46+B47</f>
         <v/>
       </c>
@@ -5656,7 +6969,7 @@
           <t>Receiving schools combined (Bourbon Central + Cane Ridge)</t>
         </is>
       </c>
-      <c r="B49" s="23">
+      <c r="B49" s="19">
         <f>D41+D42</f>
         <v/>
       </c>
@@ -5667,7 +6980,7 @@
           <t>Net receiving seats at the slides' own capacities (499 and 397)</t>
         </is>
       </c>
-      <c r="B50" s="26">
+      <c r="B50" s="22">
         <f>(499-Redistricting!B8)-(Redistricting!B9-397)</f>
         <v/>
       </c>
@@ -5687,17 +7000,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="24" t="inlineStr">
         <is>
           <t>2017 enr</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="C56" s="24" t="inlineStr">
         <is>
           <t>2017 cap</t>
         </is>
@@ -5796,32 +7109,32 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="24" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B66" s="24" t="inlineStr">
         <is>
           <t>Oct 2023 report</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>Oct 2025 report</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" s="24" t="inlineStr">
         <is>
           <t>Jul 2026 report</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E66" s="24" t="inlineStr">
         <is>
           <t>4-yr needs (Jul 2026)</t>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F66" s="24" t="inlineStr">
         <is>
           <t>Replacement value (Jul 2026)</t>
         </is>
@@ -5833,13 +7146,13 @@
           <t>Bourbon Central Elementary (1988)</t>
         </is>
       </c>
-      <c r="B67" s="40" t="n">
+      <c r="B67" s="41" t="n">
         <v>0.887637</v>
       </c>
-      <c r="C67" s="40" t="n">
+      <c r="C67" s="41" t="n">
         <v>0.819273</v>
       </c>
-      <c r="D67" s="40" t="n">
+      <c r="D67" s="41" t="n">
         <v>0.823017</v>
       </c>
       <c r="E67" s="8" t="n">
@@ -5855,13 +7168,13 @@
           <t>Cane Ridge Elementary (1992)</t>
         </is>
       </c>
-      <c r="B68" s="40" t="n">
+      <c r="B68" s="41" t="n">
         <v>0.8120579999999999</v>
       </c>
-      <c r="C68" s="40" t="n">
+      <c r="C68" s="41" t="n">
         <v>0.811765</v>
       </c>
-      <c r="D68" s="40" t="n">
+      <c r="D68" s="41" t="n">
         <v>0.728249</v>
       </c>
       <c r="E68" s="8" t="n">
@@ -5877,13 +7190,13 @@
           <t>North Middletown Elementary (1948/64)</t>
         </is>
       </c>
-      <c r="B69" s="40" t="n">
+      <c r="B69" s="41" t="n">
         <v>0.694064</v>
       </c>
-      <c r="C69" s="40" t="n">
+      <c r="C69" s="41" t="n">
         <v>0.702133</v>
       </c>
-      <c r="D69" s="40" t="n">
+      <c r="D69" s="41" t="n">
         <v>0.773295</v>
       </c>
       <c r="E69" s="8" t="n">
@@ -5899,13 +7212,13 @@
           <t>Bourbon County Middle School (1948)</t>
         </is>
       </c>
-      <c r="B70" s="40" t="n">
+      <c r="B70" s="41" t="n">
         <v>0.726249</v>
       </c>
-      <c r="C70" s="40" t="n">
+      <c r="C70" s="41" t="n">
         <v>0.727501</v>
       </c>
-      <c r="D70" s="40" t="n">
+      <c r="D70" s="41" t="n">
         <v>0.596145</v>
       </c>
       <c r="E70" s="8" t="n">
@@ -5921,13 +7234,13 @@
           <t>Bourbon County High School (1968)</t>
         </is>
       </c>
-      <c r="B71" s="40" t="n">
+      <c r="B71" s="41" t="n">
         <v>0.809819</v>
       </c>
-      <c r="C71" s="40" t="n">
+      <c r="C71" s="41" t="n">
         <v>0.802057</v>
       </c>
-      <c r="D71" s="40" t="n">
+      <c r="D71" s="41" t="n">
         <v>0.792529</v>
       </c>
       <c r="E71" s="8" t="n">
@@ -5943,7 +7256,7 @@
           <t>Check: Condition Index = 1 - (4-year renewal needs / replacement value), NMES</t>
         </is>
       </c>
-      <c r="B72" s="41">
+      <c r="B72" s="42">
         <f>1-E69/F69</f>
         <v/>
       </c>
@@ -5954,7 +7267,7 @@
           <t>NMES change between inspection cycles (2020-21 to April 2026)</t>
         </is>
       </c>
-      <c r="B73" s="41">
+      <c r="B73" s="42">
         <f>D69-B69</f>
         <v/>
       </c>
@@ -5971,7 +7284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6069,7 +7382,7 @@
           <t>Districts growing slower than benchmark after closing</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="18">
         <f>84/163</f>
         <v/>
       </c>
@@ -6095,52 +7408,52 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Students displaced</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>Spending, year before</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Spending, 3 yrs after</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>State growth</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>Counterfactual</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>Gap per year</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>Gap per student</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -6175,7 +7488,7 @@
         <f>G15-E15</f>
         <v/>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="19">
         <f>H15/C15</f>
         <v/>
       </c>
@@ -6214,7 +7527,7 @@
         <f>G16-E16</f>
         <v/>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="19">
         <f>H16/C16</f>
         <v/>
       </c>
@@ -6253,7 +7566,7 @@
         <f>G17-E17</f>
         <v/>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="19">
         <f>H17/C17</f>
         <v/>
       </c>
@@ -6292,7 +7605,7 @@
         <f>G18-E18</f>
         <v/>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="19">
         <f>H18/C18</f>
         <v/>
       </c>
@@ -6331,7 +7644,7 @@
         <f>G19-E19</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="19">
         <f>H19/C19</f>
         <v/>
       </c>
@@ -6370,7 +7683,7 @@
         <f>G20-E20</f>
         <v/>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="19">
         <f>H20/C20</f>
         <v/>
       </c>
@@ -6409,7 +7722,7 @@
         <f>G21-E21</f>
         <v/>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="19">
         <f>H21/C21</f>
         <v/>
       </c>
@@ -6448,7 +7761,7 @@
         <f>G22-E22</f>
         <v/>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="19">
         <f>H22/C22</f>
         <v/>
       </c>
@@ -6487,7 +7800,7 @@
         <f>G23-E23</f>
         <v/>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="19">
         <f>H23/C23</f>
         <v/>
       </c>
@@ -6526,7 +7839,7 @@
         <f>G24-E24</f>
         <v/>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="19">
         <f>H24/C24</f>
         <v/>
       </c>
@@ -6565,7 +7878,7 @@
         <f>G25-E25</f>
         <v/>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="19">
         <f>H25/C25</f>
         <v/>
       </c>
@@ -6604,7 +7917,7 @@
         <f>G26-E26</f>
         <v/>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="19">
         <f>H26/C26</f>
         <v/>
       </c>
@@ -6643,7 +7956,7 @@
         <f>G27-E27</f>
         <v/>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="19">
         <f>H27/C27</f>
         <v/>
       </c>
@@ -6682,7 +7995,7 @@
         <f>G28-E28</f>
         <v/>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="19">
         <f>H28/C28</f>
         <v/>
       </c>
@@ -6721,7 +8034,7 @@
         <f>G29-E29</f>
         <v/>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="19">
         <f>H29/C29</f>
         <v/>
       </c>
@@ -6760,7 +8073,7 @@
         <f>G30-E30</f>
         <v/>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="19">
         <f>H30/C30</f>
         <v/>
       </c>
@@ -6799,7 +8112,7 @@
         <f>G31-E31</f>
         <v/>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="19">
         <f>H31/C31</f>
         <v/>
       </c>
@@ -6822,11 +8135,11 @@
           <t>Plan requirement, low / high ($800K-$1M over the 128 students displaced)</t>
         </is>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="19">
         <f>800000/Assumptions!B11</f>
         <v/>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="19">
         <f>1000000/Assumptions!B11</f>
         <v/>
       </c>
@@ -6902,10 +8215,10 @@
           <t>Share of districts spending MORE than trend after closing (all / plausible-only)</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="38" t="n">
         <v>0.4</v>
       </c>
-      <c r="C41" s="36" t="n">
+      <c r="C41" s="38" t="n">
         <v>0.41</v>
       </c>
     </row>
@@ -6938,7 +8251,7 @@
       <c r="B44" s="8" t="n">
         <v>818</v>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="19">
         <f>Closure_Model!B47/Assumptions!B11</f>
         <v/>
       </c>
@@ -6985,10 +8298,10 @@
           <t>Median score change: events displacing 15%+ of district / under 15%</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="31" t="n">
         <v>-2</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="31" t="n">
         <v>-0.2</v>
       </c>
     </row>
@@ -7013,7 +8326,7 @@
           <t>Cases of a rural town's ELEMENTARY closed with clear savings and clear gains</t>
         </is>
       </c>
-      <c r="B51" s="26" t="n">
+      <c r="B51" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7029,7 +8342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7069,32 +8382,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Members</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>Total/member</t>
         </is>
@@ -7248,7 +8561,7 @@
           <t>Times 128 students</t>
         </is>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="19">
         <f>B14*128</f>
         <v/>
       </c>
@@ -7291,7 +8604,7 @@
           <t>Breakeven N at state-only revenue</t>
         </is>
       </c>
-      <c r="B18" s="42">
+      <c r="B18" s="43">
         <f>B15/B17</f>
         <v/>
       </c>
@@ -7307,7 +8620,7 @@
           <t>Same fraction with matching definitions: all-in cost / total revenue per member (2023-24)</t>
         </is>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="26">
         <f>B15/F10</f>
         <v/>
       </c>
@@ -7325,27 +8638,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Cost/pupil</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Enrolled</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Breakeven N</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Short by</t>
         </is>
@@ -7363,11 +8676,11 @@
       <c r="C23" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="29">
         <f>B23*C23/F$10</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="29">
         <f>D23-C23</f>
         <v/>
       </c>
@@ -7384,11 +8697,11 @@
       <c r="C24" s="10" t="n">
         <v>459</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="29">
         <f>B24*C24/F$10</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="29">
         <f>D24-C24</f>
         <v/>
       </c>
@@ -7405,11 +8718,11 @@
       <c r="C25" s="10" t="n">
         <v>453</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="29">
         <f>B25*C25/F$10</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="29">
         <f>D25-C25</f>
         <v/>
       </c>
@@ -7426,11 +8739,11 @@
       <c r="C26" s="10" t="n">
         <v>590</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="29">
         <f>B26*C26/F$10</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="29">
         <f>D26-C26</f>
         <v/>
       </c>
@@ -7447,11 +8760,11 @@
       <c r="C27" s="10" t="n">
         <v>766</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="29">
         <f>B27*C27/F$10</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="29">
         <f>D27-C27</f>
         <v/>
       </c>
@@ -7471,27 +8784,27 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>Fixed base</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>N (SEEK only)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>N if fed counted</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>Enrolled</t>
         </is>
@@ -7503,15 +8816,15 @@
           <t>North Middletown</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="25">
         <f>Assumptions!B51+Assumptions!B52</f>
         <v/>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="29">
         <f>B32/(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="29">
         <f>B32/(Assumptions!B6+3380-Assumptions!B62)</f>
         <v/>
       </c>
@@ -7534,11 +8847,11 @@
         <f>Assumptions!B51+Assumptions!B52*Facility_Plans!F68/Facility_Plans!F69</f>
         <v/>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="29">
         <f>B33/(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="29">
         <f>B33/(Assumptions!B6+3380-Assumptions!B62)</f>
         <v/>
       </c>
@@ -7556,11 +8869,11 @@
         <f>Assumptions!B51+Assumptions!B52*Facility_Plans!F67/Facility_Plans!F69</f>
         <v/>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="29">
         <f>B34/(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="29">
         <f>B34/(Assumptions!B6+3380-Assumptions!B62)</f>
         <v/>
       </c>
@@ -7583,32 +8896,32 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>NMES members</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>BCES</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>Cane Ridge</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>NMES vs BCES</t>
         </is>
@@ -7632,7 +8945,7 @@
       <c r="E39" s="8" t="n">
         <v>7740</v>
       </c>
-      <c r="F39" s="43">
+      <c r="F39" s="44">
         <f>B39/D39-1</f>
         <v/>
       </c>
@@ -7655,7 +8968,7 @@
       <c r="E40" s="8" t="n">
         <v>11383</v>
       </c>
-      <c r="F40" s="43">
+      <c r="F40" s="44">
         <f>B40/D40-1</f>
         <v/>
       </c>
@@ -7683,7 +8996,7 @@
       <c r="E41" s="8" t="n">
         <v>7718</v>
       </c>
-      <c r="F41" s="43">
+      <c r="F41" s="44">
         <f>B41/D41-1</f>
         <v/>
       </c>
@@ -7706,7 +9019,7 @@
       <c r="E42" s="8" t="n">
         <v>9222</v>
       </c>
-      <c r="F42" s="43">
+      <c r="F42" s="44">
         <f>B42/D42-1</f>
         <v/>
       </c>
@@ -7729,7 +9042,7 @@
       <c r="E43" s="8" t="n">
         <v>9655</v>
       </c>
-      <c r="F43" s="43">
+      <c r="F43" s="44">
         <f>B43/D43-1</f>
         <v/>
       </c>
@@ -7752,7 +9065,7 @@
       <c r="E44" s="8" t="n">
         <v>9815</v>
       </c>
-      <c r="F44" s="43">
+      <c r="F44" s="44">
         <f>B44/D44-1</f>
         <v/>
       </c>
@@ -7772,22 +9085,22 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="24" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B48" s="24" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>Reported $/student</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>Curve prediction</t>
         </is>
@@ -7809,7 +9122,7 @@
         <f>B$55+B$54*E49</f>
         <v/>
       </c>
-      <c r="E49" s="44">
+      <c r="E49" s="45">
         <f>1/B49</f>
         <v/>
       </c>
@@ -7835,7 +9148,7 @@
         <f>B$55+B$54*E50</f>
         <v/>
       </c>
-      <c r="E50" s="44">
+      <c r="E50" s="45">
         <f>1/B50</f>
         <v/>
       </c>
@@ -7856,7 +9169,7 @@
         <f>B$55+B$54*E51</f>
         <v/>
       </c>
-      <c r="E51" s="44">
+      <c r="E51" s="45">
         <f>1/B51</f>
         <v/>
       </c>
@@ -7877,7 +9190,7 @@
         <f>B$55+B$54*E52</f>
         <v/>
       </c>
-      <c r="E52" s="44">
+      <c r="E52" s="45">
         <f>1/B52</f>
         <v/>
       </c>
@@ -7888,7 +9201,7 @@
           <t>Fixed base per building (least-squares slope on 1/N)</t>
         </is>
       </c>
-      <c r="B54" s="23">
+      <c r="B54" s="19">
         <f>SLOPE(C49:C52,E49:E52)</f>
         <v/>
       </c>
@@ -7899,7 +9212,7 @@
           <t>Variable cost per student (intercept)</t>
         </is>
       </c>
-      <c r="B55" s="23">
+      <c r="B55" s="19">
         <f>INTERCEPT(C49:C52,E49:E52)</f>
         <v/>
       </c>
@@ -7910,7 +9223,7 @@
           <t>Fit quality (R-squared)</t>
         </is>
       </c>
-      <c r="B56" s="45">
+      <c r="B56" s="23">
         <f>RSQ(C49:C52,E49:E52)</f>
         <v/>
       </c>
@@ -7928,7 +9241,7 @@
           <t>Millersburg premium over its receiving school, 2000-01 (per student x students)</t>
         </is>
       </c>
-      <c r="B59" s="23">
+      <c r="B59" s="19">
         <f>(C52-C50)*B52</f>
         <v/>
       </c>
@@ -7944,7 +9257,7 @@
           <t>NMES premium over the cheaper receiving school, 2023-24 (same computation)</t>
         </is>
       </c>
-      <c r="B60" s="23">
+      <c r="B60" s="19">
         <f>(B14-18131)*128</f>
         <v/>
       </c>
@@ -8815,6 +10128,888 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Published Scenario Defaults: every headline number on the site, executive summary, and report, as live formulas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>One row per published default. Blue cells are sourced inputs; black cells compute. If a formula here disagrees with a published artifact, the artifact is wrong: say so and it will be corrected publicly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>FACT ONE AND TWO: THE SCHOOL AND ITS COST (Sections 2 and 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>NMES per-student cost, newest state file (2024-25)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>17903</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Kentucky elementary average, same file</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>19299</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>NMES below the state average</t>
+        </is>
+      </c>
+      <c r="B7" s="17">
+        <f>1-B5/B6</f>
+        <v/>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Published: 7 percent below</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>District's own cost-of-delivery table, May 21, 2026: NMES / state average</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>19080</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>19020</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Gap on the district's own table</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>B8/C8-1</f>
+        <v/>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Published: three tenths of one percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Share of middle and high schoolers who came through NMES (128 of the 1,040 elementary seats)</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>Assumptions!B11/1040</f>
+        <v/>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Published: about one in eight</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>FACT THREE: THE LEDGER WALK AND THE $661,139 CLAIM (Section 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>All-funds dollars coded to org 090, fiscal 2025 MUNIS Cost by ORG</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1285310</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Non-General-Fund dollars in that total (grants, on-behalf and other funds, per the ledger's fund split)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>182952</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>161880</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>6941</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>General Fund actuals coded to the school</t>
+        </is>
+      </c>
+      <c r="B15" s="19">
+        <f>B13-B14-C14-D14</f>
+        <v/>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Published: $933,537 (within 0.55 percent of the $938,690 budget view)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Building-bound costs on the ledger (utilities, disposal, telecom, supplies, repairs)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>79211</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>District worksheet: avoidable expense lines / insurance</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>107039</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Staff-retained saving (ledger) and building-sold ceiling (worksheet)</t>
+        </is>
+      </c>
+      <c r="B18" s="19">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="C18" s="19">
+        <f>B17+C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>The district's $661,139 decomposition: staffing + avoidable lines + insurance + supplies</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>493407</v>
+      </c>
+      <c r="C19" s="9">
+        <f>B17</f>
+        <v/>
+      </c>
+      <c r="D19" s="9">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>40693</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sum (the claim) and what remains in year one with staff retained and supplies moving</t>
+        </is>
+      </c>
+      <c r="B20" s="19">
+        <f>B19+C19+D19+E19</f>
+        <v/>
+      </c>
+      <c r="C20" s="19">
+        <f>C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>FACT FOUR: WHAT LEAVING FAMILIES COST (the published table, all four rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Per-leaver funding: SEEK base + typical add-ons</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>Assumptions!B6+500</f>
+        <v/>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>$5,126 at the FY2027 base</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Share who leave / students (of 128) / year one / per year at full effect / total by grade 12</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Year one and full effect price whole students (the site chart's convention); the grade-12 total prices the exact share times the 23.5-year factor: (6+7+8+9+10+11+12+6x13)/6 years of escalating cohorts. Reproduces the published $67K/$144K/$1.5M through $328K/$713K/$7.7M rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>10 percent of the school</t>
+        </is>
+      </c>
+      <c r="B25" s="11">
+        <f>ROUND(128*0.1,0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="9">
+        <f>B25*$B$23</f>
+        <v/>
+      </c>
+      <c r="D25" s="9">
+        <f>ROUND(B25*13/6,0)*$B$23</f>
+        <v/>
+      </c>
+      <c r="E25" s="9">
+        <f>128*0.1*$B$23*23.5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>20 percent of the school</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
+        <f>ROUND(128*0.2,0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="9">
+        <f>B26*$B$23</f>
+        <v/>
+      </c>
+      <c r="D26" s="9">
+        <f>ROUND(B26*13/6,0)*$B$23</f>
+        <v/>
+      </c>
+      <c r="E26" s="9">
+        <f>128*0.2*$B$23*23.5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>30 percent of the school</t>
+        </is>
+      </c>
+      <c r="B27" s="11">
+        <f>ROUND(128*0.3,0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="9">
+        <f>B27*$B$23</f>
+        <v/>
+      </c>
+      <c r="D27" s="9">
+        <f>ROUND(B27*13/6,0)*$B$23</f>
+        <v/>
+      </c>
+      <c r="E27" s="9">
+        <f>128*0.3*$B$23*23.5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>50 percent of the school</t>
+        </is>
+      </c>
+      <c r="B28" s="11">
+        <f>ROUND(128*0.5,0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="9">
+        <f>B28*$B$23</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>ROUND(B28*13/6,0)*$B$23</f>
+        <v/>
+      </c>
+      <c r="E28" s="9">
+        <f>128*0.5*$B$23*23.5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Carried funding of the current 128 students: grade counts (K-5) x years to grade 12</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Student-years, and the carried band at the $4,626 base / $5,126 with add-ons</t>
+        </is>
+      </c>
+      <c r="B31" s="22">
+        <f>SUMPRODUCT(B30:G30,{13,12,11,10,9,8})</f>
+        <v/>
+      </c>
+      <c r="C31" s="9">
+        <f>B31*Assumptions!B6</f>
+        <v/>
+      </c>
+      <c r="D31" s="9">
+        <f>B31*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Published: 1,339 student-years, $6.2 to $6.9 million</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>THE TWO CALCULATOR DEFAULTS (the numbers on the site's cards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Closure default: district staffing stance + our mid-range leaver and busing estimates</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>B17+C17-63000-38*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F34" s="21">
+        <f> $127,039 kept, minus $63,000 of busing, minus 38 leavers (30 percent) at $5,126: the published -$130,749, the 26th percentile of the 5,832-scenario grid; the weighted median is a $20,007 loss (Closure_Model row 50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Growth default: 30 added students at the grid's low busing and supplies</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>30*(Assumptions!B6+500-400)</f>
+        <v/>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>The published +$141,780, the weighted median of the 19,683-scenario grid (Growth_Model rows 17-19); at the central $500 busing and $700 supplies the same 30 students net about $118,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>THE PLAN: FLOOR, DEFAULT, AND TOP (the site plan calculator's three published cases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Recovered leakage students (of the 550-student pool)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>275</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Enrollment lever at $4,226 net of supplies</t>
+        </is>
+      </c>
+      <c r="B40" s="9">
+        <f>B39*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="C40" s="9">
+        <f>C39*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="D40" s="9">
+        <f>D39*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Counted-once fixed-cost package</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>760000</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>760000</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Full 2018 rate restore (live from Tax_History)</t>
+        </is>
+      </c>
+      <c r="B42" s="9">
+        <f>Tax_History!D79</f>
+        <v/>
+      </c>
+      <c r="C42" s="9">
+        <f>Tax_History!D79</f>
+        <v/>
+      </c>
+      <c r="D42" s="9">
+        <f>Tax_History!D79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Trending fiscal 2026 gap (June 2026 ledger, before transfers)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>1738653</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>1738653</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>1738653</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Surplus after the gap</t>
+        </is>
+      </c>
+      <c r="B44" s="19">
+        <f>B40+B41+B42-B43</f>
+        <v/>
+      </c>
+      <c r="C44" s="19">
+        <f>C40+C41+C42-C43</f>
+        <v/>
+      </c>
+      <c r="D44" s="19">
+        <f>D40+D41+D42-D43</f>
+        <v/>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Published: about $500,000 / $1,662,575 / $3.4 million to spare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>5 percent certified raise ($10,000,388 GF certified payroll x 5% x 1.0145)</t>
+        </is>
+      </c>
+      <c r="B45" s="9">
+        <f>10000388*0.05*1.0145</f>
+        <v/>
+      </c>
+      <c r="C45" s="9">
+        <f>10000388*0.05*1.0145</f>
+        <v/>
+      </c>
+      <c r="D45" s="9">
+        <f>10000388*0.05*1.0145</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Left for new debt service (negative at the floor: within $7,000 of the raise)</t>
+        </is>
+      </c>
+      <c r="B46" s="9">
+        <f>B44-B45</f>
+        <v/>
+      </c>
+      <c r="C46" s="9">
+        <f>C44-C45</f>
+        <v/>
+      </c>
+      <c r="D46" s="9">
+        <f>D44-D45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>New bonds at 4.5 percent, 20 years (factor below), floored at zero</t>
+        </is>
+      </c>
+      <c r="B47" s="9">
+        <f>MAX(B46,0)*$B$50</f>
+        <v/>
+      </c>
+      <c r="C47" s="9">
+        <f>MAX(C46,0)*$B$50</f>
+        <v/>
+      </c>
+      <c r="D47" s="9">
+        <f>MAX(D46,0)*$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Building capacity with the advisor's $32 million</t>
+        </is>
+      </c>
+      <c r="B48" s="19">
+        <f>B47+32000000</f>
+        <v/>
+      </c>
+      <c r="C48" s="19">
+        <f>C47+32000000</f>
+        <v/>
+      </c>
+      <c r="D48" s="19">
+        <f>D47+32000000</f>
+        <v/>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Published: the advisor's $32 million at the floor; about $47 million at the default; about $69 million at the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Annuity factor, 4.5 percent, 20 years</t>
+        </is>
+      </c>
+      <c r="B50" s="23">
+        <f>(1-1.045^-20)/0.045</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>GROWTH CONTEXT DEFAULTS (Section 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Eminence Independent, 2014 to 2024 enrollment, and its growth</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="n">
+        <v>733</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>991</v>
+      </c>
+      <c r="D53" s="18">
+        <f>C53/B53-1</f>
+        <v/>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Published: grew 35 percent in the decade Bourbon Schools shrank 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County Schools, 2014 to 2023 enrollment, and its decline</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>2912</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>2616</v>
+      </c>
+      <c r="D54" s="18">
+        <f>C54/B54-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>Leakage pool pricing: see Redistricting rows 136-140 (documented floor 483; gross $2.1-$2.5M at the full base; net $1.9-$2.3M at $4,226)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>Rate menu: see Tax_History rows 70-89 ($166,189 per real cent; the four options and the sequencing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>BREAKEVEN TABLE, LEDGER-CODED VIEW (Section 4; the all-in view is on School_Costs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Revenue per member (all-funds spending of about $41.8M across about 2,615 members)</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>15983</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>School / coded by the district / enrolled / breakeven / clears by</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>Every school clears on the ledger-coded definition; the all-in report-card definition fails every school. The swing is the definitions, which is why they should be chosen and published before any vote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>North Middletown</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>1285310</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="D61" s="11">
+        <f>ROUND(B61/$B$59,0)</f>
+        <v/>
+      </c>
+      <c r="E61" s="11">
+        <f>C61-D61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon Central</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>4033689</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>459</v>
+      </c>
+      <c r="D62" s="11">
+        <f>ROUND(B62/$B$59,0)</f>
+        <v/>
+      </c>
+      <c r="E62" s="11">
+        <f>C62-D62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Cane Ridge</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>4326733</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>453</v>
+      </c>
+      <c r="D63" s="11">
+        <f>ROUND(B63/$B$59,0)</f>
+        <v/>
+      </c>
+      <c r="E63" s="11">
+        <f>C63-D63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County Middle</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>3868106</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>590</v>
+      </c>
+      <c r="D64" s="11">
+        <f>ROUND(B64/$B$59,0)</f>
+        <v/>
+      </c>
+      <c r="E64" s="11">
+        <f>C64-D64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Bourbon County High</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>5515105</v>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>766</v>
+      </c>
+      <c r="D65" s="11">
+        <f>ROUND(B65/$B$59,0)</f>
+        <v/>
+      </c>
+      <c r="E65" s="11">
+        <f>C65-D65</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8832,18 +11027,18 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr"/>
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -8855,15 +11050,15 @@
           <t>Revenues before transfers</t>
         </is>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="25">
         <f>Assumptions!B19</f>
         <v/>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="25">
         <f>Assumptions!B20</f>
         <v/>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="25">
         <f>Assumptions!B21</f>
         <v/>
       </c>
@@ -8874,15 +11069,15 @@
           <t>Expenditures before transfers</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="25">
         <f>Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="25">
         <f>Assumptions!B23</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="25">
         <f>Assumptions!B24</f>
         <v/>
       </c>
@@ -8912,11 +11107,11 @@
           <t>Net transfers &amp; other sources</t>
         </is>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="25">
         <f>Assumptions!B25</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="25">
         <f>Assumptions!B26</f>
         <v/>
       </c>
@@ -8942,15 +11137,15 @@
           <t>Ending fund balance</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="25">
         <f>Assumptions!B27</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="25">
         <f>Assumptions!B28</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="25">
         <f>Assumptions!B29</f>
         <v/>
       </c>
@@ -8983,7 +11178,7 @@
           <t>Fund balance as % of expenditures, FY2025</t>
         </is>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="18">
         <f>D9/D5</f>
         <v/>
       </c>
@@ -9027,7 +11222,7 @@
           <t>Years of runway at current pace</t>
         </is>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="26">
         <f>IFERROR(D15/D16,0)</f>
         <v/>
       </c>
@@ -9051,7 +11246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9107,7 +11302,7 @@
           <t>Total site spending (state ESSA basis)</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="25">
         <f>Assumptions!B14*Assumptions!B11</f>
         <v/>
       </c>
@@ -9118,7 +11313,7 @@
           <t>State/local share of site spending</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="25">
         <f>Assumptions!B15*Assumptions!B11</f>
         <v/>
       </c>
@@ -9136,7 +11331,7 @@
           <t>Principal &amp; office</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="25">
         <f>Assumptions!B51</f>
         <v/>
       </c>
@@ -9147,7 +11342,7 @@
           <t>Plant, utilities, insurance (net of carrying cost)</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="25">
         <f>Assumptions!B52</f>
         <v/>
       </c>
@@ -9158,7 +11353,7 @@
           <t>Teaching positions eliminated (via attrition, GF-borne cost)</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="25">
         <f>Assumptions!B53*Assumptions!B69</f>
         <v/>
       </c>
@@ -9169,12 +11364,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Gross avoidable cost</t>
         </is>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="19">
         <f>SUM(B10:B12)</f>
         <v/>
       </c>
@@ -9192,7 +11387,7 @@
           <t>Added busing</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="25">
         <f>Assumptions!B54</f>
         <v/>
       </c>
@@ -9203,29 +11398,29 @@
           <t>SEEK revenue lost to departing students (FY2027 base)</t>
         </is>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="25">
         <f>Assumptions!B55*Assumptions!B6</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Total offsets</t>
         </is>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="19">
         <f>SUM(B16:B17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 5,832-scenario grid at row 37, median a $20,007 LOSS)</t>
         </is>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="27">
         <f>B13-B18</f>
         <v/>
       </c>
@@ -9236,11 +11431,11 @@
           <t>Share of the structural deficit ($2.65M) | of the reserve drawdown ($1.15M)</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <f>B20/(Assumptions!B24-Assumptions!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="18">
         <f>B20/GF_Summary!D16</f>
         <v/>
       </c>
@@ -9251,7 +11446,7 @@
           <t>One-time transition cost (year one)</t>
         </is>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="25">
         <f>Assumptions!B56</f>
         <v/>
       </c>
@@ -9264,12 +11459,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Students leaving</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Net recurring saving</t>
         </is>
@@ -9331,7 +11526,7 @@
           <t>All-in cost per position (salary + state-paid on-behalf; filing basis)</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="25">
         <f>Assumptions!B41</f>
         <v/>
       </c>
@@ -9347,7 +11542,7 @@
           <t>GF-borne cost per position (salary + ~5%)</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="25">
         <f>Assumptions!B69</f>
         <v/>
       </c>
@@ -9365,27 +11560,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Lever (low / central / high)</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>Central</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -9544,7 +11739,7 @@
           <t>Central case: net yearly effect</t>
         </is>
       </c>
-      <c r="B47" s="23">
+      <c r="B47" s="19">
         <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44)-C45</f>
         <v/>
       </c>
@@ -9682,7 +11877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9712,18 +11907,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr"/>
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
@@ -9735,15 +11930,15 @@
           <t>Transfer students (scenario)</t>
         </is>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="28">
         <f>Assumptions!B59</f>
         <v/>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="28">
         <f>Assumptions!B60</f>
         <v/>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="28">
         <f>Assumptions!B61</f>
         <v/>
       </c>
@@ -9773,15 +11968,15 @@
           <t>SEEK base per pupil</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="25">
         <f>Assumptions!B6</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="25">
         <f>Assumptions!B7</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="25">
         <f>Assumptions!B8</f>
         <v/>
       </c>
@@ -9844,20 +12039,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Net new recurring revenue</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="27">
         <f>B8-B9-B10</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="27">
         <f>C8-C9-C10</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="27">
         <f>D8-D9-D10</f>
         <v/>
       </c>
@@ -9921,7 +12116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9962,7 +12157,7 @@
           <t>NMES enrollment</t>
         </is>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="28">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -9973,7 +12168,7 @@
           <t>NMES rated capacity</t>
         </is>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="28">
         <f>Assumptions!B12</f>
         <v/>
       </c>
@@ -10133,7 +12328,7 @@
           <t>Average class size today</t>
         </is>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="26">
         <f>B5/B20</f>
         <v/>
       </c>
@@ -10144,7 +12339,7 @@
           <t>Average class size at capacity</t>
         </is>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="26">
         <f>B14/B20</f>
         <v/>
       </c>
@@ -10179,7 +12374,7 @@
           <t>New SEEK revenue from cross-county transfers (FY2027 base)</t>
         </is>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="25">
         <f>B13*Assumptions!B6</f>
         <v/>
       </c>
@@ -10190,7 +12385,7 @@
           <t>Variable cost of all added students</t>
         </is>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="25">
         <f>(B12+B13)*Assumptions!B62</f>
         <v/>
       </c>
@@ -10216,23 +12411,23 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Net recurring benefit, low (avoided and added sections both priced at the GF-borne $60K central; v3.8 subtracts the NMES additions)</t>
         </is>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="27">
         <f>B26-B27+(B28-B24)*Assumptions!B69</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Net recurring benefit, high (two avoided sections, same NMES debit)</t>
         </is>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="19">
         <f>B26-B27+(B29-B24)*Assumptions!B69</f>
         <v/>
       </c>
@@ -10257,7 +12452,7 @@
           <t>NMES site spending today</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="25">
         <f>Assumptions!B14*Assumptions!B11</f>
         <v/>
       </c>
@@ -10268,7 +12463,7 @@
           <t>Per student today</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="25">
         <f>Assumptions!B14</f>
         <v/>
       </c>
@@ -10290,7 +12485,7 @@
           <t>Change</t>
         </is>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="18">
         <f>B36/B35-1</f>
         <v/>
       </c>
@@ -10373,7 +12568,7 @@
           <t>NMES per pupil today</t>
         </is>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="25">
         <f>Assumptions!B14</f>
         <v/>
       </c>
@@ -10427,12 +12622,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>NMES at 174 vs cheapest receiving school</t>
         </is>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="27">
         <f>B49-MIN(B46,B47)</f>
         <v/>
       </c>
@@ -10518,7 +12713,7 @@
           <t>Reference: NMES's ENTIRE state and local spending per pupil (fixed costs included)</t>
         </is>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="25">
         <f>Assumptions!B15</f>
         <v/>
       </c>
@@ -10541,12 +12736,12 @@
           <t>Marginal cost per added student</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B64" s="24" t="inlineStr">
         <is>
           <t>At 174</t>
         </is>
       </c>
-      <c r="C64" s="17" t="inlineStr">
+      <c r="C64" s="24" t="inlineStr">
         <is>
           <t>At 154</t>
         </is>
@@ -10639,37 +12834,37 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="A74" s="24" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B74" s="24" t="inlineStr">
         <is>
           <t>NMES members</t>
         </is>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C74" s="24" t="inlineStr">
         <is>
           <t>NMES $/pupil</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D74" s="24" t="inlineStr">
         <is>
           <t>BCES $/pupil</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr">
+      <c r="E74" s="24" t="inlineStr">
         <is>
           <t>CRES $/pupil</t>
         </is>
       </c>
-      <c r="F74" s="17" t="inlineStr">
+      <c r="F74" s="24" t="inlineStr">
         <is>
           <t>NMES at 174</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
+      <c r="G74" s="24" t="inlineStr">
         <is>
           <t>NMES at 154</t>
         </is>
@@ -11000,27 +13195,27 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="17" t="inlineStr">
+      <c r="A102" s="24" t="inlineStr">
         <is>
           <t>Scenario (NMES/BCES/CRES caps)</t>
         </is>
       </c>
-      <c r="B102" s="17" t="inlineStr">
+      <c r="B102" s="24" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C102" s="17" t="inlineStr">
+      <c r="C102" s="24" t="inlineStr">
         <is>
           <t>BCES</t>
         </is>
       </c>
-      <c r="D102" s="17" t="inlineStr">
+      <c r="D102" s="24" t="inlineStr">
         <is>
           <t>CRES</t>
         </is>
       </c>
-      <c r="E102" s="17" t="inlineStr">
+      <c r="E102" s="24" t="inlineStr">
         <is>
           <t>Cheapest</t>
         </is>
@@ -11227,7 +13422,7 @@
           <t>County total registered homeschoolers (a floor; KY letter compliance is incomplete)</t>
         </is>
       </c>
-      <c r="B119" s="26">
+      <c r="B119" s="22">
         <f>B117+B118</f>
         <v/>
       </c>
@@ -11328,7 +13523,7 @@
           <t>New SEEK per returning student (FY2027 base; same cell the leaver cost uses, so the symmetry is honest)</t>
         </is>
       </c>
-      <c r="B130" s="18">
+      <c r="B130" s="25">
         <f>Assumptions!B6</f>
         <v/>
       </c>
@@ -11361,7 +13556,7 @@
           <t>Recurring SEEK revenue if all 46 open seats fill from this pool alone</t>
         </is>
       </c>
-      <c r="B133" s="23">
+      <c r="B133" s="19">
         <f>46*Assumptions!B6</f>
         <v/>
       </c>
@@ -11372,11 +13567,11 @@
           <t>Capture rate that requires: share of registered homeschoolers / share of the full ACS pool</t>
         </is>
       </c>
-      <c r="B134" s="19">
+      <c r="B134" s="18">
         <f>46/B119</f>
         <v/>
       </c>
-      <c r="C134" s="19">
+      <c r="C134" s="18">
         <f>46/B120</f>
         <v/>
       </c>
@@ -11404,7 +13599,7 @@
           <t>Documented Bourbon-specific floor: homeschool filings plus residents enrolled elsewhere</t>
         </is>
       </c>
-      <c r="B137" s="26">
+      <c r="B137" s="22">
         <f>B117+B136</f>
         <v/>
       </c>
@@ -11427,11 +13622,11 @@
           <t>Pool priced at the full SEEK base, revenue not collected today (450 and 550 x FY2027 base; the published $2.1 to $2.5 million)</t>
         </is>
       </c>
-      <c r="B139" s="23">
+      <c r="B139" s="19">
         <f>450*Assumptions!B6</f>
         <v/>
       </c>
-      <c r="C139" s="23">
+      <c r="C139" s="19">
         <f>550*Assumptions!B6</f>
         <v/>
       </c>
@@ -11456,7 +13651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11542,7 +13737,7 @@
           <t>North Middletown population, 2020</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="28">
         <f>Demographics!B29</f>
         <v/>
       </c>
@@ -11573,7 +13768,7 @@
           <t>NMES zone area (sq mi)</t>
         </is>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="29">
         <f>B5*B9</f>
         <v/>
       </c>
@@ -11584,7 +13779,7 @@
           <t>Paris-area zones (sq mi)</t>
         </is>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="29">
         <f>B5-B10</f>
         <v/>
       </c>
@@ -11595,7 +13790,7 @@
           <t>NMES elementary students</t>
         </is>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="28">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -11606,7 +13801,7 @@
           <t>Paris-area elementary students</t>
         </is>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="28">
         <f>Redistricting!B8+Redistricting!B9</f>
         <v/>
       </c>
@@ -11617,7 +13812,7 @@
           <t>Students per square mile, NMES zone</t>
         </is>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="26">
         <f>B12/B10</f>
         <v/>
       </c>
@@ -11628,7 +13823,7 @@
           <t>Students per square mile, Paris-area zones</t>
         </is>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="26">
         <f>B13/B11</f>
         <v/>
       </c>
@@ -11639,7 +13834,7 @@
           <t>Students per square mile, district elementary overall</t>
         </is>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="26">
         <f>(B12+B13)/B5</f>
         <v/>
       </c>
@@ -11749,7 +13944,7 @@
           <t>Marginal cost per bus-mile, low</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="30" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -11764,7 +13959,7 @@
           <t>Marginal cost per bus-mile, high</t>
         </is>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B28" s="30" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -11811,23 +14006,23 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Bottom-up added busing cost, low</t>
         </is>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="27">
         <f>B29</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Bottom-up added busing cost, high</t>
         </is>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="19">
         <f>B30+B31*B32</f>
         <v/>
       </c>
@@ -11864,7 +14059,7 @@
           <t>Students rezoned to NMES</t>
         </is>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="28">
         <f>Redistricting!B12</f>
         <v/>
       </c>
@@ -11947,7 +14142,7 @@
           <t>Transportation expense, FY2025</t>
         </is>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="25">
         <f>Assumptions!B42</f>
         <v/>
       </c>
@@ -11958,7 +14153,7 @@
           <t>Average Daily Attendance, FY2025</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="31" t="n">
         <v>2242.5</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -11984,14 +14179,14 @@
           <t>Optimization potential at 5 to 10 percent (Alternatives menu)</t>
         </is>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="25">
         <f>Assumptions!B42*Assumptions!B43</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr"/>
-      <c r="B52" s="18">
+      <c r="B52" s="25">
         <f>Assumptions!B42*Assumptions!B44</f>
         <v/>
       </c>
@@ -12009,7 +14204,7 @@
           <t>Straight-line, NMES to the Paris schools (miles)</t>
         </is>
       </c>
-      <c r="B55" s="29" t="n">
+      <c r="B55" s="31" t="n">
         <v>8.871</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12024,7 +14219,7 @@
           <t>Measured road distance, US 460 (miles)</t>
         </is>
       </c>
-      <c r="B56" s="29" t="n">
+      <c r="B56" s="31" t="n">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12039,7 +14234,7 @@
           <t>Implied road factor on the measured pair</t>
         </is>
       </c>
-      <c r="B57" s="30">
+      <c r="B57" s="32">
         <f>B56/B55</f>
         <v/>
       </c>
@@ -12050,7 +14245,7 @@
           <t>Road factor applied elsewhere (the measured US 460 pair implies 1.13)</t>
         </is>
       </c>
-      <c r="B58" s="28" t="n">
+      <c r="B58" s="30" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -12060,7 +14255,7 @@
           <t>Area-average added distance under closure, one way, straight-line</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n">
+      <c r="B59" s="31" t="n">
         <v>3.271</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12075,7 +14270,7 @@
           <t>Area-average added distance, road</t>
         </is>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="26">
         <f>B59*B58</f>
         <v/>
       </c>
@@ -12086,7 +14281,7 @@
           <t>Farthest corner of the zone, straight-line to Paris / to NMES</t>
         </is>
       </c>
-      <c r="B61" s="29" t="n">
+      <c r="B61" s="31" t="n">
         <v>15.1</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -12101,7 +14296,7 @@
           <t>Farthest corner by road: to Paris / to NMES (miles)</t>
         </is>
       </c>
-      <c r="B62" s="27">
+      <c r="B62" s="29">
         <f>ROUND(B61*B58,0)</f>
         <v/>
       </c>
@@ -12131,7 +14326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12163,32 +14358,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Low ($/yr)</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>High ($/yr)</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Confidence / what firms it up</t>
         </is>
@@ -12200,7 +14395,7 @@
           <t>KRS 160.470 four percent revenue mechanics (context; the published lead lever is the 2018 restore, Tax_History rows 70-91)</t>
         </is>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="25">
         <f>Tax_History!B50</f>
         <v/>
       </c>
@@ -12285,7 +14480,7 @@
           <t>Attrition-based staffing alignment</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="25">
         <f>Assumptions!B48*Assumptions!B41</f>
         <v/>
       </c>
@@ -12314,7 +14509,7 @@
           <t>Administrative restraint</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="25">
         <f>Assumptions!B47*(Assumptions!B46-Assumptions!B45)</f>
         <v/>
       </c>
@@ -12343,11 +14538,11 @@
           <t>Transportation optimization</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="25">
         <f>Assumptions!B42*Assumptions!B43</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="25">
         <f>Assumptions!B42*Assumptions!B44</f>
         <v/>
       </c>
@@ -12401,11 +14596,11 @@
           <t>Fill NMES to capacity (rebalance + transfers, net)</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="25">
         <f>Redistricting!B30</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="25">
         <f>Redistricting!B31</f>
         <v/>
       </c>
@@ -12431,11 +14626,11 @@
           <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="25">
         <f>25*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="25">
         <f>50*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
@@ -12456,16 +14651,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Total identified (ranges overlap; not additive to the penny)</t>
         </is>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="27">
         <f>SUM(B4:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="27">
         <f>SUM(C4:C12)</f>
         <v/>
       </c>
@@ -12527,7 +14722,7 @@
           <t>Average annual GF drawdown (FY2024-25)</t>
         </is>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="25">
         <f>GF_Summary!D16</f>
         <v/>
       </c>
@@ -12538,7 +14733,7 @@
           <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$20,007 at Closure_Model row 50)</t>
         </is>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="25">
         <f>Closure_Model!B20</f>
         <v/>
       </c>
@@ -12563,11 +14758,11 @@
           <t>Move 1: inspect fixed costs (every non-teaching position via attrition, administrative restructuring, transport, energy)</t>
         </is>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="19">
         <f>SUM(B7:B10)</f>
         <v/>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="19">
         <f>SUM(C7:C10)</f>
         <v/>
       </c>
@@ -12578,11 +14773,11 @@
           <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
         </is>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="19">
         <f>B6+B11+B12</f>
         <v/>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="19">
         <f>C6+C11+C12</f>
         <v/>
       </c>
@@ -12593,11 +14788,11 @@
           <t>Move 3: the honest revenue conversation, year one (this cell keeps the 4 percent + delinquency mechanics for continuity; the published lead lever is the 2018 restore, about $1.5M a year, Tax_History rows 82-89)</t>
         </is>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="19">
         <f>B4+B5</f>
         <v/>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="19">
         <f>C4+C5</f>
         <v/>
       </c>
@@ -12608,11 +14803,11 @@
           <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
         </is>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="19">
         <f>B26+B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="19">
         <f>C26+C27+C28</f>
         <v/>
       </c>
@@ -12671,7 +14866,7 @@
           <t>Recurring surplus after the trending gap (website defaults + full restore)</t>
         </is>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="19">
         <f>B31+B32-B33</f>
         <v/>
       </c>
@@ -12709,7 +14904,7 @@
           <t>New GF-leveraged bonds supported (4.5%, 20 years; same basis as Debt_Service)</t>
         </is>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="19">
         <f>B36*(1-1.045^-20)/0.045</f>
         <v/>
       </c>
@@ -12735,7 +14930,7 @@
           <t>Building capacity, together</t>
         </is>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="19">
         <f>B37+B38</f>
         <v/>
       </c>
@@ -12758,1311 +14953,6 @@
       <c r="A42" s="21" t="inlineStr">
         <is>
           <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F110"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Outstanding Bonds: Bourbon County School District Finance Corporation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Source: FY2025 audited financial statements, Note 4. Facility funds and debt are restricted; they cannot pay operating costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Series</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>Maturity</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>Outstanding 6/30/25</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>2255000</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1.90-2.10%</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>348000</v>
-      </c>
-      <c r="F5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2013R</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>468000</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2.75-4.05%</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>585000</v>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>Audit figures internally inconsistent; maturity typo in audit; district to correct</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>5700000</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1.00-3.00%</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>3145000</v>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>Refunded $5,315,000 of 2009 bonds; NPV savings $314,834</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>1560000</v>
-      </c>
-      <c r="F8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>3620000</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>0.50-1.85%</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>3405000</v>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>Refunded $3,410,000 of 2011 bonds; NPV savings $106,627</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>810000</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>3.65-4.00%</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>755000</v>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>Purpose to be confirmed from official statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>6055000</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>4.00-5.00%</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>5945290</v>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>Funds active construction program; purpose to be published</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="24">
-        <f>SUM(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>SUM(E5:E11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>ANNUAL DEBT SERVICE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>District-paid, FY2025</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>1150216</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>District-paid, FY2026</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>1578700</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Increase, FY2025 to FY2026</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>B16-B15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>FY2026 total including state (SFCC) share</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>1846159</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>SFCC-paid principal over life of bonds</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>1568809</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>BONDING CAPACITY: WHAT CLOSURE CAN AND CANNOT CHANGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Average Daily Attendance, FY2025 (SEEK basis)</t>
-        </is>
-      </c>
-      <c r="B22" s="29" t="n">
-        <v>2242.5</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>FY2025 audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Capital outlay allotment per year (KRS 157.420, $100 per ADA)</t>
-        </is>
-      </c>
-      <c r="B23" s="9">
-        <f>100*B22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Bondable share of capital outlay (702 KAR 4:160 safety factor)</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Building-fund and debt-fund property tax, FY2025 (the 'nickel' stream)</t>
-        </is>
-      </c>
-      <c r="B25" s="18">
-        <f>Tax_History!B33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>District-paid debt service, FY2026</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>1578700</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Annual restricted margin available for new debt (illustrative)</t>
-        </is>
-      </c>
-      <c r="B27" s="31">
-        <f>B23*B24+B25-B26</f>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>Simplified: KDE's official bonding potential statement is the authority and should be published</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Unused bonding capacity stated in the FY2024 audit</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>23500000</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>FY2024 audit note</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Why closing NMES does not create bonding capacity: capacity is built from the streams above, none of which</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>grows when a school closes. Each student who leaves the district subtracts $100 per year from capital outlay</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>and the SEEK base from operations. Sale proceeds are one-time and restricted to capital use. What a closure</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>changes is the facility plan's priority list, which steers SFCC offers (KRS 157.622) toward other projects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>That is a choice about priorities, not a gain in capacity, and it should be argued openly with the BG-1,</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>the official statement, and the bonding potential statement all public.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>THE $14 MILLION PLAN (JULY 15, 2026 PLANNING COMMITTEE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Stated plan: free up $800,000 to $1,000,000 a year of operating money to bond $14 million</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Proposed bond amount</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n">
-        <v>14000000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Assumed interest rate</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="n">
-        <v>0.045</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Assumed term, years</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Annual debt service on the proposed bond</t>
-        </is>
-      </c>
-      <c r="B42" s="31">
-        <f>B39*B40/(1-(1+B40)^-B41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="21" t="inlineStr">
-        <is>
-          <t>Payment is approximately the operating amount the plan frees up; compare the savings scenarios below</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>WHAT EACH SAVINGS ESTIMATE COULD ACTUALLY BOND</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Bond principal supported = annual savings x present-value annuity factor at the rate and term above</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>District's own KDE-filed excess cost of NMES vs peer elementaries</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>121220</v>
-      </c>
-      <c r="C46" s="9">
-        <f>B46*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>Above the closure model's central case ($52,514); the weighted median itself is negative (-$20,007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Closure model median (v4.5 weighted grid)</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n">
-        <v>-20007</v>
-      </c>
-      <c r="C47" s="9">
-        <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="F47" s="21" t="inlineStr">
-        <is>
-          <t>Closure_Model tab, 5,832-combination grid; the median scenario loses money</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Closure model best case (favorable tail)</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="n">
-        <v>484582</v>
-      </c>
-      <c r="C48" s="9">
-        <f>B48*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="F48" s="21" t="inlineStr">
-        <is>
-          <t>Closure_Model tab B49</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Administration's claim, July 15, 2026</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C49" s="9">
-        <f>B49*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="F49" s="21" t="inlineStr">
-        <is>
-          <t>Unpublished derivation; reconcile with KDE-filed school-level spending</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Only the administration's own number reaches $14 million. The audited excess cost supports about $1.6 million.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>DISTRICT-PAID DEBT SERVICE SCHEDULE (FY2025 AUDIT, NOTE 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Payments fall as the 2013, 2016, and 2020 series retire; this falling schedule is the room a wrap-around structure fills</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>1578700</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>1575060</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>1578719</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>1577258</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>FY2030</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n">
-        <v>1578340</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>FY2031-35 average</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n">
-        <v>1321112</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>FY2036-40 average</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n">
-        <v>398915</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>FY2041-45 average</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>260708</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>THE LEVERS THAT DO NOT CLOSE A SCHOOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Remaining restricted capacity (FY2024 audit $23.5M less local share of the 2024 issue, approximate)</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="F64" s="21" t="inlineStr">
-        <is>
-          <t>Exact figure is the fiscal agent's bonding potential statement; demand it</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Certified real and personal property assessment, FY2025</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n">
-        <v>1843569625</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Recallable nickel status: ALREADY LEVIED August 17, 2023, inside the existing rate</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>levied</t>
-        </is>
-      </c>
-      <c r="F66" s="21" t="inlineStr">
-        <is>
-          <t>KDE Nickel Levy Chart (March 2024) dates Bourbon's recallable levy 8/17/2023; KDE's levied-rates file (April 30, 2026) decomposes the 52.4-cent rate as 41.0 general fund + 5.7 FSPK + 5.7 recallable. Paris Independent, for scale: 71.5 cents with 17.4 recallable</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>New annual state equalization on the recallable nickel (full value, FY2027 schedule)</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>276246</v>
-      </c>
-      <c r="F67" s="21" t="inlineStr">
-        <is>
-          <t>Phasing in on KDE SEEK schedules: $82,866 FY2025, $55,515 FY2026, $276,246 FY2027. New restricted revenue, no board action required</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Bonds the new equalization alone supports</t>
-        </is>
-      </c>
-      <c r="B68" s="9">
-        <f>B67*(1-(1+B40)^-B41)/B40</f>
-        <v/>
-      </c>
-      <c r="F68" s="21" t="inlineStr">
-        <is>
-          <t>Additive to the FY2024 audit's bonding potential, which predates the equalization</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>SFCC offers of assistance, typical cycle</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>1750000</v>
-      </c>
-      <c r="F69" s="21" t="inlineStr">
-        <is>
-          <t>State already pays $1,568,809 of current principal</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>FY2026 YEAR-END, DISTRICT'S OWN KDE BUDGET MONITORING TOOL (UNAUDITED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>June 2026 financial packet, board agenda July 16, 2026; MUNIS run July 15, 2026. Audit will finalize these figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>General Fund revenue, FY2026 actual (excludes carryforward and on-behalf)</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>22103877</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>General Fund expenditures, FY2026 actual</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="n">
-        <v>22477866</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Net General Fund change, FY2026 (unaudited)</t>
-        </is>
-      </c>
-      <c r="B75" s="31">
-        <f>B73-B74</f>
-        <v/>
-      </c>
-      <c r="F75" s="21" t="inlineStr">
-        <is>
-          <t>Compare net changes of -$1,065,657 in FY2024 and -$1,225,465 in FY2025 (audited)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Revenues over budget per the monitoring tool</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n">
-        <v>2225835</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Salaries under budget per the monitoring tool</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n">
-        <v>587592</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>Salaries below FY2025 actuals</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n">
-        <v>223974</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>Caveat 1: miscellaneous revenue (object 1990) budgeted at zero, received</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n">
-        <v>1567829</v>
-      </c>
-      <c r="F79" s="21" t="inlineStr">
-        <is>
-          <t>Unbudgeted even in the final amended budget; the district should identify this receipt on the record</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  of which booked in June (period 12) alone</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n">
-        <v>1413929</v>
-      </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>Months 1-11 produced $153,900 combined, a normal run rate; the balance sheet shows no receivable behind the June entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Caveat 2: restricted capital money transferred INTO the General Fund in June 2026</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n">
-        <v>1320939</v>
-      </c>
-      <c r="F81" s="21" t="inlineStr">
-        <is>
-          <t>Object 5210: $1,098,663 from the Building Fund (320) + $222,276 from Capital Outlay (310), which ended the year at $0 ($1,098,663 + $222,276 = $1,320,939 per the GF receipts ledger; the packet's fund 320 page records $1,098,633, a $30 internal discrepancy in the district's own packet). Lawful under budget-act capital funds flexibility. The Building Fund piece was budgeted from September 2025 ($1,120,203); the $222,276 Capital Outlay piece appears in no version of the FY2026 budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>Net change excluding the capital transfer</t>
-        </is>
-      </c>
-      <c r="B82" s="9">
-        <f>B73-B74-B81</f>
-        <v/>
-      </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>About -$1.69 million: the operating result on operating revenue alone</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>Net change excluding the transfer and the unidentified June receipt</t>
-        </is>
-      </c>
-      <c r="B83" s="9">
-        <f>B73-B74-B81-B80</f>
-        <v/>
-      </c>
-      <c r="F83" s="21" t="inlineStr">
-        <is>
-          <t>About -$3.11 million: the same range as the audited years</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>June 2026 General Fund revenue vs June 2025 (district's monitoring tool)</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n">
-        <v>3923096</v>
-      </c>
-      <c r="C84" s="8" t="n">
-        <v>1130736</v>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>The two June entries above are 98 percent of the year-over-year June difference</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Variance identity from the packet: projected fund balance reconciles to the dollar</t>
-        </is>
-      </c>
-      <c r="B85" s="9">
-        <f>1489853+2225835+587592-224087</f>
-        <v/>
-      </c>
-      <c r="F85" s="21" t="inlineStr">
-        <is>
-          <t>Contingency + revenue over budget + salary savings - expense overrun = $4,079,193, the tool's projected balance. The June misc entry is 63 percent of the revenue beat</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>BUILDING FUND FLOWS, FY2026 (fund 320, same packet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>Building Fund transfers out, FY2026 total</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n">
-        <v>2481394</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  to Debt Service (fund 400)</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n">
-        <v>1382761</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  to the General Fund (June 2026)</t>
-        </is>
-      </c>
-      <c r="B89" s="9">
-        <f>B87-B88</f>
-        <v/>
-      </c>
-      <c r="F89" s="21" t="inlineStr">
-        <is>
-          <t>The residual after debt service. This is the restricted stream a $14 million bond would lean on; in FY2026 it plugged the operating budget instead</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>Bond capacity that residual supports at the same rate and term</t>
-        </is>
-      </c>
-      <c r="B90" s="9">
-        <f>B89*(1-(1+B40)^-B41)/B40</f>
-        <v/>
-      </c>
-      <c r="F90" s="21" t="inlineStr">
-        <is>
-          <t>About $14 million: the plan's own target, carried by restricted money. The closure's role is only to replace the sweep, and any recurring million dollars does that</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>SCENARIO: BALANCE THE BUDGET AND EXPAND BONDING CAPACITY, NO CLOSURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Two cases differ only in the operating gap assumed. Conservative treats the FY2026 $1.57M receipt as one-time;</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>trend uses the unaudited FY2026 net change. The sweep is ended in both cases; only genuine remainder services debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="inlineStr">
-        <is>
-          <t>FY2026 trend</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>Operating gap to close first</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="n">
-        <v>1787918</v>
-      </c>
-      <c r="C96" s="8" t="n">
-        <v>373989</v>
-      </c>
-      <c r="F96" s="21" t="inlineStr">
-        <is>
-          <t>Editable. $1.9M = FY2026 result excluding the unidentified receipt; $373,989 = FY2026 unaudited net change</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>New recurring revenue: 4 percent levy taken three years running (mechanics case; with the published 2018 restore instead, the gap clears in every case: Alternatives transformative check)</t>
-        </is>
-      </c>
-      <c r="B97" s="18">
-        <f>Tax_History!B32*(1.04^3-1)</f>
-        <v/>
-      </c>
-      <c r="C97" s="18">
-        <f>Tax_History!B32*(1.04^3-1)</f>
-        <v/>
-      </c>
-      <c r="F97" s="21" t="inlineStr">
-        <is>
-          <t>Same base and compounding as the levy tab; year 1 is $313,162, year 3 cumulative $977,568</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Recurring cost reductions, not from closing a school</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C98" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F98" s="21" t="inlineStr">
-        <is>
-          <t>Editable. For scale from the FY2025 audit: district administration grew $221K in one year, salaries fell $224K through attrition, spending ran $859K under budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>End the capital-to-GF sweep (required before the building-fund residual can be pledged to new bonds)</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="n">
-        <v>1320939</v>
-      </c>
-      <c r="C99" s="8" t="n">
-        <v>1320939</v>
-      </c>
-      <c r="F99" s="21" t="inlineStr">
-        <is>
-          <t>The FY2026 sweep is General Fund revenue today; pledging the residual means replacing it. Without this row the restricted stream would be counted twice</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>Operating room left for debt service after the budget balances and the sweep ends</t>
-        </is>
-      </c>
-      <c r="B100" s="9">
-        <f>MAX(0,B97+B98-B96-B99)</f>
-        <v/>
-      </c>
-      <c r="C100" s="9">
-        <f>MAX(0,C97+C98-C96-C99)</f>
-        <v/>
-      </c>
-      <c r="F100" s="21" t="inlineStr">
-        <is>
-          <t>Trend case balances with about $283K to spare; the conservative case is still about $1.24M short, so its total below leans on equalization and existing restricted capacity only</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>General-fund bond capacity from that room</t>
-        </is>
-      </c>
-      <c r="B101" s="9">
-        <f>B100*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="C101" s="9">
-        <f>C100*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>New state equalization on the already-levied recallable nickel</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="n">
-        <v>276246</v>
-      </c>
-      <c r="C102" s="8" t="n">
-        <v>276246</v>
-      </c>
-      <c r="F102" s="21" t="inlineStr">
-        <is>
-          <t>FY2027 SEEK schedule; the recallable nickel itself is already levied and its local yield is already inside the building-fund stream above</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>Bond capacity from the new equalization</t>
-        </is>
-      </c>
-      <c r="B103" s="9">
-        <f>B102*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-      <c r="C103" s="9">
-        <f>C102*(1-(1+B$40)^-B$41)/B$40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>Existing unused restricted capacity, approximate</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="C104" s="8" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
-        <is>
-          <t>FY2024 audit $23.5M less local share of the 2024 issue; fiscal agent's statement is the authority</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="22" t="inlineStr">
-        <is>
-          <t>Total capacity available without closing a school</t>
-        </is>
-      </c>
-      <c r="B105" s="24">
-        <f>B101+B103+B104</f>
-        <v/>
-      </c>
-      <c r="C105" s="24">
-        <f>C101+C103+C104</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Roughly $22.2 million in the conservative case and $42.1 million on the FY2026 trend, with the budget balanced</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>first in both. The administration's plan reaches $32 million at face value and leaves the deficit in place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Floor check: even with zero general-fund room, the restricted capacity plus new equalization alone are about $21 million.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Pledging the building-fund residual to new bonds requires ending the capital-to-operations sweep documented above,</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>which is exactly what the administration's plan implies; the only question is which recurring million replaces it.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -159,6 +159,7 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,7 +179,6 @@
     <xf numFmtId="168" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -783,32 +783,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Series</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Maturity</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Outstanding 6/30/25</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1008,11 +1008,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
@@ -1088,7 +1088,7 @@
           <t>Average Daily Attendance, FY2025 (SEEK basis)</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <v>2242.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
           <t>Building-fund and debt-fund property tax, FY2025 (the 'nickel' stream)</t>
         </is>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="26">
         <f>Tax_History!B33</f>
         <v/>
       </c>
@@ -1145,7 +1145,7 @@
           <t>Annual restricted margin available for new debt (illustrative)</t>
         </is>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="34">
         <f>B23*B24+B25-B26</f>
         <v/>
       </c>
@@ -1252,7 +1252,7 @@
           <t>Assumed term, years</t>
         </is>
       </c>
-      <c r="B41" s="34" t="n">
+      <c r="B41" s="35" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
           <t>Annual debt service on the proposed bond</t>
         </is>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="34">
         <f>B39*B40/(1-(1+B40)^-B41)</f>
         <v/>
       </c>
@@ -1598,7 +1598,7 @@
           <t>Net General Fund change, FY2026 (unaudited)</t>
         </is>
       </c>
-      <c r="B75" s="33">
+      <c r="B75" s="34">
         <f>B73-B74</f>
         <v/>
       </c>
@@ -1830,12 +1830,12 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="24" t="inlineStr">
+      <c r="B95" s="25" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="C95" s="24" t="inlineStr">
+      <c r="C95" s="25" t="inlineStr">
         <is>
           <t>FY2026 trend</t>
         </is>
@@ -1865,11 +1865,11 @@
           <t>New recurring revenue: 4 percent levy taken three years running (mechanics case; with the published 2018 restore instead, the gap clears in every case: Alternatives transformative check)</t>
         </is>
       </c>
-      <c r="B97" s="25">
+      <c r="B97" s="26">
         <f>Tax_History!B32*(1.04^3-1)</f>
         <v/>
       </c>
-      <c r="C97" s="25">
+      <c r="C97" s="26">
         <f>Tax_History!B32*(1.04^3-1)</f>
         <v/>
       </c>
@@ -2007,11 +2007,11 @@
           <t>Total capacity available without closing a school</t>
         </is>
       </c>
-      <c r="B105" s="27">
+      <c r="B105" s="28">
         <f>B101+B103+B104</f>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="28">
         <f>C101+C103+C104</f>
         <v/>
       </c>
@@ -2087,27 +2087,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Projected ending General Fund balance</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
@@ -2188,19 +2188,19 @@
           <t>2% contingency floor (approx., FY2025 basis)</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>GF_Summary!$D$14</f>
         <v/>
       </c>
@@ -2255,27 +2255,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Recurring GF impact ($/yr, by yr 3)</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Projected FY2029 balance</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>One-time costs</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>What it requires and risks</t>
         </is>
@@ -2335,7 +2335,7 @@
           <t>3. Districtwide recovery plan (menu plus levy; includes rebalancing and growing NMES)</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>Alternatives!B19</f>
         <v/>
       </c>
@@ -2411,7 +2411,7 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="32" t="n">
         <v>61.3</v>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -2426,7 +2426,7 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>60.6</v>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>55.9</v>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>54.2</v>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>49.2</v>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
           <t>Tangible/personal rate (recent)</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
           <t>Motor vehicle rate</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="32" t="n">
         <v>54.7</v>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
           <t>Fayette County</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="32" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -2548,7 +2548,7 @@
           <t>Paris Independent</t>
         </is>
       </c>
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="32" t="n">
         <v>71.5</v>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
           <t>Clark County</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="32" t="n">
         <v>65.5</v>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
           <t>Bath County</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <v>63.4</v>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
           <t>Scott County</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="32" t="n">
         <v>62.9</v>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
           <t>Harrison County</t>
         </is>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <v>57.7</v>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
           <t>Montgomery County</t>
         </is>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
           <t>Bourbon County</t>
         </is>
       </c>
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
           <t>Nicholas County</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="32" t="n">
         <v>43.1</v>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
           <t>Statewide school average (DOR Table II, 2025)</t>
         </is>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="32" t="n">
         <v>65.13</v>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
           <t>Base: FY2025 General Fund real + personal collections</t>
         </is>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="26">
         <f>B32</f>
         <v/>
       </c>
@@ -2896,82 +2896,82 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>District</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B57" s="25" t="inlineStr">
         <is>
           <t>2012-13</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C57" s="25" t="inlineStr">
         <is>
           <t>2013-14</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D57" s="25" t="inlineStr">
         <is>
           <t>2014-15</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>2015-16</t>
         </is>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="F57" s="25" t="inlineStr">
         <is>
           <t>2016-17</t>
         </is>
       </c>
-      <c r="G57" s="24" t="inlineStr">
+      <c r="G57" s="25" t="inlineStr">
         <is>
           <t>2017-18</t>
         </is>
       </c>
-      <c r="H57" s="24" t="inlineStr">
+      <c r="H57" s="25" t="inlineStr">
         <is>
           <t>2018-19</t>
         </is>
       </c>
-      <c r="I57" s="24" t="inlineStr">
+      <c r="I57" s="25" t="inlineStr">
         <is>
           <t>2019-20</t>
         </is>
       </c>
-      <c r="J57" s="24" t="inlineStr">
+      <c r="J57" s="25" t="inlineStr">
         <is>
           <t>2020-21</t>
         </is>
       </c>
-      <c r="K57" s="24" t="inlineStr">
+      <c r="K57" s="25" t="inlineStr">
         <is>
           <t>2021-22</t>
         </is>
       </c>
-      <c r="L57" s="24" t="inlineStr">
+      <c r="L57" s="25" t="inlineStr">
         <is>
           <t>2022-23</t>
         </is>
       </c>
-      <c r="M57" s="24" t="inlineStr">
+      <c r="M57" s="25" t="inlineStr">
         <is>
           <t>2023-24</t>
         </is>
       </c>
-      <c r="N57" s="24" t="inlineStr">
+      <c r="N57" s="25" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="O57" s="24" t="inlineStr">
+      <c r="O57" s="25" t="inlineStr">
         <is>
           <t>2025-26</t>
         </is>
       </c>
-      <c r="P57" s="24" t="inlineStr">
+      <c r="P57" s="25" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
@@ -2983,49 +2983,49 @@
           <t>Bath</t>
         </is>
       </c>
-      <c r="B58" s="31" t="n">
+      <c r="B58" s="32" t="n">
         <v>36.8</v>
       </c>
-      <c r="C58" s="31" t="n">
+      <c r="C58" s="32" t="n">
         <v>44</v>
       </c>
-      <c r="D58" s="31" t="n">
+      <c r="D58" s="32" t="n">
         <v>44.2</v>
       </c>
-      <c r="E58" s="31" t="n">
+      <c r="E58" s="32" t="n">
         <v>44.8</v>
       </c>
-      <c r="F58" s="31" t="n">
+      <c r="F58" s="32" t="n">
         <v>44.8</v>
       </c>
-      <c r="G58" s="31" t="n">
+      <c r="G58" s="32" t="n">
         <v>47.2</v>
       </c>
-      <c r="H58" s="31" t="n">
+      <c r="H58" s="32" t="n">
         <v>52.6</v>
       </c>
-      <c r="I58" s="31" t="n">
+      <c r="I58" s="32" t="n">
         <v>52.6</v>
       </c>
-      <c r="J58" s="31" t="n">
+      <c r="J58" s="32" t="n">
         <v>52.6</v>
       </c>
-      <c r="K58" s="31" t="n">
+      <c r="K58" s="32" t="n">
         <v>52.4</v>
       </c>
-      <c r="L58" s="31" t="n">
+      <c r="L58" s="32" t="n">
         <v>54.1</v>
       </c>
-      <c r="M58" s="31" t="n">
+      <c r="M58" s="32" t="n">
         <v>57.8</v>
       </c>
-      <c r="N58" s="31" t="n">
+      <c r="N58" s="32" t="n">
         <v>60.7</v>
       </c>
-      <c r="O58" s="31" t="n">
+      <c r="O58" s="32" t="n">
         <v>63.4</v>
       </c>
-      <c r="P58" s="35">
+      <c r="P58" s="36">
         <f>(O58/B58-1)</f>
         <v/>
       </c>
@@ -3036,49 +3036,49 @@
           <t>Scott</t>
         </is>
       </c>
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="32" t="n">
         <v>45.3</v>
       </c>
-      <c r="C59" s="31" t="n">
+      <c r="C59" s="32" t="n">
         <v>47.2</v>
       </c>
-      <c r="D59" s="31" t="n">
+      <c r="D59" s="32" t="n">
         <v>47.6</v>
       </c>
-      <c r="E59" s="31" t="n">
+      <c r="E59" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="F59" s="31" t="n">
+      <c r="F59" s="32" t="n">
         <v>49.6</v>
       </c>
-      <c r="G59" s="31" t="n">
+      <c r="G59" s="32" t="n">
         <v>56.4</v>
       </c>
-      <c r="H59" s="31" t="n">
+      <c r="H59" s="32" t="n">
         <v>56.4</v>
       </c>
-      <c r="I59" s="31" t="n">
+      <c r="I59" s="32" t="n">
         <v>57.1</v>
       </c>
-      <c r="J59" s="31" t="n">
+      <c r="J59" s="32" t="n">
         <v>57.6</v>
       </c>
-      <c r="K59" s="31" t="n">
+      <c r="K59" s="32" t="n">
         <v>58.1</v>
       </c>
-      <c r="L59" s="31" t="n">
+      <c r="L59" s="32" t="n">
         <v>58.1</v>
       </c>
-      <c r="M59" s="31" t="n">
+      <c r="M59" s="32" t="n">
         <v>62.8</v>
       </c>
-      <c r="N59" s="31" t="n">
+      <c r="N59" s="32" t="n">
         <v>62.9</v>
       </c>
-      <c r="O59" s="31" t="n">
+      <c r="O59" s="32" t="n">
         <v>62.9</v>
       </c>
-      <c r="P59" s="35">
+      <c r="P59" s="36">
         <f>(O59/B59-1)</f>
         <v/>
       </c>
@@ -3089,49 +3089,49 @@
           <t>Harrison</t>
         </is>
       </c>
-      <c r="B60" s="31" t="n">
+      <c r="B60" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="C60" s="31" t="n">
+      <c r="C60" s="32" t="n">
         <v>45.2</v>
       </c>
-      <c r="D60" s="31" t="n">
+      <c r="D60" s="32" t="n">
         <v>47.2</v>
       </c>
-      <c r="E60" s="31" t="n">
+      <c r="E60" s="32" t="n">
         <v>47.3</v>
       </c>
-      <c r="F60" s="31" t="n">
+      <c r="F60" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="G60" s="31" t="n">
+      <c r="G60" s="32" t="n">
         <v>50.5</v>
       </c>
-      <c r="H60" s="31" t="n">
+      <c r="H60" s="32" t="n">
         <v>50.5</v>
       </c>
-      <c r="I60" s="31" t="n">
+      <c r="I60" s="32" t="n">
         <v>51.7</v>
       </c>
-      <c r="J60" s="31" t="n">
+      <c r="J60" s="32" t="n">
         <v>51.7</v>
       </c>
-      <c r="K60" s="31" t="n">
+      <c r="K60" s="32" t="n">
         <v>57.7</v>
       </c>
-      <c r="L60" s="31" t="n">
+      <c r="L60" s="32" t="n">
         <v>57.7</v>
       </c>
-      <c r="M60" s="31" t="n">
+      <c r="M60" s="32" t="n">
         <v>57.7</v>
       </c>
-      <c r="N60" s="31" t="n">
+      <c r="N60" s="32" t="n">
         <v>57.7</v>
       </c>
-      <c r="O60" s="31" t="n">
+      <c r="O60" s="32" t="n">
         <v>57.7</v>
       </c>
-      <c r="P60" s="35">
+      <c r="P60" s="36">
         <f>(O60/B60-1)</f>
         <v/>
       </c>
@@ -3142,49 +3142,49 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="B61" s="31" t="n">
+      <c r="B61" s="32" t="n">
         <v>53.6</v>
       </c>
-      <c r="C61" s="31" t="n">
+      <c r="C61" s="32" t="n">
         <v>55.9</v>
       </c>
-      <c r="D61" s="31" t="n">
+      <c r="D61" s="32" t="n">
         <v>57.4</v>
       </c>
-      <c r="E61" s="31" t="n">
+      <c r="E61" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="F61" s="31" t="n">
+      <c r="F61" s="32" t="n">
         <v>62.2</v>
       </c>
-      <c r="G61" s="31" t="n">
+      <c r="G61" s="32" t="n">
         <v>62.2</v>
       </c>
-      <c r="H61" s="31" t="n">
+      <c r="H61" s="32" t="n">
         <v>62.2</v>
       </c>
-      <c r="I61" s="31" t="n">
+      <c r="I61" s="32" t="n">
         <v>63.7</v>
       </c>
-      <c r="J61" s="31" t="n">
+      <c r="J61" s="32" t="n">
         <v>63.7</v>
       </c>
-      <c r="K61" s="31" t="n">
+      <c r="K61" s="32" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="L61" s="31" t="n">
+      <c r="L61" s="32" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="M61" s="31" t="n">
+      <c r="M61" s="32" t="n">
         <v>67.5</v>
       </c>
-      <c r="N61" s="31" t="n">
+      <c r="N61" s="32" t="n">
         <v>66.8</v>
       </c>
-      <c r="O61" s="31" t="n">
+      <c r="O61" s="32" t="n">
         <v>65.5</v>
       </c>
-      <c r="P61" s="35">
+      <c r="P61" s="36">
         <f>(O61/B61-1)</f>
         <v/>
       </c>
@@ -3195,49 +3195,49 @@
           <t>Fayette</t>
         </is>
       </c>
-      <c r="B62" s="31" t="n">
+      <c r="B62" s="32" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="C62" s="31" t="n">
+      <c r="C62" s="32" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="D62" s="31" t="n">
+      <c r="D62" s="32" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E62" s="31" t="n">
+      <c r="E62" s="32" t="n">
         <v>74</v>
       </c>
-      <c r="F62" s="31" t="n">
+      <c r="F62" s="32" t="n">
         <v>75</v>
       </c>
-      <c r="G62" s="31" t="n">
+      <c r="G62" s="32" t="n">
         <v>75</v>
       </c>
-      <c r="H62" s="31" t="n">
+      <c r="H62" s="32" t="n">
         <v>81</v>
       </c>
-      <c r="I62" s="31" t="n">
+      <c r="I62" s="32" t="n">
         <v>81</v>
       </c>
-      <c r="J62" s="31" t="n">
+      <c r="J62" s="32" t="n">
         <v>81</v>
       </c>
-      <c r="K62" s="31" t="n">
+      <c r="K62" s="32" t="n">
         <v>80.8</v>
       </c>
-      <c r="L62" s="31" t="n">
+      <c r="L62" s="32" t="n">
         <v>83.3</v>
       </c>
-      <c r="M62" s="31" t="n">
+      <c r="M62" s="32" t="n">
         <v>81</v>
       </c>
-      <c r="N62" s="31" t="n">
+      <c r="N62" s="32" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="O62" s="31" t="n">
+      <c r="O62" s="32" t="n">
         <v>79.8</v>
       </c>
-      <c r="P62" s="35">
+      <c r="P62" s="36">
         <f>(O62/B62-1)</f>
         <v/>
       </c>
@@ -3248,49 +3248,49 @@
           <t>Paris Ind</t>
         </is>
       </c>
-      <c r="B63" s="31" t="n">
+      <c r="B63" s="32" t="n">
         <v>61</v>
       </c>
-      <c r="C63" s="31" t="n">
+      <c r="C63" s="32" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="D63" s="31" t="n">
+      <c r="D63" s="32" t="n">
         <v>66.5</v>
       </c>
-      <c r="E63" s="31" t="n">
+      <c r="E63" s="32" t="n">
         <v>69</v>
       </c>
-      <c r="F63" s="31" t="n">
+      <c r="F63" s="32" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="G63" s="31" t="n">
+      <c r="G63" s="32" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="H63" s="31" t="n">
+      <c r="H63" s="32" t="n">
         <v>78.3</v>
       </c>
-      <c r="I63" s="31" t="n">
+      <c r="I63" s="32" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="J63" s="31" t="n">
+      <c r="J63" s="32" t="n">
         <v>68.7</v>
       </c>
-      <c r="K63" s="31" t="n">
+      <c r="K63" s="32" t="n">
         <v>74.5</v>
       </c>
-      <c r="L63" s="31" t="n">
+      <c r="L63" s="32" t="n">
         <v>71.5</v>
       </c>
-      <c r="M63" s="31" t="n">
+      <c r="M63" s="32" t="n">
         <v>71.5</v>
       </c>
-      <c r="N63" s="31" t="n">
+      <c r="N63" s="32" t="n">
         <v>71.5</v>
       </c>
-      <c r="O63" s="31" t="n">
+      <c r="O63" s="32" t="n">
         <v>71.5</v>
       </c>
-      <c r="P63" s="35">
+      <c r="P63" s="36">
         <f>(O63/B63-1)</f>
         <v/>
       </c>
@@ -3301,49 +3301,49 @@
           <t>Nicholas</t>
         </is>
       </c>
-      <c r="B64" s="31" t="n">
+      <c r="B64" s="32" t="n">
         <v>38.4</v>
       </c>
-      <c r="C64" s="31" t="n">
+      <c r="C64" s="32" t="n">
         <v>38.7</v>
       </c>
-      <c r="D64" s="31" t="n">
+      <c r="D64" s="32" t="n">
         <v>38.5</v>
       </c>
-      <c r="E64" s="31" t="n">
+      <c r="E64" s="32" t="n">
         <v>38.3</v>
       </c>
-      <c r="F64" s="31" t="n">
+      <c r="F64" s="32" t="n">
         <v>38.5</v>
       </c>
-      <c r="G64" s="31" t="n">
+      <c r="G64" s="32" t="n">
         <v>39.5</v>
       </c>
-      <c r="H64" s="31" t="n">
+      <c r="H64" s="32" t="n">
         <v>39.6</v>
       </c>
-      <c r="I64" s="31" t="n">
+      <c r="I64" s="32" t="n">
         <v>41</v>
       </c>
-      <c r="J64" s="31" t="n">
+      <c r="J64" s="32" t="n">
         <v>40.1</v>
       </c>
-      <c r="K64" s="31" t="n">
+      <c r="K64" s="32" t="n">
         <v>40.2</v>
       </c>
-      <c r="L64" s="31" t="n">
+      <c r="L64" s="32" t="n">
         <v>41.4</v>
       </c>
-      <c r="M64" s="31" t="n">
+      <c r="M64" s="32" t="n">
         <v>42.5</v>
       </c>
-      <c r="N64" s="31" t="n">
+      <c r="N64" s="32" t="n">
         <v>43.6</v>
       </c>
-      <c r="O64" s="31" t="n">
+      <c r="O64" s="32" t="n">
         <v>43.1</v>
       </c>
-      <c r="P64" s="35">
+      <c r="P64" s="36">
         <f>(O64/B64-1)</f>
         <v/>
       </c>
@@ -3354,49 +3354,49 @@
           <t>Montgomery</t>
         </is>
       </c>
-      <c r="B65" s="31" t="n">
+      <c r="B65" s="32" t="n">
         <v>49.4</v>
       </c>
-      <c r="C65" s="31" t="n">
+      <c r="C65" s="32" t="n">
         <v>49.4</v>
       </c>
-      <c r="D65" s="31" t="n">
+      <c r="D65" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="E65" s="31" t="n">
+      <c r="E65" s="32" t="n">
         <v>48.9</v>
       </c>
-      <c r="F65" s="31" t="n">
+      <c r="F65" s="32" t="n">
         <v>50.8</v>
       </c>
-      <c r="G65" s="31" t="n">
+      <c r="G65" s="32" t="n">
         <v>51.3</v>
       </c>
-      <c r="H65" s="31" t="n">
+      <c r="H65" s="32" t="n">
         <v>52.8</v>
       </c>
-      <c r="I65" s="31" t="n">
+      <c r="I65" s="32" t="n">
         <v>52.3</v>
       </c>
-      <c r="J65" s="31" t="n">
+      <c r="J65" s="32" t="n">
         <v>52.3</v>
       </c>
-      <c r="K65" s="31" t="n">
+      <c r="K65" s="32" t="n">
         <v>52.3</v>
       </c>
-      <c r="L65" s="31" t="n">
+      <c r="L65" s="32" t="n">
         <v>52.2</v>
       </c>
-      <c r="M65" s="31" t="n">
+      <c r="M65" s="32" t="n">
         <v>52.4</v>
       </c>
-      <c r="N65" s="31" t="n">
+      <c r="N65" s="32" t="n">
         <v>52.5</v>
       </c>
-      <c r="O65" s="31" t="n">
+      <c r="O65" s="32" t="n">
         <v>52.5</v>
       </c>
-      <c r="P65" s="35">
+      <c r="P65" s="36">
         <f>(O65/B65-1)</f>
         <v/>
       </c>
@@ -3407,49 +3407,49 @@
           <t>Bourbon Co</t>
         </is>
       </c>
-      <c r="B66" s="31" t="n">
+      <c r="B66" s="32" t="n">
         <v>55.4</v>
       </c>
-      <c r="C66" s="31" t="n">
+      <c r="C66" s="32" t="n">
         <v>57.6</v>
       </c>
-      <c r="D66" s="31" t="n">
+      <c r="D66" s="32" t="n">
         <v>57.3</v>
       </c>
-      <c r="E66" s="31" t="n">
+      <c r="E66" s="32" t="n">
         <v>59.1</v>
       </c>
-      <c r="F66" s="31" t="n">
+      <c r="F66" s="32" t="n">
         <v>58.8</v>
       </c>
-      <c r="G66" s="31" t="n">
+      <c r="G66" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="H66" s="31" t="n">
+      <c r="H66" s="32" t="n">
         <v>61.3</v>
       </c>
-      <c r="I66" s="31" t="n">
+      <c r="I66" s="32" t="n">
         <v>60.6</v>
       </c>
-      <c r="J66" s="31" t="n">
+      <c r="J66" s="32" t="n">
         <v>55.9</v>
       </c>
-      <c r="K66" s="31" t="n">
+      <c r="K66" s="32" t="n">
         <v>54.2</v>
       </c>
-      <c r="L66" s="31" t="n">
+      <c r="L66" s="32" t="n">
         <v>49.2</v>
       </c>
-      <c r="M66" s="31" t="n">
+      <c r="M66" s="32" t="n">
         <v>52.4</v>
       </c>
-      <c r="N66" s="31" t="n">
+      <c r="N66" s="32" t="n">
         <v>52.4</v>
       </c>
-      <c r="O66" s="31" t="n">
+      <c r="O66" s="32" t="n">
         <v>52.4</v>
       </c>
-      <c r="P66" s="35">
+      <c r="P66" s="36">
         <f>(O66/B66-1)</f>
         <v/>
       </c>
@@ -3474,7 +3474,7 @@
           <t>General Fund share of the levied 52.4 cents (KDE levied-rates file: 41.0 GF + 5.7 FSPK + 5.7 recallable)</t>
         </is>
       </c>
-      <c r="B71" s="31" t="n">
+      <c r="B71" s="32" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
           <t>Cost per added cent to that household, per year</t>
         </is>
       </c>
-      <c r="B74" s="36">
+      <c r="B74" s="37">
         <f>B73*0.01/100</f>
         <v/>
       </c>
@@ -3521,32 +3521,32 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="inlineStr">
+      <c r="A76" s="25" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="B76" s="24" t="inlineStr">
+      <c r="B76" s="25" t="inlineStr">
         <is>
           <t>New rate</t>
         </is>
       </c>
-      <c r="C76" s="24" t="inlineStr">
+      <c r="C76" s="25" t="inlineStr">
         <is>
           <t>Added cents</t>
         </is>
       </c>
-      <c r="D76" s="24" t="inlineStr">
+      <c r="D76" s="25" t="inlineStr">
         <is>
           <t>Revenue per year</t>
         </is>
       </c>
-      <c r="E76" s="24" t="inlineStr">
+      <c r="E76" s="25" t="inlineStr">
         <is>
           <t>Median-home cost/yr</t>
         </is>
       </c>
-      <c r="F76" s="24" t="inlineStr">
+      <c r="F76" s="25" t="inlineStr">
         <is>
           <t>Direct bond capacity</t>
         </is>
@@ -3558,11 +3558,11 @@
           <t>Match Harrison County (2025-26 levied rate)</t>
         </is>
       </c>
-      <c r="B77" s="26">
+      <c r="B77" s="27">
         <f>B24</f>
         <v/>
       </c>
-      <c r="C77" s="37">
+      <c r="C77" s="38">
         <f>B77-B12</f>
         <v/>
       </c>
@@ -3590,11 +3590,11 @@
           <t>Match the regional median (eight area districts, Fayette excluded)</t>
         </is>
       </c>
-      <c r="B78" s="26">
+      <c r="B78" s="27">
         <f>MEDIAN(O58,O59,O60,O61,O63,O64,O65,O66)</f>
         <v/>
       </c>
-      <c r="C78" s="37">
+      <c r="C78" s="38">
         <f>B78-B12</f>
         <v/>
       </c>
@@ -3617,11 +3617,11 @@
           <t>Restore Bourbon's own 2018 rate</t>
         </is>
       </c>
-      <c r="B79" s="26">
+      <c r="B79" s="27">
         <f>B5</f>
         <v/>
       </c>
-      <c r="C79" s="37">
+      <c r="C79" s="38">
         <f>B79-B12</f>
         <v/>
       </c>
@@ -3644,11 +3644,11 @@
           <t>Match Clark County (2025-26 levied rate)</t>
         </is>
       </c>
-      <c r="B80" s="26">
+      <c r="B80" s="27">
         <f>O61</f>
         <v/>
       </c>
-      <c r="C80" s="37">
+      <c r="C80" s="38">
         <f>B80-B12</f>
         <v/>
       </c>
@@ -3794,7 +3794,7 @@
           <t>General Fund rate levied, cents per $100</t>
         </is>
       </c>
-      <c r="B95" s="32">
+      <c r="B95" s="33">
         <f>B71</f>
         <v/>
       </c>
@@ -3816,55 +3816,55 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="24" t="inlineStr">
+      <c r="A98" s="25" t="inlineStr">
         <is>
           <t>Assessment growth</t>
         </is>
       </c>
-      <c r="B98" s="24" t="inlineStr">
+      <c r="B98" s="25" t="inlineStr">
         <is>
           <t>Compensating rate</t>
         </is>
       </c>
-      <c r="C98" s="24" t="inlineStr">
+      <c r="C98" s="25" t="inlineStr">
         <is>
           <t>4 percent option</t>
         </is>
       </c>
-      <c r="D98" s="24" t="inlineStr">
+      <c r="D98" s="25" t="inlineStr">
         <is>
           <t>Rate raised 4 percent</t>
         </is>
       </c>
-      <c r="E98" s="24" t="inlineStr">
+      <c r="E98" s="25" t="inlineStr">
         <is>
           <t>Revenue at 4 percent option</t>
         </is>
       </c>
-      <c r="F98" s="24" t="inlineStr">
+      <c r="F98" s="25" t="inlineStr">
         <is>
           <t>Revenue at rate x 1.04</t>
         </is>
       </c>
-      <c r="G98" s="24" t="inlineStr">
+      <c r="G98" s="25" t="inlineStr">
         <is>
           <t>Above the ceiling, recallable</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="38" t="n">
+      <c r="A99" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="B99" s="32">
+      <c r="B99" s="33">
         <f>$B$95/(1+A99)</f>
         <v/>
       </c>
-      <c r="C99" s="32">
+      <c r="C99" s="33">
         <f>B99*1.04</f>
         <v/>
       </c>
-      <c r="D99" s="32">
+      <c r="D99" s="33">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -3882,18 +3882,18 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="38" t="n">
+      <c r="A100" s="39" t="n">
         <v>0.03</v>
       </c>
-      <c r="B100" s="32">
+      <c r="B100" s="33">
         <f>$B$95/(1+A100)</f>
         <v/>
       </c>
-      <c r="C100" s="32">
+      <c r="C100" s="33">
         <f>B100*1.04</f>
         <v/>
       </c>
-      <c r="D100" s="32">
+      <c r="D100" s="33">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -3911,18 +3911,18 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="38" t="n">
+      <c r="A101" s="39" t="n">
         <v>0.05</v>
       </c>
-      <c r="B101" s="32">
+      <c r="B101" s="33">
         <f>$B$95/(1+A101)</f>
         <v/>
       </c>
-      <c r="C101" s="32">
+      <c r="C101" s="33">
         <f>B101*1.04</f>
         <v/>
       </c>
-      <c r="D101" s="32">
+      <c r="D101" s="33">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -3940,18 +3940,18 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="38" t="n">
+      <c r="A102" s="39" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B102" s="32">
+      <c r="B102" s="33">
         <f>$B$95/(1+A102)</f>
         <v/>
       </c>
-      <c r="C102" s="32">
+      <c r="C102" s="33">
         <f>B102*1.04</f>
         <v/>
       </c>
-      <c r="D102" s="32">
+      <c r="D102" s="33">
         <f>$B$95*1.04</f>
         <v/>
       </c>
@@ -3995,7 +3995,7 @@
           <t>Total levied rate, tax year 2022</t>
         </is>
       </c>
-      <c r="B109" s="31" t="n">
+      <c r="B109" s="32" t="n">
         <v>49.2</v>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
           <t>Total levied rate, tax year 2023 (held at 52.4 for three years since)</t>
         </is>
       </c>
-      <c r="B110" s="31" t="n">
+      <c r="B110" s="32" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
           <t>Net change</t>
         </is>
       </c>
-      <c r="B111" s="37">
+      <c r="B111" s="38">
         <f>B110-B109</f>
         <v/>
       </c>
@@ -4026,7 +4026,7 @@
           <t>Recallable facilities nickel levied 8/17/2023 (KDE levied-rates file, current year)</t>
         </is>
       </c>
-      <c r="B112" s="31" t="n">
+      <c r="B112" s="32" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
           <t>Implied change in the rest of the rate</t>
         </is>
       </c>
-      <c r="B113" s="39">
+      <c r="B113" s="40">
         <f>B111-B112</f>
         <v/>
       </c>
@@ -4511,7 +4511,7 @@
           <t>Current rated capacity</t>
         </is>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="29">
         <f>Assumptions!B12</f>
         <v/>
       </c>
@@ -5089,55 +5089,55 @@
           <t>North Middletown (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="32" t="n">
         <v>56.5</v>
       </c>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="32" t="n">
         <v>63.9</v>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="D15" s="32" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="32" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="F15" s="31" t="n">
+      <c r="F15" s="32" t="n">
         <v>85.8</v>
       </c>
-      <c r="G15" s="31" t="n">
+      <c r="G15" s="32" t="n">
         <v>72.5</v>
       </c>
-      <c r="H15" s="31" t="n">
+      <c r="H15" s="32" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I15" s="31" t="n">
+      <c r="I15" s="32" t="n">
         <v>56.6</v>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="32" t="n">
         <v>56.9</v>
       </c>
-      <c r="K15" s="31" t="n">
+      <c r="K15" s="32" t="n">
         <v>48.7</v>
       </c>
-      <c r="L15" s="31" t="n">
+      <c r="L15" s="32" t="n">
         <v>49.3</v>
       </c>
-      <c r="M15" s="31" t="n">
+      <c r="M15" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="N15" s="31" t="n">
+      <c r="N15" s="32" t="n">
         <v>50.4</v>
       </c>
-      <c r="P15" s="31" t="n">
+      <c r="P15" s="32" t="n">
         <v>47.7</v>
       </c>
-      <c r="Q15" s="31" t="n">
+      <c r="Q15" s="32" t="n">
         <v>32.1</v>
       </c>
-      <c r="R15" s="31" t="n">
+      <c r="R15" s="32" t="n">
         <v>54.1</v>
       </c>
-      <c r="S15" s="31" t="n">
+      <c r="S15" s="32" t="n">
         <v>58.2</v>
       </c>
     </row>
@@ -5147,58 +5147,58 @@
           <t>Bourbon Central (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="32" t="n">
         <v>77.5</v>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="32" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="32" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="32" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="F16" s="31" t="n">
+      <c r="F16" s="32" t="n">
         <v>63</v>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G16" s="32" t="n">
         <v>74.7</v>
       </c>
-      <c r="H16" s="31" t="n">
+      <c r="H16" s="32" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I16" s="31" t="n">
+      <c r="I16" s="32" t="n">
         <v>51.8</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="32" t="n">
         <v>52.1</v>
       </c>
-      <c r="K16" s="31" t="n">
+      <c r="K16" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="L16" s="31" t="n">
+      <c r="L16" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="M16" s="31" t="n">
+      <c r="M16" s="32" t="n">
         <v>32.8</v>
       </c>
-      <c r="N16" s="31" t="n">
+      <c r="N16" s="32" t="n">
         <v>39.9</v>
       </c>
-      <c r="O16" s="31" t="n">
+      <c r="O16" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="P16" s="31" t="n">
+      <c r="P16" s="32" t="n">
         <v>29.9</v>
       </c>
-      <c r="Q16" s="31" t="n">
+      <c r="Q16" s="32" t="n">
         <v>29</v>
       </c>
-      <c r="R16" s="31" t="n">
+      <c r="R16" s="32" t="n">
         <v>23.8</v>
       </c>
-      <c r="S16" s="31" t="n">
+      <c r="S16" s="32" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -5208,58 +5208,58 @@
           <t>Cane Ridge (Bourbon Co.)</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>35.2</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="32" t="n">
         <v>50.9</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="32" t="n">
         <v>56.2</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="32" t="n">
         <v>65.5</v>
       </c>
-      <c r="F17" s="31" t="n">
+      <c r="F17" s="32" t="n">
         <v>34.5</v>
       </c>
-      <c r="G17" s="31" t="n">
+      <c r="G17" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="H17" s="31" t="n">
+      <c r="H17" s="32" t="n">
         <v>49.6</v>
       </c>
-      <c r="I17" s="31" t="n">
+      <c r="I17" s="32" t="n">
         <v>51</v>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="32" t="n">
         <v>51.1</v>
       </c>
-      <c r="K17" s="31" t="n">
+      <c r="K17" s="32" t="n">
         <v>57.5</v>
       </c>
-      <c r="L17" s="31" t="n">
+      <c r="L17" s="32" t="n">
         <v>50.4</v>
       </c>
-      <c r="M17" s="31" t="n">
+      <c r="M17" s="32" t="n">
         <v>41.4</v>
       </c>
-      <c r="N17" s="31" t="n">
+      <c r="N17" s="32" t="n">
         <v>38.8</v>
       </c>
-      <c r="O17" s="31" t="n">
+      <c r="O17" s="32" t="n">
         <v>23.8</v>
       </c>
-      <c r="P17" s="31" t="n">
+      <c r="P17" s="32" t="n">
         <v>38.7</v>
       </c>
-      <c r="Q17" s="31" t="n">
+      <c r="Q17" s="32" t="n">
         <v>34.6</v>
       </c>
-      <c r="R17" s="31" t="n">
+      <c r="R17" s="32" t="n">
         <v>35.8</v>
       </c>
-      <c r="S17" s="31" t="n">
+      <c r="S17" s="32" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -5269,10 +5269,10 @@
           <t>Paris Elementary (Paris Indep.)</t>
         </is>
       </c>
-      <c r="R18" s="31" t="n">
+      <c r="R18" s="32" t="n">
         <v>16.8</v>
       </c>
-      <c r="S18" s="31" t="n">
+      <c r="S18" s="32" t="n">
         <v>12.2</v>
       </c>
     </row>
@@ -5282,10 +5282,10 @@
           <t>Shearer (Clark Co.)</t>
         </is>
       </c>
-      <c r="R19" s="31" t="n">
+      <c r="R19" s="32" t="n">
         <v>30.7</v>
       </c>
-      <c r="S19" s="31" t="n">
+      <c r="S19" s="32" t="n">
         <v>42.3</v>
       </c>
     </row>
@@ -5295,10 +5295,10 @@
           <t>Justice (Clark Co.)</t>
         </is>
       </c>
-      <c r="R20" s="31" t="n">
+      <c r="R20" s="32" t="n">
         <v>43.2</v>
       </c>
-      <c r="S20" s="31" t="n">
+      <c r="S20" s="32" t="n">
         <v>39.3</v>
       </c>
     </row>
@@ -5308,10 +5308,10 @@
           <t>Strode Station (Clark Co.)</t>
         </is>
       </c>
-      <c r="R21" s="31" t="n">
+      <c r="R21" s="32" t="n">
         <v>43.2</v>
       </c>
-      <c r="S21" s="31" t="n">
+      <c r="S21" s="32" t="n">
         <v>34.2</v>
       </c>
     </row>
@@ -5321,10 +5321,10 @@
           <t>Conkwright (Clark Co.)</t>
         </is>
       </c>
-      <c r="R22" s="31" t="n">
+      <c r="R22" s="32" t="n">
         <v>15.6</v>
       </c>
-      <c r="S22" s="31" t="n">
+      <c r="S22" s="32" t="n">
         <v>17.5</v>
       </c>
     </row>
@@ -5334,10 +5334,10 @@
           <t>Northview (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R23" s="31" t="n">
+      <c r="R23" s="32" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="S23" s="31" t="n">
+      <c r="S23" s="32" t="n">
         <v>68.90000000000001</v>
       </c>
     </row>
@@ -5347,10 +5347,10 @@
           <t>Mapleton (Montgomery Co.)</t>
         </is>
       </c>
-      <c r="R24" s="31" t="n">
+      <c r="R24" s="32" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="S24" s="31" t="n">
+      <c r="S24" s="32" t="n">
         <v>65.09999999999999</v>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
           <t>Nicholas County Elementary (Nicholas Co.)</t>
         </is>
       </c>
-      <c r="R25" s="31" t="n">
+      <c r="R25" s="32" t="n">
         <v>15.9</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -5375,15 +5375,15 @@
           <t>Three-year average, 2023-2025: NMES / Bourbon Central / Cane Ridge</t>
         </is>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="27">
         <f>AVERAGE(Q15:S15)</f>
         <v/>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <f>AVERAGE(Q16:S16)</f>
         <v/>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="27">
         <f>AVERAGE(Q17:S17)</f>
         <v/>
       </c>
@@ -5465,32 +5465,32 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="B34" s="40" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="25" t="inlineStr">
         <is>
           <t>Bourbon Central</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="25" t="inlineStr">
         <is>
           <t>Cane Ridge</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="25" t="inlineStr">
         <is>
           <t>Paris Elem.</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F34" s="25" t="inlineStr">
         <is>
           <t>KY elementary avg</t>
         </is>
@@ -5707,43 +5707,43 @@
           <t>Reading: North Middletown</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="32" t="n">
         <v>51.9</v>
       </c>
-      <c r="C45" s="31" t="n">
+      <c r="C45" s="32" t="n">
         <v>59.7</v>
       </c>
-      <c r="D45" s="31" t="n">
+      <c r="D45" s="32" t="n">
         <v>63.2</v>
       </c>
-      <c r="E45" s="31" t="n">
+      <c r="E45" s="32" t="n">
         <v>53.2</v>
       </c>
-      <c r="F45" s="31" t="n">
+      <c r="F45" s="32" t="n">
         <v>56.1</v>
       </c>
-      <c r="G45" s="31" t="n">
+      <c r="G45" s="32" t="n">
         <v>55.6</v>
       </c>
-      <c r="H45" s="31" t="n">
+      <c r="H45" s="32" t="n">
         <v>42.3</v>
       </c>
-      <c r="I45" s="31" t="n">
+      <c r="I45" s="32" t="n">
         <v>48.4</v>
       </c>
-      <c r="J45" s="31" t="n">
+      <c r="J45" s="32" t="n">
         <v>21.4</v>
       </c>
-      <c r="K45" s="31" t="n">
+      <c r="K45" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="L45" s="31" t="n">
+      <c r="L45" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="M45" s="31" t="n">
+      <c r="M45" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="N45" s="31" t="n">
+      <c r="N45" s="32" t="n">
         <v>41</v>
       </c>
     </row>
@@ -5753,43 +5753,43 @@
           <t>Reading: Bourbon Central</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="32" t="n">
         <v>62.1</v>
       </c>
-      <c r="C46" s="31" t="n">
+      <c r="C46" s="32" t="n">
         <v>56.6</v>
       </c>
-      <c r="D46" s="31" t="n">
+      <c r="D46" s="32" t="n">
         <v>61.2</v>
       </c>
-      <c r="E46" s="31" t="n">
+      <c r="E46" s="32" t="n">
         <v>55.7</v>
       </c>
-      <c r="F46" s="31" t="n">
+      <c r="F46" s="32" t="n">
         <v>47.9</v>
       </c>
-      <c r="G46" s="31" t="n">
+      <c r="G46" s="32" t="n">
         <v>47.9</v>
       </c>
-      <c r="H46" s="31" t="n">
+      <c r="H46" s="32" t="n">
         <v>49.3</v>
       </c>
-      <c r="I46" s="31" t="n">
+      <c r="I46" s="32" t="n">
         <v>49.1</v>
       </c>
-      <c r="J46" s="31" t="n">
+      <c r="J46" s="32" t="n">
         <v>27.1</v>
       </c>
-      <c r="K46" s="31" t="n">
+      <c r="K46" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="L46" s="31" t="n">
+      <c r="L46" s="32" t="n">
         <v>37</v>
       </c>
-      <c r="M46" s="31" t="n">
+      <c r="M46" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="N46" s="31" t="n">
+      <c r="N46" s="32" t="n">
         <v>38</v>
       </c>
     </row>
@@ -5799,43 +5799,43 @@
           <t>Reading: Cane Ridge</t>
         </is>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="32" t="n">
         <v>42.9</v>
       </c>
-      <c r="C47" s="31" t="n">
+      <c r="C47" s="32" t="n">
         <v>47.2</v>
       </c>
-      <c r="D47" s="31" t="n">
+      <c r="D47" s="32" t="n">
         <v>54.5</v>
       </c>
-      <c r="E47" s="31" t="n">
+      <c r="E47" s="32" t="n">
         <v>55.3</v>
       </c>
-      <c r="F47" s="31" t="n">
+      <c r="F47" s="32" t="n">
         <v>59.3</v>
       </c>
-      <c r="G47" s="31" t="n">
+      <c r="G47" s="32" t="n">
         <v>57.1</v>
       </c>
-      <c r="H47" s="31" t="n">
+      <c r="H47" s="32" t="n">
         <v>52</v>
       </c>
-      <c r="I47" s="31" t="n">
+      <c r="I47" s="32" t="n">
         <v>49.6</v>
       </c>
-      <c r="J47" s="31" t="n">
+      <c r="J47" s="32" t="n">
         <v>26.5</v>
       </c>
-      <c r="K47" s="31" t="n">
+      <c r="K47" s="32" t="n">
         <v>44</v>
       </c>
-      <c r="L47" s="31" t="n">
+      <c r="L47" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="M47" s="31" t="n">
+      <c r="M47" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="N47" s="31" t="n">
+      <c r="N47" s="32" t="n">
         <v>37</v>
       </c>
     </row>
@@ -5845,43 +5845,43 @@
           <t>Reading: Paris Elementary</t>
         </is>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="32" t="n">
         <v>31</v>
       </c>
-      <c r="C48" s="31" t="n">
+      <c r="C48" s="32" t="n">
         <v>34.1</v>
       </c>
-      <c r="D48" s="31" t="n">
+      <c r="D48" s="32" t="n">
         <v>42.9</v>
       </c>
-      <c r="E48" s="31" t="n">
+      <c r="E48" s="32" t="n">
         <v>38.9</v>
       </c>
-      <c r="F48" s="31" t="n">
+      <c r="F48" s="32" t="n">
         <v>41.2</v>
       </c>
-      <c r="G48" s="31" t="n">
+      <c r="G48" s="32" t="n">
         <v>34.3</v>
       </c>
-      <c r="H48" s="31" t="n">
+      <c r="H48" s="32" t="n">
         <v>34.4</v>
       </c>
-      <c r="I48" s="31" t="n">
+      <c r="I48" s="32" t="n">
         <v>35.3</v>
       </c>
-      <c r="J48" s="31" t="n">
+      <c r="J48" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="K48" s="31" t="n">
+      <c r="K48" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="L48" s="31" t="n">
+      <c r="L48" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="M48" s="31" t="n">
+      <c r="M48" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="N48" s="31" t="n">
+      <c r="N48" s="32" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5891,43 +5891,43 @@
           <t>Mathematics: North Middletown</t>
         </is>
       </c>
-      <c r="B49" s="31" t="n">
+      <c r="B49" s="32" t="n">
         <v>53.2</v>
       </c>
-      <c r="C49" s="31" t="n">
+      <c r="C49" s="32" t="n">
         <v>49.4</v>
       </c>
-      <c r="D49" s="31" t="n">
+      <c r="D49" s="32" t="n">
         <v>55.3</v>
       </c>
-      <c r="E49" s="31" t="n">
+      <c r="E49" s="32" t="n">
         <v>59.5</v>
       </c>
-      <c r="F49" s="31" t="n">
+      <c r="F49" s="32" t="n">
         <v>62.1</v>
       </c>
-      <c r="G49" s="31" t="n">
+      <c r="G49" s="32" t="n">
         <v>50.8</v>
       </c>
-      <c r="H49" s="31" t="n">
+      <c r="H49" s="32" t="n">
         <v>47.9</v>
       </c>
-      <c r="I49" s="31" t="n">
+      <c r="I49" s="32" t="n">
         <v>48.4</v>
       </c>
-      <c r="J49" s="31" t="n">
+      <c r="J49" s="32" t="n">
         <v>17.9</v>
       </c>
-      <c r="K49" s="31" t="n">
+      <c r="K49" s="32" t="n">
         <v>31</v>
       </c>
-      <c r="L49" s="31" t="n">
+      <c r="L49" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="M49" s="31" t="n">
+      <c r="M49" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="N49" s="31" t="n">
+      <c r="N49" s="32" t="n">
         <v>31</v>
       </c>
     </row>
@@ -5937,43 +5937,43 @@
           <t>Mathematics: Bourbon Central</t>
         </is>
       </c>
-      <c r="B50" s="31" t="n">
+      <c r="B50" s="32" t="n">
         <v>47.1</v>
       </c>
-      <c r="C50" s="31" t="n">
+      <c r="C50" s="32" t="n">
         <v>47.4</v>
       </c>
-      <c r="D50" s="31" t="n">
+      <c r="D50" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="E50" s="31" t="n">
+      <c r="E50" s="32" t="n">
         <v>43.6</v>
       </c>
-      <c r="F50" s="31" t="n">
+      <c r="F50" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="G50" s="31" t="n">
+      <c r="G50" s="32" t="n">
         <v>43.5</v>
       </c>
-      <c r="H50" s="31" t="n">
+      <c r="H50" s="32" t="n">
         <v>41.8</v>
       </c>
-      <c r="I50" s="31" t="n">
+      <c r="I50" s="32" t="n">
         <v>45.1</v>
       </c>
-      <c r="J50" s="31" t="n">
+      <c r="J50" s="32" t="n">
         <v>31.7</v>
       </c>
-      <c r="K50" s="31" t="n">
+      <c r="K50" s="32" t="n">
         <v>27</v>
       </c>
-      <c r="L50" s="31" t="n">
+      <c r="L50" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="M50" s="31" t="n">
+      <c r="M50" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="N50" s="31" t="n">
+      <c r="N50" s="32" t="n">
         <v>28</v>
       </c>
     </row>
@@ -5983,43 +5983,43 @@
           <t>Mathematics: Cane Ridge</t>
         </is>
       </c>
-      <c r="B51" s="31" t="n">
+      <c r="B51" s="32" t="n">
         <v>33.3</v>
       </c>
-      <c r="C51" s="31" t="n">
+      <c r="C51" s="32" t="n">
         <v>37.7</v>
       </c>
-      <c r="D51" s="31" t="n">
+      <c r="D51" s="32" t="n">
         <v>43.1</v>
       </c>
-      <c r="E51" s="31" t="n">
+      <c r="E51" s="32" t="n">
         <v>46.1</v>
       </c>
-      <c r="F51" s="31" t="n">
+      <c r="F51" s="32" t="n">
         <v>54.4</v>
       </c>
-      <c r="G51" s="31" t="n">
+      <c r="G51" s="32" t="n">
         <v>45.9</v>
       </c>
-      <c r="H51" s="31" t="n">
+      <c r="H51" s="32" t="n">
         <v>41.5</v>
       </c>
-      <c r="I51" s="31" t="n">
+      <c r="I51" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="J51" s="31" t="n">
+      <c r="J51" s="32" t="n">
         <v>25.2</v>
       </c>
-      <c r="K51" s="31" t="n">
+      <c r="K51" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="L51" s="31" t="n">
+      <c r="L51" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="M51" s="31" t="n">
+      <c r="M51" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="N51" s="31" t="n">
+      <c r="N51" s="32" t="n">
         <v>27</v>
       </c>
     </row>
@@ -6029,43 +6029,43 @@
           <t>Mathematics: Paris Elementary</t>
         </is>
       </c>
-      <c r="B52" s="31" t="n">
+      <c r="B52" s="32" t="n">
         <v>29.7</v>
       </c>
-      <c r="C52" s="31" t="n">
+      <c r="C52" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="D52" s="31" t="n">
+      <c r="D52" s="32" t="n">
         <v>26.8</v>
       </c>
-      <c r="E52" s="31" t="n">
+      <c r="E52" s="32" t="n">
         <v>22.9</v>
       </c>
-      <c r="F52" s="31" t="n">
+      <c r="F52" s="32" t="n">
         <v>41.9</v>
       </c>
-      <c r="G52" s="31" t="n">
+      <c r="G52" s="32" t="n">
         <v>28.7</v>
       </c>
-      <c r="H52" s="31" t="n">
+      <c r="H52" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="I52" s="31" t="n">
+      <c r="I52" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="J52" s="31" t="n">
+      <c r="J52" s="32" t="n">
         <v>15.3</v>
       </c>
-      <c r="K52" s="31" t="n">
+      <c r="K52" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="L52" s="31" t="n">
+      <c r="L52" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="M52" s="31" t="n">
+      <c r="M52" s="32" t="n">
         <v>27</v>
       </c>
-      <c r="N52" s="31" t="n">
+      <c r="N52" s="32" t="n">
         <v>29</v>
       </c>
     </row>
@@ -6159,31 +6159,31 @@
           <t>North Middletown</t>
         </is>
       </c>
-      <c r="B56" s="31" t="n">
+      <c r="B56" s="32" t="n">
         <v>62.6</v>
       </c>
-      <c r="C56" s="31" t="n">
+      <c r="C56" s="32" t="n">
         <v>68.8</v>
       </c>
-      <c r="D56" s="31" t="n">
+      <c r="D56" s="32" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="E56" s="31" t="n">
+      <c r="E56" s="32" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="F56" s="31" t="n">
+      <c r="F56" s="32" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="K56" s="31" t="n">
+      <c r="K56" s="32" t="n">
         <v>51.9</v>
       </c>
-      <c r="L56" s="31" t="n">
+      <c r="L56" s="32" t="n">
         <v>62.2</v>
       </c>
-      <c r="M56" s="31" t="n">
+      <c r="M56" s="32" t="n">
         <v>74.5</v>
       </c>
-      <c r="N56" s="31" t="n">
+      <c r="N56" s="32" t="n">
         <v>54</v>
       </c>
     </row>
@@ -6193,31 +6193,31 @@
           <t>Bourbon Central</t>
         </is>
       </c>
-      <c r="B57" s="31" t="n">
+      <c r="B57" s="32" t="n">
         <v>63.2</v>
       </c>
-      <c r="C57" s="31" t="n">
+      <c r="C57" s="32" t="n">
         <v>63</v>
       </c>
-      <c r="D57" s="31" t="n">
+      <c r="D57" s="32" t="n">
         <v>69.8</v>
       </c>
-      <c r="E57" s="31" t="n">
+      <c r="E57" s="32" t="n">
         <v>67.8</v>
       </c>
-      <c r="F57" s="31" t="n">
+      <c r="F57" s="32" t="n">
         <v>56.8</v>
       </c>
-      <c r="K57" s="31" t="n">
+      <c r="K57" s="32" t="n">
         <v>52.8</v>
       </c>
-      <c r="L57" s="31" t="n">
+      <c r="L57" s="32" t="n">
         <v>56.7</v>
       </c>
-      <c r="M57" s="31" t="n">
+      <c r="M57" s="32" t="n">
         <v>50.3</v>
       </c>
-      <c r="N57" s="31" t="n">
+      <c r="N57" s="32" t="n">
         <v>55.4</v>
       </c>
     </row>
@@ -6227,31 +6227,31 @@
           <t>Cane Ridge</t>
         </is>
       </c>
-      <c r="B58" s="31" t="n">
+      <c r="B58" s="32" t="n">
         <v>53.3</v>
       </c>
-      <c r="C58" s="31" t="n">
+      <c r="C58" s="32" t="n">
         <v>58.9</v>
       </c>
-      <c r="D58" s="31" t="n">
+      <c r="D58" s="32" t="n">
         <v>69.2</v>
       </c>
-      <c r="E58" s="31" t="n">
+      <c r="E58" s="32" t="n">
         <v>68.5</v>
       </c>
-      <c r="F58" s="31" t="n">
+      <c r="F58" s="32" t="n">
         <v>65.5</v>
       </c>
-      <c r="K58" s="31" t="n">
+      <c r="K58" s="32" t="n">
         <v>54.3</v>
       </c>
-      <c r="L58" s="31" t="n">
+      <c r="L58" s="32" t="n">
         <v>51.8</v>
       </c>
-      <c r="M58" s="31" t="n">
+      <c r="M58" s="32" t="n">
         <v>60.7</v>
       </c>
-      <c r="N58" s="31" t="n">
+      <c r="N58" s="32" t="n">
         <v>47.8</v>
       </c>
     </row>
@@ -6261,31 +6261,31 @@
           <t>Paris Elementary</t>
         </is>
       </c>
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="C59" s="31" t="n">
+      <c r="C59" s="32" t="n">
         <v>49.9</v>
       </c>
-      <c r="D59" s="31" t="n">
+      <c r="D59" s="32" t="n">
         <v>59.4</v>
       </c>
-      <c r="E59" s="31" t="n">
+      <c r="E59" s="32" t="n">
         <v>54.8</v>
       </c>
-      <c r="F59" s="31" t="n">
+      <c r="F59" s="32" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="K59" s="31" t="n">
+      <c r="K59" s="32" t="n">
         <v>46.1</v>
       </c>
-      <c r="L59" s="31" t="n">
+      <c r="L59" s="32" t="n">
         <v>45.9</v>
       </c>
-      <c r="M59" s="31" t="n">
+      <c r="M59" s="32" t="n">
         <v>40.7</v>
       </c>
-      <c r="N59" s="31" t="n">
+      <c r="N59" s="32" t="n">
         <v>41.9</v>
       </c>
     </row>
@@ -6340,32 +6340,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>2013 enr</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>2013 cap</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>2021 enr</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>2021 cap</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -6557,7 +6557,7 @@
           <t>NMES students needing seats on closure</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -6666,22 +6666,22 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>2023-24 SAAR</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>Draft capacity (KFICS)</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>Change vs 2021 rating</t>
         </is>
@@ -6727,7 +6727,7 @@
           <t>North Middletown</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B32" s="29" t="n">
         <v>128</v>
       </c>
       <c r="C32" s="10" t="n">
@@ -6775,27 +6775,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Facility</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>Condition need</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>Instructional deficiency</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>Total (as printed)</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>Slide capacity</t>
         </is>
@@ -7000,17 +7000,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B56" s="25" t="inlineStr">
         <is>
           <t>2017 enr</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="25" t="inlineStr">
         <is>
           <t>2017 cap</t>
         </is>
@@ -7109,32 +7109,32 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="25" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B66" s="25" t="inlineStr">
         <is>
           <t>Oct 2023 report</t>
         </is>
       </c>
-      <c r="C66" s="24" t="inlineStr">
+      <c r="C66" s="25" t="inlineStr">
         <is>
           <t>Oct 2025 report</t>
         </is>
       </c>
-      <c r="D66" s="24" t="inlineStr">
+      <c r="D66" s="25" t="inlineStr">
         <is>
           <t>Jul 2026 report</t>
         </is>
       </c>
-      <c r="E66" s="24" t="inlineStr">
+      <c r="E66" s="25" t="inlineStr">
         <is>
           <t>4-yr needs (Jul 2026)</t>
         </is>
       </c>
-      <c r="F66" s="24" t="inlineStr">
+      <c r="F66" s="25" t="inlineStr">
         <is>
           <t>Replacement value (Jul 2026)</t>
         </is>
@@ -7146,13 +7146,13 @@
           <t>Bourbon Central Elementary (1988)</t>
         </is>
       </c>
-      <c r="B67" s="41" t="n">
+      <c r="B67" s="42" t="n">
         <v>0.887637</v>
       </c>
-      <c r="C67" s="41" t="n">
+      <c r="C67" s="42" t="n">
         <v>0.819273</v>
       </c>
-      <c r="D67" s="41" t="n">
+      <c r="D67" s="42" t="n">
         <v>0.823017</v>
       </c>
       <c r="E67" s="8" t="n">
@@ -7168,13 +7168,13 @@
           <t>Cane Ridge Elementary (1992)</t>
         </is>
       </c>
-      <c r="B68" s="41" t="n">
+      <c r="B68" s="42" t="n">
         <v>0.8120579999999999</v>
       </c>
-      <c r="C68" s="41" t="n">
+      <c r="C68" s="42" t="n">
         <v>0.811765</v>
       </c>
-      <c r="D68" s="41" t="n">
+      <c r="D68" s="42" t="n">
         <v>0.728249</v>
       </c>
       <c r="E68" s="8" t="n">
@@ -7190,13 +7190,13 @@
           <t>North Middletown Elementary (1948/64)</t>
         </is>
       </c>
-      <c r="B69" s="41" t="n">
+      <c r="B69" s="42" t="n">
         <v>0.694064</v>
       </c>
-      <c r="C69" s="41" t="n">
+      <c r="C69" s="42" t="n">
         <v>0.702133</v>
       </c>
-      <c r="D69" s="41" t="n">
+      <c r="D69" s="42" t="n">
         <v>0.773295</v>
       </c>
       <c r="E69" s="8" t="n">
@@ -7212,13 +7212,13 @@
           <t>Bourbon County Middle School (1948)</t>
         </is>
       </c>
-      <c r="B70" s="41" t="n">
+      <c r="B70" s="42" t="n">
         <v>0.726249</v>
       </c>
-      <c r="C70" s="41" t="n">
+      <c r="C70" s="42" t="n">
         <v>0.727501</v>
       </c>
-      <c r="D70" s="41" t="n">
+      <c r="D70" s="42" t="n">
         <v>0.596145</v>
       </c>
       <c r="E70" s="8" t="n">
@@ -7234,13 +7234,13 @@
           <t>Bourbon County High School (1968)</t>
         </is>
       </c>
-      <c r="B71" s="41" t="n">
+      <c r="B71" s="42" t="n">
         <v>0.809819</v>
       </c>
-      <c r="C71" s="41" t="n">
+      <c r="C71" s="42" t="n">
         <v>0.802057</v>
       </c>
-      <c r="D71" s="41" t="n">
+      <c r="D71" s="42" t="n">
         <v>0.792529</v>
       </c>
       <c r="E71" s="8" t="n">
@@ -7256,7 +7256,7 @@
           <t>Check: Condition Index = 1 - (4-year renewal needs / replacement value), NMES</t>
         </is>
       </c>
-      <c r="B72" s="42">
+      <c r="B72" s="43">
         <f>1-E69/F69</f>
         <v/>
       </c>
@@ -7267,7 +7267,7 @@
           <t>NMES change between inspection cycles (2020-21 to April 2026)</t>
         </is>
       </c>
-      <c r="B73" s="42">
+      <c r="B73" s="43">
         <f>D69-B69</f>
         <v/>
       </c>
@@ -7408,52 +7408,52 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Students displaced</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Spending, year before</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Spending, 3 yrs after</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>State growth</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>Counterfactual</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>Gap per year</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>Gap per student</t>
         </is>
       </c>
-      <c r="J14" s="24" t="inlineStr">
+      <c r="J14" s="25" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -8215,10 +8215,10 @@
           <t>Share of districts spending MORE than trend after closing (all / plausible-only)</t>
         </is>
       </c>
-      <c r="B41" s="38" t="n">
+      <c r="B41" s="39" t="n">
         <v>0.4</v>
       </c>
-      <c r="C41" s="38" t="n">
+      <c r="C41" s="39" t="n">
         <v>0.41</v>
       </c>
     </row>
@@ -8298,10 +8298,10 @@
           <t>Median score change: events displacing 15%+ of district / under 15%</t>
         </is>
       </c>
-      <c r="B49" s="31" t="n">
+      <c r="B49" s="32" t="n">
         <v>-2</v>
       </c>
-      <c r="C49" s="31" t="n">
+      <c r="C49" s="32" t="n">
         <v>-0.2</v>
       </c>
     </row>
@@ -8382,32 +8382,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Members</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Federal</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Total/member</t>
         </is>
@@ -8604,7 +8604,7 @@
           <t>Breakeven N at state-only revenue</t>
         </is>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="24">
         <f>B15/B17</f>
         <v/>
       </c>
@@ -8620,7 +8620,7 @@
           <t>Same fraction with matching definitions: all-in cost / total revenue per member (2023-24)</t>
         </is>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <f>B15/F10</f>
         <v/>
       </c>
@@ -8638,27 +8638,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Cost/pupil</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Enrolled</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Breakeven N</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Short by</t>
         </is>
@@ -8676,11 +8676,11 @@
       <c r="C23" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <f>B23*C23/F$10</f>
         <v/>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <f>D23-C23</f>
         <v/>
       </c>
@@ -8697,11 +8697,11 @@
       <c r="C24" s="10" t="n">
         <v>459</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <f>B24*C24/F$10</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <f>D24-C24</f>
         <v/>
       </c>
@@ -8718,11 +8718,11 @@
       <c r="C25" s="10" t="n">
         <v>453</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>B25*C25/F$10</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>D25-C25</f>
         <v/>
       </c>
@@ -8739,11 +8739,11 @@
       <c r="C26" s="10" t="n">
         <v>590</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <f>B26*C26/F$10</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <f>D26-C26</f>
         <v/>
       </c>
@@ -8760,11 +8760,11 @@
       <c r="C27" s="10" t="n">
         <v>766</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <f>B27*C27/F$10</f>
         <v/>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <f>D27-C27</f>
         <v/>
       </c>
@@ -8784,27 +8784,27 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>Fixed base</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>N (SEEK only)</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="25" t="inlineStr">
         <is>
           <t>N if fed counted</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>Enrolled</t>
         </is>
@@ -8816,15 +8816,15 @@
           <t>North Middletown</t>
         </is>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="26">
         <f>Assumptions!B51+Assumptions!B52</f>
         <v/>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <f>B32/(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <f>B32/(Assumptions!B6+3380-Assumptions!B62)</f>
         <v/>
       </c>
@@ -8847,11 +8847,11 @@
         <f>Assumptions!B51+Assumptions!B52*Facility_Plans!F68/Facility_Plans!F69</f>
         <v/>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <f>B33/(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <f>B33/(Assumptions!B6+3380-Assumptions!B62)</f>
         <v/>
       </c>
@@ -8869,11 +8869,11 @@
         <f>Assumptions!B51+Assumptions!B52*Facility_Plans!F67/Facility_Plans!F69</f>
         <v/>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="30">
         <f>B34/(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="30">
         <f>B34/(Assumptions!B6+3380-Assumptions!B62)</f>
         <v/>
       </c>
@@ -8896,32 +8896,32 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>NMES members</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>BCES</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>Cane Ridge</t>
         </is>
       </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>NMES vs BCES</t>
         </is>
@@ -9085,22 +9085,22 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="25" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
+      <c r="C48" s="25" t="inlineStr">
         <is>
           <t>Reported $/student</t>
         </is>
       </c>
-      <c r="D48" s="24" t="inlineStr">
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>Curve prediction</t>
         </is>
@@ -10128,7 +10128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -10996,6 +10996,238 @@
       </c>
       <c r="E65" s="11">
         <f>C65-D65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>PEER YARDSTICK: FAYETTE COUNTY, SAME FISCAL YEAR (Section 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr"/>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Bourbon</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>Fayette (audited)</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Fayette (adjusted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>General Fund expenditures, FY2025</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>29097404</v>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>685348803</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>690460223</v>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t>Bourbon and Fayette FY2025 audits, both archived under build/. The Fayette 'adjusted' column is Weaver, L.L.P.'s Audit of Budget Processes and Expenditures, presented to the Fayette board August 3, 2026 (build/fcps_weaver_audit_2026_08.pdf, Finding A.4): after unaudited corrections the district made to its own FY2025 ledger in June 2026, the ending balance was about $6,902,403, roughly 1 percent of $690,460,223. Weaver labels those figures unaudited and subject to change; they are carried here the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Operating gap before transfers</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>2648086</v>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>38907376</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Gap per dollar spent</t>
+        </is>
+      </c>
+      <c r="B71" s="18">
+        <f>B70/B69</f>
+        <v/>
+      </c>
+      <c r="C71" s="18">
+        <f>C70/C69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Fund balance, beginning of year</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>5516305</v>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>43291115</v>
+      </c>
+      <c r="D72" s="9">
+        <f>C72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Fund balance, end of year</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>4290840</v>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>28361786</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>6902403</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>Reserve per dollar spent (the published cushion)</t>
+        </is>
+      </c>
+      <c r="B74" s="17">
+        <f>B73/B69</f>
+        <v/>
+      </c>
+      <c r="C74" s="17">
+        <f>C73/C69</f>
+        <v/>
+      </c>
+      <c r="D74" s="17">
+        <f>D73/D69</f>
+        <v/>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Published: Bourbon 14.7 cents of reserve per dollar, Fayette 4.1 on its audit and about 1.0 after its own adjustments</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Drawdown during the year</t>
+        </is>
+      </c>
+      <c r="B75" s="9">
+        <f>B72-B73</f>
+        <v/>
+      </c>
+      <c r="C75" s="9">
+        <f>C72-C73</f>
+        <v/>
+      </c>
+      <c r="D75" s="9">
+        <f>D72-D73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>Drawdown per dollar spent (the burn rate)</t>
+        </is>
+      </c>
+      <c r="B76" s="17">
+        <f>B75/B69</f>
+        <v/>
+      </c>
+      <c r="C76" s="17">
+        <f>C75/C69</f>
+        <v/>
+      </c>
+      <c r="D76" s="17">
+        <f>D75/D69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>Years of cushion at that burn rate</t>
+        </is>
+      </c>
+      <c r="B77" s="24">
+        <f>B73/B75</f>
+        <v/>
+      </c>
+      <c r="C77" s="24">
+        <f>C73/C75</f>
+        <v/>
+      </c>
+      <c r="D77" s="24">
+        <f>D73/D75</f>
+        <v/>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Published: Bourbon roughly three and a half years of cushion at its current burn; Fayette essentially none, which is why it approved borrowing up to $95 million to reach fall tax collections</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Restatement: audited ending balance less the adjusted ending balance</t>
+        </is>
+      </c>
+      <c r="C78" s="19">
+        <f>C73-D73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>KRS 160.470(6)(a) 2 percent minimum reserve, on Fayette's adjusted spending</t>
+        </is>
+      </c>
+      <c r="D79" s="9">
+        <f>D69*0.02</f>
+        <v/>
+      </c>
+      <c r="F79" s="21" t="inlineStr">
+        <is>
+          <t>Weaver: the adjusted balance sits below both the statutory minimum every Kentucky district must budget and Fayette's own 6 percent policy. Weaver's 70-plus recommendations and 10 priority actions concern budget controls, forecasting, reconciliation, reporting and reserve replenishment; none is a school closure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Fayette's own 6 percent administrative threshold</t>
+        </is>
+      </c>
+      <c r="D80" s="9">
+        <f>D69*0.06</f>
         <v/>
       </c>
     </row>
@@ -11027,18 +11259,18 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr"/>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr"/>
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -11050,15 +11282,15 @@
           <t>Revenues before transfers</t>
         </is>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <f>Assumptions!B19</f>
         <v/>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <f>Assumptions!B20</f>
         <v/>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <f>Assumptions!B21</f>
         <v/>
       </c>
@@ -11069,15 +11301,15 @@
           <t>Expenditures before transfers</t>
         </is>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <f>Assumptions!B22</f>
         <v/>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <f>Assumptions!B23</f>
         <v/>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <f>Assumptions!B24</f>
         <v/>
       </c>
@@ -11107,11 +11339,11 @@
           <t>Net transfers &amp; other sources</t>
         </is>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <f>Assumptions!B25</f>
         <v/>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>Assumptions!B26</f>
         <v/>
       </c>
@@ -11137,15 +11369,15 @@
           <t>Ending fund balance</t>
         </is>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <f>Assumptions!B27</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>Assumptions!B28</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>Assumptions!B29</f>
         <v/>
       </c>
@@ -11222,7 +11454,7 @@
           <t>Years of runway at current pace</t>
         </is>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <f>IFERROR(D15/D16,0)</f>
         <v/>
       </c>
@@ -11302,7 +11534,7 @@
           <t>Total site spending (state ESSA basis)</t>
         </is>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <f>Assumptions!B14*Assumptions!B11</f>
         <v/>
       </c>
@@ -11313,7 +11545,7 @@
           <t>State/local share of site spending</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>Assumptions!B15*Assumptions!B11</f>
         <v/>
       </c>
@@ -11331,7 +11563,7 @@
           <t>Principal &amp; office</t>
         </is>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <f>Assumptions!B51</f>
         <v/>
       </c>
@@ -11342,7 +11574,7 @@
           <t>Plant, utilities, insurance (net of carrying cost)</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>Assumptions!B52</f>
         <v/>
       </c>
@@ -11353,7 +11585,7 @@
           <t>Teaching positions eliminated (via attrition, GF-borne cost)</t>
         </is>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <f>Assumptions!B53*Assumptions!B69</f>
         <v/>
       </c>
@@ -11387,7 +11619,7 @@
           <t>Added busing</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>Assumptions!B54</f>
         <v/>
       </c>
@@ -11398,7 +11630,7 @@
           <t>SEEK revenue lost to departing students (FY2027 base)</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>Assumptions!B55*Assumptions!B6</f>
         <v/>
       </c>
@@ -11420,7 +11652,7 @@
           <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 5,832-scenario grid at row 37, median a $20,007 LOSS)</t>
         </is>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="28">
         <f>B13-B18</f>
         <v/>
       </c>
@@ -11446,7 +11678,7 @@
           <t>One-time transition cost (year one)</t>
         </is>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="26">
         <f>Assumptions!B56</f>
         <v/>
       </c>
@@ -11526,7 +11758,7 @@
           <t>All-in cost per position (salary + state-paid on-behalf; filing basis)</t>
         </is>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <f>Assumptions!B41</f>
         <v/>
       </c>
@@ -11542,7 +11774,7 @@
           <t>GF-borne cost per position (salary + ~5%)</t>
         </is>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <f>Assumptions!B69</f>
         <v/>
       </c>
@@ -11560,27 +11792,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Lever (low / central / high)</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>Central</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -11907,18 +12139,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr"/>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr"/>
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
@@ -11930,15 +12162,15 @@
           <t>Transfer students (scenario)</t>
         </is>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="29">
         <f>Assumptions!B59</f>
         <v/>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="29">
         <f>Assumptions!B60</f>
         <v/>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <f>Assumptions!B61</f>
         <v/>
       </c>
@@ -11968,15 +12200,15 @@
           <t>SEEK base per pupil</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>Assumptions!B6</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <f>Assumptions!B7</f>
         <v/>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>Assumptions!B8</f>
         <v/>
       </c>
@@ -12044,15 +12276,15 @@
           <t>Net new recurring revenue</t>
         </is>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="28">
         <f>B8-B9-B10</f>
         <v/>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <f>C8-C9-C10</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <f>D8-D9-D10</f>
         <v/>
       </c>
@@ -12157,7 +12389,7 @@
           <t>NMES enrollment</t>
         </is>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="29">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -12168,7 +12400,7 @@
           <t>NMES rated capacity</t>
         </is>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="29">
         <f>Assumptions!B12</f>
         <v/>
       </c>
@@ -12328,7 +12560,7 @@
           <t>Average class size today</t>
         </is>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>B5/B20</f>
         <v/>
       </c>
@@ -12339,7 +12571,7 @@
           <t>Average class size at capacity</t>
         </is>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>B14/B20</f>
         <v/>
       </c>
@@ -12374,7 +12606,7 @@
           <t>New SEEK revenue from cross-county transfers (FY2027 base)</t>
         </is>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="26">
         <f>B13*Assumptions!B6</f>
         <v/>
       </c>
@@ -12385,7 +12617,7 @@
           <t>Variable cost of all added students</t>
         </is>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="26">
         <f>(B12+B13)*Assumptions!B62</f>
         <v/>
       </c>
@@ -12416,7 +12648,7 @@
           <t>Net recurring benefit, low (avoided and added sections both priced at the GF-borne $60K central; v3.8 subtracts the NMES additions)</t>
         </is>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="28">
         <f>B26-B27+(B28-B24)*Assumptions!B69</f>
         <v/>
       </c>
@@ -12452,7 +12684,7 @@
           <t>NMES site spending today</t>
         </is>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <f>Assumptions!B14*Assumptions!B11</f>
         <v/>
       </c>
@@ -12463,7 +12695,7 @@
           <t>Per student today</t>
         </is>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <f>Assumptions!B14</f>
         <v/>
       </c>
@@ -12568,7 +12800,7 @@
           <t>NMES per pupil today</t>
         </is>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="26">
         <f>Assumptions!B14</f>
         <v/>
       </c>
@@ -12627,7 +12859,7 @@
           <t>NMES at 174 vs cheapest receiving school</t>
         </is>
       </c>
-      <c r="B52" s="27">
+      <c r="B52" s="28">
         <f>B49-MIN(B46,B47)</f>
         <v/>
       </c>
@@ -12713,7 +12945,7 @@
           <t>Reference: NMES's ENTIRE state and local spending per pupil (fixed costs included)</t>
         </is>
       </c>
-      <c r="B61" s="25">
+      <c r="B61" s="26">
         <f>Assumptions!B15</f>
         <v/>
       </c>
@@ -12736,12 +12968,12 @@
           <t>Marginal cost per added student</t>
         </is>
       </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B64" s="25" t="inlineStr">
         <is>
           <t>At 174</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
+      <c r="C64" s="25" t="inlineStr">
         <is>
           <t>At 154</t>
         </is>
@@ -12834,37 +13066,37 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24" t="inlineStr">
+      <c r="A74" s="25" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B74" s="24" t="inlineStr">
+      <c r="B74" s="25" t="inlineStr">
         <is>
           <t>NMES members</t>
         </is>
       </c>
-      <c r="C74" s="24" t="inlineStr">
+      <c r="C74" s="25" t="inlineStr">
         <is>
           <t>NMES $/pupil</t>
         </is>
       </c>
-      <c r="D74" s="24" t="inlineStr">
+      <c r="D74" s="25" t="inlineStr">
         <is>
           <t>BCES $/pupil</t>
         </is>
       </c>
-      <c r="E74" s="24" t="inlineStr">
+      <c r="E74" s="25" t="inlineStr">
         <is>
           <t>CRES $/pupil</t>
         </is>
       </c>
-      <c r="F74" s="24" t="inlineStr">
+      <c r="F74" s="25" t="inlineStr">
         <is>
           <t>NMES at 174</t>
         </is>
       </c>
-      <c r="G74" s="24" t="inlineStr">
+      <c r="G74" s="25" t="inlineStr">
         <is>
           <t>NMES at 154</t>
         </is>
@@ -13195,27 +13427,27 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="inlineStr">
+      <c r="A102" s="25" t="inlineStr">
         <is>
           <t>Scenario (NMES/BCES/CRES caps)</t>
         </is>
       </c>
-      <c r="B102" s="24" t="inlineStr">
+      <c r="B102" s="25" t="inlineStr">
         <is>
           <t>NMES</t>
         </is>
       </c>
-      <c r="C102" s="24" t="inlineStr">
+      <c r="C102" s="25" t="inlineStr">
         <is>
           <t>BCES</t>
         </is>
       </c>
-      <c r="D102" s="24" t="inlineStr">
+      <c r="D102" s="25" t="inlineStr">
         <is>
           <t>CRES</t>
         </is>
       </c>
-      <c r="E102" s="24" t="inlineStr">
+      <c r="E102" s="25" t="inlineStr">
         <is>
           <t>Cheapest</t>
         </is>
@@ -13523,7 +13755,7 @@
           <t>New SEEK per returning student (FY2027 base; same cell the leaver cost uses, so the symmetry is honest)</t>
         </is>
       </c>
-      <c r="B130" s="25">
+      <c r="B130" s="26">
         <f>Assumptions!B6</f>
         <v/>
       </c>
@@ -13737,7 +13969,7 @@
           <t>North Middletown population, 2020</t>
         </is>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="29">
         <f>Demographics!B29</f>
         <v/>
       </c>
@@ -13768,7 +14000,7 @@
           <t>NMES zone area (sq mi)</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>B5*B9</f>
         <v/>
       </c>
@@ -13779,7 +14011,7 @@
           <t>Paris-area zones (sq mi)</t>
         </is>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>B5-B10</f>
         <v/>
       </c>
@@ -13790,7 +14022,7 @@
           <t>NMES elementary students</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="29">
         <f>Assumptions!B11</f>
         <v/>
       </c>
@@ -13801,7 +14033,7 @@
           <t>Paris-area elementary students</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>Redistricting!B8+Redistricting!B9</f>
         <v/>
       </c>
@@ -13812,7 +14044,7 @@
           <t>Students per square mile, NMES zone</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <f>B12/B10</f>
         <v/>
       </c>
@@ -13823,7 +14055,7 @@
           <t>Students per square mile, Paris-area zones</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <f>B13/B11</f>
         <v/>
       </c>
@@ -13834,7 +14066,7 @@
           <t>Students per square mile, district elementary overall</t>
         </is>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <f>(B12+B13)/B5</f>
         <v/>
       </c>
@@ -13944,7 +14176,7 @@
           <t>Marginal cost per bus-mile, low</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="31" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -13959,7 +14191,7 @@
           <t>Marginal cost per bus-mile, high</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="31" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -14011,7 +14243,7 @@
           <t>Bottom-up added busing cost, low</t>
         </is>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <f>B29</f>
         <v/>
       </c>
@@ -14059,7 +14291,7 @@
           <t>Students rezoned to NMES</t>
         </is>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="29">
         <f>Redistricting!B12</f>
         <v/>
       </c>
@@ -14142,7 +14374,7 @@
           <t>Transportation expense, FY2025</t>
         </is>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="26">
         <f>Assumptions!B42</f>
         <v/>
       </c>
@@ -14153,7 +14385,7 @@
           <t>Average Daily Attendance, FY2025</t>
         </is>
       </c>
-      <c r="B49" s="31" t="n">
+      <c r="B49" s="32" t="n">
         <v>2242.5</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -14179,14 +14411,14 @@
           <t>Optimization potential at 5 to 10 percent (Alternatives menu)</t>
         </is>
       </c>
-      <c r="B51" s="25">
+      <c r="B51" s="26">
         <f>Assumptions!B42*Assumptions!B43</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr"/>
-      <c r="B52" s="25">
+      <c r="B52" s="26">
         <f>Assumptions!B42*Assumptions!B44</f>
         <v/>
       </c>
@@ -14204,7 +14436,7 @@
           <t>Straight-line, NMES to the Paris schools (miles)</t>
         </is>
       </c>
-      <c r="B55" s="31" t="n">
+      <c r="B55" s="32" t="n">
         <v>8.871</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -14219,7 +14451,7 @@
           <t>Measured road distance, US 460 (miles)</t>
         </is>
       </c>
-      <c r="B56" s="31" t="n">
+      <c r="B56" s="32" t="n">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -14234,7 +14466,7 @@
           <t>Implied road factor on the measured pair</t>
         </is>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="33">
         <f>B56/B55</f>
         <v/>
       </c>
@@ -14245,7 +14477,7 @@
           <t>Road factor applied elsewhere (the measured US 460 pair implies 1.13)</t>
         </is>
       </c>
-      <c r="B58" s="30" t="n">
+      <c r="B58" s="31" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -14255,7 +14487,7 @@
           <t>Area-average added distance under closure, one way, straight-line</t>
         </is>
       </c>
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="32" t="n">
         <v>3.271</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -14270,7 +14502,7 @@
           <t>Area-average added distance, road</t>
         </is>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="27">
         <f>B59*B58</f>
         <v/>
       </c>
@@ -14281,7 +14513,7 @@
           <t>Farthest corner of the zone, straight-line to Paris / to NMES</t>
         </is>
       </c>
-      <c r="B61" s="31" t="n">
+      <c r="B61" s="32" t="n">
         <v>15.1</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -14296,7 +14528,7 @@
           <t>Farthest corner by road: to Paris / to NMES (miles)</t>
         </is>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="30">
         <f>ROUND(B61*B58,0)</f>
         <v/>
       </c>
@@ -14358,32 +14590,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Low ($/yr)</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>High ($/yr)</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
         <is>
           <t>Confidence / what firms it up</t>
         </is>
@@ -14395,7 +14627,7 @@
           <t>KRS 160.470 four percent revenue mechanics (context; the published lead lever is the 2018 restore, Tax_History rows 70-91)</t>
         </is>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <f>Tax_History!B50</f>
         <v/>
       </c>
@@ -14480,7 +14712,7 @@
           <t>Attrition-based staffing alignment</t>
         </is>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <f>Assumptions!B48*Assumptions!B41</f>
         <v/>
       </c>
@@ -14509,7 +14741,7 @@
           <t>Administrative restraint</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <f>Assumptions!B47*(Assumptions!B46-Assumptions!B45)</f>
         <v/>
       </c>
@@ -14538,11 +14770,11 @@
           <t>Transportation optimization</t>
         </is>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <f>Assumptions!B42*Assumptions!B43</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>Assumptions!B42*Assumptions!B44</f>
         <v/>
       </c>
@@ -14596,11 +14828,11 @@
           <t>Fill NMES to capacity (rebalance + transfers, net)</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>Redistricting!B30</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>Redistricting!B31</f>
         <v/>
       </c>
@@ -14626,11 +14858,11 @@
           <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
         </is>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <f>25*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>50*(Assumptions!B6-Assumptions!B62)</f>
         <v/>
       </c>
@@ -14656,11 +14888,11 @@
           <t>Total identified (ranges overlap; not additive to the penny)</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <f>SUM(B4:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <f>SUM(C4:C12)</f>
         <v/>
       </c>
@@ -14722,7 +14954,7 @@
           <t>Average annual GF drawdown (FY2024-25)</t>
         </is>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>GF_Summary!D16</f>
         <v/>
       </c>
@@ -14733,7 +14965,7 @@
           <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$20,007 at Closure_Model row 50)</t>
         </is>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="26">
         <f>Closure_Model!B20</f>
         <v/>
       </c>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -11086,9 +11086,10 @@
       <c r="C72" s="8" t="n">
         <v>43291115</v>
       </c>
-      <c r="D72" s="9">
-        <f>C72</f>
-        <v/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -11145,10 +11146,6 @@
         <f>C72-C73</f>
         <v/>
       </c>
-      <c r="D75" s="9">
-        <f>D72-D73</f>
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
@@ -11164,10 +11161,6 @@
         <f>C75/C69</f>
         <v/>
       </c>
-      <c r="D76" s="17">
-        <f>D75/D69</f>
-        <v/>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="20" t="inlineStr">
@@ -11183,20 +11176,16 @@
         <f>C73/C75</f>
         <v/>
       </c>
-      <c r="D77" s="24">
-        <f>D73/D75</f>
-        <v/>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Published: Bourbon roughly three and a half years of cushion at its current burn; Fayette essentially none, which is why it approved borrowing up to $95 million to reach fall tax collections</t>
+      <c r="F77" s="21" t="inlineStr">
+        <is>
+          <t>Published: Bourbon roughly three and a half years of cushion at its current burn; Fayette under two years on its audited books, and nearer none on Weaver's unaudited view, which is why it approved borrowing up to $95 million to reach fall tax collections. Drawdown and runway are computed on audited figures only; Weaver's waterfall runs from the planned contingency rather than the audited opening balance, so its closing figure is not differenced against an audited opening here.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Restatement: audited ending balance less the adjusted ending balance</t>
+          <t>Difference between the audited ending balance and Weaver's post-adjustment figure for the same date (not reconciled in Weaver's deck; the two rest on different bases)</t>
         </is>
       </c>
       <c r="C78" s="19">

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -10128,7 +10128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11165,7 +11165,7 @@
     <row r="77">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>Years of cushion at that burn rate</t>
+          <t>Years of cushion on the net-change basis (flattered by transfers in)</t>
         </is>
       </c>
       <c r="B77" s="24">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="F77" s="21" t="inlineStr">
         <is>
-          <t>Published: Bourbon roughly three and a half years of cushion at its current burn; Fayette under two years on its audited books, and nearer none on Weaver's unaudited view, which is why it approved borrowing up to $95 million to reach fall tax collections. Drawdown and runway are computed on audited figures only; Weaver's waterfall runs from the planned contingency rather than the audited opening balance, so its closing figure is not differenced against an audited opening here.</t>
+          <t>On the net-change basis Bourbon shows about three and a half years and Fayette under two, but both are flattered by transfers in; row 83 gives the operations-alone runway the artifacts publish. Drawdown and runway are computed on audited figures only; Weaver's waterfall runs from the planned contingency rather than the audited opening balance, so its closing figure is not differenced against an audited opening here.</t>
         </is>
       </c>
     </row>
@@ -11218,6 +11218,51 @@
       <c r="D80" s="9">
         <f>D69*0.06</f>
         <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Net other financing in (the gap less the net change): the transfers that flattered the burn</t>
+        </is>
+      </c>
+      <c r="B81" s="9">
+        <f>B70-B75</f>
+        <v/>
+      </c>
+      <c r="C81" s="9">
+        <f>C70-C75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>OF WHICH the capital-to-General-Fund sweep (Bourbon; the plan ends it)</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>1320939</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>Years of cushion on OPERATIONS ALONE (reserve / gap before transfers): the planning number</t>
+        </is>
+      </c>
+      <c r="B83" s="24">
+        <f>B73/B70</f>
+        <v/>
+      </c>
+      <c r="C83" s="24">
+        <f>C73/C70</f>
+        <v/>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
+          <t>Bourbon about 1.6 years, Fayette about 0.7 on their audited books. This is the basis the published comparison leads with, because the plan ends the sweep and the sweep is what holds the net-change burn down to 4.2 cents. Weaver's unaudited view puts Fayette's cushion nearer 1 percent of spending.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12,19 +12,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defaults" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GF_Summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closure_Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Model" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redistricting" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport_Geo" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt_Service" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runway" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_History" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demographics" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Data" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Plans" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY_Closures" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Costs" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exodus_Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Model" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redistricting" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport_Geo" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt_Service" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runway" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_History" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demographics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Data" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Plans" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY_Closures" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Costs" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Companion workbook to the report 'Saving North Middletown Elementary School: A Close Look at Bourbon County Schools' (v4.6, August 2026)</t>
+          <t>Companion workbook to the report 'Saving North Middletown Elementary School: A Close Look at Bourbon County Schools' (v5.0, August 2026)</t>
         </is>
       </c>
     </row>
@@ -669,7 +670,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Every published scenario default (the four facts, the leaver table, both calculator defaults, the plan floor/default/top, Eminence, the ledger breakevens) as live formulas: Defaults tab.</t>
+          <t xml:space="preserve">  Every published scenario default (the four facts, the exodus ladder, both calculator defaults, the plan floor/default/top, Eminence, the ledger breakevens) as live formulas: Defaults and Exodus_Model tabs.</t>
         </is>
       </c>
     </row>
@@ -752,6 +753,641 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue and Cost Alternatives (no school closed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Type separates new recurring revenue from recurring cost reductions; confidence names what would move each line from estimate to plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>Low ($/yr)</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>High ($/yr)</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Confidence / what firms it up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>KRS 160.470 four percent revenue mechanics (context; the published lead lever is the 2018 restore, Tax_History rows 70-91)</t>
+        </is>
+      </c>
+      <c r="B4" s="26">
+        <f>Tax_History!B50</f>
+        <v/>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>375000</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Low = year-one 4% revenue growth on the General Fund levied base; high allows base growth. A revenue cap, not a rate move.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Mechanics only; the published revenue ask anchors on restoring the 2018 rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Improve delinquent-tax recovery (partial)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25-50% of FY2025 delinquency of $239,126 (2.4% of certified yield)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs an aging and collection analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Attendance recovery (+1-2% ADA)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Approx. SEEK value per 1% of ADA</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs an attendance improvement plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Attrition-based staffing alignment</t>
+        </is>
+      </c>
+      <c r="B7" s="26">
+        <f>Assumptions!B48*Assumptions!B41</f>
+        <v/>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>425000</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Low = positions x loaded cost</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs a position-level staffing plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Administrative restraint</t>
+        </is>
+      </c>
+      <c r="B8" s="26">
+        <f>Assumptions!B47*(Assumptions!B46-Assumptions!B45)</f>
+        <v/>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Low = rollback share of 2-yr district-admin growth</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs position- and vendor-level detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Transportation optimization</t>
+        </is>
+      </c>
+      <c r="B9" s="26">
+        <f>Assumptions!B42*Assumptions!B43</f>
+        <v/>
+      </c>
+      <c r="C9" s="26">
+        <f>Assumptions!B42*Assumptions!B44</f>
+        <v/>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5-10% of FY2025 transport expense</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs a local route model (T-1 data requested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Energy performance contracting</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10-25% of utilities; authorized by 702 KAR 4:160</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Cost reduction</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Medium; contracts are structured to self-fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fill NMES to capacity (rebalance + transfers, net)</t>
+        </is>
+      </c>
+      <c r="B11" s="26">
+        <f>Redistricting!B30</f>
+        <v/>
+      </c>
+      <c r="C11" s="26">
+        <f>Redistricting!B31</f>
+        <v/>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Boundary rebalancing and cross-county scenario, Redistricting tab</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>New revenue, net of costs</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>High; board boundary authority, math on Redistricting tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
+        </is>
+      </c>
+      <c r="B12" s="26">
+        <f>25*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="C12" s="26">
+        <f>50*(Assumptions!B6-Assumptions!B62)</f>
+        <v/>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (236 in the district's own homeschool files, 247 residents enrolled in other districts, 450-550 in all with private school); 62 open seats exist at Bourbon Central's approved rating</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>New revenue</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Medium; needs an enrollment marketing plan and incentive design</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Total identified (ranges overlap; not additive to the penny)</t>
+        </is>
+      </c>
+      <c r="B13" s="28">
+        <f>SUM(B4:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>SUM(C4:C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Package midpoint (raw sum of ranges)</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>(B13+C13)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Published band, low (raw row sums, no haircut)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Published band, high (raw row sums, no haircut; the pre-v4.4 conservative $1.7M high is retired)</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Band midpoint (used in Runway sheet)</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>(B17+B18)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Average annual GF drawdown (FY2024-25)</t>
+        </is>
+      </c>
+      <c r="B20" s="26">
+        <f>GF_Summary!D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$292,348 at Closure_Model row 50)</t>
+        </is>
+      </c>
+      <c r="B21" s="26">
+        <f>Closure_Model!B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Reading: the raw-row band is $1.39M to $2.34M with no haircut (v4.4 review). The published headline is now the 2018 restore plus the counted-once cost package, $2.5M to $3.0M a year (transformative check below). Ranges overlap and are not additive to the penny, and each line carries its own confidence rating in column F. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model row 21 carries both for closure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>THE GROWTH PATH: THE SAME MENU AS A DISTRICT-WIDE RECOVERY PLAN (v3.8; backs the site card and Section 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Move 1: inspect fixed costs (every non-teaching position via attrition, administrative restructuring, transport, energy)</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>SUM(B7:B10)</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>SUM(C7:C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
+        </is>
+      </c>
+      <c r="B27" s="19">
+        <f>B6+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>C6+C11+C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Move 3: the honest revenue conversation, year one (this cell keeps the 4 percent + delinquency mechanics for continuity; the published lead lever is the 2018 restore, about $1.5M a year, Tax_History rows 82-89)</t>
+        </is>
+      </c>
+      <c r="B28" s="19">
+        <f>B4+B5</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>C4+C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>B26+B27+B28</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>C26+C27+C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>THE TRANSFORMATIVE CHECK (v4.5: enrollment lever re-based on recovered leakage students at $4,226 each; gap re-based on the trending fiscal 2026 ledger; capacity anchored on the district advisor's June 2026 presentation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,226 = $1,162,150) + costs at the $760K low end</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>1922150</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CORRECTED twice: an earlier release used $1.11M-$3.33M for the enrollment lever; the Move 2 rows price the near-term band at $260K-$530K; the website slider now prices the lever directly as recovered leakage students, 0 to the measured 550-student pool, at the $4,226 net-of-supplies cell in B49 legs. Every 100 recovered add $422,600 a year on top of this check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Full 2018 rate restore (live from Tax_History D79, certified real base; v4.6 correction from the blended $1,699,479)</t>
+        </is>
+      </c>
+      <c r="B32" s="9">
+        <f>Tax_History!D79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Trending structural gap, fiscal 2026 (June 2026 year-end ledger, before transfers)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>1738653</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>District's own June 2026 GL: $20,694,287 of revenue against $22,432,940 of spending before transfers (fund balance $3,328,472 to $2,954,484 after $1,409,590 of transfers in; on-behalf cancels in the gap). The audited fiscal 2025 gap, Assumptions!B24-B21, was $2,648,086.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Recurring surplus after the trending gap (website defaults + full restore)</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>B31+B32-B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>5% raise, every certified teacher (GF certified payroll x 5% x 1.0145 employer Medicare)</t>
+        </is>
+      </c>
+      <c r="B35" s="9">
+        <f>10000388*0.05*1.0145</f>
+        <v/>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>GF object 0110 total, FY2026 working budget (archived build/fy2026_working_budget.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Left for new debt service</t>
+        </is>
+      </c>
+      <c r="B36" s="9">
+        <f>B34-B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>New GF-leveraged bonds supported (4.5%, 20 years; same basis as Debt_Service)</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>B36*(1-1.045^-20)/0.045</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Bonding capacity per the district's own advisor (Baird, June 2026; build/baird_lpc_june2026.pdf)</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>From $3,252,893 of FY2027 bondable restricted revenues. Real only if the restricted stream pays for buildings: the $1.32M-a-year capital-to-operations sweep consumes about $17M of this capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Building capacity, together</t>
+        </is>
+      </c>
+      <c r="B39" s="19">
+        <f>B37+B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.66M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.16M for debt: about $15.0M of new GF-leveraged bonds plus the advisor's $32M, about $47 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $500K to spare, within $7,000 of the full raise; two recovered students close the difference. At the slider top (all 550 recovered, levers high) the plan runs about $3.4M ahead: the raise plus about $37M of bonds, about $69M of capacity. Every 100 recovered leakage students move the surplus by $422,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Baird sensitivities, their own June 2026 numbers: minus 50 students drops capacity to $31M (about $20,000 of bonding capacity per student); rates 100bp lower raise it to $35M. Unexpired SFCC offers of $126,250 a year expire January 2028 through January 2034.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1301,18 +1937,18 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case ($52,514); the weighted median itself is negative (-$20,007)</t>
+          <t>Above the closure model's central case, which is itself negative (-$299,327); the weighted median loses $292,348</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Closure model median (v4.5 weighted grid)</t>
+          <t>Closure model median (v5.0 weighted grid)</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-20007</v>
+        <v>-292348</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1320,7 +1956,7 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab, 5,832-combination grid; the median scenario loses money</t>
+          <t>Closure_Model tab, 14,580-combination grid; the median scenario loses money</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2208,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v4.5): at the +$484,582 best case FY2029 ends near $1.2M; at the -$20,007 weighted median the reserves go slightly FASTER than status quo; 55 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v5.0): at the +$409,190 best case FY2029 holds a modest cushion; at the -$292,348 weighted median the reserves go MUCH faster than status quo; 88 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2312,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-20007</v>
+        <v>-292348</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2325,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $20,007 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the legacy base case covers 9.1% of the $2.65M gap, the grid central case 2.0%, and the +$484,582 best-case tail 18.3%; longer rides; enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $292,348 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $299,327, and even the +$409,190 best-case tail covers only 15.4% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -2366,7 +3002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4062,7 +4698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4795,7 +5431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6308,7 +6944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6673,7 +7309,7 @@
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>2023-24 SAAR</t>
+          <t>2024-25 SAAR end-of-year membership (the draft plan's enrollment column, relabeled in v5.0; state file build/saar_enrollment_2024_25.xls)</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
@@ -7284,7 +7920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8151,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-20007/Assumptions!B11</f>
+        <f>-292348/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -8342,7 +8978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10550,15 +11186,15 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Closure default: district staffing stance + our mid-range leaver and busing estimates</t>
+          <t>Closure default: district staffing stance + the survey floor of missing students</t>
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17-63000-38*(Assumptions!B6+500)</f>
+        <f>B17+C17-63000-73*(Assumptions!B6+500)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, minus $63,000 of busing, minus 38 leavers (30 percent) at $5,126: the published -$130,749, the 26th percentile of the 5,832-scenario grid; the weighted median is a $20,007 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, minus $63,000 of busing, minus the survey floor of 73 missing students at $5,126 with nothing shed: the published -$310,159, the 47th percentile of the 14,580-scenario grid; the weighted median is a $292,348 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -11683,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 5,832-scenario grid at row 37, median a $20,007 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 14,580-scenario grid at row 37, median a $292,348 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -11821,7 +12457,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V4.2 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 5,832 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
+          <t>V5.0 TWO-TAILED SENSITIVITY: EIGHT LEVERS, 14,580 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
         </is>
       </c>
     </row>
@@ -11939,21 +12575,21 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students leaving district (grid legs 0/13/26/38/51/64)</t>
+          <t>Students missing from the rolls at steady state (grid legs 38/73/137/167/194)</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>64</v>
+        <v>38</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>194</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0 to 50 percent of 128, x ($4,626 SEEK base + the add-ons lever); exits free and funded under HB 563, homeschool and statewide virtual academy growing. CONSERVATIVE: this is the year-one wave only; if the same share of each entering class keeps leaving, the missing students more than double (x13/6) once every grade K-12 is short</t>
+          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 73 = the floor, 30 signed households' 69 children at 5.75 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior quartiles at the class midpoint; 38 = half the floor, the skeptic's leg. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
         </is>
       </c>
     </row>
@@ -11981,19 +12617,40 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Property-value loss (zone tax base)</t>
+          <t>Variable cost shed per missing student (grid legs 0/1585/2642)</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="8" t="n">
+        <v>1585</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>What the district stops spending when a student leaves, netted against the SEEK loss: $2,642 = one teacher per 25.4 students (SBDM allocation sheet: 463 students / 18.2 teachers) at the district's own $54,479.40, plus $500 non-personnel (assumption, flagged); $1,585 = 60 percent consolidation friction; $0 = the district's own stated stance that all staff are retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Property-value loss (zone tax base)</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="8" t="n">
         <v>47500</v>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D46" s="8" t="n">
         <v>95000</v>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Roughly 0-10 percent of an estimated zone base; kept as foregone revenue because the board's rate practice does not raise rates to recapture zone valuation losses; PVA records ask pending</t>
         </is>
@@ -12006,12 +12663,12 @@
         </is>
       </c>
       <c r="B47" s="19">
-        <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44)-C45</f>
+        <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44-C45)-C46</f>
         <v/>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>$52,514: about 2.0 percent of the structural deficit</t>
+          <t>-$299,327: the central case itself loses money, about 11 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12022,12 +12679,12 @@
         </is>
       </c>
       <c r="B48" s="9">
-        <f>B39+B40+B41*54479.4-D42-D43*(Assumptions!B6+D44)-D45</f>
+        <f>B39+B40+B41*54479.4-D42-D43*(Assumptions!B6+D44-B45)-D46</f>
         <v/>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$591,545 a year: the closure loses money</t>
+          <t>-$1,322,925 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -12038,19 +12695,19 @@
         </is>
       </c>
       <c r="B49" s="9">
-        <f>D39+D40+D41*54479.4-B42-B43*(Assumptions!B6+B44)-B45</f>
+        <f>D39+D40+D41*54479.4-B42-B43*(Assumptions!B6+B44-D45)-B46</f>
         <v/>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$484,582 a year: the grid's best case (every lever at its closure-friendliest), still below the plan's $800K-$1M requirement</t>
+          <t>+$409,190 a year: the grid's best case (every lever at its closure-friendliest, only the survey's skeptic-leg leavers), still below the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 5,832 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and leavers six (0/13/26/38/51/64): 3^5 x 4 x 6 = 5,832. v4.5 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers and leavers, where the record gives no defensible center. Weighted median -$20,007 (the median scenario LOSES money); middle half -$137,095 to +$98,603; 55 percent of weighted scenarios negative; range -$591,545 to +$484,582 (unweighted median -$24,431). v4.5 MUNIS pass: the fixed-position lever now uses FY2026 actuals from the district's own ledger ($214,104) instead of working-budget lines ($218,154). One-time transition costs $100K-$300K in year one are additional. REBUILT IN v4.2 on the district's own 48-page Response to the 10 Questions (archived build/response_to_the_10_questions.pdf): the capture lever uses its Appendix A worksheet, every staffing position is priced at its own fully loaded $54,479.40 (Appendix A.1), the teacher top leg follows its own Appendix B classroom count, and the leakage lever runs to 50 percent. The v3.9 grid (2,916 scenarios, median +$21,571, 45 percent negative) is retained in the version history.</t>
+          <t>Distribution of all 14,580 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, shed, property and busing levers take three values each, teachers four (0/1/2/3) and missing students five (38/73/137/167/194): 3^6 x 4 x 5 = 14,580. v5.0 lever weights: triangular 1-2-1 on the six levers with a documented central setting; uniform on teachers; survey-anchored 1-2-2-2-1 on missing students. Weighted median -$292,348 (the median scenario LOSES money); middle half -$488,920 to -$111,080; 88 percent of weighted scenarios negative; range -$1,322,925 to +$409,190 (unweighted median -$283,934). REBUILT IN v5.0 on the August 2026 school-choice survey: the leaver lever moves from guessed shares of 128 (0-64, year one only) to measured students missing at steady state, and the new shed lever nets the district's cost response against each lost student's SEEK. One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -12144,6 +12801,416 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>THE EXODUS MODEL: WHAT LEAVING FAMILIES COST, FROM THE AUGUST 2026 SCHOOL-CHOICE SURVEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Every figure reproduced by build/exodus_model.py from the anonymized survey (build/survey_school_choice_2026_08_anonymized.csv). Names and dates are never published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>THE SURVEY, CLEANED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Households answering / children covered</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Leaving households / their children</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Staying children / already left the district</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Kindergarten class years holding leavers</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Leavers per kindergarten class</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>C6/B8</f>
+        <v/>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5.75 out of every class of 19 to 24 (recent SAAR grade range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>EFFECTIVE YEARS PER LOST CHILD (district grade-to-grade survival, SAAR school files)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Survival vs own 5th-grade class: 6th / 7th / 8th</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.974</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>9th / 10th / 11th</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>12th (early graduates, dropouts, moves)</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.826</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Effective enrollment-years per lost child (6 elementary + weighted secondary)</t>
+        </is>
+      </c>
+      <c r="B15" s="22">
+        <f>6+SUM(B12:D12)+SUM(B13:D13)+B14</f>
+        <v/>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>12.62 instead of a flat 13: the model does not count years a child would not have been enrolled anyway</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>THE LADDER: STUDENTS MISSING FROM THE ROLLS EACH YEAR, AND THE SEEK LOST WITH THEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Leave share</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Kids/yr (class of 19)</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Kids/yr (class of 24)</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>$/yr range</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>signed only</t>
+        </is>
+      </c>
+      <c r="C19" s="11">
+        <f>ROUND($B$9*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="11">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="9">
+        <f>$B$9*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>The 30 signed households alone: no statistics. $371,963 a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Band low (25th pct)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>0.50575</v>
+      </c>
+      <c r="C20" s="11">
+        <f>ROUND(B20*19*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>ROUND(B20*24*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="9">
+        <f>B20*19*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>B20*24*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>0.61425</v>
+      </c>
+      <c r="C21" s="11">
+        <f>ROUND(B21*19*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="11">
+        <f>ROUND(B21*24*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="9">
+        <f>B21*19*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F21" s="9">
+        <f>B21*24*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Band high (75th pct)</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>0.71575</v>
+      </c>
+      <c r="C22" s="11">
+        <f>ROUND(B22*19*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>ROUND(B22*24*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="9">
+        <f>B22*19*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F22" s="9">
+        <f>B22*24*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>95th percentile bound</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>0.83375</v>
+      </c>
+      <c r="C23" s="11">
+        <f>ROUND(B23*19*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>ROUND(B23*24*$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="9">
+        <f>B23*19*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F23" s="9">
+        <f>B23*24*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed 1x to 8x likelier to answer (log-normal prior centered on 3x), and the shares above are the resulting quartiles. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a 21-31 norm; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>COST RESPONSE: WHAT THE DISTRICT SHEDS AS STUDENTS LEAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Teacher cost per student at the district's own ratio</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>54479.4/(463/18.2)</f>
+        <v/>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>$2,142: one teacher per 25.4 students (SBDM allocation sheet, 463/18.2) at Appendix A.1's $54,479.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Non-personnel variable per student (assumption, flagged)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Full consolidation shed / with 60 percent friction / district stance</t>
+        </is>
+      </c>
+      <c r="B30" s="9">
+        <f>B28+B29</f>
+        <v/>
+      </c>
+      <c r="C30" s="9">
+        <f>ROUND(0.6*(B28+B29),0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>At most 52 cents of each lost SEEK dollar is recoverable by cutting costs; the Closure_Model grid runs all three settings as its shed lever, and the district's own stated stance (all staff retained) is the $0 setting. Even at full consolidation, counting only the signed families, closure still nets negative at the savings median.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12382,7 +13449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13442,7 +14509,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $591,545 to plus $484,582 with a weighted median of minus $20,007, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,322,925 to plus $409,190 with a weighted median of minus $292,348, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>
@@ -13644,7 +14711,7 @@
     <row r="111">
       <c r="A111" s="21" t="inlineStr">
         <is>
-          <t>VALIDATION AGAINST ACTUALS: withdrawn in v3.9. The two-school cost slope used here depended on memberships (491 and 461, later corroborated as 2023-24 SAAR in the 2026 draft plan, Facility_Plans rows 30-31) that contradict the fall counts in B8 and B9 above, and its sign flips from plus $9,848 to minus $941 to minus $22,564 across the three plausible membership pairs. The honest bound is the break-even marginal cost already computed live in rows 57 to 60.</t>
+          <t>VALIDATION AGAINST ACTUALS: withdrawn in v3.9. The two-school cost slope used here depended on memberships (491 and 461, matching the state 2024-25 SAAR end-of-year membership file (the draft plan labels the column 2023-24; the label is corrected in v5.0), Facility_Plans rows 30-31) that contradict the fall counts in B8 and B9 above, and its sign flips from plus $9,848 to minus $941 to minus $22,564 across the three plausible membership pairs. The honest bound is the break-even marginal cost already computed live in rows 57 to 60.</t>
         </is>
       </c>
     </row>
@@ -13917,7 +14984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14590,639 +15657,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Revenue and Cost Alternatives (no school closed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Type separates new recurring revenue from recurring cost reductions; confidence names what would move each line from estimate to plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Measure</t>
-        </is>
-      </c>
-      <c r="B3" s="25" t="inlineStr">
-        <is>
-          <t>Low ($/yr)</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>High ($/yr)</t>
-        </is>
-      </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="E3" s="25" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F3" s="25" t="inlineStr">
-        <is>
-          <t>Confidence / what firms it up</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>KRS 160.470 four percent revenue mechanics (context; the published lead lever is the 2018 restore, Tax_History rows 70-91)</t>
-        </is>
-      </c>
-      <c r="B4" s="26">
-        <f>Tax_History!B50</f>
-        <v/>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>375000</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Low = year-one 4% revenue growth on the General Fund levied base; high allows base growth. A revenue cap, not a rate move.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>New revenue</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mechanics only; the published revenue ask anchors on restoring the 2018 rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Improve delinquent-tax recovery (partial)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>25-50% of FY2025 delinquency of $239,126 (2.4% of certified yield)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>New revenue</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs an aging and collection analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Attendance recovery (+1-2% ADA)</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Approx. SEEK value per 1% of ADA</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>New revenue</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs an attendance improvement plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Attrition-based staffing alignment</t>
-        </is>
-      </c>
-      <c r="B7" s="26">
-        <f>Assumptions!B48*Assumptions!B41</f>
-        <v/>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>425000</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Low = positions x loaded cost</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Cost reduction</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs a position-level staffing plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Administrative restraint</t>
-        </is>
-      </c>
-      <c r="B8" s="26">
-        <f>Assumptions!B47*(Assumptions!B46-Assumptions!B45)</f>
-        <v/>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Low = rollback share of 2-yr district-admin growth</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Cost reduction</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs position- and vendor-level detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Transportation optimization</t>
-        </is>
-      </c>
-      <c r="B9" s="26">
-        <f>Assumptions!B42*Assumptions!B43</f>
-        <v/>
-      </c>
-      <c r="C9" s="26">
-        <f>Assumptions!B42*Assumptions!B44</f>
-        <v/>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5-10% of FY2025 transport expense</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Cost reduction</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs a local route model (T-1 data requested)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Energy performance contracting</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10-25% of utilities; authorized by 702 KAR 4:160</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Cost reduction</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Medium; contracts are structured to self-fund</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Fill NMES to capacity (rebalance + transfers, net)</t>
-        </is>
-      </c>
-      <c r="B11" s="26">
-        <f>Redistricting!B30</f>
-        <v/>
-      </c>
-      <c r="C11" s="26">
-        <f>Redistricting!B31</f>
-        <v/>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Boundary rebalancing and cross-county scenario, Redistricting tab</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>New revenue, net of costs</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>High; board boundary authority, math on Redistricting tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>District-wide recruitment beyond NMES's 46 seats (homeschool, private-school, nonresident incentives; v3.8)</t>
-        </is>
-      </c>
-      <c r="B12" s="26">
-        <f>25*(Assumptions!B6-Assumptions!B62)</f>
-        <v/>
-      </c>
-      <c r="C12" s="26">
-        <f>50*(Assumptions!B6-Assumptions!B62)</f>
-        <v/>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (236 in the district's own homeschool files, 247 residents enrolled in other districts, 450-550 in all with private school); 62 open seats exist at Bourbon Central's approved rating</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>New revenue</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Medium; needs an enrollment marketing plan and incentive design</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Total identified (ranges overlap; not additive to the penny)</t>
-        </is>
-      </c>
-      <c r="B13" s="28">
-        <f>SUM(B4:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="28">
-        <f>SUM(C4:C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>COMPARISON</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Package midpoint (raw sum of ranges)</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
-        <f>(B13+C13)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Published band, low (raw row sums, no haircut)</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>B13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Published band, high (raw row sums, no haircut; the pre-v4.4 conservative $1.7M high is retired)</t>
-        </is>
-      </c>
-      <c r="B18" s="9">
-        <f>C13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Band midpoint (used in Runway sheet)</t>
-        </is>
-      </c>
-      <c r="B19" s="9">
-        <f>(B17+B18)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Average annual GF drawdown (FY2024-25)</t>
-        </is>
-      </c>
-      <c r="B20" s="26">
-        <f>GF_Summary!D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$20,007 at Closure_Model row 50)</t>
-        </is>
-      </c>
-      <c r="B21" s="26">
-        <f>Closure_Model!B20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Reading: the raw-row band is $1.39M to $2.34M with no haircut (v4.4 review). The published headline is now the 2018 restore plus the counted-once cost package, $2.5M to $3.0M a year (transformative check below). Ranges overlap and are not additive to the penny, and each line carries its own confidence rating in column F. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model row 21 carries both for closure).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>THE GROWTH PATH: THE SAME MENU AS A DISTRICT-WIDE RECOVERY PLAN (v3.8; backs the site card and Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Move 1: inspect fixed costs (every non-teaching position via attrition, administrative restructuring, transport, energy)</t>
-        </is>
-      </c>
-      <c r="B26" s="19">
-        <f>SUM(B7:B10)</f>
-        <v/>
-      </c>
-      <c r="C26" s="19">
-        <f>SUM(C7:C10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Move 2: grow enrollment instead of shrinking it (attendance recovery, fill NMES, district-wide recruitment)</t>
-        </is>
-      </c>
-      <c r="B27" s="19">
-        <f>B6+B11+B12</f>
-        <v/>
-      </c>
-      <c r="C27" s="19">
-        <f>C6+C11+C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Move 3: the honest revenue conversation, year one (this cell keeps the 4 percent + delinquency mechanics for continuity; the published lead lever is the 2018 restore, about $1.5M a year, Tax_History rows 82-89)</t>
-        </is>
-      </c>
-      <c r="B28" s="19">
-        <f>B4+B5</f>
-        <v/>
-      </c>
-      <c r="C28" s="19">
-        <f>C4+C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Growth plan total (equals the raw sum above; the published band is the conservative cut of the same rows)</t>
-        </is>
-      </c>
-      <c r="B29" s="19">
-        <f>B26+B27+B28</f>
-        <v/>
-      </c>
-      <c r="C29" s="19">
-        <f>C26+C27+C28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>THE TRANSFORMATIVE CHECK (v4.5: enrollment lever re-based on recovered leakage students at $4,226 each; gap re-based on the trending fiscal 2026 ledger; capacity anchored on the district advisor's June 2026 presentation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,226 = $1,162,150) + costs at the $760K low end</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>1922150</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>CORRECTED twice: an earlier release used $1.11M-$3.33M for the enrollment lever; the Move 2 rows price the near-term band at $260K-$530K; the website slider now prices the lever directly as recovered leakage students, 0 to the measured 550-student pool, at the $4,226 net-of-supplies cell in B49 legs. Every 100 recovered add $422,600 a year on top of this check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Full 2018 rate restore (live from Tax_History D79, certified real base; v4.6 correction from the blended $1,699,479)</t>
-        </is>
-      </c>
-      <c r="B32" s="9">
-        <f>Tax_History!D79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Trending structural gap, fiscal 2026 (June 2026 year-end ledger, before transfers)</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>1738653</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>District's own June 2026 GL: $20,694,287 of revenue against $22,432,940 of spending before transfers (fund balance $3,328,472 to $2,954,484 after $1,409,590 of transfers in; on-behalf cancels in the gap). The audited fiscal 2025 gap, Assumptions!B24-B21, was $2,648,086.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Recurring surplus after the trending gap (website defaults + full restore)</t>
-        </is>
-      </c>
-      <c r="B34" s="19">
-        <f>B31+B32-B33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>5% raise, every certified teacher (GF certified payroll x 5% x 1.0145 employer Medicare)</t>
-        </is>
-      </c>
-      <c r="B35" s="9">
-        <f>10000388*0.05*1.0145</f>
-        <v/>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>GF object 0110 total, FY2026 working budget (archived build/fy2026_working_budget.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Left for new debt service</t>
-        </is>
-      </c>
-      <c r="B36" s="9">
-        <f>B34-B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>New GF-leveraged bonds supported (4.5%, 20 years; same basis as Debt_Service)</t>
-        </is>
-      </c>
-      <c r="B37" s="19">
-        <f>B36*(1-1.045^-20)/0.045</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Bonding capacity per the district's own advisor (Baird, June 2026; build/baird_lpc_june2026.pdf)</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>From $3,252,893 of FY2027 bondable restricted revenues. Real only if the restricted stream pays for buildings: the $1.32M-a-year capital-to-operations sweep consumes about $17M of this capacity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Building capacity, together</t>
-        </is>
-      </c>
-      <c r="B39" s="19">
-        <f>B37+B38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.66M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.16M for debt: about $15.0M of new GF-leveraged bonds plus the advisor's $32M, about $47 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $500K to spare, within $7,000 of the full raise; two recovered students close the difference. At the slider top (all 550 recovered, levers high) the plan runs about $3.4M ahead: the raise plus about $37M of bonds, about $69M of capacity. Every 100 recovered leakage students move the surplus by $422,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>Baird sensitivities, their own June 2026 numbers: minus 50 students drops capacity to $31M (about $20,000 of bonding capacity per student); rates 100bp lower raise it to $35M. Unexpired SFCC offers of $126,250 a year expire January 2028 through January 2034.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="21" t="inlineStr">
-        <is>
-          <t>NMES is not the reason salaries cannot rise (its honest excess cost is about $156,000, six tenths of a percent of the budget) and not the reason capital waits (about $17.6M of restricted capacity sits unused while the sweep drains the building fund). The structural problem is district-wide; so is the fix.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$292,348 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$293,756 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$299,327); the weighted median loses $292,348</t>
+          <t>Above the closure model's central case, which is itself negative (-$299,327); the weighted median loses $293,756</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-292348</v>
+        <v>-293756</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): at the +$409,190 best case FY2029 holds a modest cushion; at the -$292,348 weighted median the reserves go MUCH faster than status quo; 88 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v5.0): at the +$409,190 best case FY2029 holds a modest cushion; at the -$293,756 weighted median the reserves go MUCH faster than status quo; 88 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-292348</v>
+        <v>-293756</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $292,348 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $299,327, and even the +$409,190 best-case tail covers only 15.4% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $293,756 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $299,327, and even the +$409,190 best-case tail covers only 15.4% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-292348/Assumptions!B11</f>
+        <f>-293756/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -11190,11 +11190,11 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17-63000-73*(Assumptions!B6+500)</f>
+        <f>B17+C17-63000-74*(Assumptions!B6+500)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, minus $63,000 of busing, minus the survey floor of 73 missing students at $5,126 with nothing shed: the published -$310,159, the 47th percentile of the 14,580-scenario grid; the weighted median is a $292,348 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, minus $63,000 of busing, minus the survey floor of 74 missing students at $5,126 with nothing shed: the published -$315,285, the 47th percentile of the 14,580-scenario grid; the weighted median is a $293,756 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 14,580-scenario grid at row 37, median a $292,348 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 14,580-scenario grid at row 37, median a $293,756 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12575,7 +12575,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students missing from the rolls at steady state (grid legs 38/73/137/167/194)</t>
+          <t>Students missing from the rolls at steady state (grid legs 38/74/137/167/194)</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 73 = the floor, 30 signed households' 69 children at 5.75 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior quartiles at the class midpoint; 38 = half the floor, the skeptic's leg. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
+          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 74 = the floor, 31 signed households' 70 children at 5.83 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior quartiles at the class midpoint; 38 = roughly half the floor, the skeptic's leg. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
         </is>
       </c>
     </row>
@@ -12707,7 +12707,7 @@
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 14,580 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, shed, property and busing levers take three values each, teachers four (0/1/2/3) and missing students five (38/73/137/167/194): 3^6 x 4 x 5 = 14,580. v5.0 lever weights: triangular 1-2-1 on the six levers with a documented central setting; uniform on teachers; survey-anchored 1-2-2-2-1 on missing students. Weighted median -$292,348 (the median scenario LOSES money); middle half -$488,920 to -$111,080; 88 percent of weighted scenarios negative; range -$1,322,925 to +$409,190 (unweighted median -$283,934). REBUILT IN v5.0 on the August 2026 school-choice survey: the leaver lever moves from guessed shares of 128 (0-64, year one only) to measured students missing at steady state, and the new shed lever nets the district's cost response against each lost student's SEEK. One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 14,580 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, shed, property and busing levers take three values each, teachers four (0/1/2/3) and missing students five (38/74/137/167/194): 3^6 x 4 x 5 = 14,580. v5.0 lever weights: triangular 1-2-1 on the six levers with a documented central setting; uniform on teachers; survey-anchored 1-2-2-2-1 on missing students. Weighted median -$293,756 (the median scenario LOSES money); middle half -$489,057 to -$113,244; 88 percent of weighted scenarios negative; range -$1,322,925 to +$409,190 (unweighted median -$284,962). REBUILT IN v5.0 on the August 2026 school-choice survey: the leaver lever moves from guessed shares of 128 (0-64, year one only) to measured students missing at steady state, and the new shed lever nets the district's cost response against each lost student's SEEK. One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -12845,10 +12845,10 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -12858,10 +12858,10 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5.75 out of every class of 19 to 24 (recent SAAR grade range)</t>
+          <t>5.83 out of every class of 19 to 24 (recent SAAR grade range)</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>The 30 signed households alone: no statistics. $371,963 a year.</t>
+          <t>The 31 signed households alone: no statistics. $377,354 a year.</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,322,925 to plus $409,190 with a weighted median of minus $292,348, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,322,925 to plus $409,190 with a weighted median of minus $293,756, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (236 in the district's own homeschool files, 247 residents enrolled in other districts, 450-550 in all with private school); 62 open seats exist at Bourbon Central's approved rating</t>
+          <t>25-50 additional students at $4,236 net; pool measured on Redistricting rows 116-135 (236 in the district's own homeschool files, 247 residents enrolled in other districts, 450-550 in all with private school); 62 open seats exist at Bourbon Central's approved rating</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$293,756 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$474,042 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1241,14 +1241,14 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>THE TRANSFORMATIVE CHECK (v4.5: enrollment lever re-based on recovered leakage students at $4,226 each; gap re-based on the trending fiscal 2026 ledger; capacity anchored on the district advisor's June 2026 presentation)</t>
+          <t>THE TRANSFORMATIVE CHECK (v4.5: enrollment lever re-based on recovered leakage students at $4,236 each; gap re-based on the trending fiscal 2026 ledger; capacity anchored on the district advisor's June 2026 presentation)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,226 = $1,162,150) + costs at the $760K low end</t>
+          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,236 = $1,164,900) + costs at the $760K low end</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CORRECTED twice: an earlier release used $1.11M-$3.33M for the enrollment lever; the Move 2 rows price the near-term band at $260K-$530K; the website slider now prices the lever directly as recovered leakage students, 0 to the measured 550-student pool, at the $4,226 net-of-supplies cell in B49 legs. Every 100 recovered add $422,600 a year on top of this check.</t>
+          <t>CORRECTED twice: an earlier release used $1.11M-$3.33M for the enrollment lever; the Move 2 rows price the near-term band at $260K-$530K; the website slider now prices the lever directly as recovered leakage students, 0 to the measured 550-student pool, at the $4,236 net-of-supplies cell in B49 legs. Every 100 recovered add $423,600 a year on top of this check.</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.66M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.16M for debt: about $15.0M of new GF-leveraged bonds plus the advisor's $32M, about $47 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $500K to spare, within $7,000 of the full raise; two recovered students close the difference. At the slider top (all 550 recovered, levers high) the plan runs about $3.4M ahead: the raise plus about $37M of bonds, about $69M of capacity. Every 100 recovered leakage students move the surplus by $422,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
+          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.66M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.16M for debt: about $15.0M of new GF-leveraged bonds plus the advisor's $32M, about $47 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $500K to spare, within $7,000 of the full raise; two recovered students close the difference. At the slider top (all 550 recovered, levers high) the plan runs about $3.4M ahead: the raise plus about $37M of bonds, about $69M of capacity. Every 100 recovered leakage students move the surplus by $423,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$299,327); the weighted median loses $293,756</t>
+          <t>Above the closure model's central case, which is itself negative (-$463,042); the weighted median loses $474,042</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-293756</v>
+        <v>-474042</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab, 14,580-combination grid; the median scenario loses money</t>
+          <t>Closure_Model tab, 4,860-combination grid; the median scenario loses money</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): at the +$409,190 best case FY2029 holds a modest cushion; at the -$293,756 weighted median the reserves go MUCH faster than status quo; 88 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v5.0): at the +$323,614 best case FY2029 holds a modest cushion; at the -$474,042 weighted median the reserves go MUCH faster than status quo; 94 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-293756</v>
+        <v>-474042</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $293,756 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $299,327, and even the +$409,190 best-case tail covers only 15.4% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $474,042 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $463,042, and even the +$323,614 best-case tail covers only 12.2% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="J30" s="21" t="inlineStr">
         <is>
-          <t>3 rural elementaries; built NEW Adair County Elementary the same year; pre-closure spending spike reverting; gap is 88 percent of everything the district then spent per student</t>
+          <t>3 rural elementaries; built NEW Adair County Elementary the same year; pre-closure spending spike reverting; gap is 94 percent of everything the district then spent per student</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-293756/Assumptions!B11</f>
+        <f>-474042/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -9979,11 +9979,11 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>4626</v>
+        <v>4636</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-2028 KY budget (HB 500)</t>
+          <t>Enacted 2026-2028 KY budget; corrected in v5.0 from the House-version $4,626</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>FACT FOUR: WHAT LEAVING FAMILIES COST (the published table, all four rows)</t>
+          <t>FACT FOUR, PRE-v5 CONVENTION (superseded by the Exodus_Model tab; kept for the version record)</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>$5,126 at the FY2027 base</t>
+          <t>$5,136 at the FY2027 base</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11155,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Student-years, and the carried band at the $4,626 base / $5,126 with add-ons</t>
+          <t>Student-years, and the carried band at the $4,636 base / $5,136 with add-ons</t>
         </is>
       </c>
       <c r="B31" s="22">
@@ -11190,11 +11190,11 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17-63000-74*(Assumptions!B6+500)</f>
+        <f>B17+C17-63000-74*(Assumptions!B6+500-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, minus $63,000 of busing, minus the survey floor of 74 missing students at $5,126 with nothing shed: the published -$315,285, the 47th percentile of the 14,580-scenario grid; the weighted median is a $293,756 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, minus $63,000 of busing, minus the survey floor of 74 missing students at $5,136 less the $400 supplies credit: the published -$286,425, the 68th percentile of the 4,860-scenario grid; the weighted median is a $474,042 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
-          <t>The published +$141,780, the weighted median of the 19,683-scenario grid (Growth_Model rows 17-19); at the central $500 busing and $700 supplies the same 30 students net about $118,000</t>
+          <t>The published +$142,080, within $140 of the 19,683-scenario grid's weighted median of $142,220 (Growth_Model rows 17-19); at the central $500 busing and $700 supplies the same 30 students net about $118,000</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Enrollment lever at $4,226 net of supplies</t>
+          <t>Enrollment lever at $4,236 net of supplies</t>
         </is>
       </c>
       <c r="B40" s="9">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Published: about $500,000 / $1,662,575 / $3.4 million to spare</t>
+          <t>Published: about $500,000 / $1,665,325 / $3.4 million to spare</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>Leakage pool pricing: see Redistricting rows 136-140 (documented floor 483; gross $2.1-$2.5M at the full base; net $1.9-$2.3M at $4,226)</t>
+          <t>Leakage pool pricing: see Redistricting rows 136-140 (documented floor 483; gross $2.1-$2.5M at the full base; net $1.9-$2.3M at $4,236)</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 14,580-scenario grid at row 37, median a $293,756 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 4,860-scenario grid at row 37, median a $474,042 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12457,7 +12457,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V5.0 TWO-TAILED SENSITIVITY: EIGHT LEVERS, 14,580 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
+          <t>V5.0 TWO-TAILED SENSITIVITY: EIGHT LEVERS, 4,860 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
         </is>
       </c>
     </row>
@@ -12617,40 +12617,19 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Variable cost shed per missing student (grid legs 0/1585/2642)</t>
+          <t>Property-value loss (zone tax base)</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>1585</v>
+        <v>47500</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>2642</v>
+        <v>95000</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>What the district stops spending when a student leaves, netted against the SEEK loss: $2,642 = one teacher per 25.4 students (SBDM allocation sheet: 463 students / 18.2 teachers) at the district's own $54,479.40, plus $500 non-personnel (assumption, flagged); $1,585 = 60 percent consolidation friction; $0 = the district's own stated stance that all staff are retained</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Property-value loss (zone tax base)</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>47500</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Roughly 0-10 percent of an estimated zone base; kept as foregone revenue because the board's rate practice does not raise rates to recapture zone valuation losses; PVA records ask pending</t>
         </is>
@@ -12663,12 +12642,12 @@
         </is>
       </c>
       <c r="B47" s="19">
-        <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44-C45)-C46</f>
+        <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44-Assumptions!B62)-C45</f>
         <v/>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-$299,327: the central case itself loses money, about 11 percent of the structural deficit added, not removed</t>
+          <t>-$463,042: the central case itself loses money, about 17 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12679,12 +12658,12 @@
         </is>
       </c>
       <c r="B48" s="9">
-        <f>B39+B40+B41*54479.4-D42-D43*(Assumptions!B6+D44-B45)-D46</f>
+        <f>B39+B40+B41*54479.4-D42-D43*(Assumptions!B6+D44-Assumptions!B62)-D45</f>
         <v/>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$1,322,925 a year: the closure loses money</t>
+          <t>-$1,247,265 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -12695,19 +12674,19 @@
         </is>
       </c>
       <c r="B49" s="9">
-        <f>D39+D40+D41*54479.4-B42-B43*(Assumptions!B6+B44-D45)-B46</f>
+        <f>D39+D40+D41*54479.4-B42-B43*(Assumptions!B6+B44-Assumptions!B62)-B45</f>
         <v/>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$409,190 a year: the grid's best case (every lever at its closure-friendliest, only the survey's skeptic-leg leavers), still below the plan's $800K-$1M requirement</t>
+          <t>+$323,614 a year: the grid's best case (every lever at its closure-friendliest, only the survey's skeptic-leg leavers), still below the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 14,580 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, shed, property and busing levers take three values each, teachers four (0/1/2/3) and missing students five (38/74/137/167/194): 3^6 x 4 x 5 = 14,580. v5.0 lever weights: triangular 1-2-1 on the six levers with a documented central setting; uniform on teachers; survey-anchored 1-2-2-2-1 on missing students. Weighted median -$293,756 (the median scenario LOSES money); middle half -$489,057 to -$113,244; 88 percent of weighted scenarios negative; range -$1,322,925 to +$409,190 (unweighted median -$284,962). REBUILT IN v5.0 on the August 2026 school-choice survey: the leaver lever moves from guessed shares of 128 (0-64, year one only) to measured students missing at steady state, and the new shed lever nets the district's cost response against each lost student's SEEK. One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 4,860 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and missing students five (38/74/137/167/194): 3^5 x 4 x 5 = 4,860. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. v5.0 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers; survey-anchored 1-2-2-2-1 on missing students. Weighted median -$474,042 (the median scenario LOSES money); middle half -$657,341 to -$217,247; 94 percent of weighted scenarios negative; range -$1,247,265 to +$323,614 (unweighted median -$469,905). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -13032,7 +13011,7 @@
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>The 31 signed households alone: no statistics. $377,354 a year.</t>
+          <t>The 31 signed households alone: no statistics. $378,090 a year.</t>
         </is>
       </c>
     </row>
@@ -13150,58 +13129,25 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>COST RESPONSE: WHAT THE DISTRICT SHEDS AS STUDENTS LEAVE</t>
+          <t>COST RESPONSE: WHAT STOPS BEING SPENT AS STUDENTS LEAVE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Teacher cost per student at the district's own ratio</t>
-        </is>
-      </c>
-      <c r="B28" s="9">
-        <f>54479.4/(463/18.2)</f>
-        <v/>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>$2,142: one teacher per 25.4 students (SBDM allocation sheet, 463/18.2) at Appendix A.1's $54,479.40</t>
-        </is>
+          <t>Supplies and materials per departed student (scales with students; the growth model charges recruits the same figure)</t>
+        </is>
+      </c>
+      <c r="B28" s="26">
+        <f>Assumptions!B62</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Non-personnel variable per student (assumption, flagged)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Full consolidation shed / with 60 percent friction / district stance</t>
-        </is>
-      </c>
-      <c r="B30" s="9">
-        <f>B28+B29</f>
-        <v/>
-      </c>
-      <c r="C30" s="9">
-        <f>ROUND(0.6*(B28+B29),0)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
-        <is>
-          <t>At most 52 cents of each lost SEEK dollar is recoverable by cutting costs; the Closure_Model grid runs all three settings as its shed lever, and the district's own stated stance (all staff retained) is the $0 setting. Even at full consolidation, counting only the signed families, closure still nets negative at the savings median.</t>
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Teacher savings are priced ONLY on the Closure_Model teachers-cut lever (the district's own 0 to 3 positions), never here, so staffing savings cannot be counted twice. Even with the supplies credit and the teacher lever at its friendliest, 94 percent of priced closure scenarios lose money.</t>
         </is>
       </c>
     </row>
@@ -13433,7 +13379,7 @@
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$141,780; middle half +$94,520 to +$182,654; floor +$3,331; ceiling +$386,904; zero negative scenarios.</t>
+          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$142,080; middle half +$94,720 to +$183,354; floor +$4,131; ceiling +$387,804; zero negative scenarios.</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14455,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,322,925 to plus $409,190 with a weighted median of minus $293,756, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,247,265 to plus $323,614 with a weighted median of minus $474,042, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -11186,15 +11186,15 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Closure default: district staffing stance + the survey floor of missing students</t>
+          <t>Closure default: district staffing stance + the statistical median of missing students</t>
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17-63000-74*(Assumptions!B6+500-Assumptions!B62)</f>
+        <f>B17+C17-63000-167*(Assumptions!B6+500-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, minus $63,000 of busing, minus the survey floor of 74 missing students at $5,136 less the $400 supplies credit: the published -$286,425, the 68th percentile of the 4,860-scenario grid; the weighted median is a $474,042 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$726,873, the 16th percentile of the 4,860-scenario grid; the weighted median is a $474,042 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$474,042 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$523,830 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$463,042); the weighted median loses $474,042</t>
+          <t>Above the closure model's central case, which is itself negative (-$463,042); the weighted median loses $523,830</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-474042</v>
+        <v>-523830</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab, 4,860-combination grid; the median scenario loses money</t>
+          <t>Closure_Model tab, 3,888-combination grid; the median scenario loses money</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): at the +$323,614 best case FY2029 holds a modest cushion; at the -$474,042 weighted median the reserves go MUCH faster than status quo; 94 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v5.0): at the +$171,118 best case FY2029 holds a modest cushion; at the -$523,830 weighted median the reserves go MUCH faster than status quo; 99 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-474042</v>
+        <v>-523830</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $474,042 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $463,042, and even the +$323,614 best-case tail covers only 12.2% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $523,830 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $463,042, and even the +$171,118 best-case tail covers only 6.5% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-474042/Assumptions!B11</f>
+        <f>-523830/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -11194,7 +11194,7 @@
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$726,873, the 16th percentile of the 4,860-scenario grid; the weighted median is a $474,042 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$726,873, the 19th percentile of the 3,888-scenario grid; the weighted median is a $523,830 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 4,860-scenario grid at row 37, median a $474,042 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 3,888-scenario grid at row 37, median a $523,830 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12457,7 +12457,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V5.0 TWO-TAILED SENSITIVITY: EIGHT LEVERS, 4,860 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
+          <t>V5.0 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 3,888 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
         </is>
       </c>
     </row>
@@ -12575,11 +12575,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students missing from the rolls at steady state (grid legs 38/74/137/167/194)</t>
+          <t>Students missing from the rolls at steady state (grid legs 74/137/167/194)</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>137</v>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 74 = the floor, 31 signed households' 70 children at 5.83 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior quartiles at the class midpoint; 38 = roughly half the floor, the skeptic's leg. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
+          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 74 = the floor, 31 signed households' 70 children at 5.83 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior quartiles at the class midpoint. The floor is the grid's low end: fewer leavers than the signed households account for is not a priced scenario. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
         </is>
       </c>
     </row>
@@ -12679,14 +12679,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$323,614 a year: the grid's best case (every lever at its closure-friendliest, only the survey's skeptic-leg leavers), still below the plan's $800K-$1M requirement</t>
+          <t>+$171,118 a year: the grid's best case (every lever at its closure-friendliest, only the survey-floor leavers the signed households account for), still below the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 4,860 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and missing students five (38/74/137/167/194): 3^5 x 4 x 5 = 4,860. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. v5.0 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers; survey-anchored 1-2-2-2-1 on missing students. Weighted median -$474,042 (the median scenario LOSES money); middle half -$657,341 to -$217,247; 94 percent of weighted scenarios negative; range -$1,247,265 to +$323,614 (unweighted median -$469,905). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 3,888 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and missing students four (74/137/167/194): 3^5 x 4 x 4 = 3,888. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. v5.0 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers; survey-anchored 2-2-2-1 on missing students, the signed-survey floor held as the low end. Weighted median -$523,830 (the median scenario LOSES money); middle half -$681,643 to -$314,250; 99 percent of weighted scenarios negative; range -$1,247,265 to +$171,118 (unweighted median -$562,162). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>Teacher savings are priced ONLY on the Closure_Model teachers-cut lever (the district's own 0 to 3 positions), never here, so staffing savings cannot be counted twice. Even with the supplies credit and the teacher lever at its friendliest, 94 percent of priced closure scenarios lose money.</t>
+          <t>Teacher savings are priced ONLY on the Closure_Model teachers-cut lever (the district's own 0 to 3 positions), never here, so staffing savings cannot be counted twice. Even with the supplies credit and the teacher lever at its friendliest, 99 percent of priced closure scenarios lose money.</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,247,265 to plus $323,614 with a weighted median of minus $474,042, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,247,265 to plus $171,118 with a weighted median of minus $523,830, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -11186,15 +11186,15 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Closure default: district staffing stance + the statistical median of missing students</t>
+          <t>Closure default: scaled savings granted (teachers included, half the fixed overhead) + the statistical median of missing students</t>
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17-63000-167*(Assumptions!B6+500-Assumptions!B62)</f>
+        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-167*(Assumptions!B6+500-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$726,873, the 19th percentile of the 3,888-scenario grid; the weighted median is a $523,830 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$456,383, the 59th percentile of the 3,888-scenario grid; the weighted median is a $523,830 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$523,830 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$456,383 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$463,042); the weighted median loses $523,830</t>
+          <t>Above the closure model's central case, which is itself negative (-$415,542); the weighted median loses $456,383</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-523830</v>
+        <v>-456383</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab, 3,888-combination grid; the median scenario loses money</t>
+          <t>Closure_Model tab, 1,296-combination grid; the median scenario loses money</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): at the +$171,118 best case FY2029 holds a modest cushion; at the -$523,830 weighted median the reserves go MUCH faster than status quo; 99 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v5.0): at the +$171,118 best case FY2029 holds a modest cushion; at the -$456,383 weighted median the reserves go MUCH faster than status quo; 97 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-523830</v>
+        <v>-456383</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $523,830 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $463,042, and even the +$171,118 best-case tail covers only 6.5% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $456,383 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $415,542, and even the +$171,118 best-case tail covers only 6.5% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-523830/Assumptions!B11</f>
+        <f>-456383/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -11194,7 +11194,7 @@
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$456,383, the 59th percentile of the 3,888-scenario grid; the weighted median is a $523,830 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$456,383, which is also the weighted median of the 1,296-scenario grid (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 3,888-scenario grid at row 37, median a $523,830 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 1,296-scenario grid at row 37, median a $456,383 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12457,7 +12457,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V5.0 TWO-TAILED SENSITIVITY: SEVEN LEVERS, 3,888 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
+          <t>V5.0 TWO-TAILED SENSITIVITY: SIX LEVERS, 1,296 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
         </is>
       </c>
     </row>
@@ -12564,11 +12564,11 @@
         <v>63000</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>190000</v>
+        <v>95000</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Derived bottom-up with uncertainty: 2-4 zone buses terminating in Paris (~9-11 road miles farther one-way), 2 loaded + 0-2 deadhead legs daily, 170 to 175 days, $3.25-$4.75/mile (KDE/NAPT band), high stop adds one $45,000 route split. Per zone student $160/$492/$1,495 vs the $1,032 district average. The July 2026 records response produced the current routes but answered N/A for any routing study or ride-time analysis.</t>
+          <t>Derived bottom-up with uncertainty: 2-4 zone buses terminating in Paris (~9-11 road miles farther one-way), 2 loaded + 0-2 deadhead legs daily, 170 to 175 days, $3.25-$4.75/mile (KDE/NAPT band). The bottom-up maximum with a route split reached $190,000; v5.0 caps the high leg at half that, $95,000. The July 2026 records response produced the current routes but answered N/A for any routing study or ride-time analysis.</t>
         </is>
       </c>
     </row>
@@ -12614,27 +12614,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Property-value loss (zone tax base)</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="8" t="n">
-        <v>47500</v>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Roughly 0-10 percent of an estimated zone base; kept as foregone revenue because the board's rate practice does not raise rates to recapture zone valuation losses; PVA records ask pending</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
@@ -12642,12 +12621,12 @@
         </is>
       </c>
       <c r="B47" s="19">
-        <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44-Assumptions!B62)-C45</f>
+        <f>C39+C40+C41*54479.4-C42-C43*(Assumptions!B6+C44-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-$463,042: the central case itself loses money, about 17 percent of the structural deficit added, not removed</t>
+          <t>-$415,542: the central case itself loses money, about 16 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12658,12 +12637,12 @@
         </is>
       </c>
       <c r="B48" s="9">
-        <f>B39+B40+B41*54479.4-D42-D43*(Assumptions!B6+D44-Assumptions!B62)-D45</f>
+        <f>B39+B40+B41*54479.4-D42-D43*(Assumptions!B6+D44-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$1,247,265 a year: the closure loses money</t>
+          <t>-$1,057,265 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12653,7 @@
         </is>
       </c>
       <c r="B49" s="9">
-        <f>D39+D40+D41*54479.4-B42-B43*(Assumptions!B6+B44-Assumptions!B62)-B45</f>
+        <f>D39+D40+D41*54479.4-B42-B43*(Assumptions!B6+B44-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12686,7 +12665,7 @@
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 3,888 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, property and busing levers take three values each, teachers four (0/1/2/3) and missing students four (74/137/167/194): 3^5 x 4 x 4 = 3,888. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. v5.0 lever weights: triangular 1-2-1 on the five levers with a documented central setting; uniform on teachers; survey-anchored 2-2-2-1 on missing students, the signed-survey floor held as the low end. Weighted median -$523,830 (the median scenario LOSES money); middle half -$681,643 to -$314,250; 99 percent of weighted scenarios negative; range -$1,247,265 to +$171,118 (unweighted median -$562,162). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 1,296 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons and busing levers take three values each, teachers four (0/1/2/3) and missing students four (74/137/167/194): 3^4 x 4 x 4 = 1,296. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending. v5.0 lever weights: triangular 1-2-1 on the four levers with a documented central setting; uniform on teachers; survey-anchored 2-2-2-1 on missing students, the signed-survey floor held as the low end. Weighted median -$456,383 (the median scenario LOSES money, and the website default IS this median scenario); middle half -$606,202 to -$241,706; 97 percent of weighted scenarios negative; range -$1,057,265 to +$171,118 (unweighted median -$488,532). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13126,7 @@
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>Teacher savings are priced ONLY on the Closure_Model teachers-cut lever (the district's own 0 to 3 positions), never here, so staffing savings cannot be counted twice. Even with the supplies credit and the teacher lever at its friendliest, 99 percent of priced closure scenarios lose money.</t>
+          <t>Teacher savings are priced ONLY on the Closure_Model teachers-cut lever (the district's own 0 to 3 positions), never here, so staffing savings cannot be counted twice. Even with the supplies credit and the teacher lever at its friendliest, 97 percent of priced closure scenarios lose money.</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14434,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,247,265 to plus $171,118 with a weighted median of minus $523,830, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,057,265 to plus $171,118 with a weighted median of minus $456,383, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$456,383 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$571,883 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$415,542); the weighted median loses $456,383</t>
+          <t>Above the closure model's central case, which is itself negative (-$557,622); the weighted median loses $571,883</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-456383</v>
+        <v>-571883</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab, 1,296-combination grid; the median scenario loses money</t>
+          <t>Closure_Model tab, 972-combination grid; the median scenario loses money</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): at the +$171,118 best case FY2029 holds a modest cushion; at the -$456,383 weighted median the reserves go MUCH faster than status quo; 97 percent of weighted scenarios lose money and drain reserves faster than doing nothing.</t>
+          <t>Closure range check (v5.0): even the -$95,750 best case drains reserves faster than status quo, the -$571,883 weighted median much faster; every weighted scenario loses money.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-456383</v>
+        <v>-571883</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $456,383 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $415,542, and even the +$171,118 best-case tail covers only 6.5% of the $2.65M gap; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $571,883 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $557,622, and even the best-case tail still loses $95,750 a year; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-456383/Assumptions!B11</f>
+        <f>-571883/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -11194,7 +11194,7 @@
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$456,383, which is also the weighted median of the 1,296-scenario grid (Closure_Model row 50)</f>
+        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$456,383, the 77th percentile of the 972-scenario grid; the weighted median is a $571,883 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 1,296-scenario grid at row 37, median a $456,383 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $571,883 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12457,7 +12457,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>V5.0 TWO-TAILED SENSITIVITY: SIX LEVERS, 1,296 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
+          <t>V5.0 TWO-TAILED SENSITIVITY: SIX LEVERS, 972 COMBINATIONS (backs Figure 5; THIS GRID, not the legacy single-point rows above, is the published closure model)</t>
         </is>
       </c>
     </row>
@@ -12575,21 +12575,21 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students missing from the rolls at steady state (grid legs 74/137/167/194)</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
-        <v>74</v>
+          <t>Students missing from the rolls at steady state (grid legs 137/167/194)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>137</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>194</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 74 = the floor, 31 signed households' 70 children at 5.83 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior quartiles at the class midpoint. The floor is the grid's low end: fewer leavers than the signed households account for is not a priced scenario. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
+          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 74 = the floor, 31 signed households' 70 children at 5.83 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior 25th/50th/75th percentiles at the class midpoint, triangular with the median central. The signed-survey floor of 74 (31 households, 70 children, 5.83 per class x 12.62 effective years) sits below every priced leg and is kept as hard evidence, not as a scenario. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-$415,542: the central case itself loses money, about 16 percent of the structural deficit added, not removed</t>
+          <t>-$557,622: the central case itself loses money, about 21 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12658,14 +12658,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$171,118 a year: the grid's best case (every lever at its closure-friendliest, only the survey-floor leavers the signed households account for), still below the plan's $800K-$1M requirement</t>
+          <t>-$95,750 a year: even the grid's best case (every lever at its closure-friendliest, the band's low leg of 137 leavers) loses money, roughly $900,000 to $1.1 million short of the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 1,296 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons and busing levers take three values each, teachers four (0/1/2/3) and missing students four (74/137/167/194): 3^4 x 4 x 4 = 1,296. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending. v5.0 lever weights: triangular 1-2-1 on the four levers with a documented central setting; uniform on teachers; survey-anchored 2-2-2-1 on missing students, the signed-survey floor held as the low end. Weighted median -$456,383 (the median scenario LOSES money, and the website default IS this median scenario); middle half -$606,202 to -$241,706; 97 percent of weighted scenarios negative; range -$1,057,265 to +$171,118 (unweighted median -$488,532). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (137/167/194), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$571,883 (the median scenario LOSES money); middle half -$679,361 to -$467,862; EVERY weighted scenario is negative, the best case still loses $95,750; range -$1,057,265 to -$95,750 (unweighted median -$566,628). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13126,7 +13126,7 @@
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>Teacher savings are priced ONLY on the Closure_Model teachers-cut lever (the district's own 0 to 3 positions), never here, so staffing savings cannot be counted twice. Even with the supplies credit and the teacher lever at its friendliest, 97 percent of priced closure scenarios lose money.</t>
+          <t>Teacher savings are priced ONLY on the Closure_Model teachers-cut lever (the district's own 0 to 3 positions), never here, so staffing savings cannot be counted twice. Even with the supplies credit and the teacher lever at its friendliest, every priced closure scenario loses money.</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,057,265 to plus $171,118 with a weighted median of minus $456,383, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,057,265 to minus $95,750 with a weighted median of minus $571,883, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -12589,7 +12589,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: 74 = the floor, 31 signed households' 70 children at 5.83 per class x 12.62 effective years of the district's own grade-to-grade survival; 137/167/194 = the response-bias-corrected posterior 25th/50th/75th percentiles at the class midpoint, triangular with the median central. The signed-survey floor of 74 (31 households, 70 children, 5.83 per class x 12.62 effective years) sits below every priced leg and is kept as hard evidence, not as a scenario. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
+          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: the response-bias-corrected posterior 25th/50th/75th percentiles of the leave share, applied to the whole feeder stream (entering class of 21.5, the recent 19-24 SAAR midpoint, x 12.62 effective years of the district's own grade-to-grade survival), triangular with the median central. The 31 signed households and their 70 children are the hard evidence behind the share, not a priced scenario. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
         </is>
       </c>
     </row>
@@ -12838,26 +12838,25 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Kindergarten class years holding leavers</t>
+          <t>Current student population (last official SAAR end-of-year count, 2024-25)</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Leavers per kindergarten class</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
-        <f>C6/B8</f>
-        <v/>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5.83 out of every class of 19 to 24 (recent SAAR grade range)</t>
+          <t>Entering class per year (midpoint of the recent 19-24 SAAR per-grade range)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>The ten-year average NMES kindergarten (SAAR school files, 2015-16 to 2025-26 observed seasons) is 22.2; the survey's hand-coded class years mark only who is enrolled now, and no per-class math is used (v5.0 method change)</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12928,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>THE LADDER: STUDENTS MISSING FROM THE ROLLS EACH YEAR, AND THE SEEK LOST WITH THEM</t>
+          <t>THE SHARE, APPLIED: TODAY'S STUDENTS, THEN THE WHOLE FEEDER STREAM</t>
         </is>
       </c>
     </row>
@@ -12946,17 +12945,17 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>Kids/yr (class of 19)</t>
+          <t>Of today's 128</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>Kids/yr (class of 24)</t>
+          <t>Per year, full feeder</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
         <is>
-          <t>$/yr range</t>
+          <t>$/yr (feeder)</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr">
@@ -12968,138 +12967,113 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Floor</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>signed only</t>
-        </is>
+          <t>Band low (25th pct)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.50575</v>
       </c>
       <c r="C19" s="11">
-        <f>ROUND($B$9*$B$15,0)</f>
+        <f>ROUND(B19*$B$8,0)</f>
         <v/>
       </c>
       <c r="D19" s="11">
-        <f>C19</f>
+        <f>ROUND(B19*$B$9*$B$15,0)</f>
         <v/>
       </c>
       <c r="E19" s="9">
-        <f>$B$9*$B$15*(Assumptions!B6+500)</f>
+        <f>B19*$B$9*$B$15*(Assumptions!B6+500)</f>
         <v/>
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>The 31 signed households alone: no statistics. $378,090 a year.</t>
+          <t>Middle half of the corrected posterior; the closure grid's low leg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Band low (25th pct)</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.50575</v>
+        <v>0.61425</v>
       </c>
       <c r="C20" s="11">
-        <f>ROUND(B20*19*$B$15,0)</f>
+        <f>ROUND(B20*$B$8,0)</f>
         <v/>
       </c>
       <c r="D20" s="11">
-        <f>ROUND(B20*24*$B$15,0)</f>
+        <f>ROUND(B20*$B$9*$B$15,0)</f>
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>B20*19*$B$15*(Assumptions!B6+500)</f>
-        <v/>
-      </c>
-      <c r="F20" s="9">
-        <f>B20*24*$B$15*(Assumptions!B6+500)</f>
-        <v/>
+        <f>B20*$B$9*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>The closure grid's central leg and the calculator default</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>Band high (75th pct)</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.61425</v>
+        <v>0.71575</v>
       </c>
       <c r="C21" s="11">
-        <f>ROUND(B21*19*$B$15,0)</f>
+        <f>ROUND(B21*$B$8,0)</f>
         <v/>
       </c>
       <c r="D21" s="11">
-        <f>ROUND(B21*24*$B$15,0)</f>
+        <f>ROUND(B21*$B$9*$B$15,0)</f>
         <v/>
       </c>
       <c r="E21" s="9">
-        <f>B21*19*$B$15*(Assumptions!B6+500)</f>
-        <v/>
-      </c>
-      <c r="F21" s="9">
-        <f>B21*24*$B$15*(Assumptions!B6+500)</f>
-        <v/>
+        <f>B21*$B$9*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>The closure grid's high leg</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Band high (75th pct)</t>
+          <t>95th percentile bound</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>0.71575</v>
+        <v>0.83375</v>
       </c>
       <c r="C22" s="11">
-        <f>ROUND(B22*19*$B$15,0)</f>
+        <f>ROUND(B22*$B$8,0)</f>
         <v/>
       </c>
       <c r="D22" s="11">
-        <f>ROUND(B22*24*$B$15,0)</f>
+        <f>ROUND(B22*$B$9*$B$15,0)</f>
         <v/>
       </c>
       <c r="E22" s="9">
-        <f>B22*19*$B$15*(Assumptions!B6+500)</f>
-        <v/>
-      </c>
-      <c r="F22" s="9">
-        <f>B22*24*$B$15*(Assumptions!B6+500)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>95th percentile bound</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>0.83375</v>
-      </c>
-      <c r="C23" s="11">
-        <f>ROUND(B23*19*$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="D23" s="11">
-        <f>ROUND(B23*24*$B$15,0)</f>
-        <v/>
-      </c>
-      <c r="E23" s="9">
-        <f>B23*19*$B$15*(Assumptions!B6+500)</f>
-        <v/>
-      </c>
-      <c r="F23" s="9">
-        <f>B23*24*$B$15*(Assumptions!B6+500)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+        <f>B22*$B$9*$B$15*(Assumptions!B6+500)</f>
+        <v/>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Not priced in the grid; the honest upper bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed 1x to 8x likelier to answer (log-normal prior centered on 3x), and the shares above are the resulting quartiles. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a 21-31 norm; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
         </is>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$571,883 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$534,433 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$557,622); the weighted median loses $571,883</t>
+          <t>Above the closure model's central case, which is itself negative (-$519,734); the weighted median loses $534,433</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-571883</v>
+        <v>-534433</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): even the -$95,750 best case drains reserves faster than status quo, the -$571,883 weighted median much faster; every weighted scenario loses money.</t>
+          <t>Closure range check (v5.0): even the -$61,862 best case drains reserves faster than status quo, the -$534,433 weighted median much faster; every weighted scenario loses money.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-571883</v>
+        <v>-534433</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $571,883 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $557,622, and even the best-case tail still loses $95,750 a year; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $534,433 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $519,734, and even the best-case tail still loses $61,862 a year; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-571883/Assumptions!B11</f>
+        <f>-534433/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -11190,11 +11190,11 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-167*(Assumptions!B6+500-Assumptions!B62)</f>
+        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-159*(Assumptions!B6+500-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 167 missing students at $5,136 less the $400 supplies credit: the published -$456,383, the 77th percentile of the 972-scenario grid; the weighted median is a $571,883 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 159 missing students at $5,136 less the $400 supplies credit: the published -$418,495, the 77th percentile of the 972-scenario grid; the weighted median is a $534,433 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $571,883 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $534,433 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12575,17 +12575,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students missing from the rolls at steady state (grid legs 137/167/194)</t>
+          <t>Students missing from the rolls at steady state (grid legs 129/159/187)</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-$557,622: the central case itself loses money, about 21 percent of the structural deficit added, not removed</t>
+          <t>-$519,734: the central case itself loses money, about 21 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$1,057,265 a year: the closure loses money</t>
+          <t>-$1,020,613 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -12658,14 +12658,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-$95,750 a year: even the grid's best case (every lever at its closure-friendliest, the band's low leg of 137 leavers) loses money, roughly $900,000 to $1.1 million short of the plan's $800K-$1M requirement</t>
+          <t>-$61,862 a year: even the grid's best case (every lever at its closure-friendliest, the band's low leg of 137 leavers) loses money, roughly $900,000 to $1.1 million short of the plan's $800K-$1M requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (137/167/194), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$571,883 (the median scenario LOSES money); middle half -$679,361 to -$467,862; EVERY weighted scenario is negative, the best case still loses $95,750; range -$1,057,265 to -$95,750 (unweighted median -$566,628). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (129/159/187), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$534,433 (the median scenario LOSES money); middle half -$643,405 to -$429,974; EVERY weighted scenario is negative, the best case still loses $61,862; range -$1,020,613 to -$61,862 (unweighted median -$530,476). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.50575</v>
+        <v>0.47475</v>
       </c>
       <c r="C19" s="11">
         <f>ROUND(B19*$B$8,0)</f>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.61425</v>
+        <v>0.58475</v>
       </c>
       <c r="C20" s="11">
         <f>ROUND(B20*$B$8,0)</f>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.71575</v>
+        <v>0.68975</v>
       </c>
       <c r="C21" s="11">
         <f>ROUND(B21*$B$8,0)</f>
@@ -13052,7 +13052,7 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>0.83375</v>
+        <v>0.81625</v>
       </c>
       <c r="C22" s="11">
         <f>ROUND(B22*$B$8,0)</f>
@@ -13075,7 +13075,7 @@
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed 1x to 8x likelier to answer (log-normal prior centered on 3x), and the shares above are the resulting quartiles. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a 21-31 norm; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
+          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed about 1x to 9x likelier to answer (log-normal prior centered on 3.5x, the high end of the published measurements, chosen for a small, emotionally charged respondent pool), and the shares above are the resulting quartiles. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a 21-31 norm; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,057,265 to minus $95,750 with a weighted median of minus $571,883, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,020,613 to minus $61,862 with a weighted median of minus $534,433, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$534,433 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$447,573 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$519,734); the weighted median loses $534,433</t>
+          <t>Above the closure model's central case, which is itself negative (-$429,750); the weighted median loses $447,573</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-534433</v>
+        <v>-447573</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>484582</v>
+        <v>1678</v>
       </c>
       <c r="C48" s="9">
         <f>B48*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab B49</t>
+          <t>Closure_Model tab B49: the grid's lone positive corner</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): even the -$61,862 best case drains reserves faster than status quo, the -$534,433 weighted median much faster; every weighted scenario loses money.</t>
+          <t>Closure range check (v5.0): the grid's lone positive corner (+$1,678) is a rounding error against the need; the -$447,573 weighted median drains reserves faster than status quo; all but one of the 972 weighted scenarios lose money.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-534433</v>
+        <v>-447573</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $534,433 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $519,734, and even the best-case tail still loses $61,862 a year; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $447,573 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $429,750, and 971 of the 972 weighted scenarios lose money (the lone best corner nets $1,678); longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-534433/Assumptions!B11</f>
+        <f>-447573/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -10525,7 +10525,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>CLOSURE SCENARIO JUDGMENTS (estimates; district must replace with actuals)</t>
+          <t>CLOSURE SCENARIO JUDGMENTS (LEGACY single-point inputs, superseded; the published closure model is the Closure_Model 972-scenario grid at its row 37)</t>
         </is>
       </c>
     </row>
@@ -11190,11 +11190,11 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-159*(Assumptions!B6+500-Assumptions!B62)</f>
+        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-140*(Assumptions!B6+500-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 159 missing students at $5,136 less the $400 supplies credit: the published -$418,495, the 77th percentile of the 972-scenario grid; the weighted median is a $534,433 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 140 missing students at $5,136 less the $400 supplies credit: the published -$328,511, the 79th percentile of the 972-scenario grid; the weighted median is a $447,573 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $534,433 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $447,573 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12575,21 +12575,21 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students missing from the rolls at steady state (grid legs 129/159/187)</t>
+          <t>Students missing from the rolls at steady state (grid legs 114/140/167)</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: the response-bias-corrected posterior 25th/50th/75th percentiles of the leave share, applied to the whole feeder stream (entering class of 21.5, the recent 19-24 SAAR midpoint, x 12.62 effective years of the district's own grade-to-grade survival), triangular with the median central. The 31 signed households and their 70 children are the hard evidence behind the share, not a priced scenario. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a 21-31 norm; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
+          <t>From the August 2026 school-choice survey (anonymized in build/) and build/exodus_model.py: the response-bias-corrected posterior 25th/50th/75th percentiles of the leave share, applied to the whole feeder stream (entering class of 21.5, the recent 19-24 SAAR midpoint, x 12.62 effective years of the district's own grade-to-grade survival), triangular with the median central. The 31 signed households and their 70 children are the hard evidence behind the share, not a priced scenario. Exits free and funded under HB 563. The state's SAAR files corroborate: kindergarten 12 in 2025-26 against a ten-year average of 22; end-of-year 141/128/115 across 2023-24 to 2025-26.</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-$519,734: the central case itself loses money, about 21 percent of the structural deficit added, not removed</t>
+          <t>-$429,750: the central case itself loses money, about 16 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$1,020,613 a year: the closure loses money</t>
+          <t>-$915,893 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -12658,14 +12658,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-$61,862 a year: even the grid's best case (every lever at its closure-friendliest, the band's low leg of 137 leavers) loses money, roughly $900,000 to $1.1 million short of the plan's $800K-$1M requirement</t>
+          <t>+$1,678 a year: the grid's single positive cell (every lever at its closure-friendliest at once: full capture, every fixed position cut, three teachers, only 114 leavers with zero add-ons, minimal busing), about $13 per displaced student and $800,000 to $1 million short of the plan's requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (129/159/187), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$534,433 (the median scenario LOSES money); middle half -$643,405 to -$429,974; EVERY weighted scenario is negative, the best case still loses $61,862; range -$1,020,613 to -$61,862 (unweighted median -$530,476). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (114/140/167), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$447,573 (the median scenario LOSES money); middle half -$552,323 to -$347,374; all but ONE of the 972 weighted scenarios are negative, and the single best corner nets +$1,678 a year, about $13 per displaced student; range -$915,893 to +$1,678 (unweighted median -$446,722). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.47475</v>
+        <v>0.42025</v>
       </c>
       <c r="C19" s="11">
         <f>ROUND(B19*$B$8,0)</f>
@@ -12982,7 +12982,7 @@
         <v/>
       </c>
       <c r="E19" s="9">
-        <f>B19*$B$9*$B$15*(Assumptions!B6+500)</f>
+        <f>D19*(Assumptions!B6+500)</f>
         <v/>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.58475</v>
+        <v>0.51625</v>
       </c>
       <c r="C20" s="11">
         <f>ROUND(B20*$B$8,0)</f>
@@ -13009,7 +13009,7 @@
         <v/>
       </c>
       <c r="E20" s="9">
-        <f>B20*$B$9*$B$15*(Assumptions!B6+500)</f>
+        <f>D20*(Assumptions!B6+500)</f>
         <v/>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.68975</v>
+        <v>0.61375</v>
       </c>
       <c r="C21" s="11">
         <f>ROUND(B21*$B$8,0)</f>
@@ -13036,7 +13036,7 @@
         <v/>
       </c>
       <c r="E21" s="9">
-        <f>B21*$B$9*$B$15*(Assumptions!B6+500)</f>
+        <f>D21*(Assumptions!B6+500)</f>
         <v/>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -13052,7 +13052,7 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>0.81625</v>
+        <v>0.74475</v>
       </c>
       <c r="C22" s="11">
         <f>ROUND(B22*$B$8,0)</f>
@@ -13063,7 +13063,7 @@
         <v/>
       </c>
       <c r="E22" s="9">
-        <f>B22*$B$9*$B$15*(Assumptions!B6+500)</f>
+        <f>D22*(Assumptions!B6+500)</f>
         <v/>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -13075,7 +13075,7 @@
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed about 1x to 9x likelier to answer (log-normal prior centered on 3.5x, the high end of the published measurements, chosen for a small, emotionally charged respondent pool), and the shares above are the resulting quartiles. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a 21-31 norm; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
+          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed 3.3x to about 9x likelier to answer (log-normal prior centered on 3.5x and FLOORED at 3.3x, the lower of Pew's high-salience benchmarks, chosen for a small, emotionally charged respondent pool reached through a campaign-circulated form), and the shares above are the resulting quartiles. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a ten-year average of 22; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$142,080; middle half +$94,720 to +$183,354; floor +$4,131; ceiling +$387,804; zero negative scenarios.</t>
+          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$142,220 (the site default, 30 students at $4,736, lands at +$142,080, within $140 of it); middle half +$94,720 to +$183,354; floor +$4,131; ceiling +$387,804; zero negative scenarios.</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $1,020,613 to minus $61,862 with a weighted median of minus $534,433, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $915,893 to plus $1,678 with a weighted median of minus $447,573, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -13075,7 +13075,7 @@
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed 3.3x to about 9x likelier to answer (log-normal prior centered on 3.5x and FLOORED at 3.3x, the lower of Pew's high-salience benchmarks, chosen for a small, emotionally charged respondent pool reached through a campaign-circulated form), and the shares above are the resulting quartiles. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a ten-year average of 22; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
+          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed 3.3x to about 9x likelier to answer (log-normal prior centered on 3.5x and FLOORED at 3.3x, the lower of Pew's high-salience benchmarks, chosen for a small, emotionally charged respondent pool reached through a campaign-circulated form), and the shares above are the resulting quartiles. The 24-child enrolled sample is the hand-coded floor: class-year designations are not assumed accurate and likely undercount who is enrolled now, so the true enrolled respondent count is probably higher at a similar leave rate, and the silent pool smaller than the correction assumes; both effects would raise the corrected share, so the published band leans low. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a ten-year average of 22; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$447,573 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$428,627 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$429,750); the weighted median loses $447,573</t>
+          <t>Above the closure model's central case, which is itself negative (-$410,806); the weighted median loses $428,627</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-447573</v>
+        <v>-428627</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1678</v>
+        <v>-11030</v>
       </c>
       <c r="C48" s="9">
         <f>B48*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>Closure_Model tab B49: the grid's lone positive corner</t>
+          <t>Closure_Model tab B49</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): the grid's lone positive corner (+$1,678) is a rounding error against the need; the -$447,573 weighted median drains reserves faster than status quo; all but one of the 972 weighted scenarios lose money.</t>
+          <t>Closure range check (v5.0): even the -$11,030 best case drains reserves faster than status quo, the -$428,627 weighted median much faster; every weighted scenario loses money.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-447573</v>
+        <v>-428627</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $447,573 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $429,750, and 971 of the 972 weighted scenarios lose money (the lone best corner nets $1,678); longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $428,627 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $410,806, and even the best-case tail still loses $11,030 a year; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-447573/Assumptions!B11</f>
+        <f>-428627/Assumptions!B11</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -11190,11 +11190,11 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-140*(Assumptions!B6+500-Assumptions!B62)</f>
+        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-136*(Assumptions!B6+500-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 140 missing students at $5,136 less the $400 supplies credit: the published -$328,511, the 79th percentile of the 972-scenario grid; the weighted median is a $447,573 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 136 missing students at $5,136 less the $400 supplies credit: the published -$309,567, the 82nd percentile of the 972-scenario grid; the weighted median is a $428,627 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $447,573 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $428,627 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12575,17 +12575,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Students missing from the rolls at steady state (grid legs 114/140/167)</t>
+          <t>Students missing from the rolls at steady state (grid legs 117/136/154)</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-$429,750: the central case itself loses money, about 16 percent of the structural deficit added, not removed</t>
+          <t>-$410,806: the central case itself loses money, about 16 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$915,893 a year: the closure loses money</t>
+          <t>-$847,825 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -12658,14 +12658,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>+$1,678 a year: the grid's single positive cell (every lever at its closure-friendliest at once: full capture, every fixed position cut, three teachers, only 114 leavers with zero add-ons, minimal busing), about $13 per displaced student and $800,000 to $1 million short of the plan's requirement</t>
+          <t>-$11,030 a year: even the grid's best case (every lever at its closure-friendliest at once) still loses money, roughly $800,000 to $1 million short of the plan's requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (114/140/167), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$447,573 (the median scenario LOSES money); middle half -$552,323 to -$347,374; all but ONE of the 972 weighted scenarios are negative, and the single best corner nets +$1,678 a year, about $13 per displaced student; range -$915,893 to +$1,678 (unweighted median -$446,722). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (117/136/154), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$428,627 (the median scenario LOSES money); middle half -$519,765 to -$340,021; EVERY weighted scenario is negative, the best case still loses $11,030; range -$847,825 to -$11,030 (unweighted median -$426,503). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.42025</v>
+        <v>0.42975</v>
       </c>
       <c r="C19" s="11">
         <f>ROUND(B19*$B$8,0)</f>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0.51625</v>
+        <v>0.50075</v>
       </c>
       <c r="C20" s="11">
         <f>ROUND(B20*$B$8,0)</f>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.61375</v>
+        <v>0.56725</v>
       </c>
       <c r="C21" s="11">
         <f>ROUND(B21*$B$8,0)</f>
@@ -13052,7 +13052,7 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>0.74475</v>
+        <v>0.65525</v>
       </c>
       <c r="C22" s="11">
         <f>ROUND(B22*$B$8,0)</f>
@@ -13075,7 +13075,7 @@
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>Leave shares are the posterior of a response-propensity model: among enrolled surveyed children the raw split is 20 leavers to 4 stayers; leaving families are assumed 3.3x to about 9x likelier to answer (log-normal prior centered on 3.5x and FLOORED at 3.3x, the lower of Pew's high-salience benchmarks, chosen for a small, emotionally charged respondent pool reached through a campaign-circulated form), and the shares above are the resulting quartiles. The 24-child enrolled sample is the hand-coded floor: class-year designations are not assumed accurate and likely undercount who is enrolled now, so the true enrolled respondent count is probably higher at a similar leave rate, and the silent pool smaller than the correction assumes; both effects would raise the corrected share, so the published band leans low. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a ten-year average of 22; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
+          <t>Leave shares are the posterior of a response-propensity model: across the sampled window the raw split is 62 leavers to 13 stayers; leaving families are assumed 3.3x to about 9x likelier to answer (log-normal prior centered on 3.5x and FLOORED at 3.3x, the lower of Pew's high-salience benchmarks, chosen for a small, emotionally charged respondent pool reached through a campaign-circulated form), and the shares above are the resulting quartiles. Class-year codes are not assumed accurate; the evidence window spans current enrollment plus the next three entering classes (62 leavers to 13 stayers of 75), so a miscoded child counts either way, and the correction still assumes the largest silent pool the coding allows, leaning the band low. Corroboration outside the survey: SAAR 2025-26 kindergarten of 12 against a ten-year average of 22; end-of-year 141 / 128 / 115 across 2023-24 to 2025-26. Losses build from six grade cohorts in year one to all thirteen by year eight (141 of 169 cohort-years across a 13-year window).</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $915,893 to plus $1,678 with a weighted median of minus $447,573, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $847,825 to minus $11,030 with a weighted median of minus $428,627, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -8768,15 +8768,15 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Plan requirement, low / high ($800K-$1M over the 128 students displaced)</t>
+          <t>Plan requirement, low / high ($800K-$1M over the 115 students displaced, the 2025-26 end-of-year count)</t>
         </is>
       </c>
       <c r="B34" s="19">
-        <f>800000/Assumptions!B11</f>
+        <f>800000/Exodus_Model!B8</f>
         <v/>
       </c>
       <c r="C34" s="19">
-        <f>1000000/Assumptions!B11</f>
+        <f>1000000/Exodus_Model!B8</f>
         <v/>
       </c>
     </row>
@@ -8787,15 +8787,15 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-428627/Assumptions!B11</f>
+        <f>-428627/Exodus_Model!B8</f>
         <v/>
       </c>
       <c r="C35" s="9">
-        <f>Closure_Model!B47/Assumptions!B11</f>
+        <f>Closure_Model!B47/Exodus_Model!B8</f>
         <v/>
       </c>
       <c r="D35" s="9">
-        <f>Closure_Model!B49/Assumptions!B11</f>
+        <f>Closure_Model!B49/Exodus_Model!B8</f>
         <v/>
       </c>
     </row>
@@ -8881,14 +8881,14 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>BRACKET CHECK (v3.9): the record's plausible median vs this model's independent bottom-up median per displaced student. These bracket rather than coincide and measure different things: the record credits a district's whole budget change to its closure (an upper bound by construction), the model prices only the levers a closure moves. Before the v3.9 fixed-cost rebuild the model read $713 and the two nearly coincided. Both remain far below the plan's $6,250-$7,813 requirement.</t>
+          <t>BRACKET CHECK (v3.9): the record's plausible median vs this model's independent bottom-up median per displaced student. These bracket rather than coincide and measure different things: the record credits a district's whole budget change to its closure (an upper bound by construction), the model prices only the levers a closure moves. Before the v3.9 fixed-cost rebuild the model read $713 and the two nearly coincided. Both remain far below the plan's $6,957-$8,696 requirement.</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
         <v>818</v>
       </c>
       <c r="C44" s="19">
-        <f>Closure_Model!B47/Assumptions!B11</f>
+        <f>Closure_Model!B47/Exodus_Model!B8</f>
         <v/>
       </c>
     </row>
@@ -12838,11 +12838,11 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Current student population (last official SAAR end-of-year count, 2024-25)</t>
+          <t>Current student population (SAAR 2025-26 end-of-year count; the 2024-25 count of 128 anchors the capacity and cost comparisons)</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>Of today's 128</t>
+          <t>Of today's 115</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
@@ -14408,7 +14408,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 128 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $847,825 to minus $11,030 with a weighted median of minus $428,627, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 115 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $847,825 to minus $11,030 with a weighted median of minus $428,627, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25-50 additional students at $4,236 net; pool measured on Redistricting rows 116-135 (236 in the district's own homeschool files, 247 residents enrolled in other districts, 450-550 in all with private school); 62 open seats exist at Bourbon Central's approved rating</t>
+          <t>25-50 additional students at $4,226 net; pool measured on Redistricting rows 116-135 (236 in the district's own homeschool files, 247 residents enrolled in other districts, 450-550 in all with private school); 62 open seats exist at Bourbon Central's approved rating</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$428,627 at Closure_Model row 50)</t>
+          <t>Closure net saving (LEGACY single-point base case, superseded by the grid median of -$427,087 at Closure_Model row 50)</t>
         </is>
       </c>
       <c r="B21" s="26">
@@ -1241,14 +1241,14 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>THE TRANSFORMATIVE CHECK (v4.5: enrollment lever re-based on recovered leakage students at $4,236 each; gap re-based on the trending fiscal 2026 ledger; capacity anchored on the district advisor's June 2026 presentation)</t>
+          <t>THE TRANSFORMATIVE CHECK (v4.5: enrollment lever re-based on recovered leakage students at $4,226 each; gap re-based on the trending fiscal 2026 ledger; capacity anchored on the district advisor's June 2026 presentation)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,236 = $1,164,900) + costs at the $760K low end</t>
+          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,226 = $1,162,150) + costs at the $760K low end</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CORRECTED twice: an earlier release used $1.11M-$3.33M for the enrollment lever; the Move 2 rows price the near-term band at $260K-$530K; the website slider now prices the lever directly as recovered leakage students, 0 to the measured 550-student pool, at the $4,236 net-of-supplies cell in B49 legs. Every 100 recovered add $423,600 a year on top of this check.</t>
+          <t>CORRECTED twice: an earlier release used $1.11M-$3.33M for the enrollment lever; the Move 2 rows price the near-term band at $260K-$530K; the website slider now prices the lever directly as recovered leakage students, 0 to the measured 550-student pool, at the $4,226 net-of-supplies cell in B49 legs. Every 100 recovered add $422,600 a year on top of this check.</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.66M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.16M for debt: about $15.0M of new GF-leveraged bonds plus the advisor's $32M, about $47 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $500K to spare, within $7,000 of the full raise; two recovered students close the difference. At the slider top (all 550 recovered, levers high) the plan runs about $3.4M ahead: the raise plus about $37M of bonds, about $69M of capacity. Every 100 recovered leakage students move the surplus by $423,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
+          <t>Reading: at the website defaults (half the pool recovered, costs at the low end, full restore) the plan runs about $1.66M ahead of the trending fiscal 2026 gap, funds the 5 percent certified raise, and leaves about $1.16M for debt: about $15.0M of new GF-leveraged bonds plus the advisor's $32M, about $47 million of building capacity with every school open. The zero-recovery floor still clears the gap with about $500K to spare, within $7,000 of the full raise; two recovered students close the difference. At the slider top (all 550 recovered, levers high) the plan runs about $3.4M ahead: the raise plus about $37M of bonds, about $69M of capacity. Every 100 recovered leakage students move the surplus by $422,600 a year. The earlier 10-percent-raise / $52M top-end claim is withdrawn with the lever correction.</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>Above the closure model's central case, which is itself negative (-$410,806); the weighted median loses $428,627</t>
+          <t>Above the closure model's central case, which is itself negative (-$409,446); the weighted median loses $427,087</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>-428627</v>
+        <v>-427087</v>
       </c>
       <c r="C47" s="9">
         <f>B47*(1-(1+B$40)^-B$41)/B$40</f>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>-11030</v>
+        <v>-9860</v>
       </c>
       <c r="C48" s="9">
         <f>B48*(1-(1+B$40)^-B$41)/B$40</f>
@@ -2844,7 +2844,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Closure range check (v5.0): even the -$11,030 best case drains reserves faster than status quo, the -$428,627 weighted median much faster; every weighted scenario loses money.</t>
+          <t>Closure range check (v5.0): even the -$9,860 best case drains reserves faster than status quo, the -$427,087 weighted median much faster; every weighted scenario loses money.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-428627</v>
+        <v>-427087</v>
       </c>
       <c r="C6" s="9">
         <f>Runway!E7</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Closure vote; the weighted median LOSES $428,627 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $410,806, and even the best-case tail still loses $11,030 a year; longer rides; measured enrollment-loss risk</t>
+          <t>Closure vote; the weighted median LOSES $427,087 a year (B6 is the grid median; the legacy single-point Closure_Model!B20 is superseded); the grid central case itself loses $409,446, and even the best-case tail still loses $9,860 a year; longer rides; measured enrollment-loss risk</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="B35" s="9">
-        <f>-428627/Exodus_Model!B8</f>
+        <f>-427087/Exodus_Model!B8</f>
         <v/>
       </c>
       <c r="C35" s="9">
@@ -9979,11 +9979,11 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>4636</v>
+        <v>4626</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Enacted 2026-2028 KY budget; corrected in v5.0 from the House-version $4,626</t>
+          <t>Enacted: 2026 Ky. Acts ch. 168 (HB 500), p. 20, archived in build/; an interim v5.0 draft wrongly moved this to $4,636; corrected here</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>$5,136 at the FY2027 base</t>
+          <t>$5,126 at the FY2027 base</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11155,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Student-years, and the carried band at the $4,636 base / $5,136 with add-ons</t>
+          <t>Student-years, and the carried band at the $4,626 base / $5,126 with add-ons</t>
         </is>
       </c>
       <c r="B31" s="22">
@@ -11194,7 +11194,7 @@
         <v/>
       </c>
       <c r="F34" s="21">
-        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 136 missing students at $5,136 less the $400 supplies credit: the published -$309,567, the 82nd percentile of the 972-scenario grid; the weighted median is a $428,627 loss (Closure_Model row 50)</f>
+        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 136 missing students at $5,126 less the $400 supplies credit: the published -$308,207, the 82nd percentile of the 972-scenario grid; the weighted median is a $427,087 loss (Closure_Model row 50)</f>
         <v/>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
-          <t>The published +$142,080, within $140 of the 19,683-scenario grid's weighted median of $142,220 (Growth_Model rows 17-19); at the central $500 busing and $700 supplies the same 30 students net about $118,000</t>
+          <t>The published +$141,780 is the grid's weighted median itself (Growth_Model rows 17-19); at the central $500 busing and $700 supplies the same 30 students net about $118,000</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Enrollment lever at $4,236 net of supplies</t>
+          <t>Enrollment lever at $4,226 net of supplies</t>
         </is>
       </c>
       <c r="B40" s="9">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Published: about $500,000 / $1,665,325 / $3.4 million to spare</t>
+          <t>Published: about $500,000 / $1,662,575 / $3.4 million to spare</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>Leakage pool pricing: see Redistricting rows 136-140 (documented floor 483; gross $2.1-$2.5M at the full base; net $1.9-$2.3M at $4,236)</t>
+          <t>Leakage pool pricing: see Redistricting rows 136-140 (documented floor 483; gross $2.1-$2.5M at the full base; net $1.9-$2.3M at $4,226)</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $428,627 LOSS)</t>
+          <t>NET RECURRING GENERAL FUND SAVING (LEGACY single-point scenario on superseded inputs; the published model is the 972-scenario grid at row 37, median a $427,087 LOSS)</t>
         </is>
       </c>
       <c r="B20" s="28">
@@ -12411,7 +12411,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Each departing student removes at least the SEEK base guarantee, every year, permanently.</t>
+          <t>Each departing student removes approximately the SEEK base guarantee, and more with the formula's weights, every year, permanently. SEEK pays on prior-year average daily attendance (about 91 percent of end-of-year enrollment here); the mostly uncounted at-risk, exceptional-child, language, and transportation weights are worth more than that haircut.</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>At-risk weight (15% of base on a ~72% FRL school), exceptional-child weights, transportation component, $100 capital outlay</t>
+          <t>The at-risk weight alone carries the central leg: 15% of base per free-lunch child, about $500 per average student at a ~72% FRL school; exceptional-child, language, and prorated transportation weights sit above it, mostly uncounted</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>-$410,806: the central case itself loses money, about 16 percent of the structural deficit added, not removed</t>
+          <t>-$409,446: the central case itself loses money, about 16 percent of the structural deficit added, not removed</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>-$847,825 a year: the closure loses money</t>
+          <t>-$846,285 a year: the closure loses money</t>
         </is>
       </c>
     </row>
@@ -12658,14 +12658,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>-$11,030 a year: even the grid's best case (every lever at its closure-friendliest at once) still loses money, roughly $800,000 to $1 million short of the plan's requirement</t>
+          <t>-$9,860 a year: even the grid's best case (every lever at its closure-friendliest at once) still loses money, roughly $800,000 to $1 million short of the plan's requirement</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,636 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (117/136/154), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$428,627 (the median scenario LOSES money); middle half -$519,765 to -$340,021; EVERY weighted scenario is negative, the best case still loses $11,030; range -$847,825 to -$11,030 (unweighted median -$426,503). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,626 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (117/136/154), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$427,087 (the median scenario LOSES money); middle half -$518,405 to -$338,727; EVERY weighted scenario is negative, the best case still loses $9,860; range -$846,285 to -$9,860 (unweighted median -$425,053). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$142,220 (the site default, 30 students at $4,736, lands at +$142,080, within $140 of it); middle half +$94,720 to +$183,354; floor +$4,131; ceiling +$387,804; zero negative scenarios.</t>
+          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$141,780, which is also the site default (30 students at $4,726); middle half +$94,520 to +$182,654; floor +$3,331; ceiling +$386,904; zero negative scenarios.</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>The same discipline applies to the closure direction: 115 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $847,825 to minus $11,030 with a weighted median of minus $428,627, and not the school's $2.5M gross cost.</t>
+          <t>The same discipline applies to the closure direction: 115 arriving students trigger the same class caps at the receiving schools, adding sections in several grades, which is exactly why the closure's net effect runs minus $846,285 to minus $9,860 with a weighted median of minus $427,087, and not the school's $2.5M gross cost.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -2567,7 +2567,7 @@
       </c>
       <c r="F100" s="21" t="inlineStr">
         <is>
-          <t>Trend case balances with about $283K to spare; the conservative case is still about $1.24M short, so its total below leans on equalization and existing restricted capacity only</t>
+          <t>Trend case balances with about $283K to spare; the conservative case is still about $1.13M short, so its total below leans on equalization and existing restricted capacity only</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Roughly $22.2 million in the conservative case and $42.1 million on the FY2026 trend, with the budget balanced</t>
+          <t>Roughly $21.2 million in the conservative case and $24.9 million on the FY2026 trend, with the budget balanced</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Closure only (central case, $52,514, from FY2027)</t>
+          <t>Closure only (central case, a -$409,446 yearly loss, from FY2027)</t>
         </is>
       </c>
       <c r="B7" s="9">
@@ -2993,7 +2993,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Reading: the question before the board is not closure versus no closure. It is which complete plan produces the best verified five-year result. Plan 2 buys roughly one extra year of runway; Plan 3 restores balance while keeping every school open. The rebalance-and-grow scenario (Redistricting tab) is one line inside Plan 3's menu.</t>
+          <t>Reading: the question before the board is not closure versus no closure. It is which complete plan produces the best verified five-year result. Plan 2 drains reserves faster than doing nothing (Runway rows 5-9); Plan 3 restores balance while keeping every school open. The rebalance-and-grow scenario (Redistricting tab) is one line inside Plan 3's menu.</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="G114" s="21" t="inlineStr">
         <is>
-          <t>About -2.5 cents, roughly -$477,000 a year. INFERENCE, NOT A DOCUMENT: KDE does not publish the year-by-year rate-type split, and a facilities nickel is an equivalent rate restated annually against the whole property base, so it drifts. The certified split by year is requested in Appendix B. What is not in doubt: the levy that rose in 2023 was restricted building money that cannot lawfully pay a teacher</t>
+          <t>About -2.5 cents, roughly -$415,000 a year. INFERENCE, NOT A DOCUMENT: KDE does not publish the year-by-year rate-type split, and a facilities nickel is an equivalent rate restated annually against the whole property base, so it drifts. The certified split by year is requested in Appendix B. What is not in doubt: the levy that rose in 2023 was restricted building money that cannot lawfully pay a teacher</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>All-funds dollars coded to org 090, fiscal 2025 MUNIS Cost by ORG</t>
+          <t>All-funds dollars coded to org 090, fiscal 2026 MUNIS Cost by ORG</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -11130,7 +11130,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Carried funding of the current 128 students: grade counts (K-5) x years to grade 12</t>
+          <t>Carried funding of the 128 students on the official 2024-25 roster: grade counts (K-5) x years to grade 12</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
@@ -11193,9 +11193,10 @@
         <f>B17+C17+Closure_Model!C40+3*54479.4-63000-136*(Assumptions!B6+500-Assumptions!B62)</f>
         <v/>
       </c>
-      <c r="F34" s="21">
-        <f> $127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 136 missing students at $5,126 less the $400 supplies credit: the published -$308,207, the 82nd percentile of the 972-scenario grid; the weighted median is a $427,087 loss (Closure_Model row 50)</f>
-        <v/>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>$127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 136 missing students at $5,126 less the $400 supplies credit: the published -$308,207, the 82nd percentile of the 972-scenario grid; the weighted median is a $427,087 loss (Closure_Model row 50)</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -12665,7 +12666,7 @@
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,626 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (117/136/154), with the signed-survey floor of 74 kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$427,087 (the median scenario LOSES money); middle half -$518,405 to -$338,727; EVERY weighted scenario is negative, the best case still loses $9,860; range -$846,285 to -$9,860 (unweighted median -$425,053). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,626 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (117/136/154), with the signed-survey floor of 74 (the 70 signed children spread over their twelve class cohorts, 5.83 per class, carried 12.62 effective years) kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$427,087 (the median scenario LOSES money); middle half -$518,405 to -$338,727; EVERY weighted scenario is negative, the best case still loses $9,860; range -$846,285 to -$9,860 (unweighted median -$425,053). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13333,7 @@
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
-          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75 at $28,500, or 1 per 50 at $37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$141,780, which is also the site default (30 students at $4,726); middle half +$94,520 to +$182,654; floor +$3,331; ceiling +$386,904; zero negative scenarios.</t>
+          <t>19,683 scenarios: added students 10 to 90; classroom-indexed hiring beyond the 25 open seats at 1 per 18/21/24; teacher cost $41,718/$49,150/$56,583 (certified schedule entry-to-mid rows); support staff none, 1 per 75, or 1 per 50, with cost legs $20,000/$28,500/$37,000 (staff-per and staff-cost enumerated as independent levers); busing $0/$500/$1,000 per recruit; marginal cost $400/$700/$1,000; SEEK add-ons $0/$500/$1,000. Weighted median +$141,780, which is also the site default (30 students at $4,726); middle half +$94,520 to +$182,654; floor +$3,331; ceiling +$386,904; zero negative scenarios.</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defaults" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GF_Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closure_Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exodus_Model" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Model" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redistricting" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport_Geo" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt_Service" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runway" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_History" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demographics" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Data" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facility_Plans" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KY_Closures" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School_Costs" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Defaults" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GF_Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Closure_Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Exodus_Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Growth_Model" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Redistricting" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Transport_Geo" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Alternatives" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Debt_Service" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Runway" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Scenarios" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Tax_History" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Demographics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="School_Data" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Facility_Plans" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="KY_Closures" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="School_Costs" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -11211,7 +11211,7 @@
       </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
-          <t>The published +$141,780 is the grid's weighted median itself (Growth_Model rows 17-19); at the central $500 busing and $700 supplies the same 30 students net about $118,000</t>
+          <t>The published +$141,780 is the grid's weighted median itself (Growth_Model rows 17-19); at the central $500 busing and $700 supplies the same 30 students net $117,780</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -1167,7 +1167,7 @@
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>Reading: the raw-row band is $1.39M to $2.34M with no haircut (v4.4 review). The published headline is now the 2018 restore plus the counted-once cost package, $2.5M to $3.0M a year (transformative check below). Ranges overlap and are not additive to the penny, and each line carries its own confidence rating in column F. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model row 21 carries both for closure).</t>
+          <t>Reading: the raw-row band is $1.39M to $2.34M with no haircut (v4.4 review). The published headline is now the 2018 restore plus the counted-once cost package, $2.2M to $2.8M a year (transformative check below). Ranges overlap and are not additive to the penny, and each line carries its own confidence rating in column F. Medicaid and reimbursement recovery were removed from the menu in v4.2 review; shared services with Paris Independent was removed in v4.4 review. Coverage is reported against both yardsticks: the $2.65M structural gap before transfers and the roughly $1.15M net drawdown after transfers (Closure_Model row 21 carries both for closure).</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,226 = $1,162,150) + costs at the $760K low end</t>
+          <t>Plan levers at the website defaults: 275 of 550 leakage students recovered (275 x $4,226 = $1,162,150) + costs at the $760K low end. Recovered students are priced at supplies-only absorption; each new section a lumpy grade forces costs about $60,000 to $85,000 against this line</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -8881,7 +8881,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>BRACKET CHECK (v3.9): the record's plausible median vs this model's independent bottom-up median per displaced student. These bracket rather than coincide and measure different things: the record credits a district's whole budget change to its closure (an upper bound by construction), the model prices only the levers a closure moves. Before the v3.9 fixed-cost rebuild the model read $713 and the two nearly coincided. Both remain far below the plan's $6,957-$8,696 requirement.</t>
+          <t>BRACKET CHECK (v3.9): the record's plausible median vs this model's independent bottom-up median per displaced student. These bracket rather than coincide and measure different things: the record credits a district's whole budget change to its closure (an upper bound by construction), the model prices only the levers a closure moves. Before the v3.9 fixed-cost rebuild the model read $713 and the two nearly coincided. Both remain far below the plan's $6,957-$8,696 requirement. The per-student column recomputes from inputs rounded to $1,000s and can differ from the report's exact CSV figures by up to $3 (Webster $3,525, Adair $6,935).</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>MUNIS FY2026 actuals: school administration $115,397 + custodial $49,655 + library $49,052 = $214,104 (the district's own A.1 prices the same four roles at $209,700, within 2 percent, and states all current staff are retained in year one; the full-cut leg is an attrition end state)</t>
+          <t>MUNIS FY2026 actuals: school administration $115,397 + custodial $49,655 + library $49,052 = $214,104 (the district's own A.1 prices the same four roles at $209,700, within about 2 percent, and states all current staff are retained in year one; the full-cut leg is an attrition end state)</t>
         </is>
       </c>
     </row>

--- a/NMES_Financial_Model.xlsx
+++ b/NMES_Financial_Model.xlsx
@@ -11190,12 +11190,12 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>B17+C17+Closure_Model!C40+3*54479.4-63000-136*(Assumptions!B6+500-Assumptions!B62)</f>
+        <f>Closure_Model!C39+3*54479.4-Closure_Model!B42-Closure_Model!D43*(Assumptions!B6+Closure_Model!B44-Assumptions!B62)</f>
         <v/>
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t>$127,039 kept, plus half the fixed overhead positions ($107,052, Closure_Model C40) and three teachers at $54,479.40, minus $63,000 of busing, minus the statistical median of 136 missing students at $5,126 less the $400 supplies credit: the published -$308,207, the 82nd percentile of the 972-scenario grid; the weighted median is a $427,087 loss (Closure_Model row 50)</t>
+          <t>The site calculator opens at the grid's weighted median cell: $80,279 captured (Closure_Model C39), no fixed positions cut, three teachers at $54,479.40, minus $20,000 of busing, minus the band's high 154 leavers at zero add-ons less the $400 supplies credit: the published -$427,087, the 50th percentile by construction (Closure_Model row 50). The savings-granted steelman (building sold, half the fixed positions, three teachers, median leavers) prices -$308,207 at the 82nd percentile and is one slider-move away</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,626 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (117/136/154), with the signed-survey floor of 74 (the 70 signed children spread over their twelve class cohorts, 5.83 per class, carried 12.62 effective years) kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$427,087 (the median scenario LOSES money); middle half -$518,405 to -$338,727; EVERY weighted scenario is negative, the best case still loses $9,860; range -$846,285 to -$9,860 (unweighted median -$425,053). One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
+          <t>Distribution of all 972 combinations enumerated by build/closure_grid.py: capture, fixed-position, add-ons, busing and missing-students levers take three values each, teachers four (0/1/2/3): 3^5 x 4 = 972. Each missing student is priced at the enacted FY2027 SEEK base of $4,626 plus the add-ons lever, minus the $400 of supplies that stop being spent (Assumptions row 62, the same figure the growth model charges each recruit); teacher savings appear ONLY on the teachers-cut lever, so staffing is never counted twice. The busing high leg is capped at half its bottom-up maximum ($95,000); a property-value lever priced in an interim draft is removed while the PVA records request is pending; the missing-students lever prices the statistical band's quartiles (117/136/154), with the signed-survey floor of 74 (the 70 signed children spread over their twelve class cohorts, 5.83 per class, carried 12.62 effective years) kept as hard evidence below every priced leg. v5.0 lever weights: triangular 1-2-1 on every three-leg lever, uniform on teachers. Weighted median -$427,087 (the median scenario LOSES money); middle half -$518,405 to -$338,727; EVERY weighted scenario is negative, the best case still loses $9,860; range -$846,285 to -$9,860 (unweighted median -$425,053). The site calculator opens at the cell AT the weighted median ($80,279 + 3 teachers - $20,000 busing - 154 x $4,226 = -$427,087, the 50th percentile); the savings-granted steelman (-$308,207, 82nd percentile) is retained beside it. One-time transition costs $100K-$300K in year one are additional. The v4.5 grid (5,832 scenarios, weighted median -$20,007, 55 percent negative) and the v3.9 grid (2,916, median +$21,571) are retained in the version history.</t>
         </is>
       </c>
     </row>
